--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2577,12 +2577,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="A255" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Administracion:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="236">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -3314,6 +3338,15 @@
   </si>
   <si>
     <t>SEPELIO FAMILIAR por integrante</t>
+  </si>
+  <si>
+    <t>DR. LUIS COSTANZI</t>
+  </si>
+  <si>
+    <t>OCT / TOMOGRAFIAS OCULARES</t>
+  </si>
+  <si>
+    <t>HRT / TOMOGRAFIAS OCULARES</t>
   </si>
 </sst>
 </file>
@@ -4840,7 +4873,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L254"/>
+  <dimension ref="A1:L257"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
@@ -11042,6 +11075,69 @@
         <v>20000</v>
       </c>
     </row>
+    <row r="255" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="87" t="s">
+        <v>233</v>
+      </c>
+      <c r="B255" s="121"/>
+      <c r="C255" s="95"/>
+      <c r="D255" s="95"/>
+      <c r="E255" s="95"/>
+      <c r="F255" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="G255" s="95" t="s">
+        <v>98</v>
+      </c>
+      <c r="H255" s="95" t="s">
+        <v>99</v>
+      </c>
+      <c r="I255" s="96" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A256" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="B256" s="84"/>
+      <c r="C256" s="84"/>
+      <c r="D256" s="84"/>
+      <c r="E256" s="84"/>
+      <c r="F256" s="102"/>
+      <c r="G256" s="102">
+        <v>35000</v>
+      </c>
+      <c r="H256" s="84">
+        <f>+G256</f>
+        <v>35000</v>
+      </c>
+      <c r="I256" s="103">
+        <f>+G256</f>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A257" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B257" s="82"/>
+      <c r="C257" s="82"/>
+      <c r="D257" s="82"/>
+      <c r="E257" s="82"/>
+      <c r="F257" s="83"/>
+      <c r="G257" s="83">
+        <v>35000</v>
+      </c>
+      <c r="H257" s="82">
+        <f>+G257</f>
+        <v>35000</v>
+      </c>
+      <c r="I257" s="98">
+        <f>+G257</f>
+        <v>35000</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:H1"/>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2606,7 +2606,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="235">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -2851,12 +2851,6 @@
     <t>MECANICOS DENTALES</t>
   </si>
   <si>
-    <t>SALON VIP 1</t>
-  </si>
-  <si>
-    <t>SALON GRANDE 2</t>
-  </si>
-  <si>
     <t>REPARACION SIMPLE</t>
   </si>
   <si>
@@ -2929,9 +2923,6 @@
     <t xml:space="preserve">CIRUGIAS ODONTOLOGICAS </t>
   </si>
   <si>
-    <t>SALON  CHICO</t>
-  </si>
-  <si>
     <t>In 180</t>
   </si>
   <si>
@@ -3013,9 +3004,6 @@
     <t>Valor por turno</t>
   </si>
   <si>
-    <t>SOCIO VALOR DIARIO</t>
-  </si>
-  <si>
     <t>VALOR FIN DE SEMANA</t>
   </si>
   <si>
@@ -3347,6 +3335,15 @@
   </si>
   <si>
     <t>HRT / TOMOGRAFIAS OCULARES</t>
+  </si>
+  <si>
+    <t>VALOR DIARIO</t>
+  </si>
+  <si>
+    <t>SALON 2</t>
+  </si>
+  <si>
+    <t>SALON 1</t>
   </si>
 </sst>
 </file>
@@ -4897,23 +4894,23 @@
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B2" s="114"/>
       <c r="C2" s="115"/>
       <c r="D2" s="115"/>
       <c r="E2" s="116"/>
       <c r="F2" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G2" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H2" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I2" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -4934,7 +4931,7 @@
         <v>5550</v>
       </c>
       <c r="G3" s="65" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H3" s="65">
         <v>4550</v>
@@ -4946,7 +4943,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B4" s="150"/>
       <c r="C4" s="150">
@@ -4963,7 +4960,7 @@
         <v>5550</v>
       </c>
       <c r="G4" s="65" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H4" s="150"/>
       <c r="I4" s="151">
@@ -4973,7 +4970,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B5" s="152"/>
       <c r="C5" s="152"/>
@@ -4986,7 +4983,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B6" s="65"/>
       <c r="C6" s="65">
@@ -5006,12 +5003,12 @@
       </c>
       <c r="H6" s="65"/>
       <c r="I6" s="145" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B7" s="150"/>
       <c r="C7" s="150">
@@ -5036,32 +5033,32 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B8" s="114"/>
       <c r="C8" s="115"/>
       <c r="D8" s="115"/>
       <c r="E8" s="116"/>
       <c r="F8" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G8" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H8" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I8" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J8" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K8" s="55"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B9" s="65"/>
       <c r="C9" s="65"/>
@@ -5102,7 +5099,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B11" s="65">
         <v>30000</v>
@@ -5144,7 +5141,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B13" s="65"/>
       <c r="C13" s="65"/>
@@ -5163,7 +5160,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B14" s="65"/>
       <c r="C14" s="65"/>
@@ -5189,19 +5186,19 @@
       <c r="D15" s="115"/>
       <c r="E15" s="116"/>
       <c r="F15" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H15" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I15" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K15" s="58"/>
     </row>
@@ -5277,7 +5274,7 @@
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="56" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B18" s="65"/>
       <c r="C18" s="65"/>
@@ -5301,21 +5298,21 @@
       <c r="D19" s="115"/>
       <c r="E19" s="116"/>
       <c r="F19" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G19" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H19" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I19" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B20" s="65">
         <v>20000</v>
@@ -5344,25 +5341,25 @@
       <c r="D21" s="115"/>
       <c r="E21" s="116"/>
       <c r="F21" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G21" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H21" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I21" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J21" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K21" s="55"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B22" s="65">
         <v>35000</v>
@@ -5402,19 +5399,19 @@
       <c r="D23" s="115"/>
       <c r="E23" s="116"/>
       <c r="F23" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G23" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H23" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I23" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K23" s="55"/>
     </row>
@@ -5433,32 +5430,32 @@
     </row>
     <row r="25" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B25" s="114"/>
       <c r="C25" s="115"/>
       <c r="D25" s="115"/>
       <c r="E25" s="116"/>
       <c r="F25" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G25" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H25" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I25" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J25" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K25" s="55"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="28" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B26" s="65">
         <v>20000</v>
@@ -5495,32 +5492,32 @@
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B27" s="114"/>
       <c r="C27" s="115"/>
       <c r="D27" s="115"/>
       <c r="E27" s="116"/>
       <c r="F27" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G27" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H27" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I27" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J27" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K27" s="55"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B28" s="65">
         <v>228334</v>
@@ -5564,25 +5561,25 @@
       <c r="D29" s="115"/>
       <c r="E29" s="116"/>
       <c r="F29" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G29" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H29" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I29" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J29" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K29" s="55"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="30" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B30" s="65">
         <v>72000</v>
@@ -5626,25 +5623,25 @@
       <c r="D31" s="115"/>
       <c r="E31" s="116"/>
       <c r="F31" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G31" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H31" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I31" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J31" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K31" s="55"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="31" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B32" s="65">
         <v>33000</v>
@@ -5688,25 +5685,25 @@
       <c r="D33" s="115"/>
       <c r="E33" s="116"/>
       <c r="F33" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G33" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H33" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I33" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J33" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K33" s="55"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="31" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B34" s="65">
         <v>24600</v>
@@ -5750,25 +5747,25 @@
       <c r="D35" s="115"/>
       <c r="E35" s="116"/>
       <c r="F35" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G35" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H35" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I35" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J35" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K35" s="55"/>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="31" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B36" s="65">
         <v>24600</v>
@@ -5812,25 +5809,25 @@
       <c r="D37" s="115"/>
       <c r="E37" s="116"/>
       <c r="F37" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G37" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H37" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I37" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J37" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K37" s="55"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="31" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B38" s="65">
         <v>24600</v>
@@ -5874,25 +5871,25 @@
       <c r="D39" s="115"/>
       <c r="E39" s="116"/>
       <c r="F39" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G39" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H39" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I39" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J39" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K39" s="55"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="31" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B40" s="65">
         <v>24600</v>
@@ -5936,25 +5933,25 @@
       <c r="D41" s="115"/>
       <c r="E41" s="116"/>
       <c r="F41" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G41" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H41" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I41" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J41" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K41" s="55"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B42" s="65">
         <v>72000</v>
@@ -5998,25 +5995,25 @@
       <c r="D43" s="115"/>
       <c r="E43" s="116"/>
       <c r="F43" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G43" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H43" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I43" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J43" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K43" s="55"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B44" s="65">
         <v>12000</v>
@@ -6053,7 +6050,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="35" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B45" s="65">
         <v>12000</v>
@@ -6090,7 +6087,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="35" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B46" s="65">
         <v>12000</v>
@@ -6127,7 +6124,7 @@
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B47" s="65">
         <v>12000</v>
@@ -6171,21 +6168,21 @@
       <c r="D48" s="115"/>
       <c r="E48" s="116"/>
       <c r="F48" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G48" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H48" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I48" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B49" s="71">
         <v>20000</v>
@@ -6217,7 +6214,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B50" s="71">
         <v>15000</v>
@@ -6249,7 +6246,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B51" s="71">
         <v>15000</v>
@@ -6280,7 +6277,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="33" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B52" s="71">
         <v>20000</v>
@@ -6311,7 +6308,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="33" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B53" s="71">
         <v>20000</v>
@@ -6342,7 +6339,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="33" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B54" s="71">
         <v>20000</v>
@@ -6373,7 +6370,7 @@
     </row>
     <row r="55" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="33" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B55" s="71">
         <v>20000</v>
@@ -6411,21 +6408,21 @@
       <c r="D56" s="115"/>
       <c r="E56" s="116"/>
       <c r="F56" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G56" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H56" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I56" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B57" s="71">
         <v>15000</v>
@@ -6454,28 +6451,28 @@
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B58" s="114"/>
       <c r="C58" s="115"/>
       <c r="D58" s="115"/>
       <c r="E58" s="116"/>
       <c r="F58" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G58" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H58" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I58" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="37" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B59" s="65">
         <v>12000</v>
@@ -6506,23 +6503,23 @@
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B60" s="114"/>
       <c r="C60" s="115"/>
       <c r="D60" s="115"/>
       <c r="E60" s="116"/>
       <c r="F60" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G60" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H60" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I60" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -6698,27 +6695,27 @@
         <v>8</v>
       </c>
       <c r="B67" s="114" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C67" s="115"/>
       <c r="D67" s="115"/>
       <c r="E67" s="116"/>
       <c r="F67" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G67" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H67" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I67" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B68" s="73">
         <v>111000</v>
@@ -6749,7 +6746,7 @@
     </row>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B69" s="118">
         <v>51000</v>
@@ -6780,30 +6777,30 @@
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="39" t="s">
-        <v>96</v>
+        <v>234</v>
       </c>
       <c r="B70" s="114" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C70" s="115"/>
       <c r="D70" s="115"/>
       <c r="E70" s="116"/>
       <c r="F70" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G70" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H70" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I70" s="76" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B71" s="73">
         <v>241000</v>
@@ -6834,7 +6831,7 @@
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="57" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B72" s="118">
         <v>68000</v>
@@ -6865,30 +6862,30 @@
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>71</v>
+        <v>233</v>
       </c>
       <c r="B73" s="114" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C73" s="115"/>
       <c r="D73" s="115"/>
       <c r="E73" s="116"/>
       <c r="F73" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G73" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H73" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I73" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B74" s="73">
         <v>551000</v>
@@ -6919,7 +6916,7 @@
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="59" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B75" s="118">
         <v>132000</v>
@@ -6950,30 +6947,30 @@
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="40" t="s">
-        <v>70</v>
+        <v>234</v>
       </c>
       <c r="B76" s="114" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C76" s="115"/>
       <c r="D76" s="115"/>
       <c r="E76" s="116"/>
       <c r="F76" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G76" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H76" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I76" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="33" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B77" s="73">
         <v>962000</v>
@@ -7004,7 +7001,7 @@
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B78" s="118">
         <v>203000</v>
@@ -7042,16 +7039,16 @@
       <c r="D79" s="115"/>
       <c r="E79" s="116"/>
       <c r="F79" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G79" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H79" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I79" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -7118,7 +7115,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B82" s="70">
         <v>41000</v>
@@ -7180,23 +7177,23 @@
     </row>
     <row r="84" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="20" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B84" s="114"/>
       <c r="C84" s="115"/>
       <c r="D84" s="115"/>
       <c r="E84" s="116"/>
       <c r="F84" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G84" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H84" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I84" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7219,27 +7216,27 @@
         <v>30</v>
       </c>
       <c r="B86" s="114" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C86" s="115"/>
       <c r="D86" s="115"/>
       <c r="E86" s="116"/>
       <c r="F86" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G86" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H86" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I86" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="45" t="s">
-        <v>124</v>
+        <v>232</v>
       </c>
       <c r="B87" s="73">
         <v>97000</v>
@@ -7270,7 +7267,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="45" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B88" s="73">
         <v>282000</v>
@@ -7301,7 +7298,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="45" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B89" s="73">
         <v>256000</v>
@@ -7332,7 +7329,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="45" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B90" s="73">
         <v>508000</v>
@@ -7363,7 +7360,7 @@
     </row>
     <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="123" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B91" s="124">
         <v>8200</v>
@@ -7397,22 +7394,22 @@
         <v>33</v>
       </c>
       <c r="B92" s="114" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C92" s="127"/>
       <c r="D92" s="127"/>
       <c r="E92" s="128"/>
       <c r="F92" s="129" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G92" s="129" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H92" s="130" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I92" s="130" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -7501,22 +7498,22 @@
         <v>37</v>
       </c>
       <c r="B96" s="114" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C96" s="115"/>
       <c r="D96" s="115"/>
       <c r="E96" s="116"/>
       <c r="F96" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G96" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H96" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I96" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -7617,22 +7614,22 @@
         <v>26</v>
       </c>
       <c r="B100" s="114" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C100" s="115"/>
       <c r="D100" s="115"/>
       <c r="E100" s="116"/>
       <c r="F100" s="68" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G100" s="68" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H100" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I100" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7712,30 +7709,30 @@
     </row>
     <row r="104" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="54" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B104" s="114" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C104" s="115"/>
       <c r="D104" s="115"/>
       <c r="E104" s="116"/>
       <c r="F104" s="81" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G104" s="81" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H104" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I104" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B105" s="65">
         <v>88886</v>
@@ -7766,7 +7763,7 @@
     </row>
     <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B106" s="65">
         <v>103703</v>
@@ -7797,7 +7794,7 @@
     </row>
     <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B107" s="65">
         <v>174729</v>
@@ -7828,7 +7825,7 @@
     </row>
     <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B108" s="65">
         <v>22223</v>
@@ -7859,7 +7856,7 @@
     </row>
     <row r="109" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B109" s="65">
         <v>111110</v>
@@ -7890,30 +7887,30 @@
     </row>
     <row r="110" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="53" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B110" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C110" s="115"/>
       <c r="D110" s="115"/>
       <c r="E110" s="116"/>
       <c r="F110" s="81" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G110" s="81" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H110" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I110" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B111" s="65">
         <v>312686</v>
@@ -7944,7 +7941,7 @@
     </row>
     <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B112" s="65">
         <v>349723</v>
@@ -7975,7 +7972,7 @@
     </row>
     <row r="113" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B113" s="65">
         <v>446016</v>
@@ -8006,30 +8003,30 @@
     </row>
     <row r="114" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="52" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B114" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C114" s="115"/>
       <c r="D114" s="115"/>
       <c r="E114" s="116"/>
       <c r="F114" s="81" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G114" s="81" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H114" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I114" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B115" s="65">
         <v>128763</v>
@@ -8060,7 +8057,7 @@
     </row>
     <row r="116" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B116" s="65">
         <v>199762</v>
@@ -8091,30 +8088,30 @@
     </row>
     <row r="117" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="52" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B117" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C117" s="115"/>
       <c r="D117" s="115"/>
       <c r="E117" s="116"/>
       <c r="F117" s="81" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G117" s="81" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H117" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I117" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B118" s="65">
         <v>477701</v>
@@ -8145,7 +8142,7 @@
     </row>
     <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B119" s="65">
         <v>236516</v>
@@ -8176,7 +8173,7 @@
     </row>
     <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B120" s="65">
         <v>274873</v>
@@ -8207,7 +8204,7 @@
     </row>
     <row r="121" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B121" s="65">
         <v>313203</v>
@@ -8238,30 +8235,30 @@
     </row>
     <row r="122" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B122" s="114" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C122" s="115"/>
       <c r="D122" s="115"/>
       <c r="E122" s="116"/>
       <c r="F122" s="81" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G122" s="81" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H122" s="69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I122" s="69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B123" s="65">
         <v>139695</v>
@@ -8292,7 +8289,7 @@
     </row>
     <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B124" s="65">
         <v>153373</v>
@@ -8323,7 +8320,7 @@
     </row>
     <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B125" s="65">
         <v>184044</v>
@@ -8354,7 +8351,7 @@
     </row>
     <row r="126" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="139" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B126" s="110">
         <v>49078</v>
@@ -8385,30 +8382,30 @@
     </row>
     <row r="127" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="141" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B127" s="138" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C127" s="127"/>
       <c r="D127" s="127"/>
       <c r="E127" s="128"/>
       <c r="F127" s="129" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G127" s="129" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H127" s="130" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I127" s="130" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="140" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B128" s="136">
         <v>661862</v>
@@ -8439,7 +8436,7 @@
     </row>
     <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B129" s="65">
         <v>692556</v>
@@ -8470,7 +8467,7 @@
     </row>
     <row r="130" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="135" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B130" s="110">
         <v>90078</v>
@@ -8501,7 +8498,7 @@
     </row>
     <row r="131" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="137" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B131" s="138"/>
       <c r="C131" s="127"/>
@@ -8509,13 +8506,13 @@
       <c r="E131" s="128"/>
       <c r="F131" s="129"/>
       <c r="G131" s="129" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H131" s="130" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I131" s="130" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -8822,7 +8819,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="146" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B150" s="110"/>
       <c r="C150" s="110"/>
@@ -8843,7 +8840,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="146" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B151" s="110"/>
       <c r="C151" s="110"/>
@@ -8909,7 +8906,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="146" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B154" s="110"/>
       <c r="C154" s="110"/>
@@ -9017,7 +9014,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="146" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B160" s="110"/>
       <c r="C160" s="110"/>
@@ -9038,7 +9035,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="146" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B161" s="110"/>
       <c r="C161" s="110"/>
@@ -9053,7 +9050,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="146" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B162" s="110"/>
       <c r="C162" s="110"/>
@@ -9075,7 +9072,7 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="146" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B163" s="110"/>
       <c r="C163" s="110"/>
@@ -9120,7 +9117,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="146" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B166" s="110"/>
       <c r="C166" s="110"/>
@@ -9213,17 +9210,17 @@
       <c r="E171" s="95"/>
       <c r="F171" s="95"/>
       <c r="G171" s="95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H171" s="95" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I171" s="96" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J171" s="158"/>
       <c r="K171" s="61" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="L171" s="66">
         <v>12000</v>
@@ -9231,7 +9228,7 @@
     </row>
     <row r="172" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B172" s="84"/>
       <c r="C172" s="84"/>
@@ -9254,7 +9251,7 @@
     </row>
     <row r="173" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B173" s="82"/>
       <c r="C173" s="82"/>
@@ -9274,7 +9271,7 @@
       </c>
       <c r="J173" s="158"/>
       <c r="K173" s="61" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L173" s="66">
         <v>22000</v>
@@ -9282,7 +9279,7 @@
     </row>
     <row r="174" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B174" s="82"/>
       <c r="C174" s="82"/>
@@ -9305,7 +9302,7 @@
     </row>
     <row r="175" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B175" s="82"/>
       <c r="C175" s="82"/>
@@ -9328,7 +9325,7 @@
     </row>
     <row r="176" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B176" s="82"/>
       <c r="C176" s="82"/>
@@ -9351,7 +9348,7 @@
     </row>
     <row r="177" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B177" s="82"/>
       <c r="C177" s="82"/>
@@ -9374,7 +9371,7 @@
     </row>
     <row r="178" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B178" s="82"/>
       <c r="C178" s="82"/>
@@ -9397,7 +9394,7 @@
     </row>
     <row r="179" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B179" s="82"/>
       <c r="C179" s="82"/>
@@ -9420,7 +9417,7 @@
     </row>
     <row r="180" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B180" s="82"/>
       <c r="C180" s="82"/>
@@ -9443,7 +9440,7 @@
     </row>
     <row r="181" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B181" s="82"/>
       <c r="C181" s="82"/>
@@ -9466,7 +9463,7 @@
     </row>
     <row r="182" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B182" s="82"/>
       <c r="C182" s="82"/>
@@ -9489,7 +9486,7 @@
     </row>
     <row r="183" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B183" s="82"/>
       <c r="C183" s="82"/>
@@ -9512,7 +9509,7 @@
     </row>
     <row r="184" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="10" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B184" s="100"/>
       <c r="C184" s="100"/>
@@ -9535,7 +9532,7 @@
     </row>
     <row r="185" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="23" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B185" s="84"/>
       <c r="C185" s="84"/>
@@ -9554,7 +9551,7 @@
     </row>
     <row r="186" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="19" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B186" s="89"/>
       <c r="C186" s="89"/>
@@ -9573,7 +9570,7 @@
     </row>
     <row r="187" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="87" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B187" s="121"/>
       <c r="C187" s="122"/>
@@ -9581,13 +9578,13 @@
       <c r="E187" s="95"/>
       <c r="F187" s="95"/>
       <c r="G187" s="95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H187" s="96" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I187" s="96" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -9613,7 +9610,7 @@
     </row>
     <row r="189" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B189" s="71"/>
       <c r="C189" s="71"/>
@@ -9632,7 +9629,7 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B190" s="85"/>
       <c r="C190" s="85"/>
@@ -9652,7 +9649,7 @@
         <v>16640</v>
       </c>
       <c r="K190" s="61" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="L190" s="66">
         <v>16640</v>
@@ -9660,7 +9657,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B191" s="85"/>
       <c r="C191" s="85"/>
@@ -9680,7 +9677,7 @@
         <v>9600</v>
       </c>
       <c r="K191" s="61" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="L191" s="66">
         <v>9600</v>
@@ -9688,7 +9685,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B192" s="85"/>
       <c r="C192" s="85"/>
@@ -9711,7 +9708,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B193" s="85"/>
       <c r="C193" s="85"/>
@@ -9731,7 +9728,7 @@
         <v>9600</v>
       </c>
       <c r="K193" s="61" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L193" s="66">
         <v>32000</v>
@@ -9739,7 +9736,7 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B194" s="85"/>
       <c r="C194" s="85"/>
@@ -9761,7 +9758,7 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B195" s="85"/>
       <c r="C195" s="85"/>
@@ -9783,7 +9780,7 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B196" s="85"/>
       <c r="C196" s="85"/>
@@ -9805,7 +9802,7 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B197" s="85"/>
       <c r="C197" s="85"/>
@@ -9827,7 +9824,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B198" s="85"/>
       <c r="C198" s="85"/>
@@ -9849,7 +9846,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B199" s="85"/>
       <c r="C199" s="85"/>
@@ -9871,7 +9868,7 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="9" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B200" s="85"/>
       <c r="C200" s="85"/>
@@ -9893,7 +9890,7 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B201" s="85"/>
       <c r="C201" s="85"/>
@@ -9915,7 +9912,7 @@
     </row>
     <row r="202" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B202" s="85"/>
       <c r="C202" s="85"/>
@@ -9937,7 +9934,7 @@
     </row>
     <row r="203" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B203" s="85"/>
       <c r="C203" s="85"/>
@@ -9959,7 +9956,7 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="63" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B204" s="85"/>
       <c r="C204" s="85"/>
@@ -9980,7 +9977,7 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="9" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B205" s="85"/>
       <c r="C205" s="85"/>
@@ -10002,7 +9999,7 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="9" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B206" s="85"/>
       <c r="C206" s="85"/>
@@ -10024,7 +10021,7 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B207" s="85"/>
       <c r="C207" s="85"/>
@@ -10046,7 +10043,7 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B208" s="85"/>
       <c r="C208" s="85"/>
@@ -10068,7 +10065,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B209" s="85"/>
       <c r="C209" s="85"/>
@@ -10134,7 +10131,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B212" s="85"/>
       <c r="C212" s="85"/>
@@ -10156,7 +10153,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B213" s="85"/>
       <c r="C213" s="85"/>
@@ -10178,7 +10175,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="35" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B214" s="85"/>
       <c r="C214" s="85"/>
@@ -10200,7 +10197,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="35" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B215" s="85"/>
       <c r="C215" s="85"/>
@@ -10222,7 +10219,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="35" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B216" s="85"/>
       <c r="C216" s="85"/>
@@ -10244,7 +10241,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="35" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B217" s="85"/>
       <c r="C217" s="85"/>
@@ -10266,7 +10263,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="35" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B218" s="85"/>
       <c r="C218" s="85"/>
@@ -10310,7 +10307,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="35" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B220" s="85"/>
       <c r="C220" s="85"/>
@@ -10332,7 +10329,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="63" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B221" s="85"/>
       <c r="C221" s="85"/>
@@ -10353,7 +10350,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="35" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B222" s="85"/>
       <c r="C222" s="85"/>
@@ -10375,7 +10372,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="35" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B223" s="85"/>
       <c r="C223" s="85"/>
@@ -10397,7 +10394,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="35" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B224" s="85"/>
       <c r="C224" s="85"/>
@@ -10419,7 +10416,7 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B225" s="85"/>
       <c r="C225" s="85"/>
@@ -10441,7 +10438,7 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B226" s="85"/>
       <c r="C226" s="85"/>
@@ -10462,7 +10459,7 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B227" s="85"/>
       <c r="C227" s="85"/>
@@ -10483,7 +10480,7 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="63" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B228" s="85"/>
       <c r="C228" s="85"/>
@@ -10504,7 +10501,7 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" s="63" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B229" s="85"/>
       <c r="C229" s="85"/>
@@ -10525,7 +10522,7 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B230" s="85"/>
       <c r="C230" s="85"/>
@@ -10547,7 +10544,7 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B231" s="85"/>
       <c r="C231" s="85"/>
@@ -10569,7 +10566,7 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B232" s="85"/>
       <c r="C232" s="85"/>
@@ -10589,7 +10586,7 @@
         <v>106880</v>
       </c>
       <c r="K232" s="61" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L232" s="66">
         <v>106880</v>
@@ -10597,7 +10594,7 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B233" s="85"/>
       <c r="C233" s="85"/>
@@ -10619,7 +10616,7 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B234" s="85"/>
       <c r="C234" s="85"/>
@@ -10641,7 +10638,7 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B235" s="85"/>
       <c r="C235" s="85"/>
@@ -10663,7 +10660,7 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B236" s="85"/>
       <c r="C236" s="85"/>
@@ -10685,7 +10682,7 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B237" s="85"/>
       <c r="C237" s="85"/>
@@ -10707,7 +10704,7 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B238" s="85"/>
       <c r="C238" s="85"/>
@@ -10729,7 +10726,7 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B239" s="85"/>
       <c r="C239" s="85"/>
@@ -10751,7 +10748,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B240" s="85"/>
       <c r="C240" s="85"/>
@@ -10773,7 +10770,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B241" s="85"/>
       <c r="C241" s="85"/>
@@ -10795,7 +10792,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B242" s="85"/>
       <c r="C242" s="85"/>
@@ -10817,7 +10814,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B243" s="85"/>
       <c r="C243" s="85"/>
@@ -10839,7 +10836,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B244" s="85"/>
       <c r="C244" s="85"/>
@@ -10861,7 +10858,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B245" s="85"/>
       <c r="C245" s="85"/>
@@ -10883,7 +10880,7 @@
     </row>
     <row r="246" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="104" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B246" s="105"/>
       <c r="C246" s="105"/>
@@ -10913,13 +10910,13 @@
       <c r="E247" s="95"/>
       <c r="F247" s="95"/>
       <c r="G247" s="95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H247" s="96" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I247" s="96" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10945,28 +10942,28 @@
     </row>
     <row r="249" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="87" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B249" s="121"/>
       <c r="C249" s="95"/>
       <c r="D249" s="95"/>
       <c r="E249" s="95"/>
       <c r="F249" s="95" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G249" s="95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H249" s="95" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I249" s="96" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="23" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B250" s="84"/>
       <c r="C250" s="84"/>
@@ -10989,7 +10986,7 @@
     </row>
     <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="23" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B251" s="82"/>
       <c r="C251" s="82"/>
@@ -11012,7 +11009,7 @@
     </row>
     <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="23" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B252" s="82"/>
       <c r="C252" s="82"/>
@@ -11035,7 +11032,7 @@
     </row>
     <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="23" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B253" s="82"/>
       <c r="C253" s="82"/>
@@ -11056,7 +11053,7 @@
     </row>
     <row r="254" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="22" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B254" s="100"/>
       <c r="C254" s="100"/>
@@ -11077,28 +11074,28 @@
     </row>
     <row r="255" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="87" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B255" s="121"/>
       <c r="C255" s="95"/>
       <c r="D255" s="95"/>
       <c r="E255" s="95"/>
       <c r="F255" s="95" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G255" s="95" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H255" s="95" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I255" s="96" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="23" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B256" s="84"/>
       <c r="C256" s="84"/>
@@ -11119,7 +11116,7 @@
     </row>
     <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="23" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B257" s="82"/>
       <c r="C257" s="82"/>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2606,7 +2606,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="236">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -3344,6 +3344,9 @@
   </si>
   <si>
     <t>SALON 1</t>
+  </si>
+  <si>
+    <t>SALON 3</t>
   </si>
 </sst>
 </file>
@@ -6947,7 +6950,7 @@
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="40" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B76" s="114" t="s">
         <v>128</v>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -124,7 +124,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Sale del promedio de las consultas particulares</t>
+Sale del promedio de consultas particulares</t>
         </r>
       </text>
     </comment>
@@ -148,7 +148,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Sale del promedio de consultas particulares</t>
+Sale del promedio de las consultas particulares</t>
         </r>
       </text>
     </comment>
@@ -2754,9 +2754,6 @@
     <t>ELECTROCARDIOGRAMA</t>
   </si>
   <si>
-    <t>AMMEN / CONVENIO NUTRICION</t>
-  </si>
-  <si>
     <t>CONDUCTOS ODONTOLOGICOS</t>
   </si>
   <si>
@@ -3347,6 +3344,9 @@
   </si>
   <si>
     <t>SALON 3</t>
+  </si>
+  <si>
+    <t>NUTRICION</t>
   </si>
 </sst>
 </file>
@@ -4190,7 +4190,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4587,6 +4587,7 @@
     <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda 2" xfId="1"/>
@@ -4897,28 +4898,28 @@
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B2" s="114"/>
       <c r="C2" s="115"/>
       <c r="D2" s="115"/>
       <c r="E2" s="116"/>
       <c r="F2" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="68" t="s">
+      <c r="H2" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I2" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="65"/>
       <c r="C3" s="65">
@@ -4934,7 +4935,7 @@
         <v>5550</v>
       </c>
       <c r="G3" s="65" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H3" s="65">
         <v>4550</v>
@@ -4946,7 +4947,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B4" s="150"/>
       <c r="C4" s="150">
@@ -4963,7 +4964,7 @@
         <v>5550</v>
       </c>
       <c r="G4" s="65" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H4" s="150"/>
       <c r="I4" s="151">
@@ -4973,7 +4974,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B5" s="152"/>
       <c r="C5" s="152"/>
@@ -4986,7 +4987,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B6" s="65"/>
       <c r="C6" s="65">
@@ -5006,12 +5007,12 @@
       </c>
       <c r="H6" s="65"/>
       <c r="I6" s="145" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B7" s="150"/>
       <c r="C7" s="150">
@@ -5036,32 +5037,32 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" s="114"/>
       <c r="C8" s="115"/>
       <c r="D8" s="115"/>
       <c r="E8" s="116"/>
       <c r="F8" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="H8" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I8" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J8" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K8" s="55"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="65"/>
       <c r="C9" s="65"/>
@@ -5071,10 +5072,11 @@
       <c r="G9" s="65"/>
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
-      <c r="J9" s="156">
+      <c r="J9" s="70">
         <v>4800</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="160">
+        <f>+J9</f>
         <v>4800</v>
       </c>
     </row>
@@ -5101,20 +5103,20 @@
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>132</v>
+      <c r="A11" s="23" t="s">
+        <v>235</v>
       </c>
       <c r="B11" s="65">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="C11" s="65"/>
       <c r="D11" s="65"/>
       <c r="E11" s="65">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F11" s="65"/>
       <c r="G11" s="70">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="H11" s="65"/>
       <c r="I11" s="65"/>
@@ -5122,20 +5124,20 @@
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
-        <v>42</v>
+      <c r="A12" s="19" t="s">
+        <v>131</v>
       </c>
       <c r="B12" s="65">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="C12" s="65"/>
       <c r="D12" s="65"/>
       <c r="E12" s="65">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F12" s="65"/>
       <c r="G12" s="70">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="H12" s="65"/>
       <c r="I12" s="65"/>
@@ -5144,7 +5146,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="65"/>
       <c r="C13" s="65"/>
@@ -5153,7 +5155,7 @@
         <v>17000</v>
       </c>
       <c r="F13" s="65"/>
-      <c r="G13" s="71">
+      <c r="G13" s="70">
         <v>18000</v>
       </c>
       <c r="H13" s="65"/>
@@ -5163,7 +5165,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B14" s="65"/>
       <c r="C14" s="65"/>
@@ -5172,12 +5174,19 @@
         <v>18400</v>
       </c>
       <c r="F14" s="65"/>
-      <c r="G14" s="71">
+      <c r="G14" s="70">
         <v>20000</v>
       </c>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="156"/>
+      <c r="H14" s="70">
+        <v>7000</v>
+      </c>
+      <c r="I14" s="65">
+        <f>+H14</f>
+        <v>7000</v>
+      </c>
+      <c r="J14" s="70">
+        <v>35000</v>
+      </c>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5189,19 +5198,19 @@
       <c r="D15" s="115"/>
       <c r="E15" s="116"/>
       <c r="F15" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="H15" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H15" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I15" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K15" s="58"/>
     </row>
@@ -5277,7 +5286,7 @@
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="56" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B18" s="65"/>
       <c r="C18" s="65"/>
@@ -5301,21 +5310,21 @@
       <c r="D19" s="115"/>
       <c r="E19" s="116"/>
       <c r="F19" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="H19" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H19" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I19" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B20" s="65">
         <v>20000</v>
@@ -5344,25 +5353,25 @@
       <c r="D21" s="115"/>
       <c r="E21" s="116"/>
       <c r="F21" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="68" t="s">
+      <c r="H21" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H21" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I21" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J21" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K21" s="55"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22" s="65">
         <v>35000</v>
@@ -5402,19 +5411,19 @@
       <c r="D23" s="115"/>
       <c r="E23" s="116"/>
       <c r="F23" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G23" s="68" t="s">
+      <c r="H23" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H23" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I23" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K23" s="55"/>
     </row>
@@ -5433,32 +5442,32 @@
     </row>
     <row r="25" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25" s="114"/>
       <c r="C25" s="115"/>
       <c r="D25" s="115"/>
       <c r="E25" s="116"/>
       <c r="F25" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G25" s="68" t="s">
+      <c r="H25" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H25" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I25" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J25" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K25" s="55"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" s="65">
         <v>20000</v>
@@ -5495,32 +5504,32 @@
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B27" s="114"/>
       <c r="C27" s="115"/>
       <c r="D27" s="115"/>
       <c r="E27" s="116"/>
       <c r="F27" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G27" s="68" t="s">
+      <c r="H27" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H27" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I27" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J27" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K27" s="55"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B28" s="65">
         <v>228334</v>
@@ -5557,32 +5566,32 @@
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="114"/>
       <c r="C29" s="115"/>
       <c r="D29" s="115"/>
       <c r="E29" s="116"/>
       <c r="F29" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G29" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G29" s="68" t="s">
+      <c r="H29" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H29" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I29" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J29" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K29" s="55"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" s="65">
         <v>72000</v>
@@ -5626,25 +5635,25 @@
       <c r="D31" s="115"/>
       <c r="E31" s="116"/>
       <c r="F31" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G31" s="68" t="s">
+      <c r="H31" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H31" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I31" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J31" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K31" s="55"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B32" s="65">
         <v>33000</v>
@@ -5688,25 +5697,25 @@
       <c r="D33" s="115"/>
       <c r="E33" s="116"/>
       <c r="F33" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G33" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="68" t="s">
+      <c r="H33" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H33" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I33" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J33" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K33" s="55"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B34" s="65">
         <v>24600</v>
@@ -5750,25 +5759,25 @@
       <c r="D35" s="115"/>
       <c r="E35" s="116"/>
       <c r="F35" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G35" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G35" s="68" t="s">
+      <c r="H35" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H35" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I35" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J35" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K35" s="55"/>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="65">
         <v>24600</v>
@@ -5812,25 +5821,25 @@
       <c r="D37" s="115"/>
       <c r="E37" s="116"/>
       <c r="F37" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G37" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G37" s="68" t="s">
+      <c r="H37" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I37" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J37" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K37" s="55"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B38" s="65">
         <v>24600</v>
@@ -5874,25 +5883,25 @@
       <c r="D39" s="115"/>
       <c r="E39" s="116"/>
       <c r="F39" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G39" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G39" s="68" t="s">
+      <c r="H39" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H39" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I39" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J39" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K39" s="55"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B40" s="65">
         <v>24600</v>
@@ -5929,32 +5938,32 @@
     </row>
     <row r="41" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B41" s="114"/>
       <c r="C41" s="115"/>
       <c r="D41" s="115"/>
       <c r="E41" s="116"/>
       <c r="F41" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G41" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G41" s="68" t="s">
+      <c r="H41" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I41" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J41" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K41" s="55"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B42" s="65">
         <v>72000</v>
@@ -5998,25 +6007,25 @@
       <c r="D43" s="115"/>
       <c r="E43" s="116"/>
       <c r="F43" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G43" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G43" s="68" t="s">
+      <c r="H43" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H43" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I43" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J43" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K43" s="55"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B44" s="65">
         <v>12000</v>
@@ -6053,7 +6062,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B45" s="65">
         <v>12000</v>
@@ -6090,7 +6099,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B46" s="65">
         <v>12000</v>
@@ -6127,7 +6136,7 @@
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B47" s="65">
         <v>12000</v>
@@ -6171,21 +6180,21 @@
       <c r="D48" s="115"/>
       <c r="E48" s="116"/>
       <c r="F48" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G48" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G48" s="68" t="s">
+      <c r="H48" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H48" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I48" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B49" s="71">
         <v>20000</v>
@@ -6217,7 +6226,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B50" s="71">
         <v>15000</v>
@@ -6249,7 +6258,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B51" s="71">
         <v>15000</v>
@@ -6280,7 +6289,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B52" s="71">
         <v>20000</v>
@@ -6311,7 +6320,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B53" s="71">
         <v>20000</v>
@@ -6342,7 +6351,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B54" s="71">
         <v>20000</v>
@@ -6373,7 +6382,7 @@
     </row>
     <row r="55" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B55" s="71">
         <v>20000</v>
@@ -6411,21 +6420,21 @@
       <c r="D56" s="115"/>
       <c r="E56" s="116"/>
       <c r="F56" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G56" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G56" s="68" t="s">
+      <c r="H56" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H56" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I56" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B57" s="71">
         <v>15000</v>
@@ -6454,28 +6463,28 @@
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B58" s="114"/>
       <c r="C58" s="115"/>
       <c r="D58" s="115"/>
       <c r="E58" s="116"/>
       <c r="F58" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G58" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G58" s="68" t="s">
+      <c r="H58" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H58" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I58" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B59" s="65">
         <v>12000</v>
@@ -6506,23 +6515,23 @@
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B60" s="114"/>
       <c r="C60" s="115"/>
       <c r="D60" s="115"/>
       <c r="E60" s="116"/>
       <c r="F60" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G60" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G60" s="68" t="s">
+      <c r="H60" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H60" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I60" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -6698,27 +6707,27 @@
         <v>8</v>
       </c>
       <c r="B67" s="114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C67" s="115"/>
       <c r="D67" s="115"/>
       <c r="E67" s="116"/>
       <c r="F67" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G67" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G67" s="68" t="s">
+      <c r="H67" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H67" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I67" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B68" s="73">
         <v>111000</v>
@@ -6749,7 +6758,7 @@
     </row>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B69" s="118">
         <v>51000</v>
@@ -6780,30 +6789,30 @@
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B70" s="114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C70" s="115"/>
       <c r="D70" s="115"/>
       <c r="E70" s="116"/>
       <c r="F70" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G70" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G70" s="68" t="s">
+      <c r="H70" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H70" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I70" s="76" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B71" s="73">
         <v>241000</v>
@@ -6834,7 +6843,7 @@
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="57" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B72" s="118">
         <v>68000</v>
@@ -6865,30 +6874,30 @@
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B73" s="114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C73" s="115"/>
       <c r="D73" s="115"/>
       <c r="E73" s="116"/>
       <c r="F73" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G73" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G73" s="68" t="s">
+      <c r="H73" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H73" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I73" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B74" s="73">
         <v>551000</v>
@@ -6919,7 +6928,7 @@
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="59" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B75" s="118">
         <v>132000</v>
@@ -6950,30 +6959,30 @@
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B76" s="114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C76" s="115"/>
       <c r="D76" s="115"/>
       <c r="E76" s="116"/>
       <c r="F76" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G76" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G76" s="68" t="s">
+      <c r="H76" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H76" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I76" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B77" s="73">
         <v>962000</v>
@@ -7004,7 +7013,7 @@
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B78" s="118">
         <v>203000</v>
@@ -7042,16 +7051,16 @@
       <c r="D79" s="115"/>
       <c r="E79" s="116"/>
       <c r="F79" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G79" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G79" s="68" t="s">
+      <c r="H79" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H79" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I79" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -7118,7 +7127,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B82" s="70">
         <v>41000</v>
@@ -7180,23 +7189,23 @@
     </row>
     <row r="84" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B84" s="114"/>
       <c r="C84" s="115"/>
       <c r="D84" s="115"/>
       <c r="E84" s="116"/>
       <c r="F84" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G84" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G84" s="68" t="s">
+      <c r="H84" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H84" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I84" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7219,27 +7228,27 @@
         <v>30</v>
       </c>
       <c r="B86" s="114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C86" s="115"/>
       <c r="D86" s="115"/>
       <c r="E86" s="116"/>
       <c r="F86" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G86" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G86" s="68" t="s">
+      <c r="H86" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H86" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I86" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="45" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B87" s="73">
         <v>97000</v>
@@ -7270,7 +7279,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B88" s="73">
         <v>282000</v>
@@ -7301,7 +7310,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B89" s="73">
         <v>256000</v>
@@ -7332,7 +7341,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B90" s="73">
         <v>508000</v>
@@ -7363,7 +7372,7 @@
     </row>
     <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="123" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B91" s="124">
         <v>8200</v>
@@ -7397,22 +7406,22 @@
         <v>33</v>
       </c>
       <c r="B92" s="114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C92" s="127"/>
       <c r="D92" s="127"/>
       <c r="E92" s="128"/>
       <c r="F92" s="129" t="s">
+        <v>93</v>
+      </c>
+      <c r="G92" s="129" t="s">
         <v>94</v>
       </c>
-      <c r="G92" s="129" t="s">
+      <c r="H92" s="130" t="s">
         <v>95</v>
       </c>
-      <c r="H92" s="130" t="s">
-        <v>96</v>
-      </c>
       <c r="I92" s="130" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -7501,22 +7510,22 @@
         <v>37</v>
       </c>
       <c r="B96" s="114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C96" s="115"/>
       <c r="D96" s="115"/>
       <c r="E96" s="116"/>
       <c r="F96" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G96" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G96" s="68" t="s">
+      <c r="H96" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H96" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I96" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -7617,27 +7626,27 @@
         <v>26</v>
       </c>
       <c r="B100" s="114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C100" s="115"/>
       <c r="D100" s="115"/>
       <c r="E100" s="116"/>
       <c r="F100" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="G100" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G100" s="68" t="s">
+      <c r="H100" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H100" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I100" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B101" s="73">
         <v>55600</v>
@@ -7668,7 +7677,7 @@
     </row>
     <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B102" s="73">
         <v>13900</v>
@@ -7699,7 +7708,7 @@
     </row>
     <row r="103" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B103" s="80"/>
       <c r="C103" s="80"/>
@@ -7712,30 +7721,30 @@
     </row>
     <row r="104" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B104" s="114" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C104" s="115"/>
       <c r="D104" s="115"/>
       <c r="E104" s="116"/>
       <c r="F104" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="G104" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="G104" s="81" t="s">
+      <c r="H104" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H104" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I104" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B105" s="65">
         <v>88886</v>
@@ -7766,7 +7775,7 @@
     </row>
     <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B106" s="65">
         <v>103703</v>
@@ -7797,7 +7806,7 @@
     </row>
     <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B107" s="65">
         <v>174729</v>
@@ -7828,7 +7837,7 @@
     </row>
     <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B108" s="65">
         <v>22223</v>
@@ -7859,7 +7868,7 @@
     </row>
     <row r="109" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B109" s="65">
         <v>111110</v>
@@ -7890,30 +7899,30 @@
     </row>
     <row r="110" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B110" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C110" s="115"/>
       <c r="D110" s="115"/>
       <c r="E110" s="116"/>
       <c r="F110" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="G110" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="G110" s="81" t="s">
+      <c r="H110" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H110" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I110" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B111" s="65">
         <v>312686</v>
@@ -7944,7 +7953,7 @@
     </row>
     <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B112" s="65">
         <v>349723</v>
@@ -7975,7 +7984,7 @@
     </row>
     <row r="113" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B113" s="65">
         <v>446016</v>
@@ -8006,30 +8015,30 @@
     </row>
     <row r="114" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B114" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C114" s="115"/>
       <c r="D114" s="115"/>
       <c r="E114" s="116"/>
       <c r="F114" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="G114" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="G114" s="81" t="s">
+      <c r="H114" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H114" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I114" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B115" s="65">
         <v>128763</v>
@@ -8060,7 +8069,7 @@
     </row>
     <row r="116" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B116" s="65">
         <v>199762</v>
@@ -8091,30 +8100,30 @@
     </row>
     <row r="117" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B117" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C117" s="115"/>
       <c r="D117" s="115"/>
       <c r="E117" s="116"/>
       <c r="F117" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="G117" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="G117" s="81" t="s">
+      <c r="H117" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H117" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I117" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B118" s="65">
         <v>477701</v>
@@ -8145,7 +8154,7 @@
     </row>
     <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B119" s="65">
         <v>236516</v>
@@ -8176,7 +8185,7 @@
     </row>
     <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B120" s="65">
         <v>274873</v>
@@ -8207,7 +8216,7 @@
     </row>
     <row r="121" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B121" s="65">
         <v>313203</v>
@@ -8238,30 +8247,30 @@
     </row>
     <row r="122" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B122" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C122" s="115"/>
       <c r="D122" s="115"/>
       <c r="E122" s="116"/>
       <c r="F122" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="G122" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="G122" s="81" t="s">
+      <c r="H122" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="H122" s="69" t="s">
-        <v>96</v>
-      </c>
       <c r="I122" s="69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B123" s="65">
         <v>139695</v>
@@ -8292,7 +8301,7 @@
     </row>
     <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B124" s="65">
         <v>153373</v>
@@ -8323,7 +8332,7 @@
     </row>
     <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B125" s="65">
         <v>184044</v>
@@ -8354,7 +8363,7 @@
     </row>
     <row r="126" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="139" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B126" s="110">
         <v>49078</v>
@@ -8385,30 +8394,30 @@
     </row>
     <row r="127" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="141" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B127" s="138" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C127" s="127"/>
       <c r="D127" s="127"/>
       <c r="E127" s="128"/>
       <c r="F127" s="129" t="s">
+        <v>93</v>
+      </c>
+      <c r="G127" s="129" t="s">
         <v>94</v>
       </c>
-      <c r="G127" s="129" t="s">
+      <c r="H127" s="130" t="s">
         <v>95</v>
       </c>
-      <c r="H127" s="130" t="s">
-        <v>96</v>
-      </c>
       <c r="I127" s="130" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="140" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B128" s="136">
         <v>661862</v>
@@ -8439,7 +8448,7 @@
     </row>
     <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B129" s="65">
         <v>692556</v>
@@ -8470,7 +8479,7 @@
     </row>
     <row r="130" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="135" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B130" s="110">
         <v>90078</v>
@@ -8501,7 +8510,7 @@
     </row>
     <row r="131" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="137" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B131" s="138"/>
       <c r="C131" s="127"/>
@@ -8509,18 +8518,18 @@
       <c r="E131" s="128"/>
       <c r="F131" s="129"/>
       <c r="G131" s="129" t="s">
+        <v>94</v>
+      </c>
+      <c r="H131" s="130" t="s">
         <v>95</v>
       </c>
-      <c r="H131" s="130" t="s">
-        <v>96</v>
-      </c>
       <c r="I131" s="130" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="142" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B132" s="136"/>
       <c r="C132" s="136"/>
@@ -8535,7 +8544,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="144" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B133" s="65"/>
       <c r="C133" s="65"/>
@@ -8556,7 +8565,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="144" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B134" s="65"/>
       <c r="C134" s="65"/>
@@ -8577,7 +8586,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="144" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B135" s="65"/>
       <c r="C135" s="65"/>
@@ -8598,7 +8607,7 @@
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="144" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B136" s="65"/>
       <c r="C136" s="65"/>
@@ -8614,7 +8623,7 @@
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="144" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B137" s="65"/>
       <c r="C137" s="65"/>
@@ -8630,7 +8639,7 @@
     </row>
     <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="144" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B138" s="65"/>
       <c r="C138" s="65"/>
@@ -8646,7 +8655,7 @@
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="144" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B139" s="65"/>
       <c r="C139" s="65"/>
@@ -8662,7 +8671,7 @@
     </row>
     <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="144" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B140" s="65"/>
       <c r="C140" s="65"/>
@@ -8678,7 +8687,7 @@
     </row>
     <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="144" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B141" s="65"/>
       <c r="C141" s="65"/>
@@ -8694,7 +8703,7 @@
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="144" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B142" s="65"/>
       <c r="C142" s="65"/>
@@ -8710,7 +8719,7 @@
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="144" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B143" s="65"/>
       <c r="C143" s="65"/>
@@ -8726,7 +8735,7 @@
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="144" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B144" s="65"/>
       <c r="C144" s="65"/>
@@ -8742,7 +8751,7 @@
     </row>
     <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="144" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B145" s="65"/>
       <c r="C145" s="65"/>
@@ -8758,7 +8767,7 @@
     </row>
     <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="144" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B146" s="65"/>
       <c r="C146" s="65"/>
@@ -8774,7 +8783,7 @@
     </row>
     <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="144" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B147" s="65"/>
       <c r="C147" s="65"/>
@@ -8790,7 +8799,7 @@
     </row>
     <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="144" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B148" s="65"/>
       <c r="C148" s="65"/>
@@ -8806,7 +8815,7 @@
     </row>
     <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="144" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B149" s="65"/>
       <c r="C149" s="65"/>
@@ -8822,7 +8831,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="146" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B150" s="110"/>
       <c r="C150" s="110"/>
@@ -8843,7 +8852,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="146" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B151" s="110"/>
       <c r="C151" s="110"/>
@@ -8865,7 +8874,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="146" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B152" s="120"/>
       <c r="C152" s="120"/>
@@ -8887,7 +8896,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="146" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B153" s="110"/>
       <c r="C153" s="110"/>
@@ -8909,7 +8918,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="146" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B154" s="110"/>
       <c r="C154" s="110"/>
@@ -8930,7 +8939,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="146" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B155" s="110"/>
       <c r="C155" s="110"/>
@@ -8945,7 +8954,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="146" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B156" s="110"/>
       <c r="C156" s="110"/>
@@ -8966,7 +8975,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="146" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B157" s="110"/>
       <c r="C157" s="110"/>
@@ -8981,7 +8990,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="146" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B158" s="110"/>
       <c r="C158" s="110"/>
@@ -9002,7 +9011,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="146" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B159" s="110"/>
       <c r="C159" s="110"/>
@@ -9017,7 +9026,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="146" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B160" s="110"/>
       <c r="C160" s="110"/>
@@ -9038,7 +9047,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="146" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B161" s="110"/>
       <c r="C161" s="110"/>
@@ -9053,7 +9062,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="146" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B162" s="110"/>
       <c r="C162" s="110"/>
@@ -9075,7 +9084,7 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="146" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B163" s="110"/>
       <c r="C163" s="110"/>
@@ -9090,7 +9099,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="146" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B164" s="110"/>
       <c r="C164" s="110"/>
@@ -9105,7 +9114,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="146" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B165" s="110"/>
       <c r="C165" s="110"/>
@@ -9120,7 +9129,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="146" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B166" s="110"/>
       <c r="C166" s="110"/>
@@ -9142,7 +9151,7 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="144" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B167" s="65"/>
       <c r="C167" s="65"/>
@@ -9157,7 +9166,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="144" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B168" s="65"/>
       <c r="C168" s="65"/>
@@ -9172,7 +9181,7 @@
     </row>
     <row r="169" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="146" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B169" s="120"/>
       <c r="C169" s="120"/>
@@ -9213,17 +9222,17 @@
       <c r="E171" s="95"/>
       <c r="F171" s="95"/>
       <c r="G171" s="95" t="s">
+        <v>94</v>
+      </c>
+      <c r="H171" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="H171" s="95" t="s">
-        <v>96</v>
-      </c>
       <c r="I171" s="96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J171" s="158"/>
       <c r="K171" s="61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L171" s="66">
         <v>12000</v>
@@ -9231,7 +9240,7 @@
     </row>
     <row r="172" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B172" s="84"/>
       <c r="C172" s="84"/>
@@ -9254,7 +9263,7 @@
     </row>
     <row r="173" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B173" s="82"/>
       <c r="C173" s="82"/>
@@ -9274,7 +9283,7 @@
       </c>
       <c r="J173" s="158"/>
       <c r="K173" s="61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L173" s="66">
         <v>22000</v>
@@ -9282,7 +9291,7 @@
     </row>
     <row r="174" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B174" s="82"/>
       <c r="C174" s="82"/>
@@ -9305,7 +9314,7 @@
     </row>
     <row r="175" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B175" s="82"/>
       <c r="C175" s="82"/>
@@ -9328,7 +9337,7 @@
     </row>
     <row r="176" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B176" s="82"/>
       <c r="C176" s="82"/>
@@ -9351,7 +9360,7 @@
     </row>
     <row r="177" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B177" s="82"/>
       <c r="C177" s="82"/>
@@ -9374,7 +9383,7 @@
     </row>
     <row r="178" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B178" s="82"/>
       <c r="C178" s="82"/>
@@ -9397,7 +9406,7 @@
     </row>
     <row r="179" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B179" s="82"/>
       <c r="C179" s="82"/>
@@ -9420,7 +9429,7 @@
     </row>
     <row r="180" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B180" s="82"/>
       <c r="C180" s="82"/>
@@ -9443,7 +9452,7 @@
     </row>
     <row r="181" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B181" s="82"/>
       <c r="C181" s="82"/>
@@ -9466,7 +9475,7 @@
     </row>
     <row r="182" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B182" s="82"/>
       <c r="C182" s="82"/>
@@ -9489,7 +9498,7 @@
     </row>
     <row r="183" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B183" s="82"/>
       <c r="C183" s="82"/>
@@ -9512,7 +9521,7 @@
     </row>
     <row r="184" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B184" s="100"/>
       <c r="C184" s="100"/>
@@ -9535,7 +9544,7 @@
     </row>
     <row r="185" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B185" s="84"/>
       <c r="C185" s="84"/>
@@ -9554,7 +9563,7 @@
     </row>
     <row r="186" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B186" s="89"/>
       <c r="C186" s="89"/>
@@ -9573,7 +9582,7 @@
     </row>
     <row r="187" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="87" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B187" s="121"/>
       <c r="C187" s="122"/>
@@ -9581,13 +9590,13 @@
       <c r="E187" s="95"/>
       <c r="F187" s="95"/>
       <c r="G187" s="95" t="s">
+        <v>94</v>
+      </c>
+      <c r="H187" s="96" t="s">
         <v>95</v>
       </c>
-      <c r="H187" s="96" t="s">
-        <v>96</v>
-      </c>
       <c r="I187" s="96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -9613,7 +9622,7 @@
     </row>
     <row r="189" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B189" s="71"/>
       <c r="C189" s="71"/>
@@ -9632,7 +9641,7 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B190" s="85"/>
       <c r="C190" s="85"/>
@@ -9652,7 +9661,7 @@
         <v>16640</v>
       </c>
       <c r="K190" s="61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L190" s="66">
         <v>16640</v>
@@ -9660,7 +9669,7 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B191" s="85"/>
       <c r="C191" s="85"/>
@@ -9680,7 +9689,7 @@
         <v>9600</v>
       </c>
       <c r="K191" s="61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L191" s="66">
         <v>9600</v>
@@ -9688,7 +9697,7 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B192" s="85"/>
       <c r="C192" s="85"/>
@@ -9711,7 +9720,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B193" s="85"/>
       <c r="C193" s="85"/>
@@ -9731,7 +9740,7 @@
         <v>9600</v>
       </c>
       <c r="K193" s="61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L193" s="66">
         <v>32000</v>
@@ -9739,7 +9748,7 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B194" s="85"/>
       <c r="C194" s="85"/>
@@ -9761,7 +9770,7 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B195" s="85"/>
       <c r="C195" s="85"/>
@@ -9783,7 +9792,7 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B196" s="85"/>
       <c r="C196" s="85"/>
@@ -9805,7 +9814,7 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B197" s="85"/>
       <c r="C197" s="85"/>
@@ -9827,7 +9836,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B198" s="85"/>
       <c r="C198" s="85"/>
@@ -9849,7 +9858,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B199" s="85"/>
       <c r="C199" s="85"/>
@@ -9871,7 +9880,7 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B200" s="85"/>
       <c r="C200" s="85"/>
@@ -9893,7 +9902,7 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B201" s="85"/>
       <c r="C201" s="85"/>
@@ -9915,7 +9924,7 @@
     </row>
     <row r="202" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B202" s="85"/>
       <c r="C202" s="85"/>
@@ -9937,7 +9946,7 @@
     </row>
     <row r="203" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B203" s="85"/>
       <c r="C203" s="85"/>
@@ -9959,7 +9968,7 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B204" s="85"/>
       <c r="C204" s="85"/>
@@ -9980,7 +9989,7 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B205" s="85"/>
       <c r="C205" s="85"/>
@@ -10002,7 +10011,7 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B206" s="85"/>
       <c r="C206" s="85"/>
@@ -10024,7 +10033,7 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B207" s="85"/>
       <c r="C207" s="85"/>
@@ -10046,7 +10055,7 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B208" s="85"/>
       <c r="C208" s="85"/>
@@ -10068,7 +10077,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B209" s="85"/>
       <c r="C209" s="85"/>
@@ -10090,7 +10099,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B210" s="85"/>
       <c r="C210" s="85"/>
@@ -10112,7 +10121,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B211" s="85"/>
       <c r="C211" s="85"/>
@@ -10134,7 +10143,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B212" s="85"/>
       <c r="C212" s="85"/>
@@ -10156,7 +10165,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B213" s="85"/>
       <c r="C213" s="85"/>
@@ -10178,7 +10187,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B214" s="85"/>
       <c r="C214" s="85"/>
@@ -10200,7 +10209,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B215" s="85"/>
       <c r="C215" s="85"/>
@@ -10222,7 +10231,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B216" s="85"/>
       <c r="C216" s="85"/>
@@ -10244,7 +10253,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B217" s="85"/>
       <c r="C217" s="85"/>
@@ -10266,7 +10275,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B218" s="85"/>
       <c r="C218" s="85"/>
@@ -10288,7 +10297,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B219" s="85"/>
       <c r="C219" s="85"/>
@@ -10310,7 +10319,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B220" s="85"/>
       <c r="C220" s="85"/>
@@ -10332,7 +10341,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="63" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B221" s="85"/>
       <c r="C221" s="85"/>
@@ -10353,7 +10362,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B222" s="85"/>
       <c r="C222" s="85"/>
@@ -10375,7 +10384,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B223" s="85"/>
       <c r="C223" s="85"/>
@@ -10397,7 +10406,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B224" s="85"/>
       <c r="C224" s="85"/>
@@ -10419,7 +10428,7 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B225" s="85"/>
       <c r="C225" s="85"/>
@@ -10441,7 +10450,7 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B226" s="85"/>
       <c r="C226" s="85"/>
@@ -10462,7 +10471,7 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B227" s="85"/>
       <c r="C227" s="85"/>
@@ -10483,7 +10492,7 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B228" s="85"/>
       <c r="C228" s="85"/>
@@ -10504,7 +10513,7 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" s="63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B229" s="85"/>
       <c r="C229" s="85"/>
@@ -10525,7 +10534,7 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B230" s="85"/>
       <c r="C230" s="85"/>
@@ -10547,7 +10556,7 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B231" s="85"/>
       <c r="C231" s="85"/>
@@ -10569,7 +10578,7 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B232" s="85"/>
       <c r="C232" s="85"/>
@@ -10589,7 +10598,7 @@
         <v>106880</v>
       </c>
       <c r="K232" s="61" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L232" s="66">
         <v>106880</v>
@@ -10597,7 +10606,7 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B233" s="85"/>
       <c r="C233" s="85"/>
@@ -10619,7 +10628,7 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B234" s="85"/>
       <c r="C234" s="85"/>
@@ -10641,7 +10650,7 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B235" s="85"/>
       <c r="C235" s="85"/>
@@ -10663,7 +10672,7 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B236" s="85"/>
       <c r="C236" s="85"/>
@@ -10685,7 +10694,7 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B237" s="85"/>
       <c r="C237" s="85"/>
@@ -10707,7 +10716,7 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B238" s="85"/>
       <c r="C238" s="85"/>
@@ -10729,7 +10738,7 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B239" s="85"/>
       <c r="C239" s="85"/>
@@ -10751,7 +10760,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B240" s="85"/>
       <c r="C240" s="85"/>
@@ -10773,7 +10782,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B241" s="85"/>
       <c r="C241" s="85"/>
@@ -10795,7 +10804,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B242" s="85"/>
       <c r="C242" s="85"/>
@@ -10817,7 +10826,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B243" s="85"/>
       <c r="C243" s="85"/>
@@ -10839,7 +10848,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B244" s="85"/>
       <c r="C244" s="85"/>
@@ -10861,7 +10870,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B245" s="85"/>
       <c r="C245" s="85"/>
@@ -10883,7 +10892,7 @@
     </row>
     <row r="246" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="104" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B246" s="105"/>
       <c r="C246" s="105"/>
@@ -10913,13 +10922,13 @@
       <c r="E247" s="95"/>
       <c r="F247" s="95"/>
       <c r="G247" s="95" t="s">
+        <v>94</v>
+      </c>
+      <c r="H247" s="96" t="s">
         <v>95</v>
       </c>
-      <c r="H247" s="96" t="s">
-        <v>96</v>
-      </c>
       <c r="I247" s="96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10945,28 +10954,28 @@
     </row>
     <row r="249" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="87" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B249" s="121"/>
       <c r="C249" s="95"/>
       <c r="D249" s="95"/>
       <c r="E249" s="95"/>
       <c r="F249" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="G249" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="G249" s="95" t="s">
+      <c r="H249" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="H249" s="95" t="s">
-        <v>96</v>
-      </c>
       <c r="I249" s="96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B250" s="84"/>
       <c r="C250" s="84"/>
@@ -10989,7 +10998,7 @@
     </row>
     <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B251" s="82"/>
       <c r="C251" s="82"/>
@@ -11012,7 +11021,7 @@
     </row>
     <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B252" s="82"/>
       <c r="C252" s="82"/>
@@ -11035,7 +11044,7 @@
     </row>
     <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B253" s="82"/>
       <c r="C253" s="82"/>
@@ -11056,7 +11065,7 @@
     </row>
     <row r="254" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B254" s="100"/>
       <c r="C254" s="100"/>
@@ -11077,34 +11086,34 @@
     </row>
     <row r="255" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="87" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B255" s="121"/>
       <c r="C255" s="95"/>
       <c r="D255" s="95"/>
       <c r="E255" s="95"/>
       <c r="F255" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="G255" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="G255" s="95" t="s">
+      <c r="H255" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="H255" s="95" t="s">
-        <v>96</v>
-      </c>
       <c r="I255" s="96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B256" s="84"/>
       <c r="C256" s="84"/>
       <c r="D256" s="84"/>
       <c r="E256" s="84"/>
-      <c r="F256" s="102"/>
+      <c r="F256" s="84"/>
       <c r="G256" s="102">
         <v>35000</v>
       </c>
@@ -11119,13 +11128,13 @@
     </row>
     <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B257" s="82"/>
       <c r="C257" s="82"/>
       <c r="D257" s="82"/>
       <c r="E257" s="82"/>
-      <c r="F257" s="83"/>
+      <c r="F257" s="82"/>
       <c r="G257" s="83">
         <v>35000</v>
       </c>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -439,7 +439,7 @@
         <v>CUOTAS SEPELIO</v>
       </c>
       <c r="E2">
-        <v>5551</v>
+        <v>12000</v>
       </c>
       <c r="F2" t="str">
         <v>incluida</v>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2553,7 +2553,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A249" authorId="0" shapeId="0">
+    <comment ref="A251" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2577,7 +2577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A255" authorId="0" shapeId="0">
+    <comment ref="A257" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2606,7 +2606,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="238">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -3031,9 +3031,6 @@
     <t>TRASLUCENCIA NUCAL</t>
   </si>
   <si>
-    <t xml:space="preserve">ECODOPPLER  </t>
-  </si>
-  <si>
     <t>CONSULTA MEDICA A</t>
   </si>
   <si>
@@ -3347,6 +3344,15 @@
   </si>
   <si>
     <t>NUTRICION</t>
+  </si>
+  <si>
+    <t>ECODOPPLER TIROIDEO</t>
+  </si>
+  <si>
+    <t>ECODOPPLER VASOS DEL CUELLO</t>
+  </si>
+  <si>
+    <t>ECODOPPLER TESTICULAR</t>
   </si>
 </sst>
 </file>
@@ -4190,7 +4196,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4381,9 +4387,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4584,10 +4587,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda 2" xfId="1"/>
@@ -4874,7 +4886,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L257"/>
+  <dimension ref="A1:L259"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
@@ -4883,7 +4895,7 @@
     <col min="5" max="5" width="10.42578125" style="67" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="11.5703125" style="67" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.5703125" style="67" customWidth="1"/>
-    <col min="10" max="10" width="18" style="155" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" style="154" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4898,12 +4910,12 @@
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="B2" s="114"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="116"/>
+        <v>224</v>
+      </c>
+      <c r="B2" s="113"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
       <c r="F2" s="68" t="s">
         <v>93</v>
       </c>
@@ -4935,59 +4947,59 @@
         <v>5550</v>
       </c>
       <c r="G3" s="65" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H3" s="65">
         <v>4550</v>
       </c>
-      <c r="I3" s="145">
+      <c r="I3" s="144">
         <f>+F3</f>
         <v>5550</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="B4" s="150"/>
-      <c r="C4" s="150">
+        <v>226</v>
+      </c>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149">
         <v>8500</v>
       </c>
-      <c r="D4" s="150">
+      <c r="D4" s="149">
         <v>8500</v>
       </c>
-      <c r="E4" s="150">
+      <c r="E4" s="149">
         <v>8500</v>
       </c>
-      <c r="F4" s="150">
+      <c r="F4" s="149">
         <f>+F3</f>
         <v>5550</v>
       </c>
       <c r="G4" s="65" t="s">
-        <v>226</v>
-      </c>
-      <c r="H4" s="150"/>
-      <c r="I4" s="151">
+        <v>225</v>
+      </c>
+      <c r="H4" s="149"/>
+      <c r="I4" s="150">
         <f>+I3*2</f>
         <v>11100</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="152"/>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
-      <c r="H5" s="152"/>
-      <c r="I5" s="153"/>
+        <v>223</v>
+      </c>
+      <c r="B5" s="151"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="152"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B6" s="65"/>
       <c r="C6" s="65">
@@ -5006,7 +5018,7 @@
         <v>30000</v>
       </c>
       <c r="H6" s="65"/>
-      <c r="I6" s="145" t="s">
+      <c r="I6" s="144" t="s">
         <v>124</v>
       </c>
     </row>
@@ -5014,35 +5026,35 @@
       <c r="A7" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="150"/>
-      <c r="C7" s="150">
+      <c r="B7" s="149"/>
+      <c r="C7" s="149">
         <v>14000</v>
       </c>
-      <c r="D7" s="150">
+      <c r="D7" s="149">
         <v>14000</v>
       </c>
-      <c r="E7" s="150">
+      <c r="E7" s="149">
         <v>20000</v>
       </c>
-      <c r="F7" s="154">
+      <c r="F7" s="153">
         <f>+F6/2</f>
         <v>7500</v>
       </c>
-      <c r="G7" s="154">
+      <c r="G7" s="153">
         <f>+G6/2</f>
         <v>15000</v>
       </c>
-      <c r="H7" s="150"/>
-      <c r="I7" s="151"/>
+      <c r="H7" s="149"/>
+      <c r="I7" s="150"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="114"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="116"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="114"/>
+      <c r="E8" s="115"/>
       <c r="F8" s="68" t="s">
         <v>93</v>
       </c>
@@ -5055,8 +5067,8 @@
       <c r="I8" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J8" s="114" t="s">
-        <v>150</v>
+      <c r="J8" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K8" s="55"/>
     </row>
@@ -5075,7 +5087,7 @@
       <c r="J9" s="70">
         <v>4800</v>
       </c>
-      <c r="K9" s="160">
+      <c r="K9" s="158">
         <f>+J9</f>
         <v>4800</v>
       </c>
@@ -5099,12 +5111,12 @@
       </c>
       <c r="H10" s="65"/>
       <c r="I10" s="65"/>
-      <c r="J10" s="156"/>
+      <c r="J10" s="155"/>
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B11" s="65">
         <v>25000</v>
@@ -5120,12 +5132,12 @@
       </c>
       <c r="H11" s="65"/>
       <c r="I11" s="65"/>
-      <c r="J11" s="156"/>
+      <c r="J11" s="155"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" s="65">
         <v>30000</v>
@@ -5141,12 +5153,12 @@
       </c>
       <c r="H12" s="65"/>
       <c r="I12" s="65"/>
-      <c r="J12" s="156"/>
+      <c r="J12" s="155"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B13" s="65"/>
       <c r="C13" s="65"/>
@@ -5160,12 +5172,12 @@
       </c>
       <c r="H13" s="65"/>
       <c r="I13" s="65"/>
-      <c r="J13" s="156"/>
+      <c r="J13" s="155"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B14" s="65"/>
       <c r="C14" s="65"/>
@@ -5193,10 +5205,10 @@
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="116"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="115"/>
       <c r="F15" s="68" t="s">
         <v>93</v>
       </c>
@@ -5209,8 +5221,8 @@
       <c r="I15" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="114" t="s">
-        <v>150</v>
+      <c r="J15" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K15" s="58"/>
     </row>
@@ -5242,7 +5254,7 @@
       <c r="I16" s="65">
         <v>0</v>
       </c>
-      <c r="J16" s="156">
+      <c r="J16" s="155">
         <v>29500</v>
       </c>
       <c r="K16" s="11">
@@ -5277,7 +5289,7 @@
       <c r="I17" s="65">
         <v>0</v>
       </c>
-      <c r="J17" s="156">
+      <c r="J17" s="155">
         <v>59000</v>
       </c>
       <c r="K17" s="11">
@@ -5298,17 +5310,17 @@
       <c r="G18" s="65"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
-      <c r="J18" s="156"/>
+      <c r="J18" s="155"/>
       <c r="K18" s="11"/>
     </row>
     <row r="19" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="114"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="116"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="115"/>
       <c r="F19" s="68" t="s">
         <v>93</v>
       </c>
@@ -5348,10 +5360,10 @@
       <c r="A21" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="114"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="115"/>
-      <c r="E21" s="116"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="115"/>
       <c r="F21" s="68" t="s">
         <v>93</v>
       </c>
@@ -5364,8 +5376,8 @@
       <c r="I21" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J21" s="114" t="s">
-        <v>150</v>
+      <c r="J21" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K21" s="55"/>
     </row>
@@ -5395,7 +5407,7 @@
       <c r="I22" s="65">
         <v>0</v>
       </c>
-      <c r="J22" s="156">
+      <c r="J22" s="155">
         <v>35000</v>
       </c>
       <c r="K22" s="11">
@@ -5406,10 +5418,10 @@
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="114"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="116"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="114"/>
+      <c r="D23" s="114"/>
+      <c r="E23" s="115"/>
       <c r="F23" s="68" t="s">
         <v>93</v>
       </c>
@@ -5422,8 +5434,8 @@
       <c r="I23" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J23" s="114" t="s">
-        <v>150</v>
+      <c r="J23" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K23" s="55"/>
     </row>
@@ -5437,17 +5449,17 @@
       <c r="G24" s="70"/>
       <c r="H24" s="65"/>
       <c r="I24" s="65"/>
-      <c r="J24" s="156"/>
+      <c r="J24" s="155"/>
       <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B25" s="114"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="115"/>
-      <c r="E25" s="116"/>
+      <c r="B25" s="113"/>
+      <c r="C25" s="114"/>
+      <c r="D25" s="114"/>
+      <c r="E25" s="115"/>
       <c r="F25" s="68" t="s">
         <v>93</v>
       </c>
@@ -5460,8 +5472,8 @@
       <c r="I25" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J25" s="114" t="s">
-        <v>150</v>
+      <c r="J25" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K25" s="55"/>
     </row>
@@ -5495,7 +5507,7 @@
       <c r="I26" s="65">
         <v>0</v>
       </c>
-      <c r="J26" s="156">
+      <c r="J26" s="155">
         <v>17400</v>
       </c>
       <c r="K26" s="11">
@@ -5506,10 +5518,10 @@
       <c r="A27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="114"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="116"/>
+      <c r="B27" s="113"/>
+      <c r="C27" s="114"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="115"/>
       <c r="F27" s="68" t="s">
         <v>93</v>
       </c>
@@ -5522,8 +5534,8 @@
       <c r="I27" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J27" s="114" t="s">
-        <v>150</v>
+      <c r="J27" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K27" s="55"/>
     </row>
@@ -5557,7 +5569,7 @@
       <c r="I28" s="65">
         <v>74000</v>
       </c>
-      <c r="J28" s="156">
+      <c r="J28" s="155">
         <v>199000</v>
       </c>
       <c r="K28" s="11">
@@ -5568,10 +5580,10 @@
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="114"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="116"/>
+      <c r="B29" s="113"/>
+      <c r="C29" s="114"/>
+      <c r="D29" s="114"/>
+      <c r="E29" s="115"/>
       <c r="F29" s="68" t="s">
         <v>93</v>
       </c>
@@ -5584,8 +5596,8 @@
       <c r="I29" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J29" s="114" t="s">
-        <v>150</v>
+      <c r="J29" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K29" s="55"/>
     </row>
@@ -5619,7 +5631,7 @@
       <c r="I30" s="65">
         <v>16800</v>
       </c>
-      <c r="J30" s="156">
+      <c r="J30" s="155">
         <v>43400</v>
       </c>
       <c r="K30" s="11">
@@ -5630,10 +5642,10 @@
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="114"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="116"/>
+      <c r="B31" s="113"/>
+      <c r="C31" s="114"/>
+      <c r="D31" s="114"/>
+      <c r="E31" s="115"/>
       <c r="F31" s="68" t="s">
         <v>93</v>
       </c>
@@ -5646,8 +5658,8 @@
       <c r="I31" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J31" s="114" t="s">
-        <v>150</v>
+      <c r="J31" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K31" s="55"/>
     </row>
@@ -5681,7 +5693,7 @@
       <c r="I32" s="65">
         <v>10800</v>
       </c>
-      <c r="J32" s="156">
+      <c r="J32" s="155">
         <v>20300</v>
       </c>
       <c r="K32" s="11">
@@ -5692,10 +5704,10 @@
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="114"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="116"/>
+      <c r="B33" s="113"/>
+      <c r="C33" s="114"/>
+      <c r="D33" s="114"/>
+      <c r="E33" s="115"/>
       <c r="F33" s="68" t="s">
         <v>93</v>
       </c>
@@ -5708,8 +5720,8 @@
       <c r="I33" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J33" s="114" t="s">
-        <v>150</v>
+      <c r="J33" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K33" s="55"/>
     </row>
@@ -5743,7 +5755,7 @@
       <c r="I34" s="65">
         <v>6300</v>
       </c>
-      <c r="J34" s="156">
+      <c r="J34" s="155">
         <v>15200</v>
       </c>
       <c r="K34" s="11">
@@ -5754,10 +5766,10 @@
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="114"/>
-      <c r="C35" s="115"/>
-      <c r="D35" s="115"/>
-      <c r="E35" s="116"/>
+      <c r="B35" s="113"/>
+      <c r="C35" s="114"/>
+      <c r="D35" s="114"/>
+      <c r="E35" s="115"/>
       <c r="F35" s="68" t="s">
         <v>93</v>
       </c>
@@ -5770,8 +5782,8 @@
       <c r="I35" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J35" s="114" t="s">
-        <v>150</v>
+      <c r="J35" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K35" s="55"/>
     </row>
@@ -5805,7 +5817,7 @@
       <c r="I36" s="65">
         <v>6300</v>
       </c>
-      <c r="J36" s="156">
+      <c r="J36" s="155">
         <v>15200</v>
       </c>
       <c r="K36" s="11">
@@ -5816,10 +5828,10 @@
       <c r="A37" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="114"/>
-      <c r="C37" s="115"/>
-      <c r="D37" s="115"/>
-      <c r="E37" s="116"/>
+      <c r="B37" s="113"/>
+      <c r="C37" s="114"/>
+      <c r="D37" s="114"/>
+      <c r="E37" s="115"/>
       <c r="F37" s="68" t="s">
         <v>93</v>
       </c>
@@ -5832,8 +5844,8 @@
       <c r="I37" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J37" s="114" t="s">
-        <v>150</v>
+      <c r="J37" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K37" s="55"/>
     </row>
@@ -5867,7 +5879,7 @@
       <c r="I38" s="65">
         <v>6300</v>
       </c>
-      <c r="J38" s="156">
+      <c r="J38" s="155">
         <v>15200</v>
       </c>
       <c r="K38" s="11">
@@ -5878,10 +5890,10 @@
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="114"/>
-      <c r="C39" s="115"/>
-      <c r="D39" s="115"/>
-      <c r="E39" s="116"/>
+      <c r="B39" s="113"/>
+      <c r="C39" s="114"/>
+      <c r="D39" s="114"/>
+      <c r="E39" s="115"/>
       <c r="F39" s="68" t="s">
         <v>93</v>
       </c>
@@ -5894,8 +5906,8 @@
       <c r="I39" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J39" s="114" t="s">
-        <v>150</v>
+      <c r="J39" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K39" s="55"/>
     </row>
@@ -5929,7 +5941,7 @@
       <c r="I40" s="65">
         <v>6300</v>
       </c>
-      <c r="J40" s="156">
+      <c r="J40" s="155">
         <v>15200</v>
       </c>
       <c r="K40" s="11">
@@ -5940,10 +5952,10 @@
       <c r="A41" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="114"/>
-      <c r="C41" s="115"/>
-      <c r="D41" s="115"/>
-      <c r="E41" s="116"/>
+      <c r="B41" s="113"/>
+      <c r="C41" s="114"/>
+      <c r="D41" s="114"/>
+      <c r="E41" s="115"/>
       <c r="F41" s="68" t="s">
         <v>93</v>
       </c>
@@ -5956,8 +5968,8 @@
       <c r="I41" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J41" s="114" t="s">
-        <v>150</v>
+      <c r="J41" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K41" s="55"/>
     </row>
@@ -5991,7 +6003,7 @@
       <c r="I42" s="65">
         <v>16800</v>
       </c>
-      <c r="J42" s="156">
+      <c r="J42" s="155">
         <v>43400</v>
       </c>
       <c r="K42" s="11">
@@ -6002,10 +6014,10 @@
       <c r="A43" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="115"/>
-      <c r="D43" s="115"/>
-      <c r="E43" s="116"/>
+      <c r="B43" s="113"/>
+      <c r="C43" s="114"/>
+      <c r="D43" s="114"/>
+      <c r="E43" s="115"/>
       <c r="F43" s="68" t="s">
         <v>93</v>
       </c>
@@ -6018,8 +6030,8 @@
       <c r="I43" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="J43" s="114" t="s">
-        <v>150</v>
+      <c r="J43" s="113" t="s">
+        <v>149</v>
       </c>
       <c r="K43" s="55"/>
     </row>
@@ -6053,7 +6065,7 @@
       <c r="I44" s="65">
         <v>0</v>
       </c>
-      <c r="J44" s="156">
+      <c r="J44" s="155">
         <v>5300</v>
       </c>
       <c r="K44" s="11">
@@ -6090,7 +6102,7 @@
       <c r="I45" s="65">
         <v>0</v>
       </c>
-      <c r="J45" s="156">
+      <c r="J45" s="155">
         <v>5300</v>
       </c>
       <c r="K45" s="11">
@@ -6127,7 +6139,7 @@
       <c r="I46" s="65">
         <v>0</v>
       </c>
-      <c r="J46" s="156">
+      <c r="J46" s="155">
         <v>5300</v>
       </c>
       <c r="K46" s="11">
@@ -6164,7 +6176,7 @@
       <c r="I47" s="65">
         <v>0</v>
       </c>
-      <c r="J47" s="156">
+      <c r="J47" s="155">
         <v>5300</v>
       </c>
       <c r="K47" s="62">
@@ -6175,10 +6187,10 @@
       <c r="A48" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="114"/>
-      <c r="C48" s="115"/>
-      <c r="D48" s="115"/>
-      <c r="E48" s="116"/>
+      <c r="B48" s="113"/>
+      <c r="C48" s="114"/>
+      <c r="D48" s="114"/>
+      <c r="E48" s="115"/>
       <c r="F48" s="68" t="s">
         <v>93</v>
       </c>
@@ -6194,7 +6206,7 @@
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B49" s="71">
         <v>20000</v>
@@ -6222,7 +6234,7 @@
       <c r="I49" s="65">
         <v>4100</v>
       </c>
-      <c r="J49" s="157"/>
+      <c r="J49" s="156"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
@@ -6254,7 +6266,7 @@
       <c r="I50" s="65">
         <v>4900</v>
       </c>
-      <c r="J50" s="157"/>
+      <c r="J50" s="156"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="33" t="s">
@@ -6415,10 +6427,10 @@
       <c r="A56" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B56" s="114"/>
-      <c r="C56" s="115"/>
-      <c r="D56" s="115"/>
-      <c r="E56" s="116"/>
+      <c r="B56" s="113"/>
+      <c r="C56" s="114"/>
+      <c r="D56" s="114"/>
+      <c r="E56" s="115"/>
       <c r="F56" s="68" t="s">
         <v>93</v>
       </c>
@@ -6465,10 +6477,10 @@
       <c r="A58" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B58" s="114"/>
-      <c r="C58" s="115"/>
-      <c r="D58" s="115"/>
-      <c r="E58" s="116"/>
+      <c r="B58" s="113"/>
+      <c r="C58" s="114"/>
+      <c r="D58" s="114"/>
+      <c r="E58" s="115"/>
       <c r="F58" s="68" t="s">
         <v>93</v>
       </c>
@@ -6517,10 +6529,10 @@
       <c r="A60" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="114"/>
-      <c r="C60" s="115"/>
-      <c r="D60" s="115"/>
-      <c r="E60" s="116"/>
+      <c r="B60" s="113"/>
+      <c r="C60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="115"/>
       <c r="F60" s="68" t="s">
         <v>93</v>
       </c>
@@ -6541,13 +6553,13 @@
       <c r="B61" s="65">
         <v>20000</v>
       </c>
-      <c r="C61" s="117">
+      <c r="C61" s="116">
         <v>10200</v>
       </c>
-      <c r="D61" s="117">
+      <c r="D61" s="116">
         <v>10200</v>
       </c>
-      <c r="E61" s="117">
+      <c r="E61" s="116">
         <v>10200</v>
       </c>
       <c r="F61" s="73">
@@ -6572,13 +6584,13 @@
       <c r="B62" s="65">
         <v>30000</v>
       </c>
-      <c r="C62" s="117">
+      <c r="C62" s="116">
         <v>15900</v>
       </c>
-      <c r="D62" s="117">
+      <c r="D62" s="116">
         <v>15900</v>
       </c>
-      <c r="E62" s="117">
+      <c r="E62" s="116">
         <v>15900</v>
       </c>
       <c r="F62" s="73">
@@ -6603,13 +6615,13 @@
       <c r="B63" s="65">
         <v>20000</v>
       </c>
-      <c r="C63" s="117">
+      <c r="C63" s="116">
         <v>10000</v>
       </c>
-      <c r="D63" s="117">
+      <c r="D63" s="116">
         <v>10000</v>
       </c>
-      <c r="E63" s="117">
+      <c r="E63" s="116">
         <v>10000</v>
       </c>
       <c r="F63" s="73">
@@ -6634,13 +6646,13 @@
       <c r="B64" s="71">
         <v>30000</v>
       </c>
-      <c r="C64" s="117">
+      <c r="C64" s="116">
         <v>10000</v>
       </c>
-      <c r="D64" s="117">
+      <c r="D64" s="116">
         <v>10000</v>
       </c>
-      <c r="E64" s="117">
+      <c r="E64" s="116">
         <v>10000</v>
       </c>
       <c r="F64" s="73">
@@ -6665,13 +6677,13 @@
       <c r="B65" s="71">
         <v>30000</v>
       </c>
-      <c r="C65" s="117">
+      <c r="C65" s="116">
         <v>12300</v>
       </c>
-      <c r="D65" s="117">
+      <c r="D65" s="116">
         <v>12300</v>
       </c>
-      <c r="E65" s="117">
+      <c r="E65" s="116">
         <v>12300</v>
       </c>
       <c r="F65" s="73">
@@ -6706,12 +6718,12 @@
       <c r="A67" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B67" s="114" t="s">
+      <c r="B67" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="C67" s="115"/>
-      <c r="D67" s="115"/>
-      <c r="E67" s="116"/>
+      <c r="C67" s="114"/>
+      <c r="D67" s="114"/>
+      <c r="E67" s="115"/>
       <c r="F67" s="68" t="s">
         <v>93</v>
       </c>
@@ -6758,18 +6770,18 @@
     </row>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" s="118">
+        <v>144</v>
+      </c>
+      <c r="B69" s="117">
         <v>51000</v>
       </c>
-      <c r="C69" s="119">
+      <c r="C69" s="118">
         <v>51000</v>
       </c>
-      <c r="D69" s="119">
+      <c r="D69" s="118">
         <v>51000</v>
       </c>
-      <c r="E69" s="120">
+      <c r="E69" s="119">
         <v>51000</v>
       </c>
       <c r="F69" s="73">
@@ -6789,14 +6801,14 @@
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="39" t="s">
-        <v>233</v>
-      </c>
-      <c r="B70" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="B70" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="C70" s="115"/>
-      <c r="D70" s="115"/>
-      <c r="E70" s="116"/>
+      <c r="C70" s="114"/>
+      <c r="D70" s="114"/>
+      <c r="E70" s="115"/>
       <c r="F70" s="68" t="s">
         <v>93</v>
       </c>
@@ -6843,18 +6855,18 @@
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="B72" s="118">
+        <v>145</v>
+      </c>
+      <c r="B72" s="117">
         <v>68000</v>
       </c>
-      <c r="C72" s="119">
+      <c r="C72" s="118">
         <v>68000</v>
       </c>
-      <c r="D72" s="119">
+      <c r="D72" s="118">
         <v>68000</v>
       </c>
-      <c r="E72" s="120">
+      <c r="E72" s="119">
         <v>68000</v>
       </c>
       <c r="F72" s="73">
@@ -6874,14 +6886,14 @@
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B73" s="114" t="s">
+        <v>231</v>
+      </c>
+      <c r="B73" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="C73" s="115"/>
-      <c r="D73" s="115"/>
-      <c r="E73" s="116"/>
+      <c r="C73" s="114"/>
+      <c r="D73" s="114"/>
+      <c r="E73" s="115"/>
       <c r="F73" s="68" t="s">
         <v>93</v>
       </c>
@@ -6928,18 +6940,18 @@
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="B75" s="118">
+        <v>144</v>
+      </c>
+      <c r="B75" s="117">
         <v>132000</v>
       </c>
-      <c r="C75" s="119">
+      <c r="C75" s="118">
         <v>132000</v>
       </c>
-      <c r="D75" s="119">
+      <c r="D75" s="118">
         <v>132000</v>
       </c>
-      <c r="E75" s="120">
+      <c r="E75" s="119">
         <v>132000</v>
       </c>
       <c r="F75" s="73">
@@ -6959,14 +6971,14 @@
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="B76" s="114" t="s">
+        <v>233</v>
+      </c>
+      <c r="B76" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="C76" s="115"/>
-      <c r="D76" s="115"/>
-      <c r="E76" s="116"/>
+      <c r="C76" s="114"/>
+      <c r="D76" s="114"/>
+      <c r="E76" s="115"/>
       <c r="F76" s="68" t="s">
         <v>93</v>
       </c>
@@ -7013,18 +7025,18 @@
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B78" s="118">
+        <v>145</v>
+      </c>
+      <c r="B78" s="117">
         <v>203000</v>
       </c>
-      <c r="C78" s="119">
+      <c r="C78" s="118">
         <v>203000</v>
       </c>
-      <c r="D78" s="119">
+      <c r="D78" s="118">
         <v>203000</v>
       </c>
-      <c r="E78" s="120">
+      <c r="E78" s="119">
         <v>203000</v>
       </c>
       <c r="F78" s="73">
@@ -7046,10 +7058,10 @@
       <c r="A79" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B79" s="114"/>
-      <c r="C79" s="115"/>
-      <c r="D79" s="115"/>
-      <c r="E79" s="116"/>
+      <c r="B79" s="113"/>
+      <c r="C79" s="114"/>
+      <c r="D79" s="114"/>
+      <c r="E79" s="115"/>
       <c r="F79" s="68" t="s">
         <v>93</v>
       </c>
@@ -7127,7 +7139,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B82" s="70">
         <v>41000</v>
@@ -7189,12 +7201,12 @@
     </row>
     <row r="84" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B84" s="114"/>
-      <c r="C84" s="115"/>
-      <c r="D84" s="115"/>
-      <c r="E84" s="116"/>
+        <v>148</v>
+      </c>
+      <c r="B84" s="113"/>
+      <c r="C84" s="114"/>
+      <c r="D84" s="114"/>
+      <c r="E84" s="115"/>
       <c r="F84" s="68" t="s">
         <v>93</v>
       </c>
@@ -7227,12 +7239,12 @@
       <c r="A86" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B86" s="114" t="s">
+      <c r="B86" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="C86" s="115"/>
-      <c r="D86" s="115"/>
-      <c r="E86" s="116"/>
+      <c r="C86" s="114"/>
+      <c r="D86" s="114"/>
+      <c r="E86" s="115"/>
       <c r="F86" s="68" t="s">
         <v>93</v>
       </c>
@@ -7248,7 +7260,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="45" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B87" s="73">
         <v>97000</v>
@@ -7310,7 +7322,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B89" s="73">
         <v>256000</v>
@@ -7371,33 +7383,33 @@
       </c>
     </row>
     <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="123" t="s">
-        <v>143</v>
-      </c>
-      <c r="B91" s="124">
+      <c r="A91" s="122" t="s">
+        <v>142</v>
+      </c>
+      <c r="B91" s="123">
         <v>8200</v>
       </c>
-      <c r="C91" s="110">
+      <c r="C91" s="109">
         <v>6200</v>
       </c>
-      <c r="D91" s="110">
+      <c r="D91" s="109">
         <v>6200</v>
       </c>
-      <c r="E91" s="110">
+      <c r="E91" s="109">
         <v>6200</v>
       </c>
-      <c r="F91" s="124">
+      <c r="F91" s="123">
         <f t="shared" si="7"/>
         <v>5740</v>
       </c>
-      <c r="G91" s="124">
+      <c r="G91" s="123">
         <f t="shared" si="6"/>
         <v>4920</v>
       </c>
-      <c r="H91" s="110">
+      <c r="H91" s="109">
         <v>2500</v>
       </c>
-      <c r="I91" s="110">
+      <c r="I91" s="109">
         <v>2500</v>
       </c>
     </row>
@@ -7405,22 +7417,22 @@
       <c r="A92" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B92" s="114" t="s">
+      <c r="B92" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="C92" s="127"/>
-      <c r="D92" s="127"/>
-      <c r="E92" s="128"/>
-      <c r="F92" s="129" t="s">
+      <c r="C92" s="126"/>
+      <c r="D92" s="126"/>
+      <c r="E92" s="127"/>
+      <c r="F92" s="128" t="s">
         <v>93</v>
       </c>
-      <c r="G92" s="129" t="s">
+      <c r="G92" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="H92" s="130" t="s">
+      <c r="H92" s="129" t="s">
         <v>95</v>
       </c>
-      <c r="I92" s="130" t="s">
+      <c r="I92" s="129" t="s">
         <v>123</v>
       </c>
     </row>
@@ -7428,20 +7440,20 @@
       <c r="A93" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="B93" s="125"/>
-      <c r="C93" s="125"/>
-      <c r="D93" s="125"/>
-      <c r="E93" s="125"/>
-      <c r="F93" s="126">
+      <c r="B93" s="124"/>
+      <c r="C93" s="124"/>
+      <c r="D93" s="124"/>
+      <c r="E93" s="124"/>
+      <c r="F93" s="125">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G93" s="126">
+      <c r="G93" s="125">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H93" s="125"/>
-      <c r="I93" s="125"/>
+      <c r="H93" s="124"/>
+      <c r="I93" s="124"/>
     </row>
     <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="46" t="s">
@@ -7509,12 +7521,12 @@
       <c r="A96" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B96" s="114" t="s">
+      <c r="B96" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="C96" s="115"/>
-      <c r="D96" s="115"/>
-      <c r="E96" s="116"/>
+      <c r="C96" s="114"/>
+      <c r="D96" s="114"/>
+      <c r="E96" s="115"/>
       <c r="F96" s="68" t="s">
         <v>93</v>
       </c>
@@ -7625,12 +7637,12 @@
       <c r="A100" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B100" s="114" t="s">
+      <c r="B100" s="113" t="s">
         <v>127</v>
       </c>
-      <c r="C100" s="115"/>
-      <c r="D100" s="115"/>
-      <c r="E100" s="116"/>
+      <c r="C100" s="114"/>
+      <c r="D100" s="114"/>
+      <c r="E100" s="115"/>
       <c r="F100" s="68" t="s">
         <v>93</v>
       </c>
@@ -7723,12 +7735,12 @@
       <c r="A104" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="B104" s="114" t="s">
-        <v>148</v>
-      </c>
-      <c r="C104" s="115"/>
-      <c r="D104" s="115"/>
-      <c r="E104" s="116"/>
+      <c r="B104" s="113" t="s">
+        <v>147</v>
+      </c>
+      <c r="C104" s="114"/>
+      <c r="D104" s="114"/>
+      <c r="E104" s="115"/>
       <c r="F104" s="81" t="s">
         <v>93</v>
       </c>
@@ -7899,14 +7911,14 @@
     </row>
     <row r="110" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="B110" s="114" t="s">
-        <v>150</v>
-      </c>
-      <c r="C110" s="115"/>
-      <c r="D110" s="115"/>
-      <c r="E110" s="116"/>
+        <v>137</v>
+      </c>
+      <c r="B110" s="113" t="s">
+        <v>149</v>
+      </c>
+      <c r="C110" s="114"/>
+      <c r="D110" s="114"/>
+      <c r="E110" s="115"/>
       <c r="F110" s="81" t="s">
         <v>93</v>
       </c>
@@ -7922,7 +7934,7 @@
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B111" s="65">
         <v>312686</v>
@@ -7953,7 +7965,7 @@
     </row>
     <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B112" s="65">
         <v>349723</v>
@@ -7984,7 +7996,7 @@
     </row>
     <row r="113" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B113" s="65">
         <v>446016</v>
@@ -8017,12 +8029,12 @@
       <c r="A114" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="B114" s="114" t="s">
-        <v>150</v>
-      </c>
-      <c r="C114" s="115"/>
-      <c r="D114" s="115"/>
-      <c r="E114" s="116"/>
+      <c r="B114" s="113" t="s">
+        <v>149</v>
+      </c>
+      <c r="C114" s="114"/>
+      <c r="D114" s="114"/>
+      <c r="E114" s="115"/>
       <c r="F114" s="81" t="s">
         <v>93</v>
       </c>
@@ -8102,12 +8114,12 @@
       <c r="A117" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="B117" s="114" t="s">
-        <v>150</v>
-      </c>
-      <c r="C117" s="115"/>
-      <c r="D117" s="115"/>
-      <c r="E117" s="116"/>
+      <c r="B117" s="113" t="s">
+        <v>149</v>
+      </c>
+      <c r="C117" s="114"/>
+      <c r="D117" s="114"/>
+      <c r="E117" s="115"/>
       <c r="F117" s="81" t="s">
         <v>93</v>
       </c>
@@ -8249,12 +8261,12 @@
       <c r="A122" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="B122" s="114" t="s">
-        <v>150</v>
-      </c>
-      <c r="C122" s="115"/>
-      <c r="D122" s="115"/>
-      <c r="E122" s="116"/>
+      <c r="B122" s="113" t="s">
+        <v>149</v>
+      </c>
+      <c r="C122" s="114"/>
+      <c r="D122" s="114"/>
+      <c r="E122" s="115"/>
       <c r="F122" s="81" t="s">
         <v>93</v>
       </c>
@@ -8362,87 +8374,87 @@
       </c>
     </row>
     <row r="126" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="139" t="s">
+      <c r="A126" s="138" t="s">
         <v>87</v>
       </c>
-      <c r="B126" s="110">
+      <c r="B126" s="109">
         <v>49078</v>
       </c>
-      <c r="C126" s="110">
+      <c r="C126" s="109">
         <v>24539</v>
       </c>
-      <c r="D126" s="110">
+      <c r="D126" s="109">
         <v>24539</v>
       </c>
-      <c r="E126" s="110">
+      <c r="E126" s="109">
         <v>24539</v>
       </c>
-      <c r="F126" s="124">
+      <c r="F126" s="123">
         <f t="shared" si="10"/>
         <v>34354.6</v>
       </c>
-      <c r="G126" s="124">
+      <c r="G126" s="123">
         <f t="shared" si="11"/>
         <v>29446.799999999999</v>
       </c>
-      <c r="H126" s="110">
+      <c r="H126" s="109">
         <v>13608</v>
       </c>
-      <c r="I126" s="110">
+      <c r="I126" s="109">
         <v>13608</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="141" t="s">
+      <c r="A127" s="140" t="s">
         <v>91</v>
       </c>
-      <c r="B127" s="138" t="s">
-        <v>150</v>
-      </c>
-      <c r="C127" s="127"/>
-      <c r="D127" s="127"/>
-      <c r="E127" s="128"/>
-      <c r="F127" s="129" t="s">
+      <c r="B127" s="137" t="s">
+        <v>149</v>
+      </c>
+      <c r="C127" s="126"/>
+      <c r="D127" s="126"/>
+      <c r="E127" s="127"/>
+      <c r="F127" s="128" t="s">
         <v>93</v>
       </c>
-      <c r="G127" s="129" t="s">
+      <c r="G127" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="H127" s="130" t="s">
+      <c r="H127" s="129" t="s">
         <v>95</v>
       </c>
-      <c r="I127" s="130" t="s">
+      <c r="I127" s="129" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="140" t="s">
+      <c r="A128" s="139" t="s">
         <v>88</v>
       </c>
-      <c r="B128" s="136">
+      <c r="B128" s="135">
         <v>661862</v>
       </c>
-      <c r="C128" s="136">
+      <c r="C128" s="135">
         <v>330931</v>
       </c>
-      <c r="D128" s="136">
+      <c r="D128" s="135">
         <v>330931</v>
       </c>
-      <c r="E128" s="136">
+      <c r="E128" s="135">
         <v>330931</v>
       </c>
-      <c r="F128" s="126">
+      <c r="F128" s="125">
         <f t="shared" si="10"/>
         <v>463303.39999999997</v>
       </c>
-      <c r="G128" s="126">
+      <c r="G128" s="125">
         <f t="shared" si="11"/>
         <v>397117.2</v>
       </c>
-      <c r="H128" s="136">
+      <c r="H128" s="135">
         <v>183523</v>
       </c>
-      <c r="I128" s="136">
+      <c r="I128" s="135">
         <v>183523</v>
       </c>
     </row>
@@ -8478,72 +8490,72 @@
       </c>
     </row>
     <row r="130" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="135" t="s">
+      <c r="A130" s="134" t="s">
         <v>90</v>
       </c>
-      <c r="B130" s="110">
+      <c r="B130" s="109">
         <v>90078</v>
       </c>
-      <c r="C130" s="110">
+      <c r="C130" s="109">
         <v>45039</v>
       </c>
-      <c r="D130" s="110">
+      <c r="D130" s="109">
         <v>45039</v>
       </c>
-      <c r="E130" s="110">
+      <c r="E130" s="109">
         <v>45039</v>
       </c>
-      <c r="F130" s="124">
+      <c r="F130" s="123">
         <f t="shared" si="10"/>
         <v>63054.6</v>
       </c>
-      <c r="G130" s="124">
+      <c r="G130" s="123">
         <f t="shared" si="11"/>
         <v>54046.799999999996</v>
       </c>
-      <c r="H130" s="110">
+      <c r="H130" s="109">
         <v>24977</v>
       </c>
-      <c r="I130" s="110">
+      <c r="I130" s="109">
         <v>24977</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="137" t="s">
-        <v>161</v>
-      </c>
-      <c r="B131" s="138"/>
-      <c r="C131" s="127"/>
-      <c r="D131" s="127"/>
-      <c r="E131" s="128"/>
-      <c r="F131" s="129"/>
-      <c r="G131" s="129" t="s">
+      <c r="A131" s="136" t="s">
+        <v>160</v>
+      </c>
+      <c r="B131" s="137"/>
+      <c r="C131" s="126"/>
+      <c r="D131" s="126"/>
+      <c r="E131" s="127"/>
+      <c r="F131" s="128"/>
+      <c r="G131" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="H131" s="130" t="s">
+      <c r="H131" s="129" t="s">
         <v>95</v>
       </c>
-      <c r="I131" s="130" t="s">
+      <c r="I131" s="129" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="142" t="s">
+      <c r="A132" s="141" t="s">
         <v>46</v>
       </c>
-      <c r="B132" s="136"/>
-      <c r="C132" s="136"/>
-      <c r="D132" s="136"/>
-      <c r="E132" s="136"/>
-      <c r="F132" s="136"/>
-      <c r="G132" s="92">
+      <c r="B132" s="135"/>
+      <c r="C132" s="135"/>
+      <c r="D132" s="135"/>
+      <c r="E132" s="135"/>
+      <c r="F132" s="135"/>
+      <c r="G132" s="91">
         <v>99890</v>
       </c>
-      <c r="H132" s="136"/>
-      <c r="I132" s="143"/>
+      <c r="H132" s="135"/>
+      <c r="I132" s="142"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="144" t="s">
+      <c r="A133" s="143" t="s">
         <v>47</v>
       </c>
       <c r="B133" s="65"/>
@@ -8558,13 +8570,13 @@
         <f>+$G$133</f>
         <v>49945</v>
       </c>
-      <c r="I133" s="145">
+      <c r="I133" s="144">
         <f>+$G$133</f>
         <v>49945</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="144" t="s">
+      <c r="A134" s="143" t="s">
         <v>48</v>
       </c>
       <c r="B134" s="65"/>
@@ -8579,13 +8591,13 @@
         <f>+$G$134</f>
         <v>95529</v>
       </c>
-      <c r="I134" s="145">
+      <c r="I134" s="144">
         <f>+$G$134</f>
         <v>95529</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="144" t="s">
+      <c r="A135" s="143" t="s">
         <v>49</v>
       </c>
       <c r="B135" s="65"/>
@@ -8600,13 +8612,13 @@
         <f>+$G$135</f>
         <v>90026</v>
       </c>
-      <c r="I135" s="145">
+      <c r="I135" s="144">
         <f>+$G$135</f>
         <v>90026</v>
       </c>
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="144" t="s">
+      <c r="A136" s="143" t="s">
         <v>50</v>
       </c>
       <c r="B136" s="65"/>
@@ -8619,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="65"/>
-      <c r="I136" s="145"/>
+      <c r="I136" s="144"/>
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="144" t="s">
+      <c r="A137" s="143" t="s">
         <v>65</v>
       </c>
       <c r="B137" s="65"/>
@@ -8635,10 +8647,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="65"/>
-      <c r="I137" s="145"/>
+      <c r="I137" s="144"/>
     </row>
     <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="144" t="s">
+      <c r="A138" s="143" t="s">
         <v>63</v>
       </c>
       <c r="B138" s="65"/>
@@ -8651,10 +8663,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="65"/>
-      <c r="I138" s="145"/>
+      <c r="I138" s="144"/>
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="144" t="s">
+      <c r="A139" s="143" t="s">
         <v>51</v>
       </c>
       <c r="B139" s="65"/>
@@ -8667,10 +8679,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="65"/>
-      <c r="I139" s="145"/>
+      <c r="I139" s="144"/>
     </row>
     <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="144" t="s">
+      <c r="A140" s="143" t="s">
         <v>52</v>
       </c>
       <c r="B140" s="65"/>
@@ -8683,10 +8695,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="65"/>
-      <c r="I140" s="145"/>
+      <c r="I140" s="144"/>
     </row>
     <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="144" t="s">
+      <c r="A141" s="143" t="s">
         <v>53</v>
       </c>
       <c r="B141" s="65"/>
@@ -8699,10 +8711,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="65"/>
-      <c r="I141" s="145"/>
+      <c r="I141" s="144"/>
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="144" t="s">
+      <c r="A142" s="143" t="s">
         <v>67</v>
       </c>
       <c r="B142" s="65"/>
@@ -8715,10 +8727,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="65"/>
-      <c r="I142" s="145"/>
+      <c r="I142" s="144"/>
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="144" t="s">
+      <c r="A143" s="143" t="s">
         <v>54</v>
       </c>
       <c r="B143" s="65"/>
@@ -8731,10 +8743,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="65"/>
-      <c r="I143" s="145"/>
+      <c r="I143" s="144"/>
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="144" t="s">
+      <c r="A144" s="143" t="s">
         <v>55</v>
       </c>
       <c r="B144" s="65"/>
@@ -8747,10 +8759,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="65"/>
-      <c r="I144" s="145"/>
+      <c r="I144" s="144"/>
     </row>
     <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="144" t="s">
+      <c r="A145" s="143" t="s">
         <v>56</v>
       </c>
       <c r="B145" s="65"/>
@@ -8763,10 +8775,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="65"/>
-      <c r="I145" s="145"/>
+      <c r="I145" s="144"/>
     </row>
     <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="144" t="s">
+      <c r="A146" s="143" t="s">
         <v>57</v>
       </c>
       <c r="B146" s="65"/>
@@ -8779,10 +8791,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="65"/>
-      <c r="I146" s="145"/>
+      <c r="I146" s="144"/>
     </row>
     <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="144" t="s">
+      <c r="A147" s="143" t="s">
         <v>58</v>
       </c>
       <c r="B147" s="65"/>
@@ -8795,10 +8807,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="65"/>
-      <c r="I147" s="145"/>
+      <c r="I147" s="144"/>
     </row>
     <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="144" t="s">
+      <c r="A148" s="143" t="s">
         <v>59</v>
       </c>
       <c r="B148" s="65"/>
@@ -8811,10 +8823,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="65"/>
-      <c r="I148" s="145"/>
+      <c r="I148" s="144"/>
     </row>
     <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="144" t="s">
+      <c r="A149" s="143" t="s">
         <v>60</v>
       </c>
       <c r="B149" s="65"/>
@@ -8827,330 +8839,330 @@
         <v>0</v>
       </c>
       <c r="H149" s="65"/>
-      <c r="I149" s="145"/>
+      <c r="I149" s="144"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="146" t="s">
-        <v>222</v>
-      </c>
-      <c r="B150" s="110"/>
-      <c r="C150" s="110"/>
-      <c r="D150" s="110"/>
-      <c r="E150" s="110"/>
-      <c r="F150" s="110"/>
-      <c r="G150" s="97">
+      <c r="A150" s="145" t="s">
+        <v>221</v>
+      </c>
+      <c r="B150" s="109"/>
+      <c r="C150" s="109"/>
+      <c r="D150" s="109"/>
+      <c r="E150" s="109"/>
+      <c r="F150" s="109"/>
+      <c r="G150" s="96">
         <v>17756</v>
       </c>
-      <c r="H150" s="132">
+      <c r="H150" s="131">
         <f t="shared" ref="G150:I153" si="13">+$G$150</f>
         <v>17756</v>
       </c>
-      <c r="I150" s="147">
+      <c r="I150" s="146">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="146" t="s">
-        <v>184</v>
-      </c>
-      <c r="B151" s="110"/>
-      <c r="C151" s="110"/>
-      <c r="D151" s="110"/>
-      <c r="E151" s="110"/>
-      <c r="F151" s="110"/>
-      <c r="G151" s="132">
+      <c r="A151" s="145" t="s">
+        <v>183</v>
+      </c>
+      <c r="B151" s="109"/>
+      <c r="C151" s="109"/>
+      <c r="D151" s="109"/>
+      <c r="E151" s="109"/>
+      <c r="F151" s="109"/>
+      <c r="G151" s="131">
         <f>+$G$150</f>
         <v>17756</v>
       </c>
-      <c r="H151" s="132">
+      <c r="H151" s="131">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="I151" s="147">
+      <c r="I151" s="146">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="146" t="s">
+      <c r="A152" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="B152" s="120"/>
-      <c r="C152" s="120"/>
-      <c r="D152" s="120"/>
-      <c r="E152" s="120"/>
-      <c r="F152" s="120"/>
-      <c r="G152" s="132">
+      <c r="B152" s="119"/>
+      <c r="C152" s="119"/>
+      <c r="D152" s="119"/>
+      <c r="E152" s="119"/>
+      <c r="F152" s="119"/>
+      <c r="G152" s="131">
         <f>+$G$150</f>
         <v>17756</v>
       </c>
-      <c r="H152" s="132">
+      <c r="H152" s="131">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="I152" s="147">
+      <c r="I152" s="146">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="146" t="s">
+      <c r="A153" s="145" t="s">
         <v>51</v>
       </c>
-      <c r="B153" s="110"/>
-      <c r="C153" s="110"/>
-      <c r="D153" s="110"/>
-      <c r="E153" s="110"/>
-      <c r="F153" s="110"/>
-      <c r="G153" s="132">
+      <c r="B153" s="109"/>
+      <c r="C153" s="109"/>
+      <c r="D153" s="109"/>
+      <c r="E153" s="109"/>
+      <c r="F153" s="109"/>
+      <c r="G153" s="131">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="H153" s="132">
+      <c r="H153" s="131">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="I153" s="147">
+      <c r="I153" s="146">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="146" t="s">
-        <v>220</v>
-      </c>
-      <c r="B154" s="110"/>
-      <c r="C154" s="110"/>
-      <c r="D154" s="110"/>
-      <c r="E154" s="110"/>
-      <c r="F154" s="110"/>
-      <c r="G154" s="134">
+      <c r="A154" s="145" t="s">
+        <v>219</v>
+      </c>
+      <c r="B154" s="109"/>
+      <c r="C154" s="109"/>
+      <c r="D154" s="109"/>
+      <c r="E154" s="109"/>
+      <c r="F154" s="109"/>
+      <c r="G154" s="133">
         <v>35512</v>
       </c>
-      <c r="H154" s="132">
+      <c r="H154" s="131">
         <f>+$G$154</f>
         <v>35512</v>
       </c>
-      <c r="I154" s="147">
+      <c r="I154" s="146">
         <f>+$G$154</f>
         <v>35512</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="146" t="s">
+      <c r="A155" s="145" t="s">
         <v>52</v>
       </c>
-      <c r="B155" s="110"/>
-      <c r="C155" s="110"/>
-      <c r="D155" s="110"/>
-      <c r="E155" s="110"/>
-      <c r="F155" s="110"/>
-      <c r="G155" s="97">
+      <c r="B155" s="109"/>
+      <c r="C155" s="109"/>
+      <c r="D155" s="109"/>
+      <c r="E155" s="109"/>
+      <c r="F155" s="109"/>
+      <c r="G155" s="96">
         <v>12772</v>
       </c>
-      <c r="H155" s="110"/>
-      <c r="I155" s="148"/>
+      <c r="H155" s="109"/>
+      <c r="I155" s="147"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="146" t="s">
+      <c r="A156" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="B156" s="110"/>
-      <c r="C156" s="110"/>
-      <c r="D156" s="110"/>
-      <c r="E156" s="110"/>
-      <c r="F156" s="110"/>
-      <c r="G156" s="97">
+      <c r="B156" s="109"/>
+      <c r="C156" s="109"/>
+      <c r="D156" s="109"/>
+      <c r="E156" s="109"/>
+      <c r="F156" s="109"/>
+      <c r="G156" s="96">
         <v>14226</v>
       </c>
-      <c r="H156" s="110">
+      <c r="H156" s="109">
         <f>+$G$156</f>
         <v>14226</v>
       </c>
-      <c r="I156" s="148">
+      <c r="I156" s="147">
         <f>+$G$156</f>
         <v>14226</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="146" t="s">
+      <c r="A157" s="145" t="s">
         <v>67</v>
       </c>
-      <c r="B157" s="110"/>
-      <c r="C157" s="110"/>
-      <c r="D157" s="110"/>
-      <c r="E157" s="110"/>
-      <c r="F157" s="110"/>
-      <c r="G157" s="97">
+      <c r="B157" s="109"/>
+      <c r="C157" s="109"/>
+      <c r="D157" s="109"/>
+      <c r="E157" s="109"/>
+      <c r="F157" s="109"/>
+      <c r="G157" s="96">
         <v>14329</v>
       </c>
-      <c r="H157" s="110"/>
-      <c r="I157" s="148"/>
+      <c r="H157" s="109"/>
+      <c r="I157" s="147"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="146" t="s">
+      <c r="A158" s="145" t="s">
         <v>54</v>
       </c>
-      <c r="B158" s="110"/>
-      <c r="C158" s="110"/>
-      <c r="D158" s="110"/>
-      <c r="E158" s="110"/>
-      <c r="F158" s="110"/>
-      <c r="G158" s="97">
+      <c r="B158" s="109"/>
+      <c r="C158" s="109"/>
+      <c r="D158" s="109"/>
+      <c r="E158" s="109"/>
+      <c r="F158" s="109"/>
+      <c r="G158" s="96">
         <v>21390</v>
       </c>
-      <c r="H158" s="110">
+      <c r="H158" s="109">
         <f>+$G$158</f>
         <v>21390</v>
       </c>
-      <c r="I158" s="148">
+      <c r="I158" s="147">
         <f>+$G$158</f>
         <v>21390</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="146" t="s">
+      <c r="A159" s="145" t="s">
         <v>55</v>
       </c>
-      <c r="B159" s="110"/>
-      <c r="C159" s="110"/>
-      <c r="D159" s="110"/>
-      <c r="E159" s="110"/>
-      <c r="F159" s="110"/>
-      <c r="G159" s="97">
+      <c r="B159" s="109"/>
+      <c r="C159" s="109"/>
+      <c r="D159" s="109"/>
+      <c r="E159" s="109"/>
+      <c r="F159" s="109"/>
+      <c r="G159" s="96">
         <v>18067</v>
       </c>
-      <c r="H159" s="110"/>
-      <c r="I159" s="148"/>
+      <c r="H159" s="109"/>
+      <c r="I159" s="147"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="146" t="s">
-        <v>221</v>
-      </c>
-      <c r="B160" s="110"/>
-      <c r="C160" s="110"/>
-      <c r="D160" s="110"/>
-      <c r="E160" s="110"/>
-      <c r="F160" s="110"/>
-      <c r="G160" s="97">
+      <c r="A160" s="145" t="s">
+        <v>220</v>
+      </c>
+      <c r="B160" s="109"/>
+      <c r="C160" s="109"/>
+      <c r="D160" s="109"/>
+      <c r="E160" s="109"/>
+      <c r="F160" s="109"/>
+      <c r="G160" s="96">
         <v>36134</v>
       </c>
-      <c r="H160" s="110">
+      <c r="H160" s="109">
         <f>+$G$160</f>
         <v>36134</v>
       </c>
-      <c r="I160" s="148">
+      <c r="I160" s="147">
         <f>+$G$160</f>
         <v>36134</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="146" t="s">
-        <v>187</v>
-      </c>
-      <c r="B161" s="110"/>
-      <c r="C161" s="110"/>
-      <c r="D161" s="110"/>
-      <c r="E161" s="110"/>
-      <c r="F161" s="110"/>
-      <c r="G161" s="97">
+      <c r="A161" s="145" t="s">
+        <v>186</v>
+      </c>
+      <c r="B161" s="109"/>
+      <c r="C161" s="109"/>
+      <c r="D161" s="109"/>
+      <c r="E161" s="109"/>
+      <c r="F161" s="109"/>
+      <c r="G161" s="96">
         <v>17029</v>
       </c>
-      <c r="H161" s="110"/>
-      <c r="I161" s="148"/>
+      <c r="H161" s="109"/>
+      <c r="I161" s="147"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="146" t="s">
-        <v>223</v>
-      </c>
-      <c r="B162" s="110"/>
-      <c r="C162" s="110"/>
-      <c r="D162" s="110"/>
-      <c r="E162" s="110"/>
-      <c r="F162" s="110"/>
-      <c r="G162" s="132">
+      <c r="A162" s="145" t="s">
+        <v>222</v>
+      </c>
+      <c r="B162" s="109"/>
+      <c r="C162" s="109"/>
+      <c r="D162" s="109"/>
+      <c r="E162" s="109"/>
+      <c r="F162" s="109"/>
+      <c r="G162" s="131">
         <f>+$G$161</f>
         <v>17029</v>
       </c>
-      <c r="H162" s="110">
+      <c r="H162" s="109">
         <f>+$G$161</f>
         <v>17029</v>
       </c>
-      <c r="I162" s="148">
+      <c r="I162" s="147">
         <f>+$G$161</f>
         <v>17029</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="146" t="s">
-        <v>177</v>
-      </c>
-      <c r="B163" s="110"/>
-      <c r="C163" s="110"/>
-      <c r="D163" s="110"/>
-      <c r="E163" s="110"/>
-      <c r="F163" s="110"/>
-      <c r="G163" s="97">
+      <c r="A163" s="145" t="s">
+        <v>176</v>
+      </c>
+      <c r="B163" s="109"/>
+      <c r="C163" s="109"/>
+      <c r="D163" s="109"/>
+      <c r="E163" s="109"/>
+      <c r="F163" s="109"/>
+      <c r="G163" s="96">
         <v>17237</v>
       </c>
-      <c r="H163" s="110"/>
-      <c r="I163" s="148"/>
+      <c r="H163" s="109"/>
+      <c r="I163" s="147"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="146" t="s">
+      <c r="A164" s="145" t="s">
         <v>59</v>
       </c>
-      <c r="B164" s="110"/>
-      <c r="C164" s="110"/>
-      <c r="D164" s="110"/>
-      <c r="E164" s="110"/>
-      <c r="F164" s="110"/>
-      <c r="G164" s="97">
+      <c r="B164" s="109"/>
+      <c r="C164" s="109"/>
+      <c r="D164" s="109"/>
+      <c r="E164" s="109"/>
+      <c r="F164" s="109"/>
+      <c r="G164" s="96">
         <v>20560</v>
       </c>
-      <c r="H164" s="110"/>
-      <c r="I164" s="148"/>
+      <c r="H164" s="109"/>
+      <c r="I164" s="147"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="146" t="s">
+      <c r="A165" s="145" t="s">
         <v>60</v>
       </c>
-      <c r="B165" s="110"/>
-      <c r="C165" s="110"/>
-      <c r="D165" s="110"/>
-      <c r="E165" s="110"/>
-      <c r="F165" s="110"/>
-      <c r="G165" s="97">
+      <c r="B165" s="109"/>
+      <c r="C165" s="109"/>
+      <c r="D165" s="109"/>
+      <c r="E165" s="109"/>
+      <c r="F165" s="109"/>
+      <c r="G165" s="96">
         <v>14952</v>
       </c>
-      <c r="H165" s="110"/>
-      <c r="I165" s="148"/>
+      <c r="H165" s="109"/>
+      <c r="I165" s="147"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="146" t="s">
-        <v>219</v>
-      </c>
-      <c r="B166" s="110"/>
-      <c r="C166" s="110"/>
-      <c r="D166" s="110"/>
-      <c r="E166" s="110"/>
-      <c r="F166" s="110"/>
-      <c r="G166" s="97">
+      <c r="A166" s="145" t="s">
+        <v>218</v>
+      </c>
+      <c r="B166" s="109"/>
+      <c r="C166" s="109"/>
+      <c r="D166" s="109"/>
+      <c r="E166" s="109"/>
+      <c r="F166" s="109"/>
+      <c r="G166" s="96">
         <f>+$G$165*2</f>
         <v>29904</v>
       </c>
-      <c r="H166" s="110">
+      <c r="H166" s="109">
         <f>+$G$166</f>
         <v>29904</v>
       </c>
-      <c r="I166" s="148">
+      <c r="I166" s="147">
         <f>+$G$166</f>
         <v>29904</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="144" t="s">
+      <c r="A167" s="143" t="s">
         <v>61</v>
       </c>
       <c r="B167" s="65"/>
@@ -9162,10 +9174,10 @@
         <v>36239</v>
       </c>
       <c r="H167" s="65"/>
-      <c r="I167" s="145"/>
+      <c r="I167" s="144"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="144" t="s">
+      <c r="A168" s="143" t="s">
         <v>62</v>
       </c>
       <c r="B168" s="65"/>
@@ -9177,93 +9189,93 @@
         <v>38835</v>
       </c>
       <c r="H168" s="65"/>
-      <c r="I168" s="145"/>
+      <c r="I168" s="144"/>
     </row>
     <row r="169" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="146" t="s">
+      <c r="A169" s="145" t="s">
         <v>64</v>
       </c>
-      <c r="B169" s="120"/>
-      <c r="C169" s="120"/>
-      <c r="D169" s="120"/>
-      <c r="E169" s="120"/>
-      <c r="F169" s="120"/>
-      <c r="G169" s="131">
+      <c r="B169" s="119"/>
+      <c r="C169" s="119"/>
+      <c r="D169" s="119"/>
+      <c r="E169" s="119"/>
+      <c r="F169" s="119"/>
+      <c r="G169" s="130">
         <v>70000</v>
       </c>
-      <c r="H169" s="133">
+      <c r="H169" s="132">
         <v>25000</v>
       </c>
-      <c r="I169" s="149">
+      <c r="I169" s="148">
         <f>+$H$169</f>
         <v>25000</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="111" t="s">
+      <c r="A170" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="B170" s="112"/>
-      <c r="C170" s="112"/>
-      <c r="D170" s="112"/>
-      <c r="E170" s="112"/>
-      <c r="F170" s="112"/>
-      <c r="G170" s="112"/>
-      <c r="H170" s="112"/>
-      <c r="I170" s="113"/>
+      <c r="B170" s="111"/>
+      <c r="C170" s="111"/>
+      <c r="D170" s="111"/>
+      <c r="E170" s="111"/>
+      <c r="F170" s="111"/>
+      <c r="G170" s="111"/>
+      <c r="H170" s="111"/>
+      <c r="I170" s="112"/>
     </row>
     <row r="171" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="B171" s="121"/>
-      <c r="C171" s="95"/>
-      <c r="D171" s="95"/>
-      <c r="E171" s="95"/>
-      <c r="F171" s="95"/>
-      <c r="G171" s="95" t="s">
+      <c r="B171" s="120"/>
+      <c r="C171" s="94"/>
+      <c r="D171" s="94"/>
+      <c r="E171" s="94"/>
+      <c r="F171" s="94"/>
+      <c r="G171" s="94" t="s">
         <v>94</v>
       </c>
-      <c r="H171" s="95" t="s">
+      <c r="H171" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="I171" s="96" t="s">
+      <c r="I171" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="J171" s="158"/>
+      <c r="J171" s="157"/>
       <c r="K171" s="61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L171" s="66">
         <v>12000</v>
       </c>
     </row>
     <row r="172" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A172" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B172" s="84"/>
-      <c r="C172" s="84"/>
-      <c r="D172" s="84"/>
-      <c r="E172" s="84"/>
-      <c r="F172" s="84"/>
-      <c r="G172" s="84">
+      <c r="A172" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B172" s="161"/>
+      <c r="C172" s="161"/>
+      <c r="D172" s="161"/>
+      <c r="E172" s="161"/>
+      <c r="F172" s="161"/>
+      <c r="G172" s="161">
         <f>+$L$171</f>
         <v>12000</v>
       </c>
-      <c r="H172" s="84">
+      <c r="H172" s="161">
         <f t="shared" ref="H172:I172" si="14">+$L$171</f>
         <v>12000</v>
       </c>
-      <c r="I172" s="103">
+      <c r="I172" s="162">
         <f t="shared" si="14"/>
         <v>12000</v>
       </c>
-      <c r="J172" s="158"/>
+      <c r="J172" s="157"/>
     </row>
     <row r="173" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B173" s="82"/>
       <c r="C173" s="82"/>
@@ -9277,11 +9289,11 @@
         <f>+G173</f>
         <v>25000</v>
       </c>
-      <c r="I173" s="98">
+      <c r="I173" s="97">
         <f>+G173</f>
         <v>25000</v>
       </c>
-      <c r="J173" s="158"/>
+      <c r="J173" s="157"/>
       <c r="K173" s="61" t="s">
         <v>128</v>
       </c>
@@ -9291,7 +9303,7 @@
     </row>
     <row r="174" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B174" s="82"/>
       <c r="C174" s="82"/>
@@ -9306,15 +9318,15 @@
         <f t="shared" ref="H174:I184" si="16">+$L$173</f>
         <v>22000</v>
       </c>
-      <c r="I174" s="98">
+      <c r="I174" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J174" s="158"/>
+      <c r="J174" s="157"/>
     </row>
     <row r="175" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B175" s="82"/>
       <c r="C175" s="82"/>
@@ -9329,15 +9341,15 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I175" s="98">
+      <c r="I175" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J175" s="158"/>
+      <c r="J175" s="157"/>
     </row>
     <row r="176" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B176" s="82"/>
       <c r="C176" s="82"/>
@@ -9352,15 +9364,15 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I176" s="98">
+      <c r="I176" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J176" s="158"/>
+      <c r="J176" s="157"/>
     </row>
     <row r="177" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B177" s="82"/>
       <c r="C177" s="82"/>
@@ -9375,15 +9387,15 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I177" s="98">
+      <c r="I177" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J177" s="158"/>
+      <c r="J177" s="157"/>
     </row>
     <row r="178" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B178" s="82"/>
       <c r="C178" s="82"/>
@@ -9398,15 +9410,15 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I178" s="98">
+      <c r="I178" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J178" s="158"/>
+      <c r="J178" s="157"/>
     </row>
     <row r="179" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B179" s="82"/>
       <c r="C179" s="82"/>
@@ -9421,15 +9433,15 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I179" s="98">
+      <c r="I179" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J179" s="158"/>
+      <c r="J179" s="157"/>
     </row>
     <row r="180" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B180" s="82"/>
       <c r="C180" s="82"/>
@@ -9444,15 +9456,15 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I180" s="98">
+      <c r="I180" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J180" s="158"/>
+      <c r="J180" s="157"/>
     </row>
     <row r="181" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B181" s="82"/>
       <c r="C181" s="82"/>
@@ -9467,15 +9479,15 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I181" s="98">
+      <c r="I181" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J181" s="158"/>
+      <c r="J181" s="157"/>
     </row>
     <row r="182" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B182" s="82"/>
       <c r="C182" s="82"/>
@@ -9490,15 +9502,15 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I182" s="98">
+      <c r="I182" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J182" s="158"/>
+      <c r="J182" s="157"/>
     </row>
     <row r="183" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B183" s="82"/>
       <c r="C183" s="82"/>
@@ -9513,191 +9525,187 @@
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I183" s="98">
+      <c r="I183" s="97">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J183" s="158"/>
-    </row>
-    <row r="184" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="B184" s="100"/>
-      <c r="C184" s="100"/>
-      <c r="D184" s="100"/>
-      <c r="E184" s="100"/>
-      <c r="F184" s="100"/>
-      <c r="G184" s="100">
+      <c r="J183" s="157"/>
+    </row>
+    <row r="184" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A184" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B184" s="82"/>
+      <c r="C184" s="82"/>
+      <c r="D184" s="82"/>
+      <c r="E184" s="82"/>
+      <c r="F184" s="82"/>
+      <c r="G184" s="88">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H184" s="100">
+      <c r="H184" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I184" s="101">
+      <c r="I184" s="160">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J184" s="158"/>
-    </row>
-    <row r="185" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B185" s="84"/>
-      <c r="C185" s="84"/>
-      <c r="D185" s="84"/>
-      <c r="E185" s="84"/>
-      <c r="F185" s="84"/>
-      <c r="G185" s="102">
+      <c r="J184" s="157"/>
+    </row>
+    <row r="185" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A185" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B185" s="82"/>
+      <c r="C185" s="82"/>
+      <c r="D185" s="82"/>
+      <c r="E185" s="82"/>
+      <c r="F185" s="82"/>
+      <c r="G185" s="83">
         <v>32000</v>
       </c>
-      <c r="H185" s="102">
-        <f t="shared" ref="H185:H186" si="17">+H184</f>
-        <v>22000</v>
-      </c>
-      <c r="I185" s="84"/>
-      <c r="J185" s="158"/>
-    </row>
-    <row r="186" spans="1:12" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="19" t="s">
+      <c r="H185" s="82">
+        <f>+G185</f>
+        <v>32000</v>
+      </c>
+      <c r="I185" s="82">
+        <f>+G185</f>
+        <v>32000</v>
+      </c>
+      <c r="J185" s="157"/>
+    </row>
+    <row r="186" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A186" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B186" s="88"/>
+      <c r="C186" s="88"/>
+      <c r="D186" s="88"/>
+      <c r="E186" s="88"/>
+      <c r="F186" s="88"/>
+      <c r="G186" s="88">
+        <f>+G185</f>
+        <v>32000</v>
+      </c>
+      <c r="H186" s="88">
+        <f>+G185</f>
+        <v>32000</v>
+      </c>
+      <c r="I186" s="82">
+        <f>+G185</f>
+        <v>32000</v>
+      </c>
+      <c r="J186" s="157"/>
+    </row>
+    <row r="187" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A187" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B187" s="88"/>
+      <c r="C187" s="88"/>
+      <c r="D187" s="88"/>
+      <c r="E187" s="88"/>
+      <c r="F187" s="88"/>
+      <c r="G187" s="88">
+        <f>+G185</f>
+        <v>32000</v>
+      </c>
+      <c r="H187" s="88">
+        <f>+G185</f>
+        <v>32000</v>
+      </c>
+      <c r="I187" s="82">
+        <f>+G185</f>
+        <v>32000</v>
+      </c>
+      <c r="J187" s="157"/>
+    </row>
+    <row r="188" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B186" s="89"/>
-      <c r="C186" s="89"/>
-      <c r="D186" s="89"/>
-      <c r="E186" s="89"/>
-      <c r="F186" s="89"/>
-      <c r="G186" s="88">
+      <c r="B188" s="99"/>
+      <c r="C188" s="99"/>
+      <c r="D188" s="99"/>
+      <c r="E188" s="99"/>
+      <c r="F188" s="99"/>
+      <c r="G188" s="98">
         <v>32000</v>
       </c>
-      <c r="H186" s="88">
+      <c r="H188" s="99">
+        <f>+G188</f>
+        <v>32000</v>
+      </c>
+      <c r="I188" s="100">
+        <f>+G188</f>
+        <v>32000</v>
+      </c>
+      <c r="J188" s="157"/>
+    </row>
+    <row r="189" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="87" t="s">
+        <v>162</v>
+      </c>
+      <c r="B189" s="120"/>
+      <c r="C189" s="121"/>
+      <c r="D189" s="121"/>
+      <c r="E189" s="94"/>
+      <c r="F189" s="94"/>
+      <c r="G189" s="94" t="s">
+        <v>94</v>
+      </c>
+      <c r="H189" s="95" t="s">
+        <v>95</v>
+      </c>
+      <c r="I189" s="95" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B190" s="92"/>
+      <c r="C190" s="92"/>
+      <c r="D190" s="92"/>
+      <c r="E190" s="92"/>
+      <c r="F190" s="92"/>
+      <c r="G190" s="91">
+        <v>24000</v>
+      </c>
+      <c r="H190" s="92">
+        <f>+G190</f>
+        <v>24000</v>
+      </c>
+      <c r="I190" s="93">
+        <f>+G190</f>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B191" s="71"/>
+      <c r="C191" s="71"/>
+      <c r="D191" s="71"/>
+      <c r="E191" s="71"/>
+      <c r="F191" s="71"/>
+      <c r="G191" s="71"/>
+      <c r="H191" s="71">
+        <f t="shared" ref="H191:I231" si="17">+G191</f>
+        <v>0</v>
+      </c>
+      <c r="I191" s="89">
         <f t="shared" si="17"/>
-        <v>22000</v>
-      </c>
-      <c r="I186" s="89"/>
-      <c r="J186" s="158"/>
-    </row>
-    <row r="187" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="87" t="s">
-        <v>163</v>
-      </c>
-      <c r="B187" s="121"/>
-      <c r="C187" s="122"/>
-      <c r="D187" s="122"/>
-      <c r="E187" s="95"/>
-      <c r="F187" s="95"/>
-      <c r="G187" s="95" t="s">
-        <v>94</v>
-      </c>
-      <c r="H187" s="96" t="s">
-        <v>95</v>
-      </c>
-      <c r="I187" s="96" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A188" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B188" s="93"/>
-      <c r="C188" s="93"/>
-      <c r="D188" s="93"/>
-      <c r="E188" s="93"/>
-      <c r="F188" s="93"/>
-      <c r="G188" s="92">
-        <v>24000</v>
-      </c>
-      <c r="H188" s="93">
-        <f>+G188</f>
-        <v>24000</v>
-      </c>
-      <c r="I188" s="94">
-        <f>+G188</f>
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="B189" s="71"/>
-      <c r="C189" s="71"/>
-      <c r="D189" s="71"/>
-      <c r="E189" s="71"/>
-      <c r="F189" s="71"/>
-      <c r="G189" s="71"/>
-      <c r="H189" s="71">
-        <f t="shared" ref="H189:I229" si="18">+G189</f>
         <v>0</v>
-      </c>
-      <c r="I189" s="90">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A190" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B190" s="85"/>
-      <c r="C190" s="85"/>
-      <c r="D190" s="85"/>
-      <c r="E190" s="85"/>
-      <c r="F190" s="85"/>
-      <c r="G190" s="85">
-        <f t="shared" ref="G190:I190" si="19">$L$190</f>
-        <v>16640</v>
-      </c>
-      <c r="H190" s="85">
-        <f t="shared" si="19"/>
-        <v>16640</v>
-      </c>
-      <c r="I190" s="91">
-        <f t="shared" si="19"/>
-        <v>16640</v>
-      </c>
-      <c r="K190" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="L190" s="66">
-        <v>16640</v>
-      </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B191" s="85"/>
-      <c r="C191" s="85"/>
-      <c r="D191" s="85"/>
-      <c r="E191" s="85"/>
-      <c r="F191" s="85"/>
-      <c r="G191" s="85">
-        <f>$L$191</f>
-        <v>9600</v>
-      </c>
-      <c r="H191" s="85">
-        <f t="shared" ref="H191:I191" si="20">$L$191</f>
-        <v>9600</v>
-      </c>
-      <c r="I191" s="91">
-        <f t="shared" si="20"/>
-        <v>9600</v>
-      </c>
-      <c r="K191" s="61" t="s">
-        <v>152</v>
-      </c>
-      <c r="L191" s="66">
-        <v>9600</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B192" s="85"/>
       <c r="C192" s="85"/>
@@ -9705,22 +9713,27 @@
       <c r="E192" s="85"/>
       <c r="F192" s="85"/>
       <c r="G192" s="85">
-        <f>$L$190</f>
+        <f t="shared" ref="G192:I192" si="18">$L$192</f>
         <v>16640</v>
       </c>
       <c r="H192" s="85">
-        <f t="shared" ref="H192:I192" si="21">$L$190</f>
+        <f t="shared" si="18"/>
         <v>16640</v>
       </c>
-      <c r="I192" s="91">
-        <f t="shared" si="21"/>
+      <c r="I192" s="90">
+        <f t="shared" si="18"/>
         <v>16640</v>
       </c>
-      <c r="L192" s="64"/>
+      <c r="K192" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="L192" s="66">
+        <v>16640</v>
+      </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B193" s="85"/>
       <c r="C193" s="85"/>
@@ -9728,27 +9741,27 @@
       <c r="E193" s="85"/>
       <c r="F193" s="85"/>
       <c r="G193" s="85">
-        <f>$L$191</f>
+        <f>$L$193</f>
         <v>9600</v>
       </c>
       <c r="H193" s="85">
-        <f t="shared" ref="H193:I193" si="22">$L$191</f>
+        <f t="shared" ref="H193:I193" si="19">$L$193</f>
         <v>9600</v>
       </c>
-      <c r="I193" s="91">
-        <f t="shared" si="22"/>
+      <c r="I193" s="90">
+        <f t="shared" si="19"/>
         <v>9600</v>
       </c>
       <c r="K193" s="61" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="L193" s="66">
-        <v>32000</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B194" s="85"/>
       <c r="C194" s="85"/>
@@ -9756,21 +9769,22 @@
       <c r="E194" s="85"/>
       <c r="F194" s="85"/>
       <c r="G194" s="85">
-        <f t="shared" ref="G194:I202" si="23">$L$190</f>
+        <f>$L$192</f>
         <v>16640</v>
       </c>
       <c r="H194" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="H194:I194" si="20">$L$192</f>
         <v>16640</v>
       </c>
-      <c r="I194" s="91">
-        <f t="shared" si="23"/>
+      <c r="I194" s="90">
+        <f t="shared" si="20"/>
         <v>16640</v>
       </c>
+      <c r="L194" s="64"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B195" s="85"/>
       <c r="C195" s="85"/>
@@ -9778,21 +9792,27 @@
       <c r="E195" s="85"/>
       <c r="F195" s="85"/>
       <c r="G195" s="85">
-        <f>$L$191</f>
+        <f>$L$193</f>
         <v>9600</v>
       </c>
       <c r="H195" s="85">
-        <f t="shared" ref="H195:I195" si="24">$L$191</f>
+        <f t="shared" ref="H195:I195" si="21">$L$193</f>
         <v>9600</v>
       </c>
-      <c r="I195" s="91">
-        <f t="shared" si="24"/>
+      <c r="I195" s="90">
+        <f t="shared" si="21"/>
         <v>9600</v>
+      </c>
+      <c r="K195" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="L195" s="66">
+        <v>32000</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B196" s="85"/>
       <c r="C196" s="85"/>
@@ -9800,21 +9820,21 @@
       <c r="E196" s="85"/>
       <c r="F196" s="85"/>
       <c r="G196" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G196:I204" si="22">$L$192</f>
         <v>16640</v>
       </c>
       <c r="H196" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I196" s="91">
-        <f t="shared" si="23"/>
+      <c r="I196" s="90">
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B197" s="85"/>
       <c r="C197" s="85"/>
@@ -9822,21 +9842,21 @@
       <c r="E197" s="85"/>
       <c r="F197" s="85"/>
       <c r="G197" s="85">
-        <f>$L$191</f>
+        <f>$L$193</f>
         <v>9600</v>
       </c>
       <c r="H197" s="85">
-        <f t="shared" ref="H197:I197" si="25">$L$191</f>
+        <f t="shared" ref="H197:I197" si="23">$L$193</f>
         <v>9600</v>
       </c>
-      <c r="I197" s="91">
-        <f t="shared" si="25"/>
+      <c r="I197" s="90">
+        <f t="shared" si="23"/>
         <v>9600</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B198" s="85"/>
       <c r="C198" s="85"/>
@@ -9844,21 +9864,21 @@
       <c r="E198" s="85"/>
       <c r="F198" s="85"/>
       <c r="G198" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
       <c r="H198" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I198" s="91">
-        <f t="shared" si="23"/>
+      <c r="I198" s="90">
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B199" s="85"/>
       <c r="C199" s="85"/>
@@ -9866,21 +9886,21 @@
       <c r="E199" s="85"/>
       <c r="F199" s="85"/>
       <c r="G199" s="85">
-        <f>$L$191</f>
+        <f>$L$193</f>
         <v>9600</v>
       </c>
       <c r="H199" s="85">
-        <f t="shared" ref="H199:I199" si="26">$L$191</f>
+        <f t="shared" ref="H199:I199" si="24">$L$193</f>
         <v>9600</v>
       </c>
-      <c r="I199" s="91">
-        <f t="shared" si="26"/>
+      <c r="I199" s="90">
+        <f t="shared" si="24"/>
         <v>9600</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B200" s="85"/>
       <c r="C200" s="85"/>
@@ -9888,21 +9908,21 @@
       <c r="E200" s="85"/>
       <c r="F200" s="85"/>
       <c r="G200" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
       <c r="H200" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I200" s="91">
-        <f t="shared" si="23"/>
+      <c r="I200" s="90">
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B201" s="85"/>
       <c r="C201" s="85"/>
@@ -9910,21 +9930,21 @@
       <c r="E201" s="85"/>
       <c r="F201" s="85"/>
       <c r="G201" s="85">
-        <f>$L$191</f>
+        <f>$L$193</f>
         <v>9600</v>
       </c>
       <c r="H201" s="85">
-        <f t="shared" ref="H201:I201" si="27">$L$191</f>
+        <f t="shared" ref="H201:I201" si="25">$L$193</f>
         <v>9600</v>
       </c>
-      <c r="I201" s="91">
-        <f t="shared" si="27"/>
+      <c r="I201" s="90">
+        <f t="shared" si="25"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B202" s="85"/>
       <c r="C202" s="85"/>
@@ -9932,21 +9952,21 @@
       <c r="E202" s="85"/>
       <c r="F202" s="85"/>
       <c r="G202" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
       <c r="H202" s="85">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I202" s="91">
-        <f t="shared" si="23"/>
+      <c r="I202" s="90">
+        <f t="shared" si="22"/>
         <v>16640</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B203" s="85"/>
       <c r="C203" s="85"/>
@@ -9954,42 +9974,43 @@
       <c r="E203" s="85"/>
       <c r="F203" s="85"/>
       <c r="G203" s="85">
-        <f>$L$191</f>
+        <f>$L$193</f>
         <v>9600</v>
       </c>
       <c r="H203" s="85">
-        <f t="shared" ref="H203:I203" si="28">$L$191</f>
+        <f t="shared" ref="H203:I203" si="26">$L$193</f>
         <v>9600</v>
       </c>
-      <c r="I203" s="91">
-        <f t="shared" si="28"/>
+      <c r="I203" s="90">
+        <f t="shared" si="26"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A204" s="63" t="s">
-        <v>155</v>
+    <row r="204" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="B204" s="85"/>
       <c r="C204" s="85"/>
       <c r="D204" s="85"/>
       <c r="E204" s="85"/>
       <c r="F204" s="85"/>
-      <c r="G204" s="86">
-        <v>36000</v>
+      <c r="G204" s="85">
+        <f t="shared" si="22"/>
+        <v>16640</v>
       </c>
       <c r="H204" s="85">
-        <f t="shared" si="18"/>
-        <v>36000</v>
-      </c>
-      <c r="I204" s="91">
-        <f>+G204</f>
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" si="22"/>
+        <v>16640</v>
+      </c>
+      <c r="I204" s="90">
+        <f t="shared" si="22"/>
+        <v>16640</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="9" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="B205" s="85"/>
       <c r="C205" s="85"/>
@@ -9998,42 +10019,41 @@
       <c r="F205" s="85"/>
       <c r="G205" s="85">
         <f>$L$193</f>
-        <v>32000</v>
+        <v>9600</v>
       </c>
       <c r="H205" s="85">
-        <f t="shared" ref="H205:I205" si="29">$L$193</f>
-        <v>32000</v>
-      </c>
-      <c r="I205" s="91">
-        <f t="shared" si="29"/>
-        <v>32000</v>
+        <f t="shared" ref="H205:I205" si="27">$L$193</f>
+        <v>9600</v>
+      </c>
+      <c r="I205" s="90">
+        <f t="shared" si="27"/>
+        <v>9600</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A206" s="9" t="s">
-        <v>172</v>
+      <c r="A206" s="63" t="s">
+        <v>154</v>
       </c>
       <c r="B206" s="85"/>
       <c r="C206" s="85"/>
       <c r="D206" s="85"/>
       <c r="E206" s="85"/>
       <c r="F206" s="85"/>
-      <c r="G206" s="85">
-        <f t="shared" ref="G206:I223" si="30">$L$193</f>
-        <v>32000</v>
+      <c r="G206" s="86">
+        <v>36000</v>
       </c>
       <c r="H206" s="85">
-        <f t="shared" si="30"/>
-        <v>32000</v>
-      </c>
-      <c r="I206" s="91">
-        <f t="shared" si="30"/>
-        <v>32000</v>
+        <f t="shared" si="17"/>
+        <v>36000</v>
+      </c>
+      <c r="I206" s="90">
+        <f>+G206</f>
+        <v>36000</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B207" s="85"/>
       <c r="C207" s="85"/>
@@ -10041,21 +10061,21 @@
       <c r="E207" s="85"/>
       <c r="F207" s="85"/>
       <c r="G207" s="85">
-        <f>$L$193</f>
+        <f>$L$195</f>
         <v>32000</v>
       </c>
       <c r="H207" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="H207:I207" si="28">$L$195</f>
         <v>32000</v>
       </c>
-      <c r="I207" s="91">
-        <f t="shared" si="30"/>
+      <c r="I207" s="90">
+        <f t="shared" si="28"/>
         <v>32000</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B208" s="85"/>
       <c r="C208" s="85"/>
@@ -10063,21 +10083,21 @@
       <c r="E208" s="85"/>
       <c r="F208" s="85"/>
       <c r="G208" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="G208:I225" si="29">$L$195</f>
         <v>32000</v>
       </c>
       <c r="H208" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I208" s="91">
-        <f t="shared" si="30"/>
+      <c r="I208" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B209" s="85"/>
       <c r="C209" s="85"/>
@@ -10085,21 +10105,21 @@
       <c r="E209" s="85"/>
       <c r="F209" s="85"/>
       <c r="G209" s="85">
-        <f t="shared" si="30"/>
+        <f>$L$195</f>
         <v>32000</v>
       </c>
       <c r="H209" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I209" s="91">
-        <f t="shared" si="30"/>
+      <c r="I209" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="9" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="B210" s="85"/>
       <c r="C210" s="85"/>
@@ -10107,21 +10127,21 @@
       <c r="E210" s="85"/>
       <c r="F210" s="85"/>
       <c r="G210" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H210" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I210" s="91">
-        <f t="shared" si="30"/>
+      <c r="I210" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="9" t="s">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="B211" s="85"/>
       <c r="C211" s="85"/>
@@ -10129,21 +10149,21 @@
       <c r="E211" s="85"/>
       <c r="F211" s="85"/>
       <c r="G211" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H211" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I211" s="91">
-        <f t="shared" si="30"/>
+      <c r="I211" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="9" t="s">
-        <v>176</v>
+        <v>54</v>
       </c>
       <c r="B212" s="85"/>
       <c r="C212" s="85"/>
@@ -10151,21 +10171,21 @@
       <c r="E212" s="85"/>
       <c r="F212" s="85"/>
       <c r="G212" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H212" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I212" s="91">
-        <f t="shared" si="30"/>
+      <c r="I212" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="9" t="s">
-        <v>177</v>
+        <v>55</v>
       </c>
       <c r="B213" s="85"/>
       <c r="C213" s="85"/>
@@ -10173,21 +10193,21 @@
       <c r="E213" s="85"/>
       <c r="F213" s="85"/>
       <c r="G213" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H213" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I213" s="91">
-        <f t="shared" si="30"/>
+      <c r="I213" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" s="35" t="s">
-        <v>178</v>
+      <c r="A214" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="B214" s="85"/>
       <c r="C214" s="85"/>
@@ -10195,21 +10215,21 @@
       <c r="E214" s="85"/>
       <c r="F214" s="85"/>
       <c r="G214" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H214" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I214" s="91">
-        <f t="shared" si="30"/>
+      <c r="I214" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="35" t="s">
-        <v>179</v>
+      <c r="A215" s="9" t="s">
+        <v>176</v>
       </c>
       <c r="B215" s="85"/>
       <c r="C215" s="85"/>
@@ -10217,21 +10237,21 @@
       <c r="E215" s="85"/>
       <c r="F215" s="85"/>
       <c r="G215" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H215" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I215" s="91">
-        <f t="shared" si="30"/>
+      <c r="I215" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="35" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B216" s="85"/>
       <c r="C216" s="85"/>
@@ -10239,21 +10259,21 @@
       <c r="E216" s="85"/>
       <c r="F216" s="85"/>
       <c r="G216" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H216" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I216" s="91">
-        <f t="shared" si="30"/>
+      <c r="I216" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="35" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B217" s="85"/>
       <c r="C217" s="85"/>
@@ -10261,21 +10281,21 @@
       <c r="E217" s="85"/>
       <c r="F217" s="85"/>
       <c r="G217" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H217" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I217" s="91">
-        <f t="shared" si="30"/>
+      <c r="I217" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="35" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B218" s="85"/>
       <c r="C218" s="85"/>
@@ -10283,21 +10303,21 @@
       <c r="E218" s="85"/>
       <c r="F218" s="85"/>
       <c r="G218" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H218" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I218" s="91">
-        <f t="shared" si="30"/>
+      <c r="I218" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="35" t="s">
-        <v>52</v>
+        <v>180</v>
       </c>
       <c r="B219" s="85"/>
       <c r="C219" s="85"/>
@@ -10305,21 +10325,21 @@
       <c r="E219" s="85"/>
       <c r="F219" s="85"/>
       <c r="G219" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H219" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I219" s="91">
-        <f t="shared" si="30"/>
+      <c r="I219" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="35" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B220" s="85"/>
       <c r="C220" s="85"/>
@@ -10327,42 +10347,43 @@
       <c r="E220" s="85"/>
       <c r="F220" s="85"/>
       <c r="G220" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H220" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I220" s="91">
-        <f t="shared" si="30"/>
+      <c r="I220" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A221" s="63" t="s">
-        <v>184</v>
+      <c r="A221" s="35" t="s">
+        <v>52</v>
       </c>
       <c r="B221" s="85"/>
       <c r="C221" s="85"/>
       <c r="D221" s="85"/>
       <c r="E221" s="85"/>
       <c r="F221" s="85"/>
-      <c r="G221" s="86">
-        <v>35000</v>
+      <c r="G221" s="85">
+        <f t="shared" si="29"/>
+        <v>32000</v>
       </c>
       <c r="H221" s="85">
-        <f>+G221</f>
-        <v>35000</v>
-      </c>
-      <c r="I221" s="91">
-        <f>+G221</f>
-        <v>35000</v>
+        <f t="shared" si="29"/>
+        <v>32000</v>
+      </c>
+      <c r="I221" s="90">
+        <f t="shared" si="29"/>
+        <v>32000</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="35" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B222" s="85"/>
       <c r="C222" s="85"/>
@@ -10370,43 +10391,42 @@
       <c r="E222" s="85"/>
       <c r="F222" s="85"/>
       <c r="G222" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H222" s="85">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I222" s="91">
-        <f t="shared" si="30"/>
+      <c r="I222" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A223" s="35" t="s">
-        <v>186</v>
+      <c r="A223" s="63" t="s">
+        <v>183</v>
       </c>
       <c r="B223" s="85"/>
       <c r="C223" s="85"/>
       <c r="D223" s="85"/>
       <c r="E223" s="85"/>
       <c r="F223" s="85"/>
-      <c r="G223" s="85">
-        <f t="shared" si="30"/>
-        <v>32000</v>
+      <c r="G223" s="86">
+        <v>35000</v>
       </c>
       <c r="H223" s="85">
-        <f t="shared" si="30"/>
-        <v>32000</v>
-      </c>
-      <c r="I223" s="91">
-        <f t="shared" si="30"/>
-        <v>32000</v>
+        <f>+G223</f>
+        <v>35000</v>
+      </c>
+      <c r="I223" s="90">
+        <f>+G223</f>
+        <v>35000</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="35" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B224" s="85"/>
       <c r="C224" s="85"/>
@@ -10414,21 +10434,21 @@
       <c r="E224" s="85"/>
       <c r="F224" s="85"/>
       <c r="G224" s="85">
-        <f t="shared" ref="G224:I225" si="31">$L$193</f>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H224" s="85">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I224" s="91">
-        <f t="shared" si="31"/>
+      <c r="I224" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A225" s="9" t="s">
-        <v>188</v>
+      <c r="A225" s="35" t="s">
+        <v>185</v>
       </c>
       <c r="B225" s="85"/>
       <c r="C225" s="85"/>
@@ -10436,21 +10456,21 @@
       <c r="E225" s="85"/>
       <c r="F225" s="85"/>
       <c r="G225" s="85">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
       <c r="H225" s="85">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I225" s="91">
-        <f t="shared" si="31"/>
+      <c r="I225" s="90">
+        <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A226" s="9" t="s">
-        <v>154</v>
+      <c r="A226" s="35" t="s">
+        <v>186</v>
       </c>
       <c r="B226" s="85"/>
       <c r="C226" s="85"/>
@@ -10458,20 +10478,21 @@
       <c r="E226" s="85"/>
       <c r="F226" s="85"/>
       <c r="G226" s="85">
-        <v>78000</v>
+        <f t="shared" ref="G226:I227" si="30">$L$195</f>
+        <v>32000</v>
       </c>
       <c r="H226" s="85">
-        <f t="shared" si="18"/>
-        <v>78000</v>
-      </c>
-      <c r="I226" s="91">
-        <f t="shared" si="18"/>
-        <v>78000</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+      <c r="I226" s="90">
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="B227" s="85"/>
       <c r="C227" s="85"/>
@@ -10479,106 +10500,105 @@
       <c r="E227" s="85"/>
       <c r="F227" s="85"/>
       <c r="G227" s="85">
-        <v>60000</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
       <c r="H227" s="85">
-        <f t="shared" si="18"/>
-        <v>60000</v>
-      </c>
-      <c r="I227" s="91">
-        <f t="shared" si="18"/>
-        <v>60000</v>
+        <f t="shared" si="30"/>
+        <v>32000</v>
+      </c>
+      <c r="I227" s="90">
+        <f t="shared" si="30"/>
+        <v>32000</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A228" s="63" t="s">
-        <v>157</v>
+      <c r="A228" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="B228" s="85"/>
       <c r="C228" s="85"/>
       <c r="D228" s="85"/>
       <c r="E228" s="85"/>
       <c r="F228" s="85"/>
-      <c r="G228" s="86">
-        <v>100000</v>
+      <c r="G228" s="85">
+        <v>78000</v>
       </c>
       <c r="H228" s="85">
-        <f t="shared" si="18"/>
-        <v>100000</v>
-      </c>
-      <c r="I228" s="91">
-        <f t="shared" si="18"/>
-        <v>100000</v>
+        <f t="shared" si="17"/>
+        <v>78000</v>
+      </c>
+      <c r="I228" s="90">
+        <f t="shared" si="17"/>
+        <v>78000</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A229" s="63" t="s">
-        <v>158</v>
+      <c r="A229" s="9" t="s">
+        <v>155</v>
       </c>
       <c r="B229" s="85"/>
       <c r="C229" s="85"/>
       <c r="D229" s="85"/>
       <c r="E229" s="85"/>
       <c r="F229" s="85"/>
-      <c r="G229" s="86">
-        <v>75000</v>
+      <c r="G229" s="85">
+        <v>60000</v>
       </c>
       <c r="H229" s="85">
-        <f t="shared" si="18"/>
-        <v>75000</v>
-      </c>
-      <c r="I229" s="91">
-        <f t="shared" si="18"/>
-        <v>75000</v>
+        <f t="shared" si="17"/>
+        <v>60000</v>
+      </c>
+      <c r="I229" s="90">
+        <f t="shared" si="17"/>
+        <v>60000</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A230" s="9" t="s">
-        <v>189</v>
+      <c r="A230" s="63" t="s">
+        <v>156</v>
       </c>
       <c r="B230" s="85"/>
       <c r="C230" s="85"/>
       <c r="D230" s="85"/>
       <c r="E230" s="85"/>
       <c r="F230" s="85"/>
-      <c r="G230" s="85">
-        <f>+$L$232</f>
-        <v>106880</v>
+      <c r="G230" s="86">
+        <v>100000</v>
       </c>
       <c r="H230" s="85">
-        <f t="shared" ref="H230:I245" si="32">+$L$232</f>
-        <v>106880</v>
-      </c>
-      <c r="I230" s="91">
-        <f t="shared" si="32"/>
-        <v>106880</v>
+        <f t="shared" si="17"/>
+        <v>100000</v>
+      </c>
+      <c r="I230" s="90">
+        <f t="shared" si="17"/>
+        <v>100000</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A231" s="9" t="s">
-        <v>190</v>
+      <c r="A231" s="63" t="s">
+        <v>157</v>
       </c>
       <c r="B231" s="85"/>
       <c r="C231" s="85"/>
       <c r="D231" s="85"/>
       <c r="E231" s="85"/>
       <c r="F231" s="85"/>
-      <c r="G231" s="85">
-        <f t="shared" ref="G231:I246" si="33">+$L$232</f>
-        <v>106880</v>
+      <c r="G231" s="86">
+        <v>75000</v>
       </c>
       <c r="H231" s="85">
-        <f t="shared" si="32"/>
-        <v>106880</v>
-      </c>
-      <c r="I231" s="91">
-        <f t="shared" si="32"/>
-        <v>106880</v>
+        <f t="shared" si="17"/>
+        <v>75000</v>
+      </c>
+      <c r="I231" s="90">
+        <f t="shared" si="17"/>
+        <v>75000</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B232" s="85"/>
       <c r="C232" s="85"/>
@@ -10586,27 +10606,21 @@
       <c r="E232" s="85"/>
       <c r="F232" s="85"/>
       <c r="G232" s="85">
-        <f t="shared" si="33"/>
+        <f>+$L$234</f>
         <v>106880</v>
       </c>
       <c r="H232" s="85">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="H232:I247" si="31">+$L$234</f>
         <v>106880</v>
       </c>
-      <c r="I232" s="91">
-        <f t="shared" si="32"/>
-        <v>106880</v>
-      </c>
-      <c r="K232" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="L232" s="66">
+      <c r="I232" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B233" s="85"/>
       <c r="C233" s="85"/>
@@ -10614,21 +10628,21 @@
       <c r="E233" s="85"/>
       <c r="F233" s="85"/>
       <c r="G233" s="85">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="G233:I248" si="32">+$L$234</f>
         <v>106880</v>
       </c>
       <c r="H233" s="85">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I233" s="91">
-        <f t="shared" si="32"/>
+      <c r="I233" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B234" s="85"/>
       <c r="C234" s="85"/>
@@ -10636,21 +10650,27 @@
       <c r="E234" s="85"/>
       <c r="F234" s="85"/>
       <c r="G234" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H234" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I234" s="91">
-        <f t="shared" si="32"/>
+      <c r="H234" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I234" s="90">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="K234" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="L234" s="66">
         <v>106880</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="9" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="B235" s="85"/>
       <c r="C235" s="85"/>
@@ -10658,21 +10678,21 @@
       <c r="E235" s="85"/>
       <c r="F235" s="85"/>
       <c r="G235" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H235" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I235" s="91">
-        <f t="shared" si="32"/>
+      <c r="H235" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I235" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B236" s="85"/>
       <c r="C236" s="85"/>
@@ -10680,21 +10700,21 @@
       <c r="E236" s="85"/>
       <c r="F236" s="85"/>
       <c r="G236" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H236" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I236" s="91">
-        <f t="shared" si="32"/>
+      <c r="H236" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I236" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="9" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B237" s="85"/>
       <c r="C237" s="85"/>
@@ -10702,21 +10722,21 @@
       <c r="E237" s="85"/>
       <c r="F237" s="85"/>
       <c r="G237" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H237" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I237" s="91">
-        <f t="shared" si="32"/>
+      <c r="H237" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I237" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B238" s="85"/>
       <c r="C238" s="85"/>
@@ -10724,21 +10744,21 @@
       <c r="E238" s="85"/>
       <c r="F238" s="85"/>
       <c r="G238" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H238" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I238" s="91">
-        <f t="shared" si="32"/>
+      <c r="H238" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I238" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B239" s="85"/>
       <c r="C239" s="85"/>
@@ -10746,21 +10766,21 @@
       <c r="E239" s="85"/>
       <c r="F239" s="85"/>
       <c r="G239" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H239" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I239" s="91">
-        <f t="shared" si="32"/>
+      <c r="H239" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I239" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B240" s="85"/>
       <c r="C240" s="85"/>
@@ -10768,21 +10788,21 @@
       <c r="E240" s="85"/>
       <c r="F240" s="85"/>
       <c r="G240" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H240" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I240" s="91">
-        <f t="shared" si="32"/>
+      <c r="H240" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I240" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B241" s="85"/>
       <c r="C241" s="85"/>
@@ -10790,21 +10810,21 @@
       <c r="E241" s="85"/>
       <c r="F241" s="85"/>
       <c r="G241" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H241" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I241" s="91">
-        <f t="shared" si="32"/>
+      <c r="H241" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I241" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B242" s="85"/>
       <c r="C242" s="85"/>
@@ -10812,21 +10832,21 @@
       <c r="E242" s="85"/>
       <c r="F242" s="85"/>
       <c r="G242" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H242" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I242" s="91">
-        <f t="shared" si="32"/>
+      <c r="H242" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I242" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B243" s="85"/>
       <c r="C243" s="85"/>
@@ -10834,21 +10854,21 @@
       <c r="E243" s="85"/>
       <c r="F243" s="85"/>
       <c r="G243" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H243" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I243" s="91">
-        <f t="shared" si="32"/>
+      <c r="H243" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I243" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B244" s="85"/>
       <c r="C244" s="85"/>
@@ -10856,21 +10876,21 @@
       <c r="E244" s="85"/>
       <c r="F244" s="85"/>
       <c r="G244" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H244" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I244" s="91">
-        <f t="shared" si="32"/>
+      <c r="H244" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I244" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B245" s="85"/>
       <c r="C245" s="85"/>
@@ -10878,272 +10898,316 @@
       <c r="E245" s="85"/>
       <c r="F245" s="85"/>
       <c r="G245" s="85">
-        <f t="shared" si="33"/>
-        <v>106880</v>
-      </c>
-      <c r="H245" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I245" s="91">
+      <c r="H245" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I245" s="90">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B246" s="85"/>
+      <c r="C246" s="85"/>
+      <c r="D246" s="85"/>
+      <c r="E246" s="85"/>
+      <c r="F246" s="85"/>
+      <c r="G246" s="85">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-    </row>
-    <row r="246" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="104" t="s">
-        <v>204</v>
-      </c>
-      <c r="B246" s="105"/>
-      <c r="C246" s="105"/>
-      <c r="D246" s="105"/>
-      <c r="E246" s="105"/>
-      <c r="F246" s="105"/>
-      <c r="G246" s="105">
-        <f t="shared" si="33"/>
+      <c r="H246" s="85">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="H246" s="105">
-        <f t="shared" si="33"/>
+      <c r="I246" s="90">
+        <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I246" s="106">
-        <f t="shared" si="33"/>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B247" s="85"/>
+      <c r="C247" s="85"/>
+      <c r="D247" s="85"/>
+      <c r="E247" s="85"/>
+      <c r="F247" s="85"/>
+      <c r="G247" s="85">
+        <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-    </row>
-    <row r="247" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="87" t="s">
-        <v>6</v>
-      </c>
-      <c r="B247" s="121"/>
-      <c r="C247" s="122"/>
-      <c r="D247" s="122"/>
-      <c r="E247" s="95"/>
-      <c r="F247" s="95"/>
-      <c r="G247" s="95" t="s">
-        <v>94</v>
-      </c>
-      <c r="H247" s="96" t="s">
-        <v>95</v>
-      </c>
-      <c r="I247" s="96" t="s">
-        <v>123</v>
+      <c r="H247" s="85">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I247" s="90">
+        <f t="shared" si="31"/>
+        <v>106880</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B248" s="108"/>
-      <c r="C248" s="108"/>
-      <c r="D248" s="108"/>
-      <c r="E248" s="108"/>
-      <c r="F248" s="108"/>
-      <c r="G248" s="107">
-        <v>40000</v>
-      </c>
-      <c r="H248" s="108">
-        <f>+G248</f>
-        <v>40000</v>
-      </c>
-      <c r="I248" s="109">
-        <f>+G248</f>
-        <v>40000</v>
+      <c r="A248" s="103" t="s">
+        <v>203</v>
+      </c>
+      <c r="B248" s="104"/>
+      <c r="C248" s="104"/>
+      <c r="D248" s="104"/>
+      <c r="E248" s="104"/>
+      <c r="F248" s="104"/>
+      <c r="G248" s="104">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="H248" s="104">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+      <c r="I248" s="105">
+        <f t="shared" si="32"/>
+        <v>106880</v>
       </c>
     </row>
     <row r="249" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="87" t="s">
-        <v>208</v>
-      </c>
-      <c r="B249" s="121"/>
-      <c r="C249" s="95"/>
-      <c r="D249" s="95"/>
-      <c r="E249" s="95"/>
-      <c r="F249" s="95" t="s">
-        <v>93</v>
-      </c>
-      <c r="G249" s="95" t="s">
+        <v>6</v>
+      </c>
+      <c r="B249" s="120"/>
+      <c r="C249" s="121"/>
+      <c r="D249" s="121"/>
+      <c r="E249" s="94"/>
+      <c r="F249" s="94"/>
+      <c r="G249" s="94" t="s">
         <v>94</v>
       </c>
       <c r="H249" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="I249" s="96" t="s">
+      <c r="I249" s="95" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A250" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B250" s="84"/>
-      <c r="C250" s="84"/>
-      <c r="D250" s="84"/>
-      <c r="E250" s="84"/>
-      <c r="F250" s="102">
-        <v>15000</v>
-      </c>
-      <c r="G250" s="102">
-        <v>15000</v>
-      </c>
-      <c r="H250" s="84">
-        <f>+$G$250</f>
-        <v>15000</v>
-      </c>
-      <c r="I250" s="103">
-        <f>+$G$250</f>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A251" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B251" s="82"/>
-      <c r="C251" s="82"/>
-      <c r="D251" s="82"/>
-      <c r="E251" s="82"/>
-      <c r="F251" s="83">
-        <v>18000</v>
-      </c>
-      <c r="G251" s="83">
-        <v>15000</v>
-      </c>
-      <c r="H251" s="82">
-        <f>+G251</f>
-        <v>15000</v>
-      </c>
-      <c r="I251" s="98">
-        <f>+G251</f>
-        <v>15000</v>
+    <row r="250" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B250" s="107"/>
+      <c r="C250" s="107"/>
+      <c r="D250" s="107"/>
+      <c r="E250" s="107"/>
+      <c r="F250" s="107"/>
+      <c r="G250" s="106">
+        <v>40000</v>
+      </c>
+      <c r="H250" s="107">
+        <f>+G250</f>
+        <v>40000</v>
+      </c>
+      <c r="I250" s="108">
+        <f>+G250</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="87" t="s">
+        <v>207</v>
+      </c>
+      <c r="B251" s="120"/>
+      <c r="C251" s="94"/>
+      <c r="D251" s="94"/>
+      <c r="E251" s="94"/>
+      <c r="F251" s="94" t="s">
+        <v>93</v>
+      </c>
+      <c r="G251" s="94" t="s">
+        <v>94</v>
+      </c>
+      <c r="H251" s="94" t="s">
+        <v>95</v>
+      </c>
+      <c r="I251" s="95" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B252" s="82"/>
-      <c r="C252" s="82"/>
-      <c r="D252" s="82"/>
-      <c r="E252" s="82"/>
-      <c r="F252" s="83">
-        <v>18000</v>
-      </c>
-      <c r="G252" s="83">
+        <v>133</v>
+      </c>
+      <c r="B252" s="84"/>
+      <c r="C252" s="84"/>
+      <c r="D252" s="84"/>
+      <c r="E252" s="84"/>
+      <c r="F252" s="101">
         <v>15000</v>
       </c>
-      <c r="H252" s="82">
-        <f>+G252</f>
+      <c r="G252" s="101">
         <v>15000</v>
       </c>
-      <c r="I252" s="98">
-        <f>+G252</f>
+      <c r="H252" s="84">
+        <f>+$G$252</f>
+        <v>15000</v>
+      </c>
+      <c r="I252" s="102">
+        <f>+$G$252</f>
         <v>15000</v>
       </c>
     </row>
     <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="23" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="B253" s="82"/>
       <c r="C253" s="82"/>
       <c r="D253" s="82"/>
       <c r="E253" s="82"/>
-      <c r="F253" s="82"/>
+      <c r="F253" s="83">
+        <v>18000</v>
+      </c>
       <c r="G253" s="83">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="H253" s="82">
         <f>+G253</f>
+        <v>15000</v>
+      </c>
+      <c r="I253" s="97">
+        <f>+G253</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A254" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B254" s="82"/>
+      <c r="C254" s="82"/>
+      <c r="D254" s="82"/>
+      <c r="E254" s="82"/>
+      <c r="F254" s="83">
+        <v>18000</v>
+      </c>
+      <c r="G254" s="83">
+        <v>15000</v>
+      </c>
+      <c r="H254" s="82">
+        <f>+G254</f>
+        <v>15000</v>
+      </c>
+      <c r="I254" s="97">
+        <f>+G254</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A255" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="B255" s="82"/>
+      <c r="C255" s="82"/>
+      <c r="D255" s="82"/>
+      <c r="E255" s="82"/>
+      <c r="F255" s="82"/>
+      <c r="G255" s="83">
         <v>20000</v>
       </c>
-      <c r="I253" s="98">
-        <f>+G253</f>
+      <c r="H255" s="82">
+        <f>+G255</f>
         <v>20000</v>
       </c>
-    </row>
-    <row r="254" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="B254" s="100"/>
-      <c r="C254" s="100"/>
-      <c r="D254" s="100"/>
-      <c r="E254" s="100"/>
-      <c r="F254" s="100"/>
-      <c r="G254" s="99">
+      <c r="I255" s="97">
+        <f>+G255</f>
         <v>20000</v>
       </c>
-      <c r="H254" s="100">
-        <f>+G254</f>
+    </row>
+    <row r="256" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B256" s="99"/>
+      <c r="C256" s="99"/>
+      <c r="D256" s="99"/>
+      <c r="E256" s="99"/>
+      <c r="F256" s="99"/>
+      <c r="G256" s="98">
         <v>20000</v>
       </c>
-      <c r="I254" s="101">
-        <f>+G254</f>
+      <c r="H256" s="99">
+        <f>+G256</f>
         <v>20000</v>
       </c>
-    </row>
-    <row r="255" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="87" t="s">
+      <c r="I256" s="100">
+        <f>+G256</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="87" t="s">
+        <v>227</v>
+      </c>
+      <c r="B257" s="120"/>
+      <c r="C257" s="94"/>
+      <c r="D257" s="94"/>
+      <c r="E257" s="94"/>
+      <c r="F257" s="94" t="s">
+        <v>93</v>
+      </c>
+      <c r="G257" s="94" t="s">
+        <v>94</v>
+      </c>
+      <c r="H257" s="94" t="s">
+        <v>95</v>
+      </c>
+      <c r="I257" s="95" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A258" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="B255" s="121"/>
-      <c r="C255" s="95"/>
-      <c r="D255" s="95"/>
-      <c r="E255" s="95"/>
-      <c r="F255" s="95" t="s">
-        <v>93</v>
-      </c>
-      <c r="G255" s="95" t="s">
-        <v>94</v>
-      </c>
-      <c r="H255" s="95" t="s">
-        <v>95</v>
-      </c>
-      <c r="I255" s="96" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A256" s="23" t="s">
+      <c r="B258" s="84"/>
+      <c r="C258" s="84"/>
+      <c r="D258" s="84"/>
+      <c r="E258" s="84"/>
+      <c r="F258" s="84"/>
+      <c r="G258" s="101">
+        <v>35000</v>
+      </c>
+      <c r="H258" s="84">
+        <f>+G258</f>
+        <v>35000</v>
+      </c>
+      <c r="I258" s="102">
+        <f>+G258</f>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A259" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B256" s="84"/>
-      <c r="C256" s="84"/>
-      <c r="D256" s="84"/>
-      <c r="E256" s="84"/>
-      <c r="F256" s="84"/>
-      <c r="G256" s="102">
+      <c r="B259" s="82"/>
+      <c r="C259" s="82"/>
+      <c r="D259" s="82"/>
+      <c r="E259" s="82"/>
+      <c r="F259" s="82"/>
+      <c r="G259" s="83">
         <v>35000</v>
       </c>
-      <c r="H256" s="84">
-        <f>+G256</f>
+      <c r="H259" s="82">
+        <f>+G259</f>
         <v>35000</v>
       </c>
-      <c r="I256" s="103">
-        <f>+G256</f>
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A257" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="B257" s="82"/>
-      <c r="C257" s="82"/>
-      <c r="D257" s="82"/>
-      <c r="E257" s="82"/>
-      <c r="F257" s="82"/>
-      <c r="G257" s="83">
-        <v>35000</v>
-      </c>
-      <c r="H257" s="82">
-        <f>+G257</f>
-        <v>35000</v>
-      </c>
-      <c r="I257" s="98">
-        <f>+G257</f>
+      <c r="I259" s="97">
+        <f>+G259</f>
         <v>35000</v>
       </c>
     </row>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2553,7 +2553,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A251" authorId="0" shapeId="0">
+    <comment ref="A252" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2577,7 +2577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A257" authorId="0" shapeId="0">
+    <comment ref="A258" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2606,7 +2606,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="238">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -3364,7 +3364,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3412,12 +3412,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Baskerville Old Face"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -3452,20 +3446,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <i/>
       <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -3490,7 +3472,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3530,12 +3512,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3594,7 +3570,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -4189,6 +4165,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -4196,7 +4183,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4208,7 +4195,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -4216,22 +4202,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4269,7 +4255,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -4282,112 +4268,98 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="16" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4396,7 +4368,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4405,31 +4377,31 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="12" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="11" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
@@ -4439,7 +4411,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4451,28 +4423,28 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4481,66 +4453,63 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="17" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="17" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4572,7 +4541,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="12" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4588,16 +4557,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4886,531 +4862,531 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L259"/>
+  <dimension ref="A1:L260"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="67" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.5703125" style="67" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.5703125" style="67" customWidth="1"/>
-    <col min="10" max="10" width="18" style="154" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.85546875" style="58" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="58" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.5703125" style="58" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.5703125" style="58" customWidth="1"/>
+    <col min="10" max="10" width="18" style="144" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="68" t="s">
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="68" t="s">
+      <c r="G2" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H2" s="69" t="s">
+      <c r="H2" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65">
+      <c r="B3" s="56"/>
+      <c r="C3" s="56">
         <v>5550</v>
       </c>
-      <c r="D3" s="65">
+      <c r="D3" s="56">
         <v>5550</v>
       </c>
-      <c r="E3" s="65">
+      <c r="E3" s="56">
         <v>5550</v>
       </c>
-      <c r="F3" s="73">
+      <c r="F3" s="64">
         <v>5550</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="56" t="s">
         <v>225</v>
       </c>
-      <c r="H3" s="65">
+      <c r="H3" s="56">
         <v>4550</v>
       </c>
-      <c r="I3" s="144">
+      <c r="I3" s="134">
         <f>+F3</f>
         <v>5550</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="149"/>
-      <c r="C4" s="149">
+      <c r="B4" s="139"/>
+      <c r="C4" s="139">
         <v>8500</v>
       </c>
-      <c r="D4" s="149">
+      <c r="D4" s="139">
         <v>8500</v>
       </c>
-      <c r="E4" s="149">
+      <c r="E4" s="139">
         <v>8500</v>
       </c>
-      <c r="F4" s="149">
+      <c r="F4" s="139">
         <f>+F3</f>
         <v>5550</v>
       </c>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="56" t="s">
         <v>225</v>
       </c>
-      <c r="H4" s="149"/>
-      <c r="I4" s="150">
+      <c r="H4" s="139"/>
+      <c r="I4" s="140">
         <f>+I3*2</f>
         <v>11100</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="B5" s="151"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="152"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="141"/>
+      <c r="F5" s="141"/>
+      <c r="G5" s="141"/>
+      <c r="H5" s="141"/>
+      <c r="I5" s="142"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65">
+      <c r="B6" s="56"/>
+      <c r="C6" s="56">
         <v>20000</v>
       </c>
-      <c r="D6" s="65">
+      <c r="D6" s="56">
         <v>20000</v>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="56">
         <v>30000</v>
       </c>
-      <c r="F6" s="65">
+      <c r="F6" s="56">
         <v>15000</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="56">
         <v>30000</v>
       </c>
-      <c r="H6" s="65"/>
-      <c r="I6" s="144" t="s">
+      <c r="H6" s="56"/>
+      <c r="I6" s="134" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="149"/>
-      <c r="C7" s="149">
+      <c r="B7" s="139"/>
+      <c r="C7" s="139">
         <v>14000</v>
       </c>
-      <c r="D7" s="149">
+      <c r="D7" s="139">
         <v>14000</v>
       </c>
-      <c r="E7" s="149">
+      <c r="E7" s="139">
         <v>20000</v>
       </c>
-      <c r="F7" s="153">
+      <c r="F7" s="143">
         <f>+F6/2</f>
         <v>7500</v>
       </c>
-      <c r="G7" s="153">
+      <c r="G7" s="143">
         <f>+G6/2</f>
         <v>15000</v>
       </c>
-      <c r="H7" s="149"/>
-      <c r="I7" s="150"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="140"/>
     </row>
     <row r="8" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="113"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="68" t="s">
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="68" t="s">
+      <c r="G8" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I8" s="69" t="s">
+      <c r="I8" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J8" s="113" t="s">
+      <c r="J8" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K8" s="55"/>
+      <c r="K8" s="47"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="70">
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="61">
         <v>4800</v>
       </c>
-      <c r="K9" s="158">
+      <c r="K9" s="148">
         <f>+J9</f>
         <v>4800</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="65">
+      <c r="B10" s="56">
         <v>10000</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65">
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56">
         <v>4200</v>
       </c>
-      <c r="F10" s="65"/>
-      <c r="G10" s="70">
+      <c r="F10" s="56"/>
+      <c r="G10" s="61">
         <f>+B10*0.6</f>
         <v>6000</v>
       </c>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="155"/>
-      <c r="K10" s="11"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="145"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="B11" s="65">
+      <c r="B11" s="56">
         <v>25000</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65">
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56">
         <v>8000</v>
       </c>
-      <c r="F11" s="65"/>
-      <c r="G11" s="70">
+      <c r="F11" s="56"/>
+      <c r="G11" s="61">
         <v>12000</v>
       </c>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="11"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="145"/>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="65">
+      <c r="B12" s="56">
         <v>30000</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65">
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56">
         <v>10000</v>
       </c>
-      <c r="F12" s="65"/>
-      <c r="G12" s="70">
+      <c r="F12" s="56"/>
+      <c r="G12" s="61">
         <v>15000</v>
       </c>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="155"/>
-      <c r="K12" s="11"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="145"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="65"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65">
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56">
         <v>17000</v>
       </c>
-      <c r="F13" s="65"/>
-      <c r="G13" s="70">
+      <c r="F13" s="56"/>
+      <c r="G13" s="61">
         <v>18000</v>
       </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="155"/>
-      <c r="K13" s="11"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65">
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56">
         <v>18400</v>
       </c>
-      <c r="F14" s="65"/>
-      <c r="G14" s="70">
+      <c r="F14" s="56"/>
+      <c r="G14" s="61">
         <v>20000</v>
       </c>
-      <c r="H14" s="70">
+      <c r="H14" s="61">
         <v>7000</v>
       </c>
-      <c r="I14" s="65">
+      <c r="I14" s="56">
         <f>+H14</f>
         <v>7000</v>
       </c>
-      <c r="J14" s="70">
+      <c r="J14" s="61">
         <v>35000</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="113"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="68" t="s">
+      <c r="B15" s="104"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="G15" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H15" s="69" t="s">
+      <c r="H15" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I15" s="69" t="s">
+      <c r="I15" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="113" t="s">
+      <c r="J15" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K15" s="58"/>
+      <c r="K15" s="50"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="65">
+      <c r="B16" s="56">
         <v>88500</v>
       </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65">
+      <c r="C16" s="56"/>
+      <c r="D16" s="56">
         <v>44800</v>
       </c>
-      <c r="E16" s="65">
+      <c r="E16" s="56">
         <v>44800</v>
       </c>
-      <c r="F16" s="70">
+      <c r="F16" s="61">
         <f>+B16*0.7</f>
         <v>61949.999999999993</v>
       </c>
-      <c r="G16" s="70">
+      <c r="G16" s="61">
         <f>+B16*0.6</f>
         <v>53100</v>
       </c>
-      <c r="H16" s="65">
+      <c r="H16" s="56">
         <v>14750</v>
       </c>
-      <c r="I16" s="65">
+      <c r="I16" s="56">
         <v>0</v>
       </c>
-      <c r="J16" s="155">
+      <c r="J16" s="145">
         <v>29500</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="10">
         <v>88500</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="65">
+      <c r="B17" s="56">
         <v>177000</v>
       </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65">
+      <c r="C17" s="56"/>
+      <c r="D17" s="56">
         <v>88500</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="56">
         <v>88500</v>
       </c>
-      <c r="F17" s="70">
+      <c r="F17" s="61">
         <f>+B17*0.7</f>
         <v>123899.99999999999</v>
       </c>
-      <c r="G17" s="70">
+      <c r="G17" s="61">
         <f>+B17*0.6</f>
         <v>106200</v>
       </c>
-      <c r="H17" s="65">
+      <c r="H17" s="56">
         <v>29500</v>
       </c>
-      <c r="I17" s="65">
+      <c r="I17" s="56">
         <v>0</v>
       </c>
-      <c r="J17" s="155">
+      <c r="J17" s="145">
         <v>59000</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="10">
         <v>177000</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65">
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56">
         <v>16000</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="155"/>
-      <c r="K18" s="11"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="10"/>
     </row>
     <row r="19" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="113"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="68" t="s">
+      <c r="B19" s="104"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="68" t="s">
+      <c r="G19" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="69" t="s">
+      <c r="H19" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="69" t="s">
+      <c r="I19" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="65">
+      <c r="B20" s="56">
         <v>20000</v>
       </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65">
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56">
         <v>8000</v>
       </c>
-      <c r="F20" s="72">
+      <c r="F20" s="63">
         <v>0</v>
       </c>
-      <c r="G20" s="70">
+      <c r="G20" s="61">
         <f>+B20*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H20" s="65"/>
-      <c r="I20" s="65"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="113"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="68" t="s">
+      <c r="B21" s="104"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="68" t="s">
+      <c r="G21" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="69" t="s">
+      <c r="H21" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I21" s="69" t="s">
+      <c r="I21" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J21" s="113" t="s">
+      <c r="J21" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K21" s="55"/>
+      <c r="K21" s="47"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="65">
+      <c r="B22" s="56">
         <v>35000</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65">
+      <c r="C22" s="56"/>
+      <c r="D22" s="56">
         <v>20000</v>
       </c>
-      <c r="E22" s="65">
+      <c r="E22" s="56">
         <v>20000</v>
       </c>
-      <c r="F22" s="72">
+      <c r="F22" s="63">
         <v>0</v>
       </c>
-      <c r="G22" s="70">
+      <c r="G22" s="61">
         <v>20000</v>
       </c>
-      <c r="H22" s="65">
+      <c r="H22" s="56">
         <v>7000</v>
       </c>
-      <c r="I22" s="65">
+      <c r="I22" s="56">
         <v>0</v>
       </c>
-      <c r="J22" s="155">
+      <c r="J22" s="145">
         <v>35000</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="10">
         <v>35000</v>
       </c>
     </row>
@@ -5418,99 +5394,99 @@
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="113"/>
-      <c r="C23" s="114"/>
-      <c r="D23" s="114"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="68" t="s">
+      <c r="B23" s="104"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G23" s="68" t="s">
+      <c r="G23" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="69" t="s">
+      <c r="H23" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I23" s="69" t="s">
+      <c r="I23" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J23" s="113" t="s">
+      <c r="J23" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K23" s="55"/>
+      <c r="K23" s="47"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="155"/>
-      <c r="K24" s="11"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="145"/>
+      <c r="K24" s="10"/>
     </row>
     <row r="25" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B25" s="113"/>
-      <c r="C25" s="114"/>
-      <c r="D25" s="114"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="68" t="s">
+      <c r="B25" s="104"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G25" s="68" t="s">
+      <c r="G25" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="69" t="s">
+      <c r="H25" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="69" t="s">
+      <c r="I25" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J25" s="113" t="s">
+      <c r="J25" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K25" s="55"/>
+      <c r="K25" s="47"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="65">
+      <c r="B26" s="56">
         <v>20000</v>
       </c>
-      <c r="C26" s="65">
+      <c r="C26" s="56">
         <v>12600</v>
       </c>
-      <c r="D26" s="65">
+      <c r="D26" s="56">
         <v>8200</v>
       </c>
-      <c r="E26" s="65">
+      <c r="E26" s="56">
         <v>12600</v>
       </c>
-      <c r="F26" s="72">
+      <c r="F26" s="63">
         <f>+B26*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G26" s="70">
+      <c r="G26" s="61">
         <f>+B26*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H26" s="65">
+      <c r="H26" s="56">
         <v>5400</v>
       </c>
-      <c r="I26" s="65">
+      <c r="I26" s="56">
         <v>0</v>
       </c>
-      <c r="J26" s="155">
+      <c r="J26" s="145">
         <v>17400</v>
       </c>
-      <c r="K26" s="11">
+      <c r="K26" s="10">
         <v>17400</v>
       </c>
     </row>
@@ -5518,61 +5494,61 @@
       <c r="A27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="113"/>
-      <c r="C27" s="114"/>
-      <c r="D27" s="114"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="68" t="s">
+      <c r="B27" s="104"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="68" t="s">
+      <c r="G27" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H27" s="69" t="s">
+      <c r="H27" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I27" s="69" t="s">
+      <c r="I27" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J27" s="113" t="s">
+      <c r="J27" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K27" s="55"/>
+      <c r="K27" s="47"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="65">
+      <c r="B28" s="56">
         <v>228334</v>
       </c>
-      <c r="C28" s="65">
+      <c r="C28" s="56">
         <v>149000</v>
       </c>
-      <c r="D28" s="65">
+      <c r="D28" s="56">
         <v>137000</v>
       </c>
-      <c r="E28" s="65">
+      <c r="E28" s="56">
         <v>149000</v>
       </c>
-      <c r="F28" s="72">
+      <c r="F28" s="63">
         <f>+B28*0.7</f>
         <v>159833.79999999999</v>
       </c>
-      <c r="G28" s="70">
+      <c r="G28" s="61">
         <f>+B28*0.6</f>
         <v>137000.4</v>
       </c>
-      <c r="H28" s="65">
+      <c r="H28" s="56">
         <v>74000</v>
       </c>
-      <c r="I28" s="65">
+      <c r="I28" s="56">
         <v>74000</v>
       </c>
-      <c r="J28" s="155">
+      <c r="J28" s="145">
         <v>199000</v>
       </c>
-      <c r="K28" s="11">
+      <c r="K28" s="10">
         <v>199000</v>
       </c>
     </row>
@@ -5580,61 +5556,61 @@
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="113"/>
-      <c r="C29" s="114"/>
-      <c r="D29" s="114"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="68" t="s">
+      <c r="B29" s="104"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G29" s="68" t="s">
+      <c r="G29" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H29" s="69" t="s">
+      <c r="H29" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I29" s="69" t="s">
+      <c r="I29" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J29" s="113" t="s">
+      <c r="J29" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K29" s="55"/>
+      <c r="K29" s="47"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="65">
+      <c r="B30" s="56">
         <v>72000</v>
       </c>
-      <c r="C30" s="65">
+      <c r="C30" s="56">
         <v>36700</v>
       </c>
-      <c r="D30" s="65">
+      <c r="D30" s="56">
         <v>31000</v>
       </c>
-      <c r="E30" s="65">
+      <c r="E30" s="56">
         <v>36700</v>
       </c>
-      <c r="F30" s="72">
+      <c r="F30" s="63">
         <f>+B30*0.7</f>
         <v>50400</v>
       </c>
-      <c r="G30" s="70">
+      <c r="G30" s="61">
         <f>+B30*0.6</f>
         <v>43200</v>
       </c>
-      <c r="H30" s="65">
+      <c r="H30" s="56">
         <v>16800</v>
       </c>
-      <c r="I30" s="65">
+      <c r="I30" s="56">
         <v>16800</v>
       </c>
-      <c r="J30" s="155">
+      <c r="J30" s="145">
         <v>43400</v>
       </c>
-      <c r="K30" s="11">
+      <c r="K30" s="10">
         <v>43400</v>
       </c>
     </row>
@@ -5642,61 +5618,61 @@
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="113"/>
-      <c r="C31" s="114"/>
-      <c r="D31" s="114"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="68" t="s">
+      <c r="B31" s="104"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G31" s="68" t="s">
+      <c r="G31" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H31" s="69" t="s">
+      <c r="H31" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I31" s="69" t="s">
+      <c r="I31" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J31" s="113" t="s">
+      <c r="J31" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K31" s="55"/>
+      <c r="K31" s="47"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="65">
+      <c r="B32" s="56">
         <v>33000</v>
       </c>
-      <c r="C32" s="65">
+      <c r="C32" s="56">
         <v>16600</v>
       </c>
-      <c r="D32" s="65">
+      <c r="D32" s="56">
         <v>16600</v>
       </c>
-      <c r="E32" s="65">
+      <c r="E32" s="56">
         <v>16600</v>
       </c>
-      <c r="F32" s="72">
+      <c r="F32" s="63">
         <f>+B32*0.7</f>
         <v>23100</v>
       </c>
-      <c r="G32" s="70">
+      <c r="G32" s="61">
         <f>+B32*0.6</f>
         <v>19800</v>
       </c>
-      <c r="H32" s="65">
+      <c r="H32" s="56">
         <v>10800</v>
       </c>
-      <c r="I32" s="65">
+      <c r="I32" s="56">
         <v>10800</v>
       </c>
-      <c r="J32" s="155">
+      <c r="J32" s="145">
         <v>20300</v>
       </c>
-      <c r="K32" s="11">
+      <c r="K32" s="10">
         <v>20300</v>
       </c>
     </row>
@@ -5704,61 +5680,61 @@
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="113"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="114"/>
-      <c r="E33" s="115"/>
-      <c r="F33" s="68" t="s">
+      <c r="B33" s="104"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G33" s="68" t="s">
+      <c r="G33" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="69" t="s">
+      <c r="H33" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I33" s="69" t="s">
+      <c r="I33" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J33" s="113" t="s">
+      <c r="J33" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K33" s="55"/>
+      <c r="K33" s="47"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="65">
+      <c r="B34" s="56">
         <v>24600</v>
       </c>
-      <c r="C34" s="65">
+      <c r="C34" s="56">
         <v>12500</v>
       </c>
-      <c r="D34" s="65">
+      <c r="D34" s="56">
         <v>12500</v>
       </c>
-      <c r="E34" s="65">
+      <c r="E34" s="56">
         <v>12500</v>
       </c>
-      <c r="F34" s="72">
+      <c r="F34" s="63">
         <f>+B34*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G34" s="70">
+      <c r="G34" s="61">
         <f>+B34*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H34" s="65">
+      <c r="H34" s="56">
         <v>6300</v>
       </c>
-      <c r="I34" s="65">
+      <c r="I34" s="56">
         <v>6300</v>
       </c>
-      <c r="J34" s="155">
+      <c r="J34" s="145">
         <v>15200</v>
       </c>
-      <c r="K34" s="11">
+      <c r="K34" s="10">
         <v>15200</v>
       </c>
     </row>
@@ -5766,61 +5742,61 @@
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="113"/>
-      <c r="C35" s="114"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="115"/>
-      <c r="F35" s="68" t="s">
+      <c r="B35" s="104"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G35" s="68" t="s">
+      <c r="G35" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H35" s="69" t="s">
+      <c r="H35" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I35" s="69" t="s">
+      <c r="I35" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J35" s="113" t="s">
+      <c r="J35" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K35" s="55"/>
+      <c r="K35" s="47"/>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="65">
+      <c r="B36" s="56">
         <v>24600</v>
       </c>
-      <c r="C36" s="65">
+      <c r="C36" s="56">
         <v>12500</v>
       </c>
-      <c r="D36" s="65">
+      <c r="D36" s="56">
         <v>12500</v>
       </c>
-      <c r="E36" s="65">
+      <c r="E36" s="56">
         <v>12500</v>
       </c>
-      <c r="F36" s="72">
+      <c r="F36" s="63">
         <f>+B36*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G36" s="70">
+      <c r="G36" s="61">
         <f>+B36*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H36" s="65">
+      <c r="H36" s="56">
         <v>6300</v>
       </c>
-      <c r="I36" s="65">
+      <c r="I36" s="56">
         <v>6300</v>
       </c>
-      <c r="J36" s="155">
+      <c r="J36" s="145">
         <v>15200</v>
       </c>
-      <c r="K36" s="11">
+      <c r="K36" s="10">
         <v>15200</v>
       </c>
     </row>
@@ -5828,61 +5804,61 @@
       <c r="A37" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B37" s="113"/>
-      <c r="C37" s="114"/>
-      <c r="D37" s="114"/>
-      <c r="E37" s="115"/>
-      <c r="F37" s="68" t="s">
+      <c r="B37" s="104"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G37" s="68" t="s">
+      <c r="G37" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H37" s="69" t="s">
+      <c r="H37" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I37" s="69" t="s">
+      <c r="I37" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J37" s="113" t="s">
+      <c r="J37" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K37" s="55"/>
+      <c r="K37" s="47"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B38" s="65">
+      <c r="B38" s="56">
         <v>24600</v>
       </c>
-      <c r="C38" s="65">
+      <c r="C38" s="56">
         <v>12500</v>
       </c>
-      <c r="D38" s="65">
+      <c r="D38" s="56">
         <v>12500</v>
       </c>
-      <c r="E38" s="65">
+      <c r="E38" s="56">
         <v>12500</v>
       </c>
-      <c r="F38" s="72">
+      <c r="F38" s="63">
         <f>+B38*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G38" s="70">
+      <c r="G38" s="61">
         <f>+B38*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H38" s="65">
+      <c r="H38" s="56">
         <v>6300</v>
       </c>
-      <c r="I38" s="65">
+      <c r="I38" s="56">
         <v>6300</v>
       </c>
-      <c r="J38" s="155">
+      <c r="J38" s="145">
         <v>15200</v>
       </c>
-      <c r="K38" s="11">
+      <c r="K38" s="10">
         <v>15200</v>
       </c>
     </row>
@@ -5890,123 +5866,123 @@
       <c r="A39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="113"/>
-      <c r="C39" s="114"/>
-      <c r="D39" s="114"/>
-      <c r="E39" s="115"/>
-      <c r="F39" s="68" t="s">
+      <c r="B39" s="104"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="106"/>
+      <c r="F39" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G39" s="68" t="s">
+      <c r="G39" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H39" s="69" t="s">
+      <c r="H39" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I39" s="69" t="s">
+      <c r="I39" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J39" s="113" t="s">
+      <c r="J39" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K39" s="55"/>
+      <c r="K39" s="47"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="65">
+      <c r="B40" s="56">
         <v>24600</v>
       </c>
-      <c r="C40" s="65">
+      <c r="C40" s="56">
         <v>12500</v>
       </c>
-      <c r="D40" s="65">
+      <c r="D40" s="56">
         <v>12500</v>
       </c>
-      <c r="E40" s="65">
+      <c r="E40" s="56">
         <v>12500</v>
       </c>
-      <c r="F40" s="72">
+      <c r="F40" s="63">
         <f>+B40*0.7</f>
         <v>17220</v>
       </c>
-      <c r="G40" s="70">
+      <c r="G40" s="61">
         <f>+B40*0.6</f>
         <v>14760</v>
       </c>
-      <c r="H40" s="65">
+      <c r="H40" s="56">
         <v>6300</v>
       </c>
-      <c r="I40" s="65">
+      <c r="I40" s="56">
         <v>6300</v>
       </c>
-      <c r="J40" s="155">
+      <c r="J40" s="145">
         <v>15200</v>
       </c>
-      <c r="K40" s="11">
+      <c r="K40" s="10">
         <v>15200</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="113"/>
-      <c r="C41" s="114"/>
-      <c r="D41" s="114"/>
-      <c r="E41" s="115"/>
-      <c r="F41" s="68" t="s">
+      <c r="B41" s="104"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="106"/>
+      <c r="F41" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G41" s="68" t="s">
+      <c r="G41" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H41" s="69" t="s">
+      <c r="H41" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I41" s="69" t="s">
+      <c r="I41" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J41" s="113" t="s">
+      <c r="J41" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K41" s="55"/>
+      <c r="K41" s="47"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="33" t="s">
+      <c r="A42" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="B42" s="65">
+      <c r="B42" s="56">
         <v>72000</v>
       </c>
-      <c r="C42" s="65">
+      <c r="C42" s="56">
         <v>36700</v>
       </c>
-      <c r="D42" s="65">
+      <c r="D42" s="56">
         <v>31000</v>
       </c>
-      <c r="E42" s="65">
+      <c r="E42" s="56">
         <v>36700</v>
       </c>
-      <c r="F42" s="72">
+      <c r="F42" s="63">
         <f>+B42*0.7</f>
         <v>50400</v>
       </c>
-      <c r="G42" s="70">
+      <c r="G42" s="61">
         <f>+B42*0.6</f>
         <v>43200</v>
       </c>
-      <c r="H42" s="65">
+      <c r="H42" s="56">
         <v>16800</v>
       </c>
-      <c r="I42" s="65">
+      <c r="I42" s="56">
         <v>16800</v>
       </c>
-      <c r="J42" s="155">
+      <c r="J42" s="145">
         <v>43400</v>
       </c>
-      <c r="K42" s="11">
+      <c r="K42" s="10">
         <v>43400</v>
       </c>
     </row>
@@ -6014,412 +5990,412 @@
       <c r="A43" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="113"/>
-      <c r="C43" s="114"/>
-      <c r="D43" s="114"/>
-      <c r="E43" s="115"/>
-      <c r="F43" s="68" t="s">
+      <c r="B43" s="104"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="106"/>
+      <c r="F43" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="68" t="s">
+      <c r="G43" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H43" s="69" t="s">
+      <c r="H43" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I43" s="69" t="s">
+      <c r="I43" s="60" t="s">
         <v>123</v>
       </c>
-      <c r="J43" s="113" t="s">
+      <c r="J43" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="K43" s="55"/>
+      <c r="K43" s="47"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="34" t="s">
+      <c r="A44" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="B44" s="65">
+      <c r="B44" s="56">
         <v>12000</v>
       </c>
-      <c r="C44" s="65">
+      <c r="C44" s="56">
         <v>4200</v>
       </c>
-      <c r="D44" s="65">
+      <c r="D44" s="56">
         <v>0</v>
       </c>
-      <c r="E44" s="65">
+      <c r="E44" s="56">
         <v>4200</v>
       </c>
-      <c r="F44" s="72">
+      <c r="F44" s="63">
         <f>+B44*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G44" s="72">
+      <c r="G44" s="63">
         <f>+B44*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H44" s="65">
+      <c r="H44" s="56">
         <v>0</v>
       </c>
-      <c r="I44" s="65">
+      <c r="I44" s="56">
         <v>0</v>
       </c>
-      <c r="J44" s="155">
+      <c r="J44" s="145">
         <v>5300</v>
       </c>
-      <c r="K44" s="11">
+      <c r="K44" s="10">
         <v>5300</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="35" t="s">
+      <c r="A45" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="B45" s="65">
+      <c r="B45" s="56">
         <v>12000</v>
       </c>
-      <c r="C45" s="65">
+      <c r="C45" s="56">
         <v>4200</v>
       </c>
-      <c r="D45" s="65">
+      <c r="D45" s="56">
         <v>0</v>
       </c>
-      <c r="E45" s="65">
+      <c r="E45" s="56">
         <v>4200</v>
       </c>
-      <c r="F45" s="72">
+      <c r="F45" s="63">
         <f t="shared" ref="F45:F47" si="0">+B45*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G45" s="72">
+      <c r="G45" s="63">
         <f t="shared" ref="G45:G47" si="1">+B45*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H45" s="65">
+      <c r="H45" s="56">
         <v>0</v>
       </c>
-      <c r="I45" s="65">
+      <c r="I45" s="56">
         <v>0</v>
       </c>
-      <c r="J45" s="155">
+      <c r="J45" s="145">
         <v>5300</v>
       </c>
-      <c r="K45" s="11">
+      <c r="K45" s="10">
         <v>5300</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="B46" s="65">
+      <c r="B46" s="56">
         <v>12000</v>
       </c>
-      <c r="C46" s="65">
+      <c r="C46" s="56">
         <v>4200</v>
       </c>
-      <c r="D46" s="65">
+      <c r="D46" s="56">
         <v>0</v>
       </c>
-      <c r="E46" s="65">
+      <c r="E46" s="56">
         <v>4200</v>
       </c>
-      <c r="F46" s="72">
+      <c r="F46" s="63">
         <f t="shared" si="0"/>
         <v>8400</v>
       </c>
-      <c r="G46" s="72">
+      <c r="G46" s="63">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="H46" s="65">
+      <c r="H46" s="56">
         <v>0</v>
       </c>
-      <c r="I46" s="65">
+      <c r="I46" s="56">
         <v>0</v>
       </c>
-      <c r="J46" s="155">
+      <c r="J46" s="145">
         <v>5300</v>
       </c>
-      <c r="K46" s="11">
+      <c r="K46" s="10">
         <v>5300</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="65">
+      <c r="B47" s="56">
         <v>12000</v>
       </c>
-      <c r="C47" s="65">
+      <c r="C47" s="56">
         <v>4200</v>
       </c>
-      <c r="D47" s="65">
+      <c r="D47" s="56">
         <v>0</v>
       </c>
-      <c r="E47" s="65">
+      <c r="E47" s="56">
         <v>4200</v>
       </c>
-      <c r="F47" s="72">
+      <c r="F47" s="63">
         <f t="shared" si="0"/>
         <v>8400</v>
       </c>
-      <c r="G47" s="72">
+      <c r="G47" s="63">
         <f t="shared" si="1"/>
         <v>7200</v>
       </c>
-      <c r="H47" s="65">
+      <c r="H47" s="56">
         <v>0</v>
       </c>
-      <c r="I47" s="65">
+      <c r="I47" s="56">
         <v>0</v>
       </c>
-      <c r="J47" s="155">
+      <c r="J47" s="145">
         <v>5300</v>
       </c>
-      <c r="K47" s="62">
+      <c r="K47" s="53">
         <v>5300</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="113"/>
-      <c r="C48" s="114"/>
-      <c r="D48" s="114"/>
-      <c r="E48" s="115"/>
-      <c r="F48" s="68" t="s">
+      <c r="B48" s="104"/>
+      <c r="C48" s="105"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="106"/>
+      <c r="F48" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G48" s="68" t="s">
+      <c r="G48" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H48" s="69" t="s">
+      <c r="H48" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I48" s="69" t="s">
+      <c r="I48" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="B49" s="71">
+      <c r="B49" s="62">
         <v>20000</v>
       </c>
-      <c r="C49" s="71">
+      <c r="C49" s="62">
         <v>9500</v>
       </c>
-      <c r="D49" s="71">
+      <c r="D49" s="62">
         <v>9500</v>
       </c>
-      <c r="E49" s="71">
+      <c r="E49" s="62">
         <v>9500</v>
       </c>
-      <c r="F49" s="72">
+      <c r="F49" s="63">
         <f>+B49*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G49" s="72">
+      <c r="G49" s="63">
         <f>+B49*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H49" s="65">
+      <c r="H49" s="56">
         <v>4100</v>
       </c>
-      <c r="I49" s="65">
+      <c r="I49" s="56">
         <v>4100</v>
       </c>
-      <c r="J49" s="156"/>
+      <c r="J49" s="146"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="33" t="s">
+      <c r="A50" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="71">
+      <c r="B50" s="62">
         <v>15000</v>
       </c>
-      <c r="C50" s="71">
+      <c r="C50" s="62">
         <v>5900</v>
       </c>
-      <c r="D50" s="71">
+      <c r="D50" s="62">
         <v>5900</v>
       </c>
-      <c r="E50" s="71">
+      <c r="E50" s="62">
         <v>5900</v>
       </c>
-      <c r="F50" s="72">
+      <c r="F50" s="63">
         <f t="shared" ref="F50:F55" si="2">+B50*0.7</f>
         <v>10500</v>
       </c>
-      <c r="G50" s="72">
+      <c r="G50" s="63">
         <f t="shared" ref="G50:G55" si="3">+B50*0.6</f>
         <v>9000</v>
       </c>
-      <c r="H50" s="65">
+      <c r="H50" s="56">
         <v>4900</v>
       </c>
-      <c r="I50" s="65">
+      <c r="I50" s="56">
         <v>4900</v>
       </c>
-      <c r="J50" s="156"/>
+      <c r="J50" s="146"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="33" t="s">
+      <c r="A51" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="B51" s="71">
+      <c r="B51" s="62">
         <v>15000</v>
       </c>
-      <c r="C51" s="71">
+      <c r="C51" s="62">
         <v>5800</v>
       </c>
-      <c r="D51" s="71">
+      <c r="D51" s="62">
         <v>5800</v>
       </c>
-      <c r="E51" s="71">
+      <c r="E51" s="62">
         <v>5800</v>
       </c>
-      <c r="F51" s="72">
+      <c r="F51" s="63">
         <f t="shared" si="2"/>
         <v>10500</v>
       </c>
-      <c r="G51" s="72">
+      <c r="G51" s="63">
         <f t="shared" si="3"/>
         <v>9000</v>
       </c>
-      <c r="H51" s="65">
+      <c r="H51" s="56">
         <v>3400</v>
       </c>
-      <c r="I51" s="65">
+      <c r="I51" s="56">
         <v>3400</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="33" t="s">
+      <c r="A52" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="71">
+      <c r="B52" s="62">
         <v>20000</v>
       </c>
-      <c r="C52" s="71">
+      <c r="C52" s="62">
         <v>5800</v>
       </c>
-      <c r="D52" s="71">
+      <c r="D52" s="62">
         <v>5800</v>
       </c>
-      <c r="E52" s="71">
+      <c r="E52" s="62">
         <v>5800</v>
       </c>
-      <c r="F52" s="72">
+      <c r="F52" s="63">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G52" s="72">
+      <c r="G52" s="63">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H52" s="65">
+      <c r="H52" s="56">
         <v>3400</v>
       </c>
-      <c r="I52" s="65">
+      <c r="I52" s="56">
         <v>3400</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="33" t="s">
+      <c r="A53" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="B53" s="71">
+      <c r="B53" s="62">
         <v>20000</v>
       </c>
-      <c r="C53" s="71">
+      <c r="C53" s="62">
         <v>9500</v>
       </c>
-      <c r="D53" s="71">
+      <c r="D53" s="62">
         <v>9500</v>
       </c>
-      <c r="E53" s="71">
+      <c r="E53" s="62">
         <v>9500</v>
       </c>
-      <c r="F53" s="72">
+      <c r="F53" s="63">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G53" s="72">
+      <c r="G53" s="63">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H53" s="65">
+      <c r="H53" s="56">
         <v>3400</v>
       </c>
-      <c r="I53" s="65">
+      <c r="I53" s="56">
         <v>3400</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="33" t="s">
+      <c r="A54" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="B54" s="71">
+      <c r="B54" s="62">
         <v>20000</v>
       </c>
-      <c r="C54" s="71">
+      <c r="C54" s="62">
         <v>9500</v>
       </c>
-      <c r="D54" s="71">
+      <c r="D54" s="62">
         <v>9500</v>
       </c>
-      <c r="E54" s="71">
+      <c r="E54" s="62">
         <v>9500</v>
       </c>
-      <c r="F54" s="72">
+      <c r="F54" s="63">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G54" s="72">
+      <c r="G54" s="63">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H54" s="65">
+      <c r="H54" s="56">
         <v>3400</v>
       </c>
-      <c r="I54" s="65">
+      <c r="I54" s="56">
         <v>3400</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="33" t="s">
+      <c r="A55" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="B55" s="71">
+      <c r="B55" s="62">
         <v>20000</v>
       </c>
-      <c r="C55" s="71">
+      <c r="C55" s="62">
         <v>13800</v>
       </c>
-      <c r="D55" s="71">
+      <c r="D55" s="62">
         <v>13800</v>
       </c>
-      <c r="E55" s="71">
+      <c r="E55" s="62">
         <v>13800</v>
       </c>
-      <c r="F55" s="72">
+      <c r="F55" s="63">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="G55" s="72">
+      <c r="G55" s="63">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="H55" s="65">
+      <c r="H55" s="56">
         <v>5700</v>
       </c>
-      <c r="I55" s="65">
+      <c r="I55" s="56">
         <v>5700</v>
       </c>
     </row>
@@ -6427,49 +6403,49 @@
       <c r="A56" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B56" s="113"/>
-      <c r="C56" s="114"/>
-      <c r="D56" s="114"/>
-      <c r="E56" s="115"/>
-      <c r="F56" s="68" t="s">
+      <c r="B56" s="104"/>
+      <c r="C56" s="105"/>
+      <c r="D56" s="105"/>
+      <c r="E56" s="106"/>
+      <c r="F56" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G56" s="68" t="s">
+      <c r="G56" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H56" s="69" t="s">
+      <c r="H56" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I56" s="69" t="s">
+      <c r="I56" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="71">
+      <c r="B57" s="62">
         <v>15000</v>
       </c>
-      <c r="C57" s="65">
+      <c r="C57" s="56">
         <v>7800</v>
       </c>
-      <c r="D57" s="65">
+      <c r="D57" s="56">
         <v>7800</v>
       </c>
-      <c r="E57" s="65">
+      <c r="E57" s="56">
         <v>7800</v>
       </c>
-      <c r="F57" s="73">
+      <c r="F57" s="64">
         <v>9000</v>
       </c>
-      <c r="G57" s="73">
+      <c r="G57" s="64">
         <v>7500</v>
       </c>
-      <c r="H57" s="65">
+      <c r="H57" s="56">
         <v>2700</v>
       </c>
-      <c r="I57" s="65">
+      <c r="I57" s="56">
         <v>0</v>
       </c>
     </row>
@@ -6477,51 +6453,51 @@
       <c r="A58" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B58" s="113"/>
-      <c r="C58" s="114"/>
-      <c r="D58" s="114"/>
-      <c r="E58" s="115"/>
-      <c r="F58" s="68" t="s">
+      <c r="B58" s="104"/>
+      <c r="C58" s="105"/>
+      <c r="D58" s="105"/>
+      <c r="E58" s="106"/>
+      <c r="F58" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G58" s="68" t="s">
+      <c r="G58" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H58" s="69" t="s">
+      <c r="H58" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I58" s="69" t="s">
+      <c r="I58" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="37" t="s">
+      <c r="A59" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="65">
+      <c r="B59" s="56">
         <v>12000</v>
       </c>
-      <c r="C59" s="65">
+      <c r="C59" s="56">
         <v>6400</v>
       </c>
-      <c r="D59" s="65">
+      <c r="D59" s="56">
         <v>6400</v>
       </c>
-      <c r="E59" s="65">
+      <c r="E59" s="56">
         <v>6400</v>
       </c>
-      <c r="F59" s="73">
+      <c r="F59" s="64">
         <f>+B59*0.7</f>
         <v>8400</v>
       </c>
-      <c r="G59" s="73">
+      <c r="G59" s="64">
         <f>+B59*0.6</f>
         <v>7200</v>
       </c>
-      <c r="H59" s="65">
+      <c r="H59" s="56">
         <v>3900</v>
       </c>
-      <c r="I59" s="65">
+      <c r="I59" s="56">
         <v>2700</v>
       </c>
     </row>
@@ -6529,611 +6505,611 @@
       <c r="A60" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="113"/>
-      <c r="C60" s="114"/>
-      <c r="D60" s="114"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="68" t="s">
+      <c r="B60" s="104"/>
+      <c r="C60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G60" s="68" t="s">
+      <c r="G60" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H60" s="69" t="s">
+      <c r="H60" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I60" s="69" t="s">
+      <c r="I60" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="34" t="s">
+      <c r="A61" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B61" s="65">
+      <c r="B61" s="56">
         <v>20000</v>
       </c>
-      <c r="C61" s="116">
+      <c r="C61" s="107">
         <v>10200</v>
       </c>
-      <c r="D61" s="116">
+      <c r="D61" s="107">
         <v>10200</v>
       </c>
-      <c r="E61" s="116">
+      <c r="E61" s="107">
         <v>10200</v>
       </c>
-      <c r="F61" s="73">
+      <c r="F61" s="64">
         <f>+B61*0.7</f>
         <v>14000</v>
       </c>
-      <c r="G61" s="73">
+      <c r="G61" s="64">
         <f>+B61*0.6</f>
         <v>12000</v>
       </c>
-      <c r="H61" s="65">
+      <c r="H61" s="56">
         <v>5500</v>
       </c>
-      <c r="I61" s="65">
+      <c r="I61" s="56">
         <v>5500</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="35" t="s">
+      <c r="A62" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B62" s="65">
+      <c r="B62" s="56">
         <v>30000</v>
       </c>
-      <c r="C62" s="116">
+      <c r="C62" s="107">
         <v>15900</v>
       </c>
-      <c r="D62" s="116">
+      <c r="D62" s="107">
         <v>15900</v>
       </c>
-      <c r="E62" s="116">
+      <c r="E62" s="107">
         <v>15900</v>
       </c>
-      <c r="F62" s="73">
+      <c r="F62" s="64">
         <f t="shared" ref="F62:F65" si="4">+B62*0.7</f>
         <v>21000</v>
       </c>
-      <c r="G62" s="73">
+      <c r="G62" s="64">
         <f t="shared" ref="G62:G65" si="5">+B62*0.6</f>
         <v>18000</v>
       </c>
-      <c r="H62" s="65">
+      <c r="H62" s="56">
         <v>8400</v>
       </c>
-      <c r="I62" s="65">
+      <c r="I62" s="56">
         <v>8400</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="35" t="s">
+      <c r="A63" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B63" s="65">
+      <c r="B63" s="56">
         <v>20000</v>
       </c>
-      <c r="C63" s="116">
+      <c r="C63" s="107">
         <v>10000</v>
       </c>
-      <c r="D63" s="116">
+      <c r="D63" s="107">
         <v>10000</v>
       </c>
-      <c r="E63" s="116">
+      <c r="E63" s="107">
         <v>10000</v>
       </c>
-      <c r="F63" s="73">
+      <c r="F63" s="64">
         <f t="shared" si="4"/>
         <v>14000</v>
       </c>
-      <c r="G63" s="73">
+      <c r="G63" s="64">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="H63" s="65">
+      <c r="H63" s="56">
         <v>5000</v>
       </c>
-      <c r="I63" s="65">
+      <c r="I63" s="56">
         <v>5000</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="38" t="s">
+      <c r="A64" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B64" s="71">
+      <c r="B64" s="62">
         <v>30000</v>
       </c>
-      <c r="C64" s="116">
+      <c r="C64" s="107">
         <v>10000</v>
       </c>
-      <c r="D64" s="116">
+      <c r="D64" s="107">
         <v>10000</v>
       </c>
-      <c r="E64" s="116">
+      <c r="E64" s="107">
         <v>10000</v>
       </c>
-      <c r="F64" s="73">
+      <c r="F64" s="64">
         <f t="shared" si="4"/>
         <v>21000</v>
       </c>
-      <c r="G64" s="73">
+      <c r="G64" s="64">
         <f t="shared" si="5"/>
         <v>18000</v>
       </c>
-      <c r="H64" s="65">
+      <c r="H64" s="56">
         <v>5200</v>
       </c>
-      <c r="I64" s="65">
+      <c r="I64" s="56">
         <v>5200</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B65" s="71">
+      <c r="B65" s="62">
         <v>30000</v>
       </c>
-      <c r="C65" s="116">
+      <c r="C65" s="107">
         <v>12300</v>
       </c>
-      <c r="D65" s="116">
+      <c r="D65" s="107">
         <v>12300</v>
       </c>
-      <c r="E65" s="116">
+      <c r="E65" s="107">
         <v>12300</v>
       </c>
-      <c r="F65" s="73">
+      <c r="F65" s="64">
         <f t="shared" si="4"/>
         <v>21000</v>
       </c>
-      <c r="G65" s="73">
+      <c r="G65" s="64">
         <f t="shared" si="5"/>
         <v>18000</v>
       </c>
-      <c r="H65" s="65">
+      <c r="H65" s="56">
         <v>7900</v>
       </c>
-      <c r="I65" s="65">
+      <c r="I65" s="56">
         <v>7900</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B66" s="74"/>
-      <c r="C66" s="74"/>
-      <c r="D66" s="74"/>
-      <c r="E66" s="74"/>
-      <c r="F66" s="74"/>
-      <c r="G66" s="74"/>
-      <c r="H66" s="74"/>
-      <c r="I66" s="74"/>
+      <c r="B66" s="65"/>
+      <c r="C66" s="65"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="65"/>
+      <c r="G66" s="65"/>
+      <c r="H66" s="65"/>
+      <c r="I66" s="65"/>
     </row>
     <row r="67" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="39" t="s">
+      <c r="A67" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="B67" s="113" t="s">
+      <c r="B67" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="C67" s="114"/>
-      <c r="D67" s="114"/>
-      <c r="E67" s="115"/>
-      <c r="F67" s="68" t="s">
+      <c r="C67" s="105"/>
+      <c r="D67" s="105"/>
+      <c r="E67" s="106"/>
+      <c r="F67" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G67" s="68" t="s">
+      <c r="G67" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H67" s="69" t="s">
+      <c r="H67" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I67" s="69" t="s">
+      <c r="I67" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B68" s="73">
+      <c r="B68" s="64">
         <v>111000</v>
       </c>
-      <c r="C68" s="65">
+      <c r="C68" s="56">
         <v>83700</v>
       </c>
-      <c r="D68" s="65">
+      <c r="D68" s="56">
         <v>83700</v>
       </c>
-      <c r="E68" s="65">
+      <c r="E68" s="56">
         <v>83700</v>
       </c>
-      <c r="F68" s="73">
+      <c r="F68" s="64">
         <f>+B68*0.7</f>
         <v>77700</v>
       </c>
-      <c r="G68" s="73">
+      <c r="G68" s="64">
         <f>+B68*0.6</f>
         <v>66600</v>
       </c>
-      <c r="H68" s="65">
+      <c r="H68" s="56">
         <v>46700</v>
       </c>
-      <c r="I68" s="65">
+      <c r="I68" s="56">
         <v>46700</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="57" t="s">
+      <c r="A69" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="117">
+      <c r="B69" s="108">
         <v>51000</v>
       </c>
-      <c r="C69" s="118">
+      <c r="C69" s="109">
         <v>51000</v>
       </c>
-      <c r="D69" s="118">
+      <c r="D69" s="109">
         <v>51000</v>
       </c>
-      <c r="E69" s="119">
+      <c r="E69" s="110">
         <v>51000</v>
       </c>
-      <c r="F69" s="73">
+      <c r="F69" s="64">
         <f>+B69*0.7</f>
         <v>35700</v>
       </c>
-      <c r="G69" s="73">
+      <c r="G69" s="64">
         <f>+B69*0.6</f>
         <v>30600</v>
       </c>
-      <c r="H69" s="75">
+      <c r="H69" s="66">
         <v>21300</v>
       </c>
-      <c r="I69" s="65">
+      <c r="I69" s="56">
         <v>21300</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="39" t="s">
+      <c r="A70" s="154" t="s">
         <v>232</v>
       </c>
-      <c r="B70" s="113" t="s">
+      <c r="B70" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="C70" s="114"/>
-      <c r="D70" s="114"/>
-      <c r="E70" s="115"/>
-      <c r="F70" s="68" t="s">
+      <c r="C70" s="105"/>
+      <c r="D70" s="105"/>
+      <c r="E70" s="106"/>
+      <c r="F70" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G70" s="68" t="s">
+      <c r="G70" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H70" s="69" t="s">
+      <c r="H70" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I70" s="76" t="s">
+      <c r="I70" s="67" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B71" s="73">
+      <c r="B71" s="64">
         <v>241000</v>
       </c>
-      <c r="C71" s="65">
+      <c r="C71" s="56">
         <v>165000</v>
       </c>
-      <c r="D71" s="65">
+      <c r="D71" s="56">
         <v>165000</v>
       </c>
-      <c r="E71" s="65">
+      <c r="E71" s="56">
         <v>165000</v>
       </c>
-      <c r="F71" s="73">
+      <c r="F71" s="64">
         <f>+B71*0.7</f>
         <v>168700</v>
       </c>
-      <c r="G71" s="73">
+      <c r="G71" s="64">
         <f>+B71*0.6</f>
         <v>144600</v>
       </c>
-      <c r="H71" s="65">
+      <c r="H71" s="56">
         <v>76000</v>
       </c>
-      <c r="I71" s="65">
+      <c r="I71" s="56">
         <v>76000</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="57" t="s">
+      <c r="A72" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="B72" s="117">
+      <c r="B72" s="108">
         <v>68000</v>
       </c>
-      <c r="C72" s="118">
+      <c r="C72" s="109">
         <v>68000</v>
       </c>
-      <c r="D72" s="118">
+      <c r="D72" s="109">
         <v>68000</v>
       </c>
-      <c r="E72" s="119">
+      <c r="E72" s="110">
         <v>68000</v>
       </c>
-      <c r="F72" s="73">
+      <c r="F72" s="64">
         <f>+B72*0.7</f>
         <v>47600</v>
       </c>
-      <c r="G72" s="73">
+      <c r="G72" s="64">
         <f t="shared" ref="G72:G99" si="6">+B72*0.6</f>
         <v>40800</v>
       </c>
-      <c r="H72" s="75">
+      <c r="H72" s="66">
         <v>48000</v>
       </c>
-      <c r="I72" s="75">
+      <c r="I72" s="66">
         <v>48000</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="154" t="s">
         <v>231</v>
       </c>
-      <c r="B73" s="113" t="s">
+      <c r="B73" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="C73" s="114"/>
-      <c r="D73" s="114"/>
-      <c r="E73" s="115"/>
-      <c r="F73" s="68" t="s">
+      <c r="C73" s="105"/>
+      <c r="D73" s="105"/>
+      <c r="E73" s="106"/>
+      <c r="F73" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G73" s="68" t="s">
+      <c r="G73" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H73" s="69" t="s">
+      <c r="H73" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I73" s="69" t="s">
+      <c r="I73" s="60" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
+    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B74" s="73">
+      <c r="B74" s="64">
         <v>551000</v>
       </c>
-      <c r="C74" s="65">
+      <c r="C74" s="56">
         <v>418000</v>
       </c>
-      <c r="D74" s="65">
+      <c r="D74" s="56">
         <v>418000</v>
       </c>
-      <c r="E74" s="65">
+      <c r="E74" s="56">
         <v>418000</v>
       </c>
-      <c r="F74" s="73">
+      <c r="F74" s="64">
         <f t="shared" ref="F74:F99" si="7">+B74*0.7</f>
         <v>385700</v>
       </c>
-      <c r="G74" s="73">
+      <c r="G74" s="64">
         <f t="shared" si="6"/>
         <v>330600</v>
       </c>
-      <c r="H74" s="65">
+      <c r="H74" s="56">
         <v>209000</v>
       </c>
-      <c r="I74" s="65">
+      <c r="I74" s="56">
         <v>209000</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="59" t="s">
+      <c r="A75" s="153" t="s">
         <v>144</v>
       </c>
-      <c r="B75" s="117">
+      <c r="B75" s="108">
         <v>132000</v>
       </c>
-      <c r="C75" s="118">
+      <c r="C75" s="109">
         <v>132000</v>
       </c>
-      <c r="D75" s="118">
+      <c r="D75" s="109">
         <v>132000</v>
       </c>
-      <c r="E75" s="119">
+      <c r="E75" s="110">
         <v>132000</v>
       </c>
-      <c r="F75" s="73">
+      <c r="F75" s="64">
         <f t="shared" si="7"/>
         <v>92400</v>
       </c>
-      <c r="G75" s="73">
+      <c r="G75" s="64">
         <f t="shared" si="6"/>
         <v>79200</v>
       </c>
-      <c r="H75" s="75">
+      <c r="H75" s="66">
         <v>75000</v>
       </c>
-      <c r="I75" s="75">
+      <c r="I75" s="66">
         <v>75000</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="40" t="s">
+      <c r="A76" s="154" t="s">
         <v>233</v>
       </c>
-      <c r="B76" s="113" t="s">
+      <c r="B76" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="C76" s="114"/>
-      <c r="D76" s="114"/>
-      <c r="E76" s="115"/>
-      <c r="F76" s="68" t="s">
+      <c r="C76" s="105"/>
+      <c r="D76" s="105"/>
+      <c r="E76" s="106"/>
+      <c r="F76" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G76" s="68" t="s">
+      <c r="G76" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H76" s="69" t="s">
+      <c r="H76" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I76" s="69" t="s">
+      <c r="I76" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="33" t="s">
+      <c r="A77" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="B77" s="73">
+      <c r="B77" s="64">
         <v>962000</v>
       </c>
-      <c r="C77" s="65">
+      <c r="C77" s="56">
         <v>706000</v>
       </c>
-      <c r="D77" s="65">
+      <c r="D77" s="56">
         <v>706000</v>
       </c>
-      <c r="E77" s="65">
+      <c r="E77" s="56">
         <v>706000</v>
       </c>
-      <c r="F77" s="73">
+      <c r="F77" s="64">
         <f t="shared" si="7"/>
         <v>673400</v>
       </c>
-      <c r="G77" s="73">
+      <c r="G77" s="64">
         <f t="shared" si="6"/>
         <v>577200</v>
       </c>
-      <c r="H77" s="65">
+      <c r="H77" s="56">
         <v>464000</v>
       </c>
-      <c r="I77" s="65">
+      <c r="I77" s="56">
         <v>464000</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B78" s="117">
+      <c r="B78" s="108">
         <v>203000</v>
       </c>
-      <c r="C78" s="118">
+      <c r="C78" s="109">
         <v>203000</v>
       </c>
-      <c r="D78" s="118">
+      <c r="D78" s="109">
         <v>203000</v>
       </c>
-      <c r="E78" s="119">
+      <c r="E78" s="110">
         <v>203000</v>
       </c>
-      <c r="F78" s="73">
+      <c r="F78" s="64">
         <f t="shared" si="7"/>
         <v>142100</v>
       </c>
-      <c r="G78" s="73">
+      <c r="G78" s="64">
         <f t="shared" si="6"/>
         <v>121800</v>
       </c>
-      <c r="H78" s="75">
+      <c r="H78" s="66">
         <v>139000</v>
       </c>
-      <c r="I78" s="75">
+      <c r="I78" s="66">
         <v>139000</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="41" t="s">
+      <c r="A79" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="B79" s="113"/>
-      <c r="C79" s="114"/>
-      <c r="D79" s="114"/>
-      <c r="E79" s="115"/>
-      <c r="F79" s="68" t="s">
+      <c r="B79" s="104"/>
+      <c r="C79" s="105"/>
+      <c r="D79" s="105"/>
+      <c r="E79" s="106"/>
+      <c r="F79" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G79" s="68" t="s">
+      <c r="G79" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H79" s="69" t="s">
+      <c r="H79" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I79" s="69" t="s">
+      <c r="I79" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="34" t="s">
+      <c r="A80" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B80" s="70">
+      <c r="B80" s="61">
         <v>176000</v>
       </c>
-      <c r="C80" s="65">
+      <c r="C80" s="56">
         <v>176000</v>
       </c>
-      <c r="D80" s="65">
+      <c r="D80" s="56">
         <v>176000</v>
       </c>
-      <c r="E80" s="65">
+      <c r="E80" s="56">
         <v>176000</v>
       </c>
-      <c r="F80" s="73">
+      <c r="F80" s="64">
         <f t="shared" si="7"/>
         <v>123199.99999999999</v>
       </c>
-      <c r="G80" s="73">
+      <c r="G80" s="64">
         <f t="shared" si="6"/>
         <v>105600</v>
       </c>
-      <c r="H80" s="65">
+      <c r="H80" s="56">
         <v>176000</v>
       </c>
-      <c r="I80" s="65">
+      <c r="I80" s="56">
         <v>176000</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="42" t="s">
+      <c r="A81" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B81" s="70">
+      <c r="B81" s="61">
         <v>233000</v>
       </c>
-      <c r="C81" s="65">
+      <c r="C81" s="56">
         <v>233000</v>
       </c>
-      <c r="D81" s="65">
+      <c r="D81" s="56">
         <v>233000</v>
       </c>
-      <c r="E81" s="65">
+      <c r="E81" s="56">
         <v>233000</v>
       </c>
-      <c r="F81" s="73">
+      <c r="F81" s="64">
         <f t="shared" si="7"/>
         <v>163100</v>
       </c>
-      <c r="G81" s="73">
+      <c r="G81" s="64">
         <f t="shared" si="6"/>
         <v>139800</v>
       </c>
-      <c r="H81" s="65">
+      <c r="H81" s="56">
         <v>233000</v>
       </c>
-      <c r="I81" s="65">
+      <c r="I81" s="56">
         <v>233000</v>
       </c>
     </row>
@@ -7141,4073 +7117,4095 @@
       <c r="A82" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B82" s="70">
+      <c r="B82" s="61">
         <v>41000</v>
       </c>
-      <c r="C82" s="65">
+      <c r="C82" s="56">
         <v>41000</v>
       </c>
-      <c r="D82" s="65">
+      <c r="D82" s="56">
         <v>41000</v>
       </c>
-      <c r="E82" s="65">
+      <c r="E82" s="56">
         <v>41000</v>
       </c>
-      <c r="F82" s="73">
+      <c r="F82" s="64">
         <f t="shared" si="7"/>
         <v>28699.999999999996</v>
       </c>
-      <c r="G82" s="73">
+      <c r="G82" s="64">
         <f t="shared" si="6"/>
         <v>24600</v>
       </c>
-      <c r="H82" s="65">
+      <c r="H82" s="56">
         <v>41000</v>
       </c>
-      <c r="I82" s="65">
+      <c r="I82" s="56">
         <v>41000</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="43" t="s">
+      <c r="A83" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B83" s="70">
+      <c r="B83" s="61">
         <v>7700</v>
       </c>
-      <c r="C83" s="65">
+      <c r="C83" s="56">
         <v>7700</v>
       </c>
-      <c r="D83" s="65">
+      <c r="D83" s="56">
         <v>7700</v>
       </c>
-      <c r="E83" s="65">
+      <c r="E83" s="56">
         <v>7700</v>
       </c>
-      <c r="F83" s="73">
+      <c r="F83" s="64">
         <f t="shared" si="7"/>
         <v>5390</v>
       </c>
-      <c r="G83" s="73">
+      <c r="G83" s="64">
         <f t="shared" si="6"/>
         <v>4620</v>
       </c>
-      <c r="H83" s="65">
+      <c r="H83" s="56">
         <v>7700</v>
       </c>
-      <c r="I83" s="65">
+      <c r="I83" s="56">
         <v>7700</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="20" t="s">
+      <c r="A84" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B84" s="113"/>
-      <c r="C84" s="114"/>
-      <c r="D84" s="114"/>
-      <c r="E84" s="115"/>
-      <c r="F84" s="68" t="s">
+      <c r="B84" s="104"/>
+      <c r="C84" s="105"/>
+      <c r="D84" s="105"/>
+      <c r="E84" s="106"/>
+      <c r="F84" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G84" s="68" t="s">
+      <c r="G84" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H84" s="69" t="s">
+      <c r="H84" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I84" s="69" t="s">
+      <c r="I84" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="44" t="s">
+      <c r="A85" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B85" s="78">
+      <c r="B85" s="69">
         <v>64600</v>
       </c>
-      <c r="C85" s="78"/>
-      <c r="D85" s="78"/>
-      <c r="E85" s="78"/>
-      <c r="F85" s="77"/>
-      <c r="G85" s="77"/>
-      <c r="H85" s="78"/>
-      <c r="I85" s="78"/>
+      <c r="C85" s="69"/>
+      <c r="D85" s="69"/>
+      <c r="E85" s="69"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="68"/>
+      <c r="H85" s="69"/>
+      <c r="I85" s="69"/>
     </row>
     <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="60" t="s">
+      <c r="A86" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="B86" s="113" t="s">
+      <c r="B86" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="C86" s="114"/>
-      <c r="D86" s="114"/>
-      <c r="E86" s="115"/>
-      <c r="F86" s="68" t="s">
+      <c r="C86" s="105"/>
+      <c r="D86" s="105"/>
+      <c r="E86" s="106"/>
+      <c r="F86" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G86" s="68" t="s">
+      <c r="G86" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H86" s="69" t="s">
+      <c r="H86" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I86" s="69" t="s">
+      <c r="I86" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="45" t="s">
+      <c r="A87" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="B87" s="73">
+      <c r="B87" s="64">
         <v>97000</v>
       </c>
-      <c r="C87" s="65">
+      <c r="C87" s="56">
         <v>57000</v>
       </c>
-      <c r="D87" s="65">
+      <c r="D87" s="56">
         <v>57000</v>
       </c>
-      <c r="E87" s="65">
+      <c r="E87" s="56">
         <v>57000</v>
       </c>
-      <c r="F87" s="73">
+      <c r="F87" s="64">
         <f t="shared" si="7"/>
         <v>67900</v>
       </c>
-      <c r="G87" s="73">
+      <c r="G87" s="64">
         <f>+B87*0.6</f>
         <v>58200</v>
       </c>
-      <c r="H87" s="65">
+      <c r="H87" s="56">
         <v>23500</v>
       </c>
-      <c r="I87" s="65">
+      <c r="I87" s="56">
         <v>23500</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="45" t="s">
+      <c r="A88" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="B88" s="73">
+      <c r="B88" s="64">
         <v>282000</v>
       </c>
-      <c r="C88" s="65">
+      <c r="C88" s="56">
         <v>168000</v>
       </c>
-      <c r="D88" s="65">
+      <c r="D88" s="56">
         <v>168000</v>
       </c>
-      <c r="E88" s="65">
+      <c r="E88" s="56">
         <v>168000</v>
       </c>
-      <c r="F88" s="73">
+      <c r="F88" s="64">
         <f t="shared" si="7"/>
         <v>197400</v>
       </c>
-      <c r="G88" s="73">
+      <c r="G88" s="64">
         <f>+B88*0.6</f>
         <v>169200</v>
       </c>
-      <c r="H88" s="65">
+      <c r="H88" s="56">
         <v>72000</v>
       </c>
-      <c r="I88" s="65">
+      <c r="I88" s="56">
         <v>72000</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="45" t="s">
+      <c r="A89" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="B89" s="73">
+      <c r="B89" s="64">
         <v>256000</v>
       </c>
-      <c r="C89" s="65">
+      <c r="C89" s="56">
         <v>140000</v>
       </c>
-      <c r="D89" s="65">
+      <c r="D89" s="56">
         <v>140000</v>
       </c>
-      <c r="E89" s="65">
+      <c r="E89" s="56">
         <v>140000</v>
       </c>
-      <c r="F89" s="73">
+      <c r="F89" s="64">
         <f t="shared" si="7"/>
         <v>179200</v>
       </c>
-      <c r="G89" s="73">
+      <c r="G89" s="64">
         <f t="shared" si="6"/>
         <v>153600</v>
       </c>
-      <c r="H89" s="65">
+      <c r="H89" s="56">
         <v>62000</v>
       </c>
-      <c r="I89" s="65">
+      <c r="I89" s="56">
         <v>62000</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="45" t="s">
+      <c r="A90" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="B90" s="73">
+      <c r="B90" s="64">
         <v>508000</v>
       </c>
-      <c r="C90" s="65">
+      <c r="C90" s="56">
         <v>287000</v>
       </c>
-      <c r="D90" s="65">
+      <c r="D90" s="56">
         <v>287000</v>
       </c>
-      <c r="E90" s="65">
+      <c r="E90" s="56">
         <v>287000</v>
       </c>
-      <c r="F90" s="73">
+      <c r="F90" s="64">
         <f t="shared" si="7"/>
         <v>355600</v>
       </c>
-      <c r="G90" s="73">
+      <c r="G90" s="64">
         <f t="shared" si="6"/>
         <v>304800</v>
       </c>
-      <c r="H90" s="65">
+      <c r="H90" s="56">
         <v>124000</v>
       </c>
-      <c r="I90" s="65">
+      <c r="I90" s="56">
         <v>1240000</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="122" t="s">
+      <c r="A91" s="113" t="s">
         <v>142</v>
       </c>
-      <c r="B91" s="123">
+      <c r="B91" s="114">
         <v>8200</v>
       </c>
-      <c r="C91" s="109">
+      <c r="C91" s="100">
         <v>6200</v>
       </c>
-      <c r="D91" s="109">
+      <c r="D91" s="100">
         <v>6200</v>
       </c>
-      <c r="E91" s="109">
+      <c r="E91" s="100">
         <v>6200</v>
       </c>
-      <c r="F91" s="123">
+      <c r="F91" s="114">
         <f t="shared" si="7"/>
         <v>5740</v>
       </c>
-      <c r="G91" s="123">
+      <c r="G91" s="114">
         <f t="shared" si="6"/>
         <v>4920</v>
       </c>
-      <c r="H91" s="109">
+      <c r="H91" s="100">
         <v>2500</v>
       </c>
-      <c r="I91" s="109">
+      <c r="I91" s="100">
         <v>2500</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="20" t="s">
+      <c r="A92" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B92" s="113" t="s">
+      <c r="B92" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="C92" s="126"/>
-      <c r="D92" s="126"/>
-      <c r="E92" s="127"/>
-      <c r="F92" s="128" t="s">
+      <c r="C92" s="117"/>
+      <c r="D92" s="117"/>
+      <c r="E92" s="118"/>
+      <c r="F92" s="119" t="s">
         <v>93</v>
       </c>
-      <c r="G92" s="128" t="s">
+      <c r="G92" s="119" t="s">
         <v>94</v>
       </c>
-      <c r="H92" s="129" t="s">
+      <c r="H92" s="120" t="s">
         <v>95</v>
       </c>
-      <c r="I92" s="129" t="s">
+      <c r="I92" s="120" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="47" t="s">
+      <c r="A93" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="B93" s="124"/>
-      <c r="C93" s="124"/>
-      <c r="D93" s="124"/>
-      <c r="E93" s="124"/>
-      <c r="F93" s="125">
+      <c r="B93" s="115"/>
+      <c r="C93" s="115"/>
+      <c r="D93" s="115"/>
+      <c r="E93" s="115"/>
+      <c r="F93" s="116">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G93" s="125">
+      <c r="G93" s="116">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H93" s="124"/>
-      <c r="I93" s="124"/>
+      <c r="H93" s="115"/>
+      <c r="I93" s="115"/>
     </row>
     <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="46" t="s">
+      <c r="A94" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B94" s="73">
+      <c r="B94" s="64">
         <v>104000</v>
       </c>
-      <c r="C94" s="65">
+      <c r="C94" s="56">
         <v>94000</v>
       </c>
-      <c r="D94" s="65">
+      <c r="D94" s="56">
         <v>94000</v>
       </c>
-      <c r="E94" s="65">
+      <c r="E94" s="56">
         <v>94000</v>
       </c>
-      <c r="F94" s="73">
+      <c r="F94" s="64">
         <f t="shared" si="7"/>
         <v>72800</v>
       </c>
-      <c r="G94" s="73">
+      <c r="G94" s="64">
         <f t="shared" si="6"/>
         <v>62400</v>
       </c>
-      <c r="H94" s="65">
+      <c r="H94" s="56">
         <v>41600</v>
       </c>
-      <c r="I94" s="65">
+      <c r="I94" s="56">
         <v>41600</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="46" t="s">
+      <c r="A95" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="B95" s="73">
+      <c r="B95" s="64">
         <v>144750</v>
       </c>
-      <c r="C95" s="65">
+      <c r="C95" s="56">
         <v>106000</v>
       </c>
-      <c r="D95" s="65">
+      <c r="D95" s="56">
         <v>106000</v>
       </c>
-      <c r="E95" s="65">
+      <c r="E95" s="56">
         <v>106000</v>
       </c>
-      <c r="F95" s="73">
+      <c r="F95" s="64">
         <f t="shared" si="7"/>
         <v>101325</v>
       </c>
-      <c r="G95" s="73">
+      <c r="G95" s="64">
         <f t="shared" si="6"/>
         <v>86850</v>
       </c>
-      <c r="H95" s="65">
+      <c r="H95" s="56">
         <v>57900</v>
       </c>
-      <c r="I95" s="65">
+      <c r="I95" s="56">
         <v>57900</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="48" t="s">
+    <row r="96" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B96" s="113" t="s">
+      <c r="B96" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="C96" s="114"/>
-      <c r="D96" s="114"/>
-      <c r="E96" s="115"/>
-      <c r="F96" s="68" t="s">
+      <c r="C96" s="105"/>
+      <c r="D96" s="105"/>
+      <c r="E96" s="106"/>
+      <c r="F96" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G96" s="68" t="s">
+      <c r="G96" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H96" s="69" t="s">
+      <c r="H96" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I96" s="69" t="s">
+      <c r="I96" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="46" t="s">
+      <c r="A97" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="B97" s="73">
+      <c r="B97" s="64">
         <f>+E97/0.7</f>
         <v>13428.571428571429</v>
       </c>
-      <c r="C97" s="65">
+      <c r="C97" s="56">
         <v>9400</v>
       </c>
-      <c r="D97" s="65">
+      <c r="D97" s="56">
         <v>9400</v>
       </c>
-      <c r="E97" s="65">
+      <c r="E97" s="56">
         <v>9400</v>
       </c>
-      <c r="F97" s="73">
+      <c r="F97" s="64">
         <f t="shared" si="7"/>
         <v>9400</v>
       </c>
-      <c r="G97" s="73">
+      <c r="G97" s="64">
         <f t="shared" si="6"/>
         <v>8057.1428571428569</v>
       </c>
-      <c r="H97" s="77">
+      <c r="H97" s="68">
         <f>+B97*0.4</f>
         <v>5371.4285714285725</v>
       </c>
-      <c r="I97" s="65"/>
+      <c r="I97" s="56"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="45" t="s">
+      <c r="A98" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B98" s="73">
+      <c r="B98" s="64">
         <f t="shared" ref="B98:B99" si="8">+E98/0.7</f>
         <v>19714.285714285714</v>
       </c>
-      <c r="C98" s="65">
+      <c r="C98" s="56">
         <v>13800</v>
       </c>
-      <c r="D98" s="65">
+      <c r="D98" s="56">
         <v>13800</v>
       </c>
-      <c r="E98" s="65">
+      <c r="E98" s="56">
         <v>13800</v>
       </c>
-      <c r="F98" s="73">
+      <c r="F98" s="64">
         <f t="shared" si="7"/>
         <v>13799.999999999998</v>
       </c>
-      <c r="G98" s="73">
+      <c r="G98" s="64">
         <f t="shared" si="6"/>
         <v>11828.571428571428</v>
       </c>
-      <c r="H98" s="77">
+      <c r="H98" s="68">
         <f t="shared" ref="H98:H99" si="9">+B98*0.4</f>
         <v>7885.7142857142862</v>
       </c>
-      <c r="I98" s="65"/>
+      <c r="I98" s="56"/>
     </row>
     <row r="99" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="46" t="s">
+      <c r="A99" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B99" s="73">
+      <c r="B99" s="64">
         <f t="shared" si="8"/>
         <v>19714.285714285714</v>
       </c>
-      <c r="C99" s="65">
+      <c r="C99" s="56">
         <v>13800</v>
       </c>
-      <c r="D99" s="65">
+      <c r="D99" s="56">
         <v>13800</v>
       </c>
-      <c r="E99" s="65">
+      <c r="E99" s="56">
         <v>13800</v>
       </c>
-      <c r="F99" s="73">
+      <c r="F99" s="64">
         <f t="shared" si="7"/>
         <v>13799.999999999998</v>
       </c>
-      <c r="G99" s="73">
+      <c r="G99" s="64">
         <f t="shared" si="6"/>
         <v>11828.571428571428</v>
       </c>
-      <c r="H99" s="77">
+      <c r="H99" s="68">
         <f t="shared" si="9"/>
         <v>7885.7142857142862</v>
       </c>
-      <c r="I99" s="65"/>
+      <c r="I99" s="56"/>
     </row>
     <row r="100" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="20" t="s">
+      <c r="A100" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B100" s="113" t="s">
+      <c r="B100" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="C100" s="114"/>
-      <c r="D100" s="114"/>
-      <c r="E100" s="115"/>
-      <c r="F100" s="68" t="s">
+      <c r="C100" s="105"/>
+      <c r="D100" s="105"/>
+      <c r="E100" s="106"/>
+      <c r="F100" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="G100" s="68" t="s">
+      <c r="G100" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="H100" s="69" t="s">
+      <c r="H100" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I100" s="69" t="s">
+      <c r="I100" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="49" t="s">
+      <c r="A101" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="B101" s="73">
+      <c r="B101" s="64">
         <v>55600</v>
       </c>
-      <c r="C101" s="65">
+      <c r="C101" s="56">
         <v>38700</v>
       </c>
-      <c r="D101" s="65">
+      <c r="D101" s="56">
         <v>38700</v>
       </c>
-      <c r="E101" s="65">
+      <c r="E101" s="56">
         <v>38700</v>
       </c>
-      <c r="F101" s="73">
+      <c r="F101" s="64">
         <f>+B101*0.7</f>
         <v>38920</v>
       </c>
-      <c r="G101" s="73">
+      <c r="G101" s="64">
         <f>+B101*0.6</f>
         <v>33360</v>
       </c>
-      <c r="H101" s="65">
+      <c r="H101" s="56">
         <v>26800</v>
       </c>
-      <c r="I101" s="65">
+      <c r="I101" s="56">
         <v>26800</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="50" t="s">
+      <c r="A102" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="B102" s="73">
+      <c r="B102" s="64">
         <v>13900</v>
       </c>
-      <c r="C102" s="65">
+      <c r="C102" s="56">
         <v>13900</v>
       </c>
-      <c r="D102" s="65">
+      <c r="D102" s="56">
         <v>13900</v>
       </c>
-      <c r="E102" s="65">
+      <c r="E102" s="56">
         <v>13900</v>
       </c>
-      <c r="F102" s="73">
+      <c r="F102" s="64">
         <f>+B102*0.7</f>
         <v>9730</v>
       </c>
-      <c r="G102" s="73">
+      <c r="G102" s="64">
         <f>+B102*0.6</f>
         <v>8340</v>
       </c>
-      <c r="H102" s="79">
+      <c r="H102" s="70">
         <v>13900</v>
       </c>
-      <c r="I102" s="65">
+      <c r="I102" s="56">
         <v>13600</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="51" t="s">
+    <row r="103" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B103" s="80"/>
-      <c r="C103" s="80"/>
-      <c r="D103" s="80"/>
-      <c r="E103" s="80"/>
-      <c r="F103" s="80"/>
-      <c r="G103" s="80"/>
-      <c r="H103" s="80"/>
-      <c r="I103" s="80"/>
+      <c r="B103" s="71"/>
+      <c r="C103" s="71"/>
+      <c r="D103" s="71"/>
+      <c r="E103" s="71"/>
+      <c r="F103" s="71"/>
+      <c r="G103" s="71"/>
+      <c r="H103" s="71"/>
+      <c r="I103" s="71"/>
     </row>
     <row r="104" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="54" t="s">
+      <c r="A104" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="B104" s="113" t="s">
+      <c r="B104" s="104" t="s">
         <v>147</v>
       </c>
-      <c r="C104" s="114"/>
-      <c r="D104" s="114"/>
-      <c r="E104" s="115"/>
-      <c r="F104" s="81" t="s">
+      <c r="C104" s="105"/>
+      <c r="D104" s="105"/>
+      <c r="E104" s="106"/>
+      <c r="F104" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="G104" s="81" t="s">
+      <c r="G104" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="H104" s="69" t="s">
+      <c r="H104" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I104" s="69" t="s">
+      <c r="I104" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="13" t="s">
+      <c r="A105" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B105" s="65">
+      <c r="B105" s="56">
         <v>88886</v>
       </c>
-      <c r="C105" s="65">
+      <c r="C105" s="56">
         <v>44443</v>
       </c>
-      <c r="D105" s="65">
+      <c r="D105" s="56">
         <v>44443</v>
       </c>
-      <c r="E105" s="65">
+      <c r="E105" s="56">
         <v>44443</v>
       </c>
-      <c r="F105" s="73">
+      <c r="F105" s="64">
         <f>+B105*0.7</f>
         <v>62220.2</v>
       </c>
-      <c r="G105" s="73">
+      <c r="G105" s="64">
         <f>+B105*0.6</f>
         <v>53331.6</v>
       </c>
-      <c r="H105" s="65">
+      <c r="H105" s="56">
         <v>24647</v>
       </c>
-      <c r="I105" s="65">
+      <c r="I105" s="56">
         <v>24647</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="14" t="s">
+      <c r="A106" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B106" s="65">
+      <c r="B106" s="56">
         <v>103703</v>
       </c>
-      <c r="C106" s="65">
+      <c r="C106" s="56">
         <v>51852</v>
       </c>
-      <c r="D106" s="65">
+      <c r="D106" s="56">
         <v>51852</v>
       </c>
-      <c r="E106" s="65">
+      <c r="E106" s="56">
         <v>51852</v>
       </c>
-      <c r="F106" s="73">
+      <c r="F106" s="64">
         <f t="shared" ref="F106:F130" si="10">+B106*0.7</f>
         <v>72592.099999999991</v>
       </c>
-      <c r="G106" s="73">
+      <c r="G106" s="64">
         <f t="shared" ref="G106:G130" si="11">+B106*0.6</f>
         <v>62221.799999999996</v>
       </c>
-      <c r="H106" s="65">
+      <c r="H106" s="56">
         <v>28755</v>
       </c>
-      <c r="I106" s="65">
+      <c r="I106" s="56">
         <v>28755</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="14" t="s">
+      <c r="A107" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B107" s="65">
+      <c r="B107" s="56">
         <v>174729</v>
       </c>
-      <c r="C107" s="65">
+      <c r="C107" s="56">
         <v>87365</v>
       </c>
-      <c r="D107" s="65">
+      <c r="D107" s="56">
         <v>87365</v>
       </c>
-      <c r="E107" s="65">
+      <c r="E107" s="56">
         <v>87365</v>
       </c>
-      <c r="F107" s="73">
+      <c r="F107" s="64">
         <f t="shared" si="10"/>
         <v>122310.29999999999</v>
       </c>
-      <c r="G107" s="73">
+      <c r="G107" s="64">
         <f t="shared" si="11"/>
         <v>104837.4</v>
       </c>
-      <c r="H107" s="65">
+      <c r="H107" s="56">
         <v>48449</v>
       </c>
-      <c r="I107" s="65">
+      <c r="I107" s="56">
         <v>48449</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="14" t="s">
+      <c r="A108" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B108" s="65">
+      <c r="B108" s="56">
         <v>22223</v>
       </c>
-      <c r="C108" s="65">
+      <c r="C108" s="56">
         <v>11112</v>
       </c>
-      <c r="D108" s="65">
+      <c r="D108" s="56">
         <v>11112</v>
       </c>
-      <c r="E108" s="65">
+      <c r="E108" s="56">
         <v>11112</v>
       </c>
-      <c r="F108" s="73">
+      <c r="F108" s="64">
         <f t="shared" si="10"/>
         <v>15556.099999999999</v>
       </c>
-      <c r="G108" s="73">
+      <c r="G108" s="64">
         <f t="shared" si="11"/>
         <v>13333.8</v>
       </c>
-      <c r="H108" s="65">
+      <c r="H108" s="56">
         <v>6162</v>
       </c>
-      <c r="I108" s="65">
+      <c r="I108" s="56">
         <v>6162</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="15" t="s">
+      <c r="A109" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B109" s="65">
+      <c r="B109" s="56">
         <v>111110</v>
       </c>
-      <c r="C109" s="65">
+      <c r="C109" s="56">
         <v>55555</v>
       </c>
-      <c r="D109" s="65">
+      <c r="D109" s="56">
         <v>55555</v>
       </c>
-      <c r="E109" s="65">
+      <c r="E109" s="56">
         <v>55555</v>
       </c>
-      <c r="F109" s="73">
+      <c r="F109" s="64">
         <f t="shared" si="10"/>
         <v>77777</v>
       </c>
-      <c r="G109" s="73">
+      <c r="G109" s="64">
         <f t="shared" si="11"/>
         <v>66666</v>
       </c>
-      <c r="H109" s="65">
+      <c r="H109" s="56">
         <v>30809</v>
       </c>
-      <c r="I109" s="65">
+      <c r="I109" s="56">
         <v>30809</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="53" t="s">
+      <c r="A110" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="B110" s="113" t="s">
+      <c r="B110" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="C110" s="114"/>
-      <c r="D110" s="114"/>
-      <c r="E110" s="115"/>
-      <c r="F110" s="81" t="s">
+      <c r="C110" s="105"/>
+      <c r="D110" s="105"/>
+      <c r="E110" s="106"/>
+      <c r="F110" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="G110" s="81" t="s">
+      <c r="G110" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="H110" s="69" t="s">
+      <c r="H110" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I110" s="69" t="s">
+      <c r="I110" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="16" t="s">
+      <c r="A111" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="B111" s="65">
+      <c r="B111" s="56">
         <v>312686</v>
       </c>
-      <c r="C111" s="65">
+      <c r="C111" s="56">
         <v>156343</v>
       </c>
-      <c r="D111" s="65">
+      <c r="D111" s="56">
         <v>156343</v>
       </c>
-      <c r="E111" s="65">
+      <c r="E111" s="56">
         <v>156343</v>
       </c>
-      <c r="F111" s="73">
+      <c r="F111" s="64">
         <f t="shared" si="10"/>
         <v>218880.19999999998</v>
       </c>
-      <c r="G111" s="73">
+      <c r="G111" s="64">
         <f t="shared" si="11"/>
         <v>187611.6</v>
       </c>
-      <c r="H111" s="65">
+      <c r="H111" s="56">
         <v>85421</v>
       </c>
-      <c r="I111" s="65">
+      <c r="I111" s="56">
         <v>85421</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="18" t="s">
+      <c r="A112" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="B112" s="65">
+      <c r="B112" s="56">
         <v>349723</v>
       </c>
-      <c r="C112" s="65">
+      <c r="C112" s="56">
         <v>174861</v>
       </c>
-      <c r="D112" s="65">
+      <c r="D112" s="56">
         <v>174861</v>
       </c>
-      <c r="E112" s="65">
+      <c r="E112" s="56">
         <v>174861</v>
       </c>
-      <c r="F112" s="73">
+      <c r="F112" s="64">
         <f t="shared" si="10"/>
         <v>244806.09999999998</v>
       </c>
-      <c r="G112" s="73">
+      <c r="G112" s="64">
         <f t="shared" si="11"/>
         <v>209833.8</v>
       </c>
-      <c r="H112" s="65">
+      <c r="H112" s="56">
         <v>95539</v>
       </c>
-      <c r="I112" s="65">
+      <c r="I112" s="56">
         <v>95539</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="17" t="s">
+      <c r="A113" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B113" s="65">
+      <c r="B113" s="56">
         <v>446016</v>
       </c>
-      <c r="C113" s="65">
+      <c r="C113" s="56">
         <v>223008</v>
       </c>
-      <c r="D113" s="65">
+      <c r="D113" s="56">
         <v>223008</v>
       </c>
-      <c r="E113" s="65">
+      <c r="E113" s="56">
         <v>223008</v>
       </c>
-      <c r="F113" s="73">
+      <c r="F113" s="64">
         <f t="shared" si="10"/>
         <v>312211.19999999995</v>
       </c>
-      <c r="G113" s="73">
+      <c r="G113" s="64">
         <f t="shared" si="11"/>
         <v>267609.59999999998</v>
       </c>
-      <c r="H113" s="65">
+      <c r="H113" s="56">
         <v>121845</v>
       </c>
-      <c r="I113" s="65">
+      <c r="I113" s="56">
         <v>121845</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="52" t="s">
+      <c r="A114" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="B114" s="113" t="s">
+      <c r="B114" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="C114" s="114"/>
-      <c r="D114" s="114"/>
-      <c r="E114" s="115"/>
-      <c r="F114" s="81" t="s">
+      <c r="C114" s="105"/>
+      <c r="D114" s="105"/>
+      <c r="E114" s="106"/>
+      <c r="F114" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="G114" s="81" t="s">
+      <c r="G114" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="H114" s="69" t="s">
+      <c r="H114" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I114" s="69" t="s">
+      <c r="I114" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="16" t="s">
+      <c r="A115" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B115" s="65">
+      <c r="B115" s="56">
         <v>128763</v>
       </c>
-      <c r="C115" s="65">
+      <c r="C115" s="56">
         <v>64381</v>
       </c>
-      <c r="D115" s="65">
+      <c r="D115" s="56">
         <v>64381</v>
       </c>
-      <c r="E115" s="65">
+      <c r="E115" s="56">
         <v>64381</v>
       </c>
-      <c r="F115" s="73">
+      <c r="F115" s="64">
         <f t="shared" si="10"/>
         <v>90134.099999999991</v>
       </c>
-      <c r="G115" s="73">
+      <c r="G115" s="64">
         <f t="shared" si="11"/>
         <v>77257.8</v>
       </c>
-      <c r="H115" s="65">
+      <c r="H115" s="56">
         <v>35704</v>
       </c>
-      <c r="I115" s="65">
+      <c r="I115" s="56">
         <v>35704</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="17" t="s">
+      <c r="A116" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B116" s="65">
+      <c r="B116" s="56">
         <v>199762</v>
       </c>
-      <c r="C116" s="65">
+      <c r="C116" s="56">
         <v>99881</v>
       </c>
-      <c r="D116" s="65">
+      <c r="D116" s="56">
         <v>99881</v>
       </c>
-      <c r="E116" s="65">
+      <c r="E116" s="56">
         <v>99881</v>
       </c>
-      <c r="F116" s="73">
+      <c r="F116" s="64">
         <f t="shared" si="10"/>
         <v>139833.4</v>
       </c>
-      <c r="G116" s="73">
+      <c r="G116" s="64">
         <f t="shared" si="11"/>
         <v>119857.2</v>
       </c>
-      <c r="H116" s="65">
+      <c r="H116" s="56">
         <v>55391</v>
       </c>
-      <c r="I116" s="65">
+      <c r="I116" s="56">
         <v>55391</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="52" t="s">
+      <c r="A117" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="B117" s="113" t="s">
+      <c r="B117" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="C117" s="114"/>
-      <c r="D117" s="114"/>
-      <c r="E117" s="115"/>
-      <c r="F117" s="81" t="s">
+      <c r="C117" s="105"/>
+      <c r="D117" s="105"/>
+      <c r="E117" s="106"/>
+      <c r="F117" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="G117" s="81" t="s">
+      <c r="G117" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="H117" s="69" t="s">
+      <c r="H117" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I117" s="69" t="s">
+      <c r="I117" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="16" t="s">
+      <c r="A118" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B118" s="65">
+      <c r="B118" s="56">
         <v>477701</v>
       </c>
-      <c r="C118" s="65">
+      <c r="C118" s="56">
         <v>238851</v>
       </c>
-      <c r="D118" s="65">
+      <c r="D118" s="56">
         <v>238851</v>
       </c>
-      <c r="E118" s="65">
+      <c r="E118" s="56">
         <v>238851</v>
       </c>
-      <c r="F118" s="73">
+      <c r="F118" s="64">
         <f t="shared" si="10"/>
         <v>334390.69999999995</v>
       </c>
-      <c r="G118" s="73">
+      <c r="G118" s="64">
         <f t="shared" si="11"/>
         <v>286620.59999999998</v>
       </c>
-      <c r="H118" s="65">
+      <c r="H118" s="56">
         <v>132458</v>
       </c>
-      <c r="I118" s="65">
+      <c r="I118" s="56">
         <v>132458</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="18" t="s">
+      <c r="A119" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B119" s="65">
+      <c r="B119" s="56">
         <v>236516</v>
       </c>
-      <c r="C119" s="65">
+      <c r="C119" s="56">
         <v>118258</v>
       </c>
-      <c r="D119" s="65">
+      <c r="D119" s="56">
         <v>118258</v>
       </c>
-      <c r="E119" s="65">
+      <c r="E119" s="56">
         <v>118258</v>
       </c>
-      <c r="F119" s="73">
+      <c r="F119" s="64">
         <f t="shared" si="10"/>
         <v>165561.19999999998</v>
       </c>
-      <c r="G119" s="73">
+      <c r="G119" s="64">
         <f t="shared" si="11"/>
         <v>141909.6</v>
       </c>
-      <c r="H119" s="65">
+      <c r="H119" s="56">
         <v>65582</v>
       </c>
-      <c r="I119" s="65">
+      <c r="I119" s="56">
         <v>65582</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="18" t="s">
+      <c r="A120" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B120" s="65">
+      <c r="B120" s="56">
         <v>274873</v>
       </c>
-      <c r="C120" s="65">
+      <c r="C120" s="56">
         <v>137436</v>
       </c>
-      <c r="D120" s="65">
+      <c r="D120" s="56">
         <v>137436</v>
       </c>
-      <c r="E120" s="65">
+      <c r="E120" s="56">
         <v>137436</v>
       </c>
-      <c r="F120" s="73">
+      <c r="F120" s="64">
         <f t="shared" si="10"/>
         <v>192411.09999999998</v>
       </c>
-      <c r="G120" s="73">
+      <c r="G120" s="64">
         <f t="shared" si="11"/>
         <v>164923.79999999999</v>
       </c>
-      <c r="H120" s="65">
+      <c r="H120" s="56">
         <v>76217</v>
       </c>
-      <c r="I120" s="65">
+      <c r="I120" s="56">
         <v>76217</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="17" t="s">
+      <c r="A121" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="B121" s="65">
+      <c r="B121" s="56">
         <v>313203</v>
       </c>
-      <c r="C121" s="65">
+      <c r="C121" s="56">
         <v>156601</v>
       </c>
-      <c r="D121" s="65">
+      <c r="D121" s="56">
         <v>156601</v>
       </c>
-      <c r="E121" s="65">
+      <c r="E121" s="56">
         <v>156601</v>
       </c>
-      <c r="F121" s="73">
+      <c r="F121" s="64">
         <f t="shared" si="10"/>
         <v>219242.09999999998</v>
       </c>
-      <c r="G121" s="73">
+      <c r="G121" s="64">
         <f t="shared" si="11"/>
         <v>187921.8</v>
       </c>
-      <c r="H121" s="65">
+      <c r="H121" s="56">
         <v>86846</v>
       </c>
-      <c r="I121" s="65">
+      <c r="I121" s="56">
         <v>86846</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="52" t="s">
+      <c r="A122" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="B122" s="113" t="s">
+      <c r="B122" s="104" t="s">
         <v>149</v>
       </c>
-      <c r="C122" s="114"/>
-      <c r="D122" s="114"/>
-      <c r="E122" s="115"/>
-      <c r="F122" s="81" t="s">
+      <c r="C122" s="105"/>
+      <c r="D122" s="105"/>
+      <c r="E122" s="106"/>
+      <c r="F122" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="G122" s="81" t="s">
+      <c r="G122" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="H122" s="69" t="s">
+      <c r="H122" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="I122" s="69" t="s">
+      <c r="I122" s="60" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="16" t="s">
+      <c r="A123" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B123" s="65">
+      <c r="B123" s="56">
         <v>139695</v>
       </c>
-      <c r="C123" s="65">
+      <c r="C123" s="56">
         <v>69848</v>
       </c>
-      <c r="D123" s="65">
+      <c r="D123" s="56">
         <v>69848</v>
       </c>
-      <c r="E123" s="65">
+      <c r="E123" s="56">
         <v>69848</v>
       </c>
-      <c r="F123" s="73">
+      <c r="F123" s="64">
         <f t="shared" si="10"/>
         <v>97786.5</v>
       </c>
-      <c r="G123" s="73">
+      <c r="G123" s="64">
         <f t="shared" si="11"/>
         <v>83817</v>
       </c>
-      <c r="H123" s="65">
+      <c r="H123" s="56">
         <v>38735</v>
       </c>
-      <c r="I123" s="65">
+      <c r="I123" s="56">
         <v>38735</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="18" t="s">
+      <c r="A124" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B124" s="65">
+      <c r="B124" s="56">
         <v>153373</v>
       </c>
-      <c r="C124" s="65">
+      <c r="C124" s="56">
         <v>76687</v>
       </c>
-      <c r="D124" s="65">
+      <c r="D124" s="56">
         <v>76687</v>
       </c>
-      <c r="E124" s="65">
+      <c r="E124" s="56">
         <v>76687</v>
       </c>
-      <c r="F124" s="73">
+      <c r="F124" s="64">
         <f t="shared" si="10"/>
         <v>107361.09999999999</v>
       </c>
-      <c r="G124" s="73">
+      <c r="G124" s="64">
         <f t="shared" si="11"/>
         <v>92023.8</v>
       </c>
-      <c r="H124" s="65">
+      <c r="H124" s="56">
         <v>42528</v>
       </c>
-      <c r="I124" s="65">
+      <c r="I124" s="56">
         <v>42528</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="18" t="s">
+      <c r="A125" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B125" s="65">
+      <c r="B125" s="56">
         <v>184044</v>
       </c>
-      <c r="C125" s="65">
+      <c r="C125" s="56">
         <v>92022</v>
       </c>
-      <c r="D125" s="65">
+      <c r="D125" s="56">
         <v>92022</v>
       </c>
-      <c r="E125" s="65">
+      <c r="E125" s="56">
         <v>92022</v>
       </c>
-      <c r="F125" s="73">
+      <c r="F125" s="64">
         <f t="shared" si="10"/>
         <v>128830.79999999999</v>
       </c>
-      <c r="G125" s="73">
+      <c r="G125" s="64">
         <f t="shared" si="11"/>
         <v>110426.4</v>
       </c>
-      <c r="H125" s="65">
+      <c r="H125" s="56">
         <v>51032</v>
       </c>
-      <c r="I125" s="65">
+      <c r="I125" s="56">
         <v>51032</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="138" t="s">
+      <c r="A126" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="B126" s="109">
+      <c r="B126" s="100">
         <v>49078</v>
       </c>
-      <c r="C126" s="109">
+      <c r="C126" s="100">
         <v>24539</v>
       </c>
-      <c r="D126" s="109">
+      <c r="D126" s="100">
         <v>24539</v>
       </c>
-      <c r="E126" s="109">
+      <c r="E126" s="100">
         <v>24539</v>
       </c>
-      <c r="F126" s="123">
+      <c r="F126" s="114">
         <f t="shared" si="10"/>
         <v>34354.6</v>
       </c>
-      <c r="G126" s="123">
+      <c r="G126" s="114">
         <f t="shared" si="11"/>
         <v>29446.799999999999</v>
       </c>
-      <c r="H126" s="109">
+      <c r="H126" s="100">
         <v>13608</v>
       </c>
-      <c r="I126" s="109">
+      <c r="I126" s="100">
         <v>13608</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="140" t="s">
+      <c r="A127" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B127" s="137" t="s">
+      <c r="B127" s="128" t="s">
         <v>149</v>
       </c>
-      <c r="C127" s="126"/>
-      <c r="D127" s="126"/>
-      <c r="E127" s="127"/>
-      <c r="F127" s="128" t="s">
+      <c r="C127" s="117"/>
+      <c r="D127" s="117"/>
+      <c r="E127" s="118"/>
+      <c r="F127" s="119" t="s">
         <v>93</v>
       </c>
-      <c r="G127" s="128" t="s">
+      <c r="G127" s="119" t="s">
         <v>94</v>
       </c>
-      <c r="H127" s="129" t="s">
+      <c r="H127" s="120" t="s">
         <v>95</v>
       </c>
-      <c r="I127" s="129" t="s">
+      <c r="I127" s="120" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="139" t="s">
+      <c r="A128" s="130" t="s">
         <v>88</v>
       </c>
-      <c r="B128" s="135">
+      <c r="B128" s="126">
         <v>661862</v>
       </c>
-      <c r="C128" s="135">
+      <c r="C128" s="126">
         <v>330931</v>
       </c>
-      <c r="D128" s="135">
+      <c r="D128" s="126">
         <v>330931</v>
       </c>
-      <c r="E128" s="135">
+      <c r="E128" s="126">
         <v>330931</v>
       </c>
-      <c r="F128" s="125">
+      <c r="F128" s="116">
         <f t="shared" si="10"/>
         <v>463303.39999999997</v>
       </c>
-      <c r="G128" s="125">
+      <c r="G128" s="116">
         <f t="shared" si="11"/>
         <v>397117.2</v>
       </c>
-      <c r="H128" s="135">
+      <c r="H128" s="126">
         <v>183523</v>
       </c>
-      <c r="I128" s="135">
+      <c r="I128" s="126">
         <v>183523</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="18" t="s">
+      <c r="A129" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B129" s="65">
+      <c r="B129" s="56">
         <v>692556</v>
       </c>
-      <c r="C129" s="65">
+      <c r="C129" s="56">
         <v>346278</v>
       </c>
-      <c r="D129" s="65">
+      <c r="D129" s="56">
         <v>346278</v>
       </c>
-      <c r="E129" s="65">
+      <c r="E129" s="56">
         <v>346278</v>
       </c>
-      <c r="F129" s="73">
+      <c r="F129" s="64">
         <f t="shared" si="10"/>
         <v>484789.19999999995</v>
       </c>
-      <c r="G129" s="73">
+      <c r="G129" s="64">
         <f t="shared" si="11"/>
         <v>415533.6</v>
       </c>
-      <c r="H129" s="65">
+      <c r="H129" s="56">
         <v>192034</v>
       </c>
-      <c r="I129" s="65">
+      <c r="I129" s="56">
         <v>192034</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="134" t="s">
+      <c r="A130" s="125" t="s">
         <v>90</v>
       </c>
-      <c r="B130" s="109">
+      <c r="B130" s="100">
         <v>90078</v>
       </c>
-      <c r="C130" s="109">
+      <c r="C130" s="100">
         <v>45039</v>
       </c>
-      <c r="D130" s="109">
+      <c r="D130" s="100">
         <v>45039</v>
       </c>
-      <c r="E130" s="109">
+      <c r="E130" s="100">
         <v>45039</v>
       </c>
-      <c r="F130" s="123">
+      <c r="F130" s="114">
         <f t="shared" si="10"/>
         <v>63054.6</v>
       </c>
-      <c r="G130" s="123">
+      <c r="G130" s="114">
         <f t="shared" si="11"/>
         <v>54046.799999999996</v>
       </c>
-      <c r="H130" s="109">
+      <c r="H130" s="100">
         <v>24977</v>
       </c>
-      <c r="I130" s="109">
+      <c r="I130" s="100">
         <v>24977</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="136" t="s">
+      <c r="A131" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="B131" s="137"/>
-      <c r="C131" s="126"/>
-      <c r="D131" s="126"/>
-      <c r="E131" s="127"/>
-      <c r="F131" s="128"/>
-      <c r="G131" s="128" t="s">
+      <c r="B131" s="128"/>
+      <c r="C131" s="117"/>
+      <c r="D131" s="117"/>
+      <c r="E131" s="118"/>
+      <c r="F131" s="119"/>
+      <c r="G131" s="119" t="s">
         <v>94</v>
       </c>
-      <c r="H131" s="129" t="s">
+      <c r="H131" s="120" t="s">
         <v>95</v>
       </c>
-      <c r="I131" s="129" t="s">
+      <c r="I131" s="120" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="141" t="s">
+      <c r="A132" s="131" t="s">
         <v>46</v>
       </c>
-      <c r="B132" s="135"/>
-      <c r="C132" s="135"/>
-      <c r="D132" s="135"/>
-      <c r="E132" s="135"/>
-      <c r="F132" s="135"/>
-      <c r="G132" s="91">
+      <c r="B132" s="126"/>
+      <c r="C132" s="126"/>
+      <c r="D132" s="126"/>
+      <c r="E132" s="126"/>
+      <c r="F132" s="126"/>
+      <c r="G132" s="82">
         <v>99890</v>
       </c>
-      <c r="H132" s="135"/>
-      <c r="I132" s="142"/>
+      <c r="H132" s="126"/>
+      <c r="I132" s="132"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="143" t="s">
+      <c r="A133" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="B133" s="65"/>
-      <c r="C133" s="65"/>
-      <c r="D133" s="65"/>
-      <c r="E133" s="65"/>
-      <c r="F133" s="65"/>
-      <c r="G133" s="70">
+      <c r="B133" s="56"/>
+      <c r="C133" s="56"/>
+      <c r="D133" s="56"/>
+      <c r="E133" s="56"/>
+      <c r="F133" s="56"/>
+      <c r="G133" s="61">
         <v>49945</v>
       </c>
-      <c r="H133" s="65">
+      <c r="H133" s="56">
         <f>+$G$133</f>
         <v>49945</v>
       </c>
-      <c r="I133" s="144">
+      <c r="I133" s="134">
         <f>+$G$133</f>
         <v>49945</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="143" t="s">
+      <c r="A134" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="B134" s="65"/>
-      <c r="C134" s="65"/>
-      <c r="D134" s="65"/>
-      <c r="E134" s="65"/>
-      <c r="F134" s="65"/>
-      <c r="G134" s="70">
+      <c r="B134" s="56"/>
+      <c r="C134" s="56"/>
+      <c r="D134" s="56"/>
+      <c r="E134" s="56"/>
+      <c r="F134" s="56"/>
+      <c r="G134" s="61">
         <v>95529</v>
       </c>
-      <c r="H134" s="65">
+      <c r="H134" s="56">
         <f>+$G$134</f>
         <v>95529</v>
       </c>
-      <c r="I134" s="144">
+      <c r="I134" s="134">
         <f>+$G$134</f>
         <v>95529</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="143" t="s">
+      <c r="A135" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="B135" s="65"/>
-      <c r="C135" s="65"/>
-      <c r="D135" s="65"/>
-      <c r="E135" s="65"/>
-      <c r="F135" s="65"/>
-      <c r="G135" s="70">
+      <c r="B135" s="56"/>
+      <c r="C135" s="56"/>
+      <c r="D135" s="56"/>
+      <c r="E135" s="56"/>
+      <c r="F135" s="56"/>
+      <c r="G135" s="61">
         <v>90026</v>
       </c>
-      <c r="H135" s="65">
+      <c r="H135" s="56">
         <f>+$G$135</f>
         <v>90026</v>
       </c>
-      <c r="I135" s="144">
+      <c r="I135" s="134">
         <f>+$G$135</f>
         <v>90026</v>
       </c>
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="143" t="s">
+      <c r="A136" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="B136" s="65"/>
-      <c r="C136" s="65"/>
-      <c r="D136" s="65"/>
-      <c r="E136" s="65"/>
-      <c r="F136" s="65"/>
-      <c r="G136" s="70">
+      <c r="B136" s="56"/>
+      <c r="C136" s="56"/>
+      <c r="D136" s="56"/>
+      <c r="E136" s="56"/>
+      <c r="F136" s="56"/>
+      <c r="G136" s="61">
         <f t="shared" ref="G136:G149" si="12">+E136</f>
         <v>0</v>
       </c>
-      <c r="H136" s="65"/>
-      <c r="I136" s="144"/>
+      <c r="H136" s="56"/>
+      <c r="I136" s="134"/>
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="143" t="s">
+      <c r="A137" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="B137" s="65"/>
-      <c r="C137" s="65"/>
-      <c r="D137" s="65"/>
-      <c r="E137" s="65"/>
-      <c r="F137" s="65"/>
-      <c r="G137" s="70">
+      <c r="B137" s="56"/>
+      <c r="C137" s="56"/>
+      <c r="D137" s="56"/>
+      <c r="E137" s="56"/>
+      <c r="F137" s="56"/>
+      <c r="G137" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H137" s="65"/>
-      <c r="I137" s="144"/>
+      <c r="H137" s="56"/>
+      <c r="I137" s="134"/>
     </row>
     <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="143" t="s">
+      <c r="A138" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="B138" s="65"/>
-      <c r="C138" s="65"/>
-      <c r="D138" s="65"/>
-      <c r="E138" s="65"/>
-      <c r="F138" s="65"/>
-      <c r="G138" s="70">
+      <c r="B138" s="56"/>
+      <c r="C138" s="56"/>
+      <c r="D138" s="56"/>
+      <c r="E138" s="56"/>
+      <c r="F138" s="56"/>
+      <c r="G138" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H138" s="65"/>
-      <c r="I138" s="144"/>
+      <c r="H138" s="56"/>
+      <c r="I138" s="134"/>
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="143" t="s">
+      <c r="A139" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="B139" s="65"/>
-      <c r="C139" s="65"/>
-      <c r="D139" s="65"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="65"/>
-      <c r="G139" s="70">
+      <c r="B139" s="56"/>
+      <c r="C139" s="56"/>
+      <c r="D139" s="56"/>
+      <c r="E139" s="56"/>
+      <c r="F139" s="56"/>
+      <c r="G139" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H139" s="65"/>
-      <c r="I139" s="144"/>
+      <c r="H139" s="56"/>
+      <c r="I139" s="134"/>
     </row>
     <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="143" t="s">
+      <c r="A140" s="133" t="s">
         <v>52</v>
       </c>
-      <c r="B140" s="65"/>
-      <c r="C140" s="65"/>
-      <c r="D140" s="65"/>
-      <c r="E140" s="65"/>
-      <c r="F140" s="65"/>
-      <c r="G140" s="70">
+      <c r="B140" s="56"/>
+      <c r="C140" s="56"/>
+      <c r="D140" s="56"/>
+      <c r="E140" s="56"/>
+      <c r="F140" s="56"/>
+      <c r="G140" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H140" s="65"/>
-      <c r="I140" s="144"/>
+      <c r="H140" s="56"/>
+      <c r="I140" s="134"/>
     </row>
     <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="143" t="s">
+      <c r="A141" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="B141" s="65"/>
-      <c r="C141" s="65"/>
-      <c r="D141" s="65"/>
-      <c r="E141" s="65"/>
-      <c r="F141" s="65"/>
-      <c r="G141" s="70">
+      <c r="B141" s="56"/>
+      <c r="C141" s="56"/>
+      <c r="D141" s="56"/>
+      <c r="E141" s="56"/>
+      <c r="F141" s="56"/>
+      <c r="G141" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H141" s="65"/>
-      <c r="I141" s="144"/>
+      <c r="H141" s="56"/>
+      <c r="I141" s="134"/>
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="143" t="s">
+      <c r="A142" s="133" t="s">
         <v>67</v>
       </c>
-      <c r="B142" s="65"/>
-      <c r="C142" s="65"/>
-      <c r="D142" s="65"/>
-      <c r="E142" s="65"/>
-      <c r="F142" s="65"/>
-      <c r="G142" s="70">
+      <c r="B142" s="56"/>
+      <c r="C142" s="56"/>
+      <c r="D142" s="56"/>
+      <c r="E142" s="56"/>
+      <c r="F142" s="56"/>
+      <c r="G142" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H142" s="65"/>
-      <c r="I142" s="144"/>
+      <c r="H142" s="56"/>
+      <c r="I142" s="134"/>
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="143" t="s">
+      <c r="A143" s="133" t="s">
         <v>54</v>
       </c>
-      <c r="B143" s="65"/>
-      <c r="C143" s="65"/>
-      <c r="D143" s="65"/>
-      <c r="E143" s="65"/>
-      <c r="F143" s="65"/>
-      <c r="G143" s="70">
+      <c r="B143" s="56"/>
+      <c r="C143" s="56"/>
+      <c r="D143" s="56"/>
+      <c r="E143" s="56"/>
+      <c r="F143" s="56"/>
+      <c r="G143" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H143" s="65"/>
-      <c r="I143" s="144"/>
+      <c r="H143" s="56"/>
+      <c r="I143" s="134"/>
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="143" t="s">
+      <c r="A144" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="B144" s="65"/>
-      <c r="C144" s="65"/>
-      <c r="D144" s="65"/>
-      <c r="E144" s="65"/>
-      <c r="F144" s="65"/>
-      <c r="G144" s="70">
+      <c r="B144" s="56"/>
+      <c r="C144" s="56"/>
+      <c r="D144" s="56"/>
+      <c r="E144" s="56"/>
+      <c r="F144" s="56"/>
+      <c r="G144" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H144" s="65"/>
-      <c r="I144" s="144"/>
+      <c r="H144" s="56"/>
+      <c r="I144" s="134"/>
     </row>
     <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="143" t="s">
+      <c r="A145" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="B145" s="65"/>
-      <c r="C145" s="65"/>
-      <c r="D145" s="65"/>
-      <c r="E145" s="65"/>
-      <c r="F145" s="65"/>
-      <c r="G145" s="70">
+      <c r="B145" s="56"/>
+      <c r="C145" s="56"/>
+      <c r="D145" s="56"/>
+      <c r="E145" s="56"/>
+      <c r="F145" s="56"/>
+      <c r="G145" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H145" s="65"/>
-      <c r="I145" s="144"/>
+      <c r="H145" s="56"/>
+      <c r="I145" s="134"/>
     </row>
     <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="143" t="s">
+      <c r="A146" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="B146" s="65"/>
-      <c r="C146" s="65"/>
-      <c r="D146" s="65"/>
-      <c r="E146" s="65"/>
-      <c r="F146" s="65"/>
-      <c r="G146" s="70">
+      <c r="B146" s="56"/>
+      <c r="C146" s="56"/>
+      <c r="D146" s="56"/>
+      <c r="E146" s="56"/>
+      <c r="F146" s="56"/>
+      <c r="G146" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H146" s="65"/>
-      <c r="I146" s="144"/>
+      <c r="H146" s="56"/>
+      <c r="I146" s="134"/>
     </row>
     <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="143" t="s">
+      <c r="A147" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="B147" s="65"/>
-      <c r="C147" s="65"/>
-      <c r="D147" s="65"/>
-      <c r="E147" s="65"/>
-      <c r="F147" s="65"/>
-      <c r="G147" s="70">
+      <c r="B147" s="56"/>
+      <c r="C147" s="56"/>
+      <c r="D147" s="56"/>
+      <c r="E147" s="56"/>
+      <c r="F147" s="56"/>
+      <c r="G147" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H147" s="65"/>
-      <c r="I147" s="144"/>
+      <c r="H147" s="56"/>
+      <c r="I147" s="134"/>
     </row>
     <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="143" t="s">
+      <c r="A148" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="B148" s="65"/>
-      <c r="C148" s="65"/>
-      <c r="D148" s="65"/>
-      <c r="E148" s="65"/>
-      <c r="F148" s="65"/>
-      <c r="G148" s="70">
+      <c r="B148" s="56"/>
+      <c r="C148" s="56"/>
+      <c r="D148" s="56"/>
+      <c r="E148" s="56"/>
+      <c r="F148" s="56"/>
+      <c r="G148" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H148" s="65"/>
-      <c r="I148" s="144"/>
+      <c r="H148" s="56"/>
+      <c r="I148" s="134"/>
     </row>
     <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="143" t="s">
+      <c r="A149" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="B149" s="65"/>
-      <c r="C149" s="65"/>
-      <c r="D149" s="65"/>
-      <c r="E149" s="65"/>
-      <c r="F149" s="65"/>
-      <c r="G149" s="70">
+      <c r="B149" s="56"/>
+      <c r="C149" s="56"/>
+      <c r="D149" s="56"/>
+      <c r="E149" s="56"/>
+      <c r="F149" s="56"/>
+      <c r="G149" s="61">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H149" s="65"/>
-      <c r="I149" s="144"/>
+      <c r="H149" s="56"/>
+      <c r="I149" s="134"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="145" t="s">
+      <c r="A150" s="135" t="s">
         <v>221</v>
       </c>
-      <c r="B150" s="109"/>
-      <c r="C150" s="109"/>
-      <c r="D150" s="109"/>
-      <c r="E150" s="109"/>
-      <c r="F150" s="109"/>
-      <c r="G150" s="96">
+      <c r="B150" s="100"/>
+      <c r="C150" s="100"/>
+      <c r="D150" s="100"/>
+      <c r="E150" s="100"/>
+      <c r="F150" s="100"/>
+      <c r="G150" s="87">
         <v>17756</v>
       </c>
-      <c r="H150" s="131">
+      <c r="H150" s="122">
         <f t="shared" ref="G150:I153" si="13">+$G$150</f>
         <v>17756</v>
       </c>
-      <c r="I150" s="146">
+      <c r="I150" s="136">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="145" t="s">
+      <c r="A151" s="135" t="s">
         <v>183</v>
       </c>
-      <c r="B151" s="109"/>
-      <c r="C151" s="109"/>
-      <c r="D151" s="109"/>
-      <c r="E151" s="109"/>
-      <c r="F151" s="109"/>
-      <c r="G151" s="131">
+      <c r="B151" s="100"/>
+      <c r="C151" s="100"/>
+      <c r="D151" s="100"/>
+      <c r="E151" s="100"/>
+      <c r="F151" s="100"/>
+      <c r="G151" s="122">
         <f>+$G$150</f>
         <v>17756</v>
       </c>
-      <c r="H151" s="131">
+      <c r="H151" s="122">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="I151" s="146">
+      <c r="I151" s="136">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="145" t="s">
+      <c r="A152" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="B152" s="119"/>
-      <c r="C152" s="119"/>
-      <c r="D152" s="119"/>
-      <c r="E152" s="119"/>
-      <c r="F152" s="119"/>
-      <c r="G152" s="131">
+      <c r="B152" s="110"/>
+      <c r="C152" s="110"/>
+      <c r="D152" s="110"/>
+      <c r="E152" s="110"/>
+      <c r="F152" s="110"/>
+      <c r="G152" s="122">
         <f>+$G$150</f>
         <v>17756</v>
       </c>
-      <c r="H152" s="131">
+      <c r="H152" s="122">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="I152" s="146">
+      <c r="I152" s="136">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="145" t="s">
+      <c r="A153" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="B153" s="109"/>
-      <c r="C153" s="109"/>
-      <c r="D153" s="109"/>
-      <c r="E153" s="109"/>
-      <c r="F153" s="109"/>
-      <c r="G153" s="131">
+      <c r="B153" s="100"/>
+      <c r="C153" s="100"/>
+      <c r="D153" s="100"/>
+      <c r="E153" s="100"/>
+      <c r="F153" s="100"/>
+      <c r="G153" s="122">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="H153" s="131">
+      <c r="H153" s="122">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
-      <c r="I153" s="146">
+      <c r="I153" s="136">
         <f t="shared" si="13"/>
         <v>17756</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="145" t="s">
+      <c r="A154" s="135" t="s">
         <v>219</v>
       </c>
-      <c r="B154" s="109"/>
-      <c r="C154" s="109"/>
-      <c r="D154" s="109"/>
-      <c r="E154" s="109"/>
-      <c r="F154" s="109"/>
-      <c r="G154" s="133">
+      <c r="B154" s="100"/>
+      <c r="C154" s="100"/>
+      <c r="D154" s="100"/>
+      <c r="E154" s="100"/>
+      <c r="F154" s="100"/>
+      <c r="G154" s="124">
         <v>35512</v>
       </c>
-      <c r="H154" s="131">
+      <c r="H154" s="122">
         <f>+$G$154</f>
         <v>35512</v>
       </c>
-      <c r="I154" s="146">
+      <c r="I154" s="136">
         <f>+$G$154</f>
         <v>35512</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="145" t="s">
+      <c r="A155" s="135" t="s">
         <v>52</v>
       </c>
-      <c r="B155" s="109"/>
-      <c r="C155" s="109"/>
-      <c r="D155" s="109"/>
-      <c r="E155" s="109"/>
-      <c r="F155" s="109"/>
-      <c r="G155" s="96">
+      <c r="B155" s="100"/>
+      <c r="C155" s="100"/>
+      <c r="D155" s="100"/>
+      <c r="E155" s="100"/>
+      <c r="F155" s="100"/>
+      <c r="G155" s="87">
         <v>12772</v>
       </c>
-      <c r="H155" s="109"/>
-      <c r="I155" s="147"/>
+      <c r="H155" s="100"/>
+      <c r="I155" s="137"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="145" t="s">
+      <c r="A156" s="135" t="s">
         <v>53</v>
       </c>
-      <c r="B156" s="109"/>
-      <c r="C156" s="109"/>
-      <c r="D156" s="109"/>
-      <c r="E156" s="109"/>
-      <c r="F156" s="109"/>
-      <c r="G156" s="96">
+      <c r="B156" s="100"/>
+      <c r="C156" s="100"/>
+      <c r="D156" s="100"/>
+      <c r="E156" s="100"/>
+      <c r="F156" s="100"/>
+      <c r="G156" s="87">
         <v>14226</v>
       </c>
-      <c r="H156" s="109">
+      <c r="H156" s="100">
         <f>+$G$156</f>
         <v>14226</v>
       </c>
-      <c r="I156" s="147">
+      <c r="I156" s="137">
         <f>+$G$156</f>
         <v>14226</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="145" t="s">
+      <c r="A157" s="135" t="s">
         <v>67</v>
       </c>
-      <c r="B157" s="109"/>
-      <c r="C157" s="109"/>
-      <c r="D157" s="109"/>
-      <c r="E157" s="109"/>
-      <c r="F157" s="109"/>
-      <c r="G157" s="96">
+      <c r="B157" s="100"/>
+      <c r="C157" s="100"/>
+      <c r="D157" s="100"/>
+      <c r="E157" s="100"/>
+      <c r="F157" s="100"/>
+      <c r="G157" s="87">
         <v>14329</v>
       </c>
-      <c r="H157" s="109"/>
-      <c r="I157" s="147"/>
+      <c r="H157" s="100"/>
+      <c r="I157" s="137"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="145" t="s">
+      <c r="A158" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="B158" s="109"/>
-      <c r="C158" s="109"/>
-      <c r="D158" s="109"/>
-      <c r="E158" s="109"/>
-      <c r="F158" s="109"/>
-      <c r="G158" s="96">
+      <c r="B158" s="100"/>
+      <c r="C158" s="100"/>
+      <c r="D158" s="100"/>
+      <c r="E158" s="100"/>
+      <c r="F158" s="100"/>
+      <c r="G158" s="87">
         <v>21390</v>
       </c>
-      <c r="H158" s="109">
+      <c r="H158" s="100">
         <f>+$G$158</f>
         <v>21390</v>
       </c>
-      <c r="I158" s="147">
+      <c r="I158" s="137">
         <f>+$G$158</f>
         <v>21390</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="145" t="s">
+      <c r="A159" s="135" t="s">
         <v>55</v>
       </c>
-      <c r="B159" s="109"/>
-      <c r="C159" s="109"/>
-      <c r="D159" s="109"/>
-      <c r="E159" s="109"/>
-      <c r="F159" s="109"/>
-      <c r="G159" s="96">
+      <c r="B159" s="100"/>
+      <c r="C159" s="100"/>
+      <c r="D159" s="100"/>
+      <c r="E159" s="100"/>
+      <c r="F159" s="100"/>
+      <c r="G159" s="87">
         <v>18067</v>
       </c>
-      <c r="H159" s="109"/>
-      <c r="I159" s="147"/>
+      <c r="H159" s="100"/>
+      <c r="I159" s="137"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="145" t="s">
+      <c r="A160" s="135" t="s">
         <v>220</v>
       </c>
-      <c r="B160" s="109"/>
-      <c r="C160" s="109"/>
-      <c r="D160" s="109"/>
-      <c r="E160" s="109"/>
-      <c r="F160" s="109"/>
-      <c r="G160" s="96">
+      <c r="B160" s="100"/>
+      <c r="C160" s="100"/>
+      <c r="D160" s="100"/>
+      <c r="E160" s="100"/>
+      <c r="F160" s="100"/>
+      <c r="G160" s="87">
         <v>36134</v>
       </c>
-      <c r="H160" s="109">
+      <c r="H160" s="100">
         <f>+$G$160</f>
         <v>36134</v>
       </c>
-      <c r="I160" s="147">
+      <c r="I160" s="137">
         <f>+$G$160</f>
         <v>36134</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="145" t="s">
+      <c r="A161" s="135" t="s">
         <v>186</v>
       </c>
-      <c r="B161" s="109"/>
-      <c r="C161" s="109"/>
-      <c r="D161" s="109"/>
-      <c r="E161" s="109"/>
-      <c r="F161" s="109"/>
-      <c r="G161" s="96">
+      <c r="B161" s="100"/>
+      <c r="C161" s="100"/>
+      <c r="D161" s="100"/>
+      <c r="E161" s="100"/>
+      <c r="F161" s="100"/>
+      <c r="G161" s="87">
         <v>17029</v>
       </c>
-      <c r="H161" s="109"/>
-      <c r="I161" s="147"/>
+      <c r="H161" s="100"/>
+      <c r="I161" s="137"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="145" t="s">
+      <c r="A162" s="135" t="s">
         <v>222</v>
       </c>
-      <c r="B162" s="109"/>
-      <c r="C162" s="109"/>
-      <c r="D162" s="109"/>
-      <c r="E162" s="109"/>
-      <c r="F162" s="109"/>
-      <c r="G162" s="131">
+      <c r="B162" s="100"/>
+      <c r="C162" s="100"/>
+      <c r="D162" s="100"/>
+      <c r="E162" s="100"/>
+      <c r="F162" s="100"/>
+      <c r="G162" s="122">
         <f>+$G$161</f>
         <v>17029</v>
       </c>
-      <c r="H162" s="109">
+      <c r="H162" s="100">
         <f>+$G$161</f>
         <v>17029</v>
       </c>
-      <c r="I162" s="147">
+      <c r="I162" s="137">
         <f>+$G$161</f>
         <v>17029</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="145" t="s">
+      <c r="A163" s="135" t="s">
         <v>176</v>
       </c>
-      <c r="B163" s="109"/>
-      <c r="C163" s="109"/>
-      <c r="D163" s="109"/>
-      <c r="E163" s="109"/>
-      <c r="F163" s="109"/>
-      <c r="G163" s="96">
+      <c r="B163" s="100"/>
+      <c r="C163" s="100"/>
+      <c r="D163" s="100"/>
+      <c r="E163" s="100"/>
+      <c r="F163" s="100"/>
+      <c r="G163" s="87">
         <v>17237</v>
       </c>
-      <c r="H163" s="109"/>
-      <c r="I163" s="147"/>
+      <c r="H163" s="100"/>
+      <c r="I163" s="137"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="145" t="s">
+      <c r="A164" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="B164" s="109"/>
-      <c r="C164" s="109"/>
-      <c r="D164" s="109"/>
-      <c r="E164" s="109"/>
-      <c r="F164" s="109"/>
-      <c r="G164" s="96">
+      <c r="B164" s="100"/>
+      <c r="C164" s="100"/>
+      <c r="D164" s="100"/>
+      <c r="E164" s="100"/>
+      <c r="F164" s="100"/>
+      <c r="G164" s="87">
         <v>20560</v>
       </c>
-      <c r="H164" s="109"/>
-      <c r="I164" s="147"/>
+      <c r="H164" s="100"/>
+      <c r="I164" s="137"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="145" t="s">
+      <c r="A165" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="B165" s="109"/>
-      <c r="C165" s="109"/>
-      <c r="D165" s="109"/>
-      <c r="E165" s="109"/>
-      <c r="F165" s="109"/>
-      <c r="G165" s="96">
+      <c r="B165" s="100"/>
+      <c r="C165" s="100"/>
+      <c r="D165" s="100"/>
+      <c r="E165" s="100"/>
+      <c r="F165" s="100"/>
+      <c r="G165" s="87">
         <v>14952</v>
       </c>
-      <c r="H165" s="109"/>
-      <c r="I165" s="147"/>
+      <c r="H165" s="100"/>
+      <c r="I165" s="137"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="145" t="s">
+      <c r="A166" s="135" t="s">
         <v>218</v>
       </c>
-      <c r="B166" s="109"/>
-      <c r="C166" s="109"/>
-      <c r="D166" s="109"/>
-      <c r="E166" s="109"/>
-      <c r="F166" s="109"/>
-      <c r="G166" s="96">
+      <c r="B166" s="100"/>
+      <c r="C166" s="100"/>
+      <c r="D166" s="100"/>
+      <c r="E166" s="100"/>
+      <c r="F166" s="100"/>
+      <c r="G166" s="87">
         <f>+$G$165*2</f>
         <v>29904</v>
       </c>
-      <c r="H166" s="109">
+      <c r="H166" s="100">
         <f>+$G$166</f>
         <v>29904</v>
       </c>
-      <c r="I166" s="147">
+      <c r="I166" s="137">
         <f>+$G$166</f>
         <v>29904</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="143" t="s">
+      <c r="A167" s="133" t="s">
         <v>61</v>
       </c>
-      <c r="B167" s="65"/>
-      <c r="C167" s="65"/>
-      <c r="D167" s="65"/>
-      <c r="E167" s="65"/>
-      <c r="F167" s="65"/>
-      <c r="G167" s="70">
+      <c r="B167" s="56"/>
+      <c r="C167" s="56"/>
+      <c r="D167" s="56"/>
+      <c r="E167" s="56"/>
+      <c r="F167" s="56"/>
+      <c r="G167" s="61">
         <v>36239</v>
       </c>
-      <c r="H167" s="65"/>
-      <c r="I167" s="144"/>
+      <c r="H167" s="56"/>
+      <c r="I167" s="134"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="143" t="s">
+      <c r="A168" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="B168" s="65"/>
-      <c r="C168" s="65"/>
-      <c r="D168" s="65"/>
-      <c r="E168" s="65"/>
-      <c r="F168" s="65"/>
-      <c r="G168" s="70">
+      <c r="B168" s="56"/>
+      <c r="C168" s="56"/>
+      <c r="D168" s="56"/>
+      <c r="E168" s="56"/>
+      <c r="F168" s="56"/>
+      <c r="G168" s="61">
         <v>38835</v>
       </c>
-      <c r="H168" s="65"/>
-      <c r="I168" s="144"/>
+      <c r="H168" s="56"/>
+      <c r="I168" s="134"/>
     </row>
     <row r="169" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="145" t="s">
+      <c r="A169" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="B169" s="119"/>
-      <c r="C169" s="119"/>
-      <c r="D169" s="119"/>
-      <c r="E169" s="119"/>
-      <c r="F169" s="119"/>
-      <c r="G169" s="130">
+      <c r="B169" s="110"/>
+      <c r="C169" s="110"/>
+      <c r="D169" s="110"/>
+      <c r="E169" s="110"/>
+      <c r="F169" s="110"/>
+      <c r="G169" s="121">
         <v>70000</v>
       </c>
-      <c r="H169" s="132">
+      <c r="H169" s="123">
         <v>25000</v>
       </c>
-      <c r="I169" s="148">
+      <c r="I169" s="138">
         <f>+$H$169</f>
         <v>25000</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="110" t="s">
+      <c r="A170" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B170" s="111"/>
-      <c r="C170" s="111"/>
-      <c r="D170" s="111"/>
-      <c r="E170" s="111"/>
-      <c r="F170" s="111"/>
-      <c r="G170" s="111"/>
-      <c r="H170" s="111"/>
-      <c r="I170" s="112"/>
-    </row>
-    <row r="171" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="87" t="s">
+      <c r="B170" s="102"/>
+      <c r="C170" s="102"/>
+      <c r="D170" s="102"/>
+      <c r="E170" s="102"/>
+      <c r="F170" s="102"/>
+      <c r="G170" s="102"/>
+      <c r="H170" s="102"/>
+      <c r="I170" s="103"/>
+    </row>
+    <row r="171" spans="1:12" s="11" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B171" s="120"/>
-      <c r="C171" s="94"/>
-      <c r="D171" s="94"/>
-      <c r="E171" s="94"/>
-      <c r="F171" s="94"/>
-      <c r="G171" s="94" t="s">
+      <c r="B171" s="111"/>
+      <c r="C171" s="85"/>
+      <c r="D171" s="85"/>
+      <c r="E171" s="85"/>
+      <c r="F171" s="85"/>
+      <c r="G171" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="H171" s="94" t="s">
+      <c r="H171" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="I171" s="95" t="s">
+      <c r="I171" s="86" t="s">
         <v>123</v>
       </c>
-      <c r="J171" s="157"/>
-      <c r="K171" s="61" t="s">
+      <c r="J171" s="147"/>
+      <c r="K171" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="L171" s="66">
+      <c r="L171" s="57">
         <v>12000</v>
       </c>
     </row>
-    <row r="172" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A172" s="6" t="s">
+    <row r="172" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A172" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B172" s="161"/>
-      <c r="C172" s="161"/>
-      <c r="D172" s="161"/>
-      <c r="E172" s="161"/>
-      <c r="F172" s="161"/>
-      <c r="G172" s="161">
+      <c r="B172" s="150"/>
+      <c r="C172" s="150"/>
+      <c r="D172" s="150"/>
+      <c r="E172" s="150"/>
+      <c r="F172" s="150"/>
+      <c r="G172" s="150">
         <f>+$L$171</f>
         <v>12000</v>
       </c>
-      <c r="H172" s="161">
+      <c r="H172" s="150">
         <f t="shared" ref="H172:I172" si="14">+$L$171</f>
         <v>12000</v>
       </c>
-      <c r="I172" s="162">
+      <c r="I172" s="151">
         <f t="shared" si="14"/>
         <v>12000</v>
       </c>
-      <c r="J172" s="157"/>
-    </row>
-    <row r="173" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A173" s="9" t="s">
+      <c r="J172" s="147"/>
+    </row>
+    <row r="173" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A173" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="B173" s="82"/>
-      <c r="C173" s="82"/>
-      <c r="D173" s="82"/>
-      <c r="E173" s="82"/>
-      <c r="F173" s="82"/>
-      <c r="G173" s="83">
+      <c r="B173" s="73"/>
+      <c r="C173" s="73"/>
+      <c r="D173" s="73"/>
+      <c r="E173" s="73"/>
+      <c r="F173" s="73"/>
+      <c r="G173" s="74">
         <v>25000</v>
       </c>
-      <c r="H173" s="82">
+      <c r="H173" s="73">
         <f>+G173</f>
         <v>25000</v>
       </c>
-      <c r="I173" s="97">
+      <c r="I173" s="88">
         <f>+G173</f>
         <v>25000</v>
       </c>
-      <c r="J173" s="157"/>
-      <c r="K173" s="61" t="s">
+      <c r="J173" s="147"/>
+      <c r="K173" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="L173" s="66">
+      <c r="L173" s="57">
         <v>22000</v>
       </c>
     </row>
-    <row r="174" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A174" s="9" t="s">
+    <row r="174" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A174" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B174" s="82"/>
-      <c r="C174" s="82"/>
-      <c r="D174" s="82"/>
-      <c r="E174" s="82"/>
-      <c r="F174" s="82"/>
-      <c r="G174" s="82">
+      <c r="B174" s="73"/>
+      <c r="C174" s="73"/>
+      <c r="D174" s="73"/>
+      <c r="E174" s="73"/>
+      <c r="F174" s="73"/>
+      <c r="G174" s="73">
         <f t="shared" ref="G174:G184" si="15">+$L$173</f>
         <v>22000</v>
       </c>
-      <c r="H174" s="82">
+      <c r="H174" s="73">
         <f t="shared" ref="H174:I184" si="16">+$L$173</f>
         <v>22000</v>
       </c>
-      <c r="I174" s="97">
+      <c r="I174" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J174" s="157"/>
-    </row>
-    <row r="175" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="9" t="s">
+      <c r="J174" s="147"/>
+    </row>
+    <row r="175" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A175" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B175" s="82"/>
-      <c r="C175" s="82"/>
-      <c r="D175" s="82"/>
-      <c r="E175" s="82"/>
-      <c r="F175" s="82"/>
-      <c r="G175" s="82">
+      <c r="B175" s="73"/>
+      <c r="C175" s="73"/>
+      <c r="D175" s="73"/>
+      <c r="E175" s="73"/>
+      <c r="F175" s="73"/>
+      <c r="G175" s="73">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H175" s="82">
+      <c r="H175" s="73">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I175" s="97">
+      <c r="I175" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J175" s="157"/>
-    </row>
-    <row r="176" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="9" t="s">
+      <c r="J175" s="147"/>
+    </row>
+    <row r="176" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A176" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B176" s="82"/>
-      <c r="C176" s="82"/>
-      <c r="D176" s="82"/>
-      <c r="E176" s="82"/>
-      <c r="F176" s="82"/>
-      <c r="G176" s="82">
+      <c r="B176" s="73"/>
+      <c r="C176" s="73"/>
+      <c r="D176" s="73"/>
+      <c r="E176" s="73"/>
+      <c r="F176" s="73"/>
+      <c r="G176" s="73">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H176" s="82">
+      <c r="H176" s="73">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I176" s="97">
+      <c r="I176" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J176" s="157"/>
-    </row>
-    <row r="177" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" s="9" t="s">
+      <c r="J176" s="147"/>
+    </row>
+    <row r="177" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A177" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="B177" s="82"/>
-      <c r="C177" s="82"/>
-      <c r="D177" s="82"/>
-      <c r="E177" s="82"/>
-      <c r="F177" s="82"/>
-      <c r="G177" s="82">
+      <c r="B177" s="73"/>
+      <c r="C177" s="73"/>
+      <c r="D177" s="73"/>
+      <c r="E177" s="73"/>
+      <c r="F177" s="73"/>
+      <c r="G177" s="73">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H177" s="82">
+      <c r="H177" s="73">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I177" s="97">
+      <c r="I177" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J177" s="157"/>
-    </row>
-    <row r="178" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A178" s="9" t="s">
+      <c r="J177" s="147"/>
+    </row>
+    <row r="178" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A178" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="B178" s="82"/>
-      <c r="C178" s="82"/>
-      <c r="D178" s="82"/>
-      <c r="E178" s="82"/>
-      <c r="F178" s="82"/>
-      <c r="G178" s="82">
+      <c r="B178" s="73"/>
+      <c r="C178" s="73"/>
+      <c r="D178" s="73"/>
+      <c r="E178" s="73"/>
+      <c r="F178" s="73"/>
+      <c r="G178" s="73">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H178" s="82">
+      <c r="H178" s="73">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I178" s="97">
+      <c r="I178" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J178" s="157"/>
-    </row>
-    <row r="179" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A179" s="9" t="s">
+      <c r="J178" s="147"/>
+    </row>
+    <row r="179" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A179" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B179" s="82"/>
-      <c r="C179" s="82"/>
-      <c r="D179" s="82"/>
-      <c r="E179" s="82"/>
-      <c r="F179" s="82"/>
-      <c r="G179" s="82">
+      <c r="B179" s="73"/>
+      <c r="C179" s="73"/>
+      <c r="D179" s="73"/>
+      <c r="E179" s="73"/>
+      <c r="F179" s="73"/>
+      <c r="G179" s="73">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H179" s="82">
+      <c r="H179" s="73">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I179" s="97">
+      <c r="I179" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J179" s="157"/>
-    </row>
-    <row r="180" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A180" s="9" t="s">
+      <c r="J179" s="147"/>
+    </row>
+    <row r="180" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A180" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="B180" s="82"/>
-      <c r="C180" s="82"/>
-      <c r="D180" s="82"/>
-      <c r="E180" s="82"/>
-      <c r="F180" s="82"/>
-      <c r="G180" s="82">
+      <c r="B180" s="73"/>
+      <c r="C180" s="73"/>
+      <c r="D180" s="73"/>
+      <c r="E180" s="73"/>
+      <c r="F180" s="73"/>
+      <c r="G180" s="73">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H180" s="82">
+      <c r="H180" s="73">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I180" s="97">
+      <c r="I180" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J180" s="157"/>
-    </row>
-    <row r="181" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A181" s="9" t="s">
+      <c r="J180" s="147"/>
+    </row>
+    <row r="181" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A181" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B181" s="82"/>
-      <c r="C181" s="82"/>
-      <c r="D181" s="82"/>
-      <c r="E181" s="82"/>
-      <c r="F181" s="82"/>
-      <c r="G181" s="82">
+      <c r="B181" s="73"/>
+      <c r="C181" s="73"/>
+      <c r="D181" s="73"/>
+      <c r="E181" s="73"/>
+      <c r="F181" s="73"/>
+      <c r="G181" s="73">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H181" s="82">
+      <c r="H181" s="73">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I181" s="97">
+      <c r="I181" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J181" s="157"/>
-    </row>
-    <row r="182" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A182" s="9" t="s">
+      <c r="J181" s="147"/>
+    </row>
+    <row r="182" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A182" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B182" s="82"/>
-      <c r="C182" s="82"/>
-      <c r="D182" s="82"/>
-      <c r="E182" s="82"/>
-      <c r="F182" s="82"/>
-      <c r="G182" s="82">
+      <c r="B182" s="73"/>
+      <c r="C182" s="73"/>
+      <c r="D182" s="73"/>
+      <c r="E182" s="73"/>
+      <c r="F182" s="73"/>
+      <c r="G182" s="73">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H182" s="82">
+      <c r="H182" s="73">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I182" s="97">
+      <c r="I182" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J182" s="157"/>
-    </row>
-    <row r="183" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A183" s="9" t="s">
+      <c r="J182" s="147"/>
+    </row>
+    <row r="183" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A183" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B183" s="82"/>
-      <c r="C183" s="82"/>
-      <c r="D183" s="82"/>
-      <c r="E183" s="82"/>
-      <c r="F183" s="82"/>
-      <c r="G183" s="82">
+      <c r="B183" s="73"/>
+      <c r="C183" s="73"/>
+      <c r="D183" s="73"/>
+      <c r="E183" s="73"/>
+      <c r="F183" s="73"/>
+      <c r="G183" s="73">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H183" s="82">
+      <c r="H183" s="73">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I183" s="97">
+      <c r="I183" s="88">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J183" s="157"/>
-    </row>
-    <row r="184" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" s="9" t="s">
+      <c r="J183" s="147"/>
+    </row>
+    <row r="184" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A184" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="B184" s="82"/>
-      <c r="C184" s="82"/>
-      <c r="D184" s="82"/>
-      <c r="E184" s="82"/>
-      <c r="F184" s="82"/>
-      <c r="G184" s="88">
+      <c r="B184" s="73"/>
+      <c r="C184" s="73"/>
+      <c r="D184" s="73"/>
+      <c r="E184" s="73"/>
+      <c r="F184" s="73"/>
+      <c r="G184" s="79">
         <f t="shared" si="15"/>
         <v>22000</v>
       </c>
-      <c r="H184" s="88">
+      <c r="H184" s="79">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="I184" s="160">
+      <c r="I184" s="149">
         <f t="shared" si="16"/>
         <v>22000</v>
       </c>
-      <c r="J184" s="157"/>
-    </row>
-    <row r="185" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A185" s="9" t="s">
+      <c r="J184" s="147"/>
+    </row>
+    <row r="185" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A185" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="B185" s="82"/>
-      <c r="C185" s="82"/>
-      <c r="D185" s="82"/>
-      <c r="E185" s="82"/>
-      <c r="F185" s="82"/>
-      <c r="G185" s="83">
+      <c r="B185" s="73"/>
+      <c r="C185" s="73"/>
+      <c r="D185" s="73"/>
+      <c r="E185" s="73"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="74">
         <v>32000</v>
       </c>
-      <c r="H185" s="82">
+      <c r="H185" s="73">
         <f>+G185</f>
         <v>32000</v>
       </c>
-      <c r="I185" s="82">
+      <c r="I185" s="73">
         <f>+G185</f>
         <v>32000</v>
       </c>
-      <c r="J185" s="157"/>
-    </row>
-    <row r="186" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A186" s="9" t="s">
+      <c r="J185" s="147"/>
+    </row>
+    <row r="186" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A186" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="B186" s="88"/>
-      <c r="C186" s="88"/>
-      <c r="D186" s="88"/>
-      <c r="E186" s="88"/>
-      <c r="F186" s="88"/>
-      <c r="G186" s="88">
+      <c r="B186" s="79"/>
+      <c r="C186" s="79"/>
+      <c r="D186" s="79"/>
+      <c r="E186" s="79"/>
+      <c r="F186" s="79"/>
+      <c r="G186" s="79">
         <f>+G185</f>
         <v>32000</v>
       </c>
-      <c r="H186" s="88">
+      <c r="H186" s="79">
         <f>+G185</f>
         <v>32000</v>
       </c>
-      <c r="I186" s="82">
+      <c r="I186" s="73">
         <f>+G185</f>
         <v>32000</v>
       </c>
-      <c r="J186" s="157"/>
-    </row>
-    <row r="187" spans="1:12" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A187" s="9" t="s">
+      <c r="J186" s="147"/>
+    </row>
+    <row r="187" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A187" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="B187" s="88"/>
-      <c r="C187" s="88"/>
-      <c r="D187" s="88"/>
-      <c r="E187" s="88"/>
-      <c r="F187" s="88"/>
-      <c r="G187" s="88">
+      <c r="B187" s="79"/>
+      <c r="C187" s="79"/>
+      <c r="D187" s="79"/>
+      <c r="E187" s="79"/>
+      <c r="F187" s="79"/>
+      <c r="G187" s="79">
         <f>+G185</f>
         <v>32000</v>
       </c>
-      <c r="H187" s="88">
+      <c r="H187" s="79">
         <f>+G185</f>
         <v>32000</v>
       </c>
-      <c r="I187" s="82">
+      <c r="I187" s="73">
         <f>+G185</f>
         <v>32000</v>
       </c>
-      <c r="J187" s="157"/>
-    </row>
-    <row r="188" spans="1:12" s="12" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B188" s="99"/>
-      <c r="C188" s="99"/>
-      <c r="D188" s="99"/>
-      <c r="E188" s="99"/>
-      <c r="F188" s="99"/>
-      <c r="G188" s="98">
+      <c r="J187" s="147"/>
+    </row>
+    <row r="188" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A188" s="94" t="s">
+        <v>157</v>
+      </c>
+      <c r="B188" s="79"/>
+      <c r="C188" s="79"/>
+      <c r="D188" s="79"/>
+      <c r="E188" s="79"/>
+      <c r="F188" s="79"/>
+      <c r="G188" s="74">
         <v>32000</v>
       </c>
-      <c r="H188" s="99">
+      <c r="H188" s="79">
         <f>+G188</f>
         <v>32000</v>
       </c>
-      <c r="I188" s="100">
+      <c r="I188" s="155">
         <f>+G188</f>
         <v>32000</v>
       </c>
-      <c r="J188" s="157"/>
-    </row>
-    <row r="189" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="87" t="s">
+      <c r="J188" s="147"/>
+    </row>
+    <row r="189" spans="1:10" s="11" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B189" s="90"/>
+      <c r="C189" s="90"/>
+      <c r="D189" s="90"/>
+      <c r="E189" s="90"/>
+      <c r="F189" s="90"/>
+      <c r="G189" s="89">
+        <v>32000</v>
+      </c>
+      <c r="H189" s="90">
+        <f>+G189</f>
+        <v>32000</v>
+      </c>
+      <c r="I189" s="91">
+        <f>+G189</f>
+        <v>32000</v>
+      </c>
+      <c r="J189" s="147"/>
+    </row>
+    <row r="190" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="B189" s="120"/>
-      <c r="C189" s="121"/>
-      <c r="D189" s="121"/>
-      <c r="E189" s="94"/>
-      <c r="F189" s="94"/>
-      <c r="G189" s="94" t="s">
+      <c r="B190" s="111"/>
+      <c r="C190" s="112"/>
+      <c r="D190" s="112"/>
+      <c r="E190" s="85"/>
+      <c r="F190" s="85"/>
+      <c r="G190" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="H189" s="95" t="s">
+      <c r="H190" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="I189" s="95" t="s">
+      <c r="I190" s="86" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A190" s="8" t="s">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B190" s="92"/>
-      <c r="C190" s="92"/>
-      <c r="D190" s="92"/>
-      <c r="E190" s="92"/>
-      <c r="F190" s="92"/>
-      <c r="G190" s="91">
+      <c r="B191" s="83"/>
+      <c r="C191" s="83"/>
+      <c r="D191" s="83"/>
+      <c r="E191" s="83"/>
+      <c r="F191" s="83"/>
+      <c r="G191" s="82">
         <v>24000</v>
       </c>
-      <c r="H190" s="92">
-        <f>+G190</f>
+      <c r="H191" s="83">
+        <f>+G191</f>
         <v>24000</v>
       </c>
-      <c r="I190" s="93">
-        <f>+G190</f>
+      <c r="I191" s="84">
+        <f>+G191</f>
         <v>24000</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="10" t="s">
+    <row r="192" spans="1:10" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B191" s="71"/>
-      <c r="C191" s="71"/>
-      <c r="D191" s="71"/>
-      <c r="E191" s="71"/>
-      <c r="F191" s="71"/>
-      <c r="G191" s="71"/>
-      <c r="H191" s="71">
-        <f t="shared" ref="H191:I231" si="17">+G191</f>
+      <c r="B192" s="62"/>
+      <c r="C192" s="62"/>
+      <c r="D192" s="62"/>
+      <c r="E192" s="62"/>
+      <c r="F192" s="62"/>
+      <c r="G192" s="62"/>
+      <c r="H192" s="62">
+        <f t="shared" ref="H192:I232" si="17">+G192</f>
         <v>0</v>
       </c>
-      <c r="I191" s="89">
+      <c r="I192" s="80">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A192" s="9" t="s">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B192" s="85"/>
-      <c r="C192" s="85"/>
-      <c r="D192" s="85"/>
-      <c r="E192" s="85"/>
-      <c r="F192" s="85"/>
-      <c r="G192" s="85">
-        <f t="shared" ref="G192:I192" si="18">$L$192</f>
+      <c r="B193" s="76"/>
+      <c r="C193" s="76"/>
+      <c r="D193" s="76"/>
+      <c r="E193" s="76"/>
+      <c r="F193" s="76"/>
+      <c r="G193" s="76">
+        <f t="shared" ref="G193:I193" si="18">$L$193</f>
         <v>16640</v>
       </c>
-      <c r="H192" s="85">
+      <c r="H193" s="76">
         <f t="shared" si="18"/>
         <v>16640</v>
       </c>
-      <c r="I192" s="90">
+      <c r="I193" s="81">
         <f t="shared" si="18"/>
         <v>16640</v>
       </c>
-      <c r="K192" s="61" t="s">
+      <c r="K193" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="L192" s="66">
+      <c r="L193" s="57">
         <v>16640</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A193" s="9" t="s">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A194" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B193" s="85"/>
-      <c r="C193" s="85"/>
-      <c r="D193" s="85"/>
-      <c r="E193" s="85"/>
-      <c r="F193" s="85"/>
-      <c r="G193" s="85">
-        <f>$L$193</f>
+      <c r="B194" s="76"/>
+      <c r="C194" s="76"/>
+      <c r="D194" s="76"/>
+      <c r="E194" s="76"/>
+      <c r="F194" s="76"/>
+      <c r="G194" s="76">
+        <f>$L$194</f>
         <v>9600</v>
       </c>
-      <c r="H193" s="85">
-        <f t="shared" ref="H193:I193" si="19">$L$193</f>
+      <c r="H194" s="76">
+        <f t="shared" ref="H194:I194" si="19">$L$194</f>
         <v>9600</v>
       </c>
-      <c r="I193" s="90">
+      <c r="I194" s="81">
         <f t="shared" si="19"/>
         <v>9600</v>
       </c>
-      <c r="K193" s="61" t="s">
+      <c r="K194" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="L193" s="66">
+      <c r="L194" s="57">
         <v>9600</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A194" s="9" t="s">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B194" s="85"/>
-      <c r="C194" s="85"/>
-      <c r="D194" s="85"/>
-      <c r="E194" s="85"/>
-      <c r="F194" s="85"/>
-      <c r="G194" s="85">
-        <f>$L$192</f>
+      <c r="B195" s="76"/>
+      <c r="C195" s="76"/>
+      <c r="D195" s="76"/>
+      <c r="E195" s="76"/>
+      <c r="F195" s="76"/>
+      <c r="G195" s="76">
+        <f>$L$193</f>
         <v>16640</v>
       </c>
-      <c r="H194" s="85">
-        <f t="shared" ref="H194:I194" si="20">$L$192</f>
+      <c r="H195" s="76">
+        <f t="shared" ref="H195:I195" si="20">$L$193</f>
         <v>16640</v>
       </c>
-      <c r="I194" s="90">
+      <c r="I195" s="81">
         <f t="shared" si="20"/>
         <v>16640</v>
       </c>
-      <c r="L194" s="64"/>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A195" s="9" t="s">
+      <c r="L195" s="55"/>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B195" s="85"/>
-      <c r="C195" s="85"/>
-      <c r="D195" s="85"/>
-      <c r="E195" s="85"/>
-      <c r="F195" s="85"/>
-      <c r="G195" s="85">
-        <f>$L$193</f>
+      <c r="B196" s="76"/>
+      <c r="C196" s="76"/>
+      <c r="D196" s="76"/>
+      <c r="E196" s="76"/>
+      <c r="F196" s="76"/>
+      <c r="G196" s="76">
+        <f>$L$194</f>
         <v>9600</v>
       </c>
-      <c r="H195" s="85">
-        <f t="shared" ref="H195:I195" si="21">$L$193</f>
+      <c r="H196" s="76">
+        <f t="shared" ref="H196:I196" si="21">$L$194</f>
         <v>9600</v>
       </c>
-      <c r="I195" s="90">
+      <c r="I196" s="81">
         <f t="shared" si="21"/>
         <v>9600</v>
       </c>
-      <c r="K195" s="61" t="s">
+      <c r="K196" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="L195" s="66">
+      <c r="L196" s="57">
         <v>32000</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A196" s="9" t="s">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B196" s="85"/>
-      <c r="C196" s="85"/>
-      <c r="D196" s="85"/>
-      <c r="E196" s="85"/>
-      <c r="F196" s="85"/>
-      <c r="G196" s="85">
-        <f t="shared" ref="G196:I204" si="22">$L$192</f>
+      <c r="B197" s="76"/>
+      <c r="C197" s="76"/>
+      <c r="D197" s="76"/>
+      <c r="E197" s="76"/>
+      <c r="F197" s="76"/>
+      <c r="G197" s="76">
+        <f t="shared" ref="G197:I205" si="22">$L$193</f>
         <v>16640</v>
       </c>
-      <c r="H196" s="85">
+      <c r="H197" s="76">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I196" s="90">
+      <c r="I197" s="81">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="9" t="s">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A198" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B197" s="85"/>
-      <c r="C197" s="85"/>
-      <c r="D197" s="85"/>
-      <c r="E197" s="85"/>
-      <c r="F197" s="85"/>
-      <c r="G197" s="85">
-        <f>$L$193</f>
+      <c r="B198" s="76"/>
+      <c r="C198" s="76"/>
+      <c r="D198" s="76"/>
+      <c r="E198" s="76"/>
+      <c r="F198" s="76"/>
+      <c r="G198" s="76">
+        <f>$L$194</f>
         <v>9600</v>
       </c>
-      <c r="H197" s="85">
-        <f t="shared" ref="H197:I197" si="23">$L$193</f>
+      <c r="H198" s="76">
+        <f t="shared" ref="H198:I198" si="23">$L$194</f>
         <v>9600</v>
       </c>
-      <c r="I197" s="90">
+      <c r="I198" s="81">
         <f t="shared" si="23"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A198" s="9" t="s">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B198" s="85"/>
-      <c r="C198" s="85"/>
-      <c r="D198" s="85"/>
-      <c r="E198" s="85"/>
-      <c r="F198" s="85"/>
-      <c r="G198" s="85">
+      <c r="B199" s="76"/>
+      <c r="C199" s="76"/>
+      <c r="D199" s="76"/>
+      <c r="E199" s="76"/>
+      <c r="F199" s="76"/>
+      <c r="G199" s="76">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="H198" s="85">
+      <c r="H199" s="76">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I198" s="90">
+      <c r="I199" s="81">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A199" s="9" t="s">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B199" s="85"/>
-      <c r="C199" s="85"/>
-      <c r="D199" s="85"/>
-      <c r="E199" s="85"/>
-      <c r="F199" s="85"/>
-      <c r="G199" s="85">
-        <f>$L$193</f>
+      <c r="B200" s="76"/>
+      <c r="C200" s="76"/>
+      <c r="D200" s="76"/>
+      <c r="E200" s="76"/>
+      <c r="F200" s="76"/>
+      <c r="G200" s="76">
+        <f>$L$194</f>
         <v>9600</v>
       </c>
-      <c r="H199" s="85">
-        <f t="shared" ref="H199:I199" si="24">$L$193</f>
+      <c r="H200" s="76">
+        <f t="shared" ref="H200:I200" si="24">$L$194</f>
         <v>9600</v>
       </c>
-      <c r="I199" s="90">
+      <c r="I200" s="81">
         <f t="shared" si="24"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A200" s="9" t="s">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B200" s="85"/>
-      <c r="C200" s="85"/>
-      <c r="D200" s="85"/>
-      <c r="E200" s="85"/>
-      <c r="F200" s="85"/>
-      <c r="G200" s="85">
+      <c r="B201" s="76"/>
+      <c r="C201" s="76"/>
+      <c r="D201" s="76"/>
+      <c r="E201" s="76"/>
+      <c r="F201" s="76"/>
+      <c r="G201" s="76">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="H200" s="85">
+      <c r="H201" s="76">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I200" s="90">
+      <c r="I201" s="81">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="9" t="s">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A202" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B201" s="85"/>
-      <c r="C201" s="85"/>
-      <c r="D201" s="85"/>
-      <c r="E201" s="85"/>
-      <c r="F201" s="85"/>
-      <c r="G201" s="85">
-        <f>$L$193</f>
+      <c r="B202" s="76"/>
+      <c r="C202" s="76"/>
+      <c r="D202" s="76"/>
+      <c r="E202" s="76"/>
+      <c r="F202" s="76"/>
+      <c r="G202" s="76">
+        <f>$L$194</f>
         <v>9600</v>
       </c>
-      <c r="H201" s="85">
-        <f t="shared" ref="H201:I201" si="25">$L$193</f>
+      <c r="H202" s="76">
+        <f t="shared" ref="H202:I202" si="25">$L$194</f>
         <v>9600</v>
       </c>
-      <c r="I201" s="90">
+      <c r="I202" s="81">
         <f t="shared" si="25"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A202" s="9" t="s">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A203" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B202" s="85"/>
-      <c r="C202" s="85"/>
-      <c r="D202" s="85"/>
-      <c r="E202" s="85"/>
-      <c r="F202" s="85"/>
-      <c r="G202" s="85">
+      <c r="B203" s="76"/>
+      <c r="C203" s="76"/>
+      <c r="D203" s="76"/>
+      <c r="E203" s="76"/>
+      <c r="F203" s="76"/>
+      <c r="G203" s="76">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="H202" s="85">
+      <c r="H203" s="76">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I202" s="90">
+      <c r="I203" s="81">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A203" s="9" t="s">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A204" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B203" s="85"/>
-      <c r="C203" s="85"/>
-      <c r="D203" s="85"/>
-      <c r="E203" s="85"/>
-      <c r="F203" s="85"/>
-      <c r="G203" s="85">
-        <f>$L$193</f>
+      <c r="B204" s="76"/>
+      <c r="C204" s="76"/>
+      <c r="D204" s="76"/>
+      <c r="E204" s="76"/>
+      <c r="F204" s="76"/>
+      <c r="G204" s="76">
+        <f>$L$194</f>
         <v>9600</v>
       </c>
-      <c r="H203" s="85">
-        <f t="shared" ref="H203:I203" si="26">$L$193</f>
+      <c r="H204" s="76">
+        <f t="shared" ref="H204:I204" si="26">$L$194</f>
         <v>9600</v>
       </c>
-      <c r="I203" s="90">
+      <c r="I204" s="81">
         <f t="shared" si="26"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="9" t="s">
+    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B204" s="85"/>
-      <c r="C204" s="85"/>
-      <c r="D204" s="85"/>
-      <c r="E204" s="85"/>
-      <c r="F204" s="85"/>
-      <c r="G204" s="85">
+      <c r="B205" s="76"/>
+      <c r="C205" s="76"/>
+      <c r="D205" s="76"/>
+      <c r="E205" s="76"/>
+      <c r="F205" s="76"/>
+      <c r="G205" s="76">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="H204" s="85">
+      <c r="H205" s="76">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
-      <c r="I204" s="90">
+      <c r="I205" s="81">
         <f t="shared" si="22"/>
         <v>16640</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="9" t="s">
+    <row r="206" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B205" s="85"/>
-      <c r="C205" s="85"/>
-      <c r="D205" s="85"/>
-      <c r="E205" s="85"/>
-      <c r="F205" s="85"/>
-      <c r="G205" s="85">
-        <f>$L$193</f>
+      <c r="B206" s="76"/>
+      <c r="C206" s="76"/>
+      <c r="D206" s="76"/>
+      <c r="E206" s="76"/>
+      <c r="F206" s="76"/>
+      <c r="G206" s="76">
+        <f>$L$194</f>
         <v>9600</v>
       </c>
-      <c r="H205" s="85">
-        <f t="shared" ref="H205:I205" si="27">$L$193</f>
+      <c r="H206" s="76">
+        <f t="shared" ref="H206:I206" si="27">$L$194</f>
         <v>9600</v>
       </c>
-      <c r="I205" s="90">
+      <c r="I206" s="81">
         <f t="shared" si="27"/>
         <v>9600</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A206" s="63" t="s">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A207" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="B206" s="85"/>
-      <c r="C206" s="85"/>
-      <c r="D206" s="85"/>
-      <c r="E206" s="85"/>
-      <c r="F206" s="85"/>
-      <c r="G206" s="86">
+      <c r="B207" s="76"/>
+      <c r="C207" s="76"/>
+      <c r="D207" s="76"/>
+      <c r="E207" s="76"/>
+      <c r="F207" s="76"/>
+      <c r="G207" s="77">
         <v>36000</v>
       </c>
-      <c r="H206" s="85">
+      <c r="H207" s="76">
         <f t="shared" si="17"/>
         <v>36000</v>
       </c>
-      <c r="I206" s="90">
-        <f>+G206</f>
+      <c r="I207" s="81">
+        <f>+G207</f>
         <v>36000</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A207" s="9" t="s">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A208" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B207" s="85"/>
-      <c r="C207" s="85"/>
-      <c r="D207" s="85"/>
-      <c r="E207" s="85"/>
-      <c r="F207" s="85"/>
-      <c r="G207" s="85">
-        <f>$L$195</f>
+      <c r="B208" s="76"/>
+      <c r="C208" s="76"/>
+      <c r="D208" s="76"/>
+      <c r="E208" s="76"/>
+      <c r="F208" s="76"/>
+      <c r="G208" s="76">
+        <f>$L$196</f>
         <v>32000</v>
       </c>
-      <c r="H207" s="85">
-        <f t="shared" ref="H207:I207" si="28">$L$195</f>
+      <c r="H208" s="76">
+        <f t="shared" ref="H208:I208" si="28">$L$196</f>
         <v>32000</v>
       </c>
-      <c r="I207" s="90">
+      <c r="I208" s="81">
         <f t="shared" si="28"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A208" s="9" t="s">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B208" s="85"/>
-      <c r="C208" s="85"/>
-      <c r="D208" s="85"/>
-      <c r="E208" s="85"/>
-      <c r="F208" s="85"/>
-      <c r="G208" s="85">
-        <f t="shared" ref="G208:I225" si="29">$L$195</f>
+      <c r="B209" s="76"/>
+      <c r="C209" s="76"/>
+      <c r="D209" s="76"/>
+      <c r="E209" s="76"/>
+      <c r="F209" s="76"/>
+      <c r="G209" s="76">
+        <f t="shared" ref="G209:I226" si="29">$L$196</f>
         <v>32000</v>
       </c>
-      <c r="H208" s="85">
+      <c r="H209" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I208" s="90">
+      <c r="I209" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A209" s="9" t="s">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B209" s="85"/>
-      <c r="C209" s="85"/>
-      <c r="D209" s="85"/>
-      <c r="E209" s="85"/>
-      <c r="F209" s="85"/>
-      <c r="G209" s="85">
-        <f>$L$195</f>
+      <c r="B210" s="76"/>
+      <c r="C210" s="76"/>
+      <c r="D210" s="76"/>
+      <c r="E210" s="76"/>
+      <c r="F210" s="76"/>
+      <c r="G210" s="76">
+        <f>$L$196</f>
         <v>32000</v>
       </c>
-      <c r="H209" s="85">
+      <c r="H210" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I209" s="90">
+      <c r="I210" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" s="9" t="s">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="B210" s="85"/>
-      <c r="C210" s="85"/>
-      <c r="D210" s="85"/>
-      <c r="E210" s="85"/>
-      <c r="F210" s="85"/>
-      <c r="G210" s="85">
+      <c r="B211" s="76"/>
+      <c r="C211" s="76"/>
+      <c r="D211" s="76"/>
+      <c r="E211" s="76"/>
+      <c r="F211" s="76"/>
+      <c r="G211" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H210" s="85">
+      <c r="H211" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I210" s="90">
+      <c r="I211" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A211" s="9" t="s">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B211" s="85"/>
-      <c r="C211" s="85"/>
-      <c r="D211" s="85"/>
-      <c r="E211" s="85"/>
-      <c r="F211" s="85"/>
-      <c r="G211" s="85">
+      <c r="B212" s="76"/>
+      <c r="C212" s="76"/>
+      <c r="D212" s="76"/>
+      <c r="E212" s="76"/>
+      <c r="F212" s="76"/>
+      <c r="G212" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H211" s="85">
+      <c r="H212" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I211" s="90">
+      <c r="I212" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A212" s="9" t="s">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B212" s="85"/>
-      <c r="C212" s="85"/>
-      <c r="D212" s="85"/>
-      <c r="E212" s="85"/>
-      <c r="F212" s="85"/>
-      <c r="G212" s="85">
+      <c r="B213" s="76"/>
+      <c r="C213" s="76"/>
+      <c r="D213" s="76"/>
+      <c r="E213" s="76"/>
+      <c r="F213" s="76"/>
+      <c r="G213" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H212" s="85">
+      <c r="H213" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I212" s="90">
+      <c r="I213" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" s="9" t="s">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B213" s="85"/>
-      <c r="C213" s="85"/>
-      <c r="D213" s="85"/>
-      <c r="E213" s="85"/>
-      <c r="F213" s="85"/>
-      <c r="G213" s="85">
+      <c r="B214" s="76"/>
+      <c r="C214" s="76"/>
+      <c r="D214" s="76"/>
+      <c r="E214" s="76"/>
+      <c r="F214" s="76"/>
+      <c r="G214" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H213" s="85">
+      <c r="H214" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I213" s="90">
+      <c r="I214" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" s="9" t="s">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B214" s="85"/>
-      <c r="C214" s="85"/>
-      <c r="D214" s="85"/>
-      <c r="E214" s="85"/>
-      <c r="F214" s="85"/>
-      <c r="G214" s="85">
+      <c r="B215" s="76"/>
+      <c r="C215" s="76"/>
+      <c r="D215" s="76"/>
+      <c r="E215" s="76"/>
+      <c r="F215" s="76"/>
+      <c r="G215" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H214" s="85">
+      <c r="H215" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I214" s="90">
+      <c r="I215" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="9" t="s">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B215" s="85"/>
-      <c r="C215" s="85"/>
-      <c r="D215" s="85"/>
-      <c r="E215" s="85"/>
-      <c r="F215" s="85"/>
-      <c r="G215" s="85">
+      <c r="B216" s="76"/>
+      <c r="C216" s="76"/>
+      <c r="D216" s="76"/>
+      <c r="E216" s="76"/>
+      <c r="F216" s="76"/>
+      <c r="G216" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H215" s="85">
+      <c r="H216" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I215" s="90">
+      <c r="I216" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A216" s="35" t="s">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="B216" s="85"/>
-      <c r="C216" s="85"/>
-      <c r="D216" s="85"/>
-      <c r="E216" s="85"/>
-      <c r="F216" s="85"/>
-      <c r="G216" s="85">
+      <c r="B217" s="76"/>
+      <c r="C217" s="76"/>
+      <c r="D217" s="76"/>
+      <c r="E217" s="76"/>
+      <c r="F217" s="76"/>
+      <c r="G217" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H216" s="85">
+      <c r="H217" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I216" s="90">
+      <c r="I217" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" s="35" t="s">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="B217" s="85"/>
-      <c r="C217" s="85"/>
-      <c r="D217" s="85"/>
-      <c r="E217" s="85"/>
-      <c r="F217" s="85"/>
-      <c r="G217" s="85">
+      <c r="B218" s="76"/>
+      <c r="C218" s="76"/>
+      <c r="D218" s="76"/>
+      <c r="E218" s="76"/>
+      <c r="F218" s="76"/>
+      <c r="G218" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H217" s="85">
+      <c r="H218" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I217" s="90">
+      <c r="I218" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A218" s="35" t="s">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="B218" s="85"/>
-      <c r="C218" s="85"/>
-      <c r="D218" s="85"/>
-      <c r="E218" s="85"/>
-      <c r="F218" s="85"/>
-      <c r="G218" s="85">
+      <c r="B219" s="76"/>
+      <c r="C219" s="76"/>
+      <c r="D219" s="76"/>
+      <c r="E219" s="76"/>
+      <c r="F219" s="76"/>
+      <c r="G219" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H218" s="85">
+      <c r="H219" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I218" s="90">
+      <c r="I219" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" s="35" t="s">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="B219" s="85"/>
-      <c r="C219" s="85"/>
-      <c r="D219" s="85"/>
-      <c r="E219" s="85"/>
-      <c r="F219" s="85"/>
-      <c r="G219" s="85">
+      <c r="B220" s="76"/>
+      <c r="C220" s="76"/>
+      <c r="D220" s="76"/>
+      <c r="E220" s="76"/>
+      <c r="F220" s="76"/>
+      <c r="G220" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H219" s="85">
+      <c r="H220" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I219" s="90">
+      <c r="I220" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A220" s="35" t="s">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="B220" s="85"/>
-      <c r="C220" s="85"/>
-      <c r="D220" s="85"/>
-      <c r="E220" s="85"/>
-      <c r="F220" s="85"/>
-      <c r="G220" s="85">
+      <c r="B221" s="76"/>
+      <c r="C221" s="76"/>
+      <c r="D221" s="76"/>
+      <c r="E221" s="76"/>
+      <c r="F221" s="76"/>
+      <c r="G221" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H220" s="85">
+      <c r="H221" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I220" s="90">
+      <c r="I221" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A221" s="35" t="s">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="B221" s="85"/>
-      <c r="C221" s="85"/>
-      <c r="D221" s="85"/>
-      <c r="E221" s="85"/>
-      <c r="F221" s="85"/>
-      <c r="G221" s="85">
+      <c r="B222" s="76"/>
+      <c r="C222" s="76"/>
+      <c r="D222" s="76"/>
+      <c r="E222" s="76"/>
+      <c r="F222" s="76"/>
+      <c r="G222" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H221" s="85">
+      <c r="H222" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I221" s="90">
+      <c r="I222" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A222" s="35" t="s">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="B222" s="85"/>
-      <c r="C222" s="85"/>
-      <c r="D222" s="85"/>
-      <c r="E222" s="85"/>
-      <c r="F222" s="85"/>
-      <c r="G222" s="85">
+      <c r="B223" s="76"/>
+      <c r="C223" s="76"/>
+      <c r="D223" s="76"/>
+      <c r="E223" s="76"/>
+      <c r="F223" s="76"/>
+      <c r="G223" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H222" s="85">
+      <c r="H223" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I222" s="90">
+      <c r="I223" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A223" s="63" t="s">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="54" t="s">
         <v>183</v>
       </c>
-      <c r="B223" s="85"/>
-      <c r="C223" s="85"/>
-      <c r="D223" s="85"/>
-      <c r="E223" s="85"/>
-      <c r="F223" s="85"/>
-      <c r="G223" s="86">
+      <c r="B224" s="76"/>
+      <c r="C224" s="76"/>
+      <c r="D224" s="76"/>
+      <c r="E224" s="76"/>
+      <c r="F224" s="76"/>
+      <c r="G224" s="77">
         <v>35000</v>
       </c>
-      <c r="H223" s="85">
-        <f>+G223</f>
+      <c r="H224" s="76">
+        <f>+G224</f>
         <v>35000</v>
       </c>
-      <c r="I223" s="90">
-        <f>+G223</f>
+      <c r="I224" s="81">
+        <f>+G224</f>
         <v>35000</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A224" s="35" t="s">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A225" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="B224" s="85"/>
-      <c r="C224" s="85"/>
-      <c r="D224" s="85"/>
-      <c r="E224" s="85"/>
-      <c r="F224" s="85"/>
-      <c r="G224" s="85">
+      <c r="B225" s="76"/>
+      <c r="C225" s="76"/>
+      <c r="D225" s="76"/>
+      <c r="E225" s="76"/>
+      <c r="F225" s="76"/>
+      <c r="G225" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H224" s="85">
+      <c r="H225" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I224" s="90">
+      <c r="I225" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A225" s="35" t="s">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A226" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="B225" s="85"/>
-      <c r="C225" s="85"/>
-      <c r="D225" s="85"/>
-      <c r="E225" s="85"/>
-      <c r="F225" s="85"/>
-      <c r="G225" s="85">
+      <c r="B226" s="76"/>
+      <c r="C226" s="76"/>
+      <c r="D226" s="76"/>
+      <c r="E226" s="76"/>
+      <c r="F226" s="76"/>
+      <c r="G226" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="H225" s="85">
+      <c r="H226" s="76">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
-      <c r="I225" s="90">
+      <c r="I226" s="81">
         <f t="shared" si="29"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A226" s="35" t="s">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A227" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="B226" s="85"/>
-      <c r="C226" s="85"/>
-      <c r="D226" s="85"/>
-      <c r="E226" s="85"/>
-      <c r="F226" s="85"/>
-      <c r="G226" s="85">
-        <f t="shared" ref="G226:I227" si="30">$L$195</f>
+      <c r="B227" s="76"/>
+      <c r="C227" s="76"/>
+      <c r="D227" s="76"/>
+      <c r="E227" s="76"/>
+      <c r="F227" s="76"/>
+      <c r="G227" s="76">
+        <f t="shared" ref="G227:I228" si="30">$L$196</f>
         <v>32000</v>
       </c>
-      <c r="H226" s="85">
+      <c r="H227" s="76">
         <f t="shared" si="30"/>
         <v>32000</v>
       </c>
-      <c r="I226" s="90">
+      <c r="I227" s="81">
         <f t="shared" si="30"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A227" s="9" t="s">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A228" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B227" s="85"/>
-      <c r="C227" s="85"/>
-      <c r="D227" s="85"/>
-      <c r="E227" s="85"/>
-      <c r="F227" s="85"/>
-      <c r="G227" s="85">
+      <c r="B228" s="76"/>
+      <c r="C228" s="76"/>
+      <c r="D228" s="76"/>
+      <c r="E228" s="76"/>
+      <c r="F228" s="76"/>
+      <c r="G228" s="76">
         <f t="shared" si="30"/>
         <v>32000</v>
       </c>
-      <c r="H227" s="85">
+      <c r="H228" s="76">
         <f t="shared" si="30"/>
         <v>32000</v>
       </c>
-      <c r="I227" s="90">
+      <c r="I228" s="81">
         <f t="shared" si="30"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A228" s="9" t="s">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A229" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B228" s="85"/>
-      <c r="C228" s="85"/>
-      <c r="D228" s="85"/>
-      <c r="E228" s="85"/>
-      <c r="F228" s="85"/>
-      <c r="G228" s="85">
+      <c r="B229" s="76"/>
+      <c r="C229" s="76"/>
+      <c r="D229" s="76"/>
+      <c r="E229" s="76"/>
+      <c r="F229" s="76"/>
+      <c r="G229" s="76">
         <v>78000</v>
       </c>
-      <c r="H228" s="85">
+      <c r="H229" s="76">
         <f t="shared" si="17"/>
         <v>78000</v>
       </c>
-      <c r="I228" s="90">
+      <c r="I229" s="81">
         <f t="shared" si="17"/>
         <v>78000</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A229" s="9" t="s">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A230" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B229" s="85"/>
-      <c r="C229" s="85"/>
-      <c r="D229" s="85"/>
-      <c r="E229" s="85"/>
-      <c r="F229" s="85"/>
-      <c r="G229" s="85">
+      <c r="B230" s="76"/>
+      <c r="C230" s="76"/>
+      <c r="D230" s="76"/>
+      <c r="E230" s="76"/>
+      <c r="F230" s="76"/>
+      <c r="G230" s="76">
         <v>60000</v>
       </c>
-      <c r="H229" s="85">
+      <c r="H230" s="76">
         <f t="shared" si="17"/>
         <v>60000</v>
       </c>
-      <c r="I229" s="90">
+      <c r="I230" s="81">
         <f t="shared" si="17"/>
         <v>60000</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A230" s="63" t="s">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A231" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="B230" s="85"/>
-      <c r="C230" s="85"/>
-      <c r="D230" s="85"/>
-      <c r="E230" s="85"/>
-      <c r="F230" s="85"/>
-      <c r="G230" s="86">
+      <c r="B231" s="76"/>
+      <c r="C231" s="76"/>
+      <c r="D231" s="76"/>
+      <c r="E231" s="76"/>
+      <c r="F231" s="76"/>
+      <c r="G231" s="77">
         <v>100000</v>
       </c>
-      <c r="H230" s="85">
+      <c r="H231" s="76">
         <f t="shared" si="17"/>
         <v>100000</v>
       </c>
-      <c r="I230" s="90">
+      <c r="I231" s="81">
         <f t="shared" si="17"/>
         <v>100000</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A231" s="63" t="s">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A232" s="54" t="s">
         <v>157</v>
       </c>
-      <c r="B231" s="85"/>
-      <c r="C231" s="85"/>
-      <c r="D231" s="85"/>
-      <c r="E231" s="85"/>
-      <c r="F231" s="85"/>
-      <c r="G231" s="86">
+      <c r="B232" s="76"/>
+      <c r="C232" s="76"/>
+      <c r="D232" s="76"/>
+      <c r="E232" s="76"/>
+      <c r="F232" s="76"/>
+      <c r="G232" s="77">
         <v>75000</v>
       </c>
-      <c r="H231" s="85">
+      <c r="H232" s="76">
         <f t="shared" si="17"/>
         <v>75000</v>
       </c>
-      <c r="I231" s="90">
+      <c r="I232" s="81">
         <f t="shared" si="17"/>
         <v>75000</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A232" s="9" t="s">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A233" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B232" s="85"/>
-      <c r="C232" s="85"/>
-      <c r="D232" s="85"/>
-      <c r="E232" s="85"/>
-      <c r="F232" s="85"/>
-      <c r="G232" s="85">
-        <f>+$L$234</f>
+      <c r="B233" s="76"/>
+      <c r="C233" s="76"/>
+      <c r="D233" s="76"/>
+      <c r="E233" s="76"/>
+      <c r="F233" s="76"/>
+      <c r="G233" s="76">
+        <f>+$L$235</f>
         <v>106880</v>
       </c>
-      <c r="H232" s="85">
-        <f t="shared" ref="H232:I247" si="31">+$L$234</f>
+      <c r="H233" s="76">
+        <f t="shared" ref="H233:I248" si="31">+$L$235</f>
         <v>106880</v>
       </c>
-      <c r="I232" s="90">
+      <c r="I233" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A233" s="9" t="s">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A234" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="B233" s="85"/>
-      <c r="C233" s="85"/>
-      <c r="D233" s="85"/>
-      <c r="E233" s="85"/>
-      <c r="F233" s="85"/>
-      <c r="G233" s="85">
-        <f t="shared" ref="G233:I248" si="32">+$L$234</f>
+      <c r="B234" s="76"/>
+      <c r="C234" s="76"/>
+      <c r="D234" s="76"/>
+      <c r="E234" s="76"/>
+      <c r="F234" s="76"/>
+      <c r="G234" s="76">
+        <f t="shared" ref="G234:I249" si="32">+$L$235</f>
         <v>106880</v>
       </c>
-      <c r="H233" s="85">
+      <c r="H234" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I233" s="90">
+      <c r="I234" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A234" s="9" t="s">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A235" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B234" s="85"/>
-      <c r="C234" s="85"/>
-      <c r="D234" s="85"/>
-      <c r="E234" s="85"/>
-      <c r="F234" s="85"/>
-      <c r="G234" s="85">
+      <c r="B235" s="76"/>
+      <c r="C235" s="76"/>
+      <c r="D235" s="76"/>
+      <c r="E235" s="76"/>
+      <c r="F235" s="76"/>
+      <c r="G235" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H234" s="85">
+      <c r="H235" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I234" s="90">
+      <c r="I235" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="K234" s="61" t="s">
+      <c r="K235" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="L234" s="66">
+      <c r="L235" s="57">
         <v>106880</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A235" s="9" t="s">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A236" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B235" s="85"/>
-      <c r="C235" s="85"/>
-      <c r="D235" s="85"/>
-      <c r="E235" s="85"/>
-      <c r="F235" s="85"/>
-      <c r="G235" s="85">
+      <c r="B236" s="76"/>
+      <c r="C236" s="76"/>
+      <c r="D236" s="76"/>
+      <c r="E236" s="76"/>
+      <c r="F236" s="76"/>
+      <c r="G236" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H235" s="85">
+      <c r="H236" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I235" s="90">
+      <c r="I236" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A236" s="9" t="s">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A237" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="B236" s="85"/>
-      <c r="C236" s="85"/>
-      <c r="D236" s="85"/>
-      <c r="E236" s="85"/>
-      <c r="F236" s="85"/>
-      <c r="G236" s="85">
+      <c r="B237" s="76"/>
+      <c r="C237" s="76"/>
+      <c r="D237" s="76"/>
+      <c r="E237" s="76"/>
+      <c r="F237" s="76"/>
+      <c r="G237" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H236" s="85">
+      <c r="H237" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I236" s="90">
+      <c r="I237" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A237" s="9" t="s">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A238" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="B237" s="85"/>
-      <c r="C237" s="85"/>
-      <c r="D237" s="85"/>
-      <c r="E237" s="85"/>
-      <c r="F237" s="85"/>
-      <c r="G237" s="85">
+      <c r="B238" s="76"/>
+      <c r="C238" s="76"/>
+      <c r="D238" s="76"/>
+      <c r="E238" s="76"/>
+      <c r="F238" s="76"/>
+      <c r="G238" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H237" s="85">
+      <c r="H238" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I237" s="90">
+      <c r="I238" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A238" s="9" t="s">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A239" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B238" s="85"/>
-      <c r="C238" s="85"/>
-      <c r="D238" s="85"/>
-      <c r="E238" s="85"/>
-      <c r="F238" s="85"/>
-      <c r="G238" s="85">
+      <c r="B239" s="76"/>
+      <c r="C239" s="76"/>
+      <c r="D239" s="76"/>
+      <c r="E239" s="76"/>
+      <c r="F239" s="76"/>
+      <c r="G239" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H238" s="85">
+      <c r="H239" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I238" s="90">
+      <c r="I239" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A239" s="9" t="s">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A240" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B239" s="85"/>
-      <c r="C239" s="85"/>
-      <c r="D239" s="85"/>
-      <c r="E239" s="85"/>
-      <c r="F239" s="85"/>
-      <c r="G239" s="85">
+      <c r="B240" s="76"/>
+      <c r="C240" s="76"/>
+      <c r="D240" s="76"/>
+      <c r="E240" s="76"/>
+      <c r="F240" s="76"/>
+      <c r="G240" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H239" s="85">
+      <c r="H240" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I239" s="90">
+      <c r="I240" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A240" s="9" t="s">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B240" s="85"/>
-      <c r="C240" s="85"/>
-      <c r="D240" s="85"/>
-      <c r="E240" s="85"/>
-      <c r="F240" s="85"/>
-      <c r="G240" s="85">
+      <c r="B241" s="76"/>
+      <c r="C241" s="76"/>
+      <c r="D241" s="76"/>
+      <c r="E241" s="76"/>
+      <c r="F241" s="76"/>
+      <c r="G241" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H240" s="85">
+      <c r="H241" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I240" s="90">
+      <c r="I241" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A241" s="9" t="s">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B241" s="85"/>
-      <c r="C241" s="85"/>
-      <c r="D241" s="85"/>
-      <c r="E241" s="85"/>
-      <c r="F241" s="85"/>
-      <c r="G241" s="85">
+      <c r="B242" s="76"/>
+      <c r="C242" s="76"/>
+      <c r="D242" s="76"/>
+      <c r="E242" s="76"/>
+      <c r="F242" s="76"/>
+      <c r="G242" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H241" s="85">
+      <c r="H242" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I241" s="90">
+      <c r="I242" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A242" s="9" t="s">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="B242" s="85"/>
-      <c r="C242" s="85"/>
-      <c r="D242" s="85"/>
-      <c r="E242" s="85"/>
-      <c r="F242" s="85"/>
-      <c r="G242" s="85">
+      <c r="B243" s="76"/>
+      <c r="C243" s="76"/>
+      <c r="D243" s="76"/>
+      <c r="E243" s="76"/>
+      <c r="F243" s="76"/>
+      <c r="G243" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H242" s="85">
+      <c r="H243" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I242" s="90">
+      <c r="I243" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A243" s="9" t="s">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B243" s="85"/>
-      <c r="C243" s="85"/>
-      <c r="D243" s="85"/>
-      <c r="E243" s="85"/>
-      <c r="F243" s="85"/>
-      <c r="G243" s="85">
+      <c r="B244" s="76"/>
+      <c r="C244" s="76"/>
+      <c r="D244" s="76"/>
+      <c r="E244" s="76"/>
+      <c r="F244" s="76"/>
+      <c r="G244" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H243" s="85">
+      <c r="H244" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I243" s="90">
+      <c r="I244" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A244" s="9" t="s">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="B244" s="85"/>
-      <c r="C244" s="85"/>
-      <c r="D244" s="85"/>
-      <c r="E244" s="85"/>
-      <c r="F244" s="85"/>
-      <c r="G244" s="85">
+      <c r="B245" s="76"/>
+      <c r="C245" s="76"/>
+      <c r="D245" s="76"/>
+      <c r="E245" s="76"/>
+      <c r="F245" s="76"/>
+      <c r="G245" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H244" s="85">
+      <c r="H245" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I244" s="90">
+      <c r="I245" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A245" s="9" t="s">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B245" s="85"/>
-      <c r="C245" s="85"/>
-      <c r="D245" s="85"/>
-      <c r="E245" s="85"/>
-      <c r="F245" s="85"/>
-      <c r="G245" s="85">
+      <c r="B246" s="76"/>
+      <c r="C246" s="76"/>
+      <c r="D246" s="76"/>
+      <c r="E246" s="76"/>
+      <c r="F246" s="76"/>
+      <c r="G246" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H245" s="85">
+      <c r="H246" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I245" s="90">
+      <c r="I246" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A246" s="9" t="s">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B246" s="85"/>
-      <c r="C246" s="85"/>
-      <c r="D246" s="85"/>
-      <c r="E246" s="85"/>
-      <c r="F246" s="85"/>
-      <c r="G246" s="85">
+      <c r="B247" s="76"/>
+      <c r="C247" s="76"/>
+      <c r="D247" s="76"/>
+      <c r="E247" s="76"/>
+      <c r="F247" s="76"/>
+      <c r="G247" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H246" s="85">
+      <c r="H247" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I246" s="90">
+      <c r="I247" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A247" s="9" t="s">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="B247" s="85"/>
-      <c r="C247" s="85"/>
-      <c r="D247" s="85"/>
-      <c r="E247" s="85"/>
-      <c r="F247" s="85"/>
-      <c r="G247" s="85">
+      <c r="B248" s="76"/>
+      <c r="C248" s="76"/>
+      <c r="D248" s="76"/>
+      <c r="E248" s="76"/>
+      <c r="F248" s="76"/>
+      <c r="G248" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H247" s="85">
+      <c r="H248" s="76">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="I247" s="90">
+      <c r="I248" s="81">
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="103" t="s">
+    <row r="249" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="94" t="s">
         <v>203</v>
       </c>
-      <c r="B248" s="104"/>
-      <c r="C248" s="104"/>
-      <c r="D248" s="104"/>
-      <c r="E248" s="104"/>
-      <c r="F248" s="104"/>
-      <c r="G248" s="104">
+      <c r="B249" s="95"/>
+      <c r="C249" s="95"/>
+      <c r="D249" s="95"/>
+      <c r="E249" s="95"/>
+      <c r="F249" s="95"/>
+      <c r="G249" s="95">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H248" s="104">
+      <c r="H249" s="95">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I248" s="105">
+      <c r="I249" s="96">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="87" t="s">
+    <row r="250" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B249" s="120"/>
-      <c r="C249" s="121"/>
-      <c r="D249" s="121"/>
-      <c r="E249" s="94"/>
-      <c r="F249" s="94"/>
-      <c r="G249" s="94" t="s">
+      <c r="B250" s="111"/>
+      <c r="C250" s="112"/>
+      <c r="D250" s="112"/>
+      <c r="E250" s="85"/>
+      <c r="F250" s="85"/>
+      <c r="G250" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="H249" s="95" t="s">
+      <c r="H250" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="I249" s="95" t="s">
+      <c r="I250" s="86" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="22" t="s">
+    <row r="251" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B250" s="107"/>
-      <c r="C250" s="107"/>
-      <c r="D250" s="107"/>
-      <c r="E250" s="107"/>
-      <c r="F250" s="107"/>
-      <c r="G250" s="106">
+      <c r="B251" s="98"/>
+      <c r="C251" s="98"/>
+      <c r="D251" s="98"/>
+      <c r="E251" s="98"/>
+      <c r="F251" s="98"/>
+      <c r="G251" s="97">
         <v>40000</v>
       </c>
-      <c r="H250" s="107">
-        <f>+G250</f>
+      <c r="H251" s="98">
+        <f>+G251</f>
         <v>40000</v>
       </c>
-      <c r="I250" s="108">
-        <f>+G250</f>
+      <c r="I251" s="99">
+        <f>+G251</f>
         <v>40000</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="87" t="s">
+    <row r="252" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="78" t="s">
         <v>207</v>
       </c>
-      <c r="B251" s="120"/>
-      <c r="C251" s="94"/>
-      <c r="D251" s="94"/>
-      <c r="E251" s="94"/>
-      <c r="F251" s="94" t="s">
+      <c r="B252" s="111"/>
+      <c r="C252" s="85"/>
+      <c r="D252" s="85"/>
+      <c r="E252" s="85"/>
+      <c r="F252" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G251" s="94" t="s">
+      <c r="G252" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="H251" s="94" t="s">
+      <c r="H252" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="I251" s="95" t="s">
+      <c r="I252" s="86" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A252" s="23" t="s">
+    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A253" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="B252" s="84"/>
-      <c r="C252" s="84"/>
-      <c r="D252" s="84"/>
-      <c r="E252" s="84"/>
-      <c r="F252" s="101">
+      <c r="B253" s="75"/>
+      <c r="C253" s="75"/>
+      <c r="D253" s="75"/>
+      <c r="E253" s="75"/>
+      <c r="F253" s="92">
         <v>15000</v>
       </c>
-      <c r="G252" s="101">
+      <c r="G253" s="92">
         <v>15000</v>
       </c>
-      <c r="H252" s="84">
-        <f>+$G$252</f>
+      <c r="H253" s="75">
+        <f>+$G$253</f>
         <v>15000</v>
       </c>
-      <c r="I252" s="102">
-        <f>+$G$252</f>
+      <c r="I253" s="93">
+        <f>+$G$253</f>
         <v>15000</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A253" s="23" t="s">
+    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A254" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B253" s="82"/>
-      <c r="C253" s="82"/>
-      <c r="D253" s="82"/>
-      <c r="E253" s="82"/>
-      <c r="F253" s="83">
+      <c r="B254" s="73"/>
+      <c r="C254" s="73"/>
+      <c r="D254" s="73"/>
+      <c r="E254" s="73"/>
+      <c r="F254" s="74">
         <v>18000</v>
       </c>
-      <c r="G253" s="83">
+      <c r="G254" s="74">
         <v>15000</v>
       </c>
-      <c r="H253" s="82">
-        <f>+G253</f>
-        <v>15000</v>
-      </c>
-      <c r="I253" s="97">
-        <f>+G253</f>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A254" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B254" s="82"/>
-      <c r="C254" s="82"/>
-      <c r="D254" s="82"/>
-      <c r="E254" s="82"/>
-      <c r="F254" s="83">
-        <v>18000</v>
-      </c>
-      <c r="G254" s="83">
-        <v>15000</v>
-      </c>
-      <c r="H254" s="82">
+      <c r="H254" s="73">
         <f>+G254</f>
         <v>15000</v>
       </c>
-      <c r="I254" s="97">
+      <c r="I254" s="88">
         <f>+G254</f>
         <v>15000</v>
       </c>
     </row>
     <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A255" s="23" t="s">
+      <c r="A255" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B255" s="73"/>
+      <c r="C255" s="73"/>
+      <c r="D255" s="73"/>
+      <c r="E255" s="73"/>
+      <c r="F255" s="74">
+        <v>18000</v>
+      </c>
+      <c r="G255" s="74">
+        <v>15000</v>
+      </c>
+      <c r="H255" s="73">
+        <f>+G255</f>
+        <v>15000</v>
+      </c>
+      <c r="I255" s="88">
+        <f>+G255</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A256" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="B255" s="82"/>
-      <c r="C255" s="82"/>
-      <c r="D255" s="82"/>
-      <c r="E255" s="82"/>
-      <c r="F255" s="82"/>
-      <c r="G255" s="83">
+      <c r="B256" s="73"/>
+      <c r="C256" s="73"/>
+      <c r="D256" s="73"/>
+      <c r="E256" s="73"/>
+      <c r="F256" s="73"/>
+      <c r="G256" s="74">
         <v>20000</v>
       </c>
-      <c r="H255" s="82">
-        <f>+G255</f>
-        <v>20000</v>
-      </c>
-      <c r="I255" s="97">
-        <f>+G255</f>
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="B256" s="99"/>
-      <c r="C256" s="99"/>
-      <c r="D256" s="99"/>
-      <c r="E256" s="99"/>
-      <c r="F256" s="99"/>
-      <c r="G256" s="98">
-        <v>20000</v>
-      </c>
-      <c r="H256" s="99">
+      <c r="H256" s="73">
         <f>+G256</f>
         <v>20000</v>
       </c>
-      <c r="I256" s="100">
+      <c r="I256" s="88">
         <f>+G256</f>
         <v>20000</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="87" t="s">
+      <c r="A257" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B257" s="90"/>
+      <c r="C257" s="90"/>
+      <c r="D257" s="90"/>
+      <c r="E257" s="90"/>
+      <c r="F257" s="90"/>
+      <c r="G257" s="89">
+        <v>20000</v>
+      </c>
+      <c r="H257" s="90">
+        <f>+G257</f>
+        <v>20000</v>
+      </c>
+      <c r="I257" s="91">
+        <f>+G257</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="78" t="s">
         <v>227</v>
       </c>
-      <c r="B257" s="120"/>
-      <c r="C257" s="94"/>
-      <c r="D257" s="94"/>
-      <c r="E257" s="94"/>
-      <c r="F257" s="94" t="s">
+      <c r="B258" s="111"/>
+      <c r="C258" s="85"/>
+      <c r="D258" s="85"/>
+      <c r="E258" s="85"/>
+      <c r="F258" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G257" s="94" t="s">
+      <c r="G258" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="H257" s="94" t="s">
+      <c r="H258" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="I257" s="95" t="s">
+      <c r="I258" s="86" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A258" s="23" t="s">
+    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A259" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="B258" s="84"/>
-      <c r="C258" s="84"/>
-      <c r="D258" s="84"/>
-      <c r="E258" s="84"/>
-      <c r="F258" s="84"/>
-      <c r="G258" s="101">
+      <c r="B259" s="75"/>
+      <c r="C259" s="75"/>
+      <c r="D259" s="75"/>
+      <c r="E259" s="75"/>
+      <c r="F259" s="75"/>
+      <c r="G259" s="92">
         <v>35000</v>
       </c>
-      <c r="H258" s="84">
-        <f>+G258</f>
-        <v>35000</v>
-      </c>
-      <c r="I258" s="102">
-        <f>+G258</f>
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A259" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="B259" s="82"/>
-      <c r="C259" s="82"/>
-      <c r="D259" s="82"/>
-      <c r="E259" s="82"/>
-      <c r="F259" s="82"/>
-      <c r="G259" s="83">
-        <v>35000</v>
-      </c>
-      <c r="H259" s="82">
+      <c r="H259" s="75">
         <f>+G259</f>
         <v>35000</v>
       </c>
-      <c r="I259" s="97">
+      <c r="I259" s="93">
         <f>+G259</f>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A260" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="B260" s="73"/>
+      <c r="C260" s="73"/>
+      <c r="D260" s="73"/>
+      <c r="E260" s="73"/>
+      <c r="F260" s="73"/>
+      <c r="G260" s="74">
+        <v>35000</v>
+      </c>
+      <c r="H260" s="73">
+        <f>+G260</f>
+        <v>35000</v>
+      </c>
+      <c r="I260" s="88">
+        <f>+G260</f>
         <v>35000</v>
       </c>
     </row>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -3028,9 +3028,6 @@
     <t>ECOGRAFIAS</t>
   </si>
   <si>
-    <t>TRASLUCENCIA NUCAL</t>
-  </si>
-  <si>
     <t>CONSULTA MEDICA A</t>
   </si>
   <si>
@@ -3353,6 +3350,9 @@
   </si>
   <si>
     <t>ECODOPPLER TESTICULAR</t>
+  </si>
+  <si>
+    <t>TRANSLUCENCIA NUCAL</t>
   </si>
 </sst>
 </file>
@@ -4566,14 +4566,14 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4876,17 +4876,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
     </row>
     <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B2" s="104"/>
       <c r="C2" s="105"/>
@@ -4923,7 +4923,7 @@
         <v>5550</v>
       </c>
       <c r="G3" s="56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H3" s="56">
         <v>4550</v>
@@ -4935,7 +4935,7 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B4" s="139"/>
       <c r="C4" s="139">
@@ -4952,7 +4952,7 @@
         <v>5550</v>
       </c>
       <c r="G4" s="56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H4" s="139"/>
       <c r="I4" s="140">
@@ -4962,7 +4962,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="141"/>
       <c r="C5" s="141"/>
@@ -4975,7 +4975,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6" s="56"/>
       <c r="C6" s="56">
@@ -5044,7 +5044,7 @@
         <v>123</v>
       </c>
       <c r="J8" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K8" s="47"/>
     </row>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B11" s="56">
         <v>25000</v>
@@ -5113,7 +5113,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="56">
         <v>30000</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B13" s="56"/>
       <c r="C13" s="56"/>
@@ -5153,7 +5153,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B14" s="56"/>
       <c r="C14" s="56"/>
@@ -5198,7 +5198,7 @@
         <v>123</v>
       </c>
       <c r="J15" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K15" s="50"/>
     </row>
@@ -5353,7 +5353,7 @@
         <v>123</v>
       </c>
       <c r="J21" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K21" s="47"/>
     </row>
@@ -5411,7 +5411,7 @@
         <v>123</v>
       </c>
       <c r="J23" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K23" s="47"/>
     </row>
@@ -5449,7 +5449,7 @@
         <v>123</v>
       </c>
       <c r="J25" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K25" s="47"/>
     </row>
@@ -5511,7 +5511,7 @@
         <v>123</v>
       </c>
       <c r="J27" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K27" s="47"/>
     </row>
@@ -5573,7 +5573,7 @@
         <v>123</v>
       </c>
       <c r="J29" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K29" s="47"/>
     </row>
@@ -5635,7 +5635,7 @@
         <v>123</v>
       </c>
       <c r="J31" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K31" s="47"/>
     </row>
@@ -5697,7 +5697,7 @@
         <v>123</v>
       </c>
       <c r="J33" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K33" s="47"/>
     </row>
@@ -5759,7 +5759,7 @@
         <v>123</v>
       </c>
       <c r="J35" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K35" s="47"/>
     </row>
@@ -5821,7 +5821,7 @@
         <v>123</v>
       </c>
       <c r="J37" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K37" s="47"/>
     </row>
@@ -5883,7 +5883,7 @@
         <v>123</v>
       </c>
       <c r="J39" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K39" s="47"/>
     </row>
@@ -5945,7 +5945,7 @@
         <v>123</v>
       </c>
       <c r="J41" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K41" s="47"/>
     </row>
@@ -6007,7 +6007,7 @@
         <v>123</v>
       </c>
       <c r="J43" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K43" s="47"/>
     </row>
@@ -6182,7 +6182,7 @@
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B49" s="62">
         <v>20000</v>
@@ -6691,7 +6691,7 @@
       <c r="I66" s="65"/>
     </row>
     <row r="67" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="154" t="s">
+      <c r="A67" s="153" t="s">
         <v>8</v>
       </c>
       <c r="B67" s="104" t="s">
@@ -6746,7 +6746,7 @@
     </row>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B69" s="108">
         <v>51000</v>
@@ -6776,8 +6776,8 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="154" t="s">
-        <v>232</v>
+      <c r="A70" s="153" t="s">
+        <v>231</v>
       </c>
       <c r="B70" s="104" t="s">
         <v>127</v>
@@ -6831,7 +6831,7 @@
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B72" s="108">
         <v>68000</v>
@@ -6861,8 +6861,8 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="154" t="s">
-        <v>231</v>
+      <c r="A73" s="153" t="s">
+        <v>230</v>
       </c>
       <c r="B73" s="104" t="s">
         <v>127</v>
@@ -6915,8 +6915,8 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="153" t="s">
-        <v>144</v>
+      <c r="A75" s="152" t="s">
+        <v>143</v>
       </c>
       <c r="B75" s="108">
         <v>132000</v>
@@ -6946,8 +6946,8 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="154" t="s">
-        <v>233</v>
+      <c r="A76" s="153" t="s">
+        <v>232</v>
       </c>
       <c r="B76" s="104" t="s">
         <v>127</v>
@@ -7001,7 +7001,7 @@
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B78" s="108">
         <v>203000</v>
@@ -7031,7 +7031,7 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="154" t="s">
+      <c r="A79" s="153" t="s">
         <v>9</v>
       </c>
       <c r="B79" s="104"/>
@@ -7115,7 +7115,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B82" s="61">
         <v>41000</v>
@@ -7177,7 +7177,7 @@
     </row>
     <row r="84" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B84" s="104"/>
       <c r="C84" s="105"/>
@@ -7236,7 +7236,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B87" s="64">
         <v>97000</v>
@@ -7298,7 +7298,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B89" s="64">
         <v>256000</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="113" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B91" s="114">
         <v>8200</v>
@@ -7712,7 +7712,7 @@
         <v>73</v>
       </c>
       <c r="B104" s="104" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C104" s="105"/>
       <c r="D104" s="105"/>
@@ -7887,10 +7887,10 @@
     </row>
     <row r="110" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B110" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C110" s="105"/>
       <c r="D110" s="105"/>
@@ -7910,7 +7910,7 @@
     </row>
     <row r="111" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B111" s="56">
         <v>312686</v>
@@ -7941,7 +7941,7 @@
     </row>
     <row r="112" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B112" s="56">
         <v>349723</v>
@@ -7972,7 +7972,7 @@
     </row>
     <row r="113" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B113" s="56">
         <v>446016</v>
@@ -8006,7 +8006,7 @@
         <v>75</v>
       </c>
       <c r="B114" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C114" s="105"/>
       <c r="D114" s="105"/>
@@ -8091,7 +8091,7 @@
         <v>78</v>
       </c>
       <c r="B117" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C117" s="105"/>
       <c r="D117" s="105"/>
@@ -8238,7 +8238,7 @@
         <v>83</v>
       </c>
       <c r="B122" s="104" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C122" s="105"/>
       <c r="D122" s="105"/>
@@ -8385,7 +8385,7 @@
         <v>91</v>
       </c>
       <c r="B127" s="128" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C127" s="117"/>
       <c r="D127" s="117"/>
@@ -8498,7 +8498,7 @@
     </row>
     <row r="131" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="127" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B131" s="128"/>
       <c r="C131" s="117"/>
@@ -8819,7 +8819,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="135" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B150" s="100"/>
       <c r="C150" s="100"/>
@@ -8840,7 +8840,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="135" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B151" s="100"/>
       <c r="C151" s="100"/>
@@ -8906,7 +8906,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="135" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B154" s="100"/>
       <c r="C154" s="100"/>
@@ -9014,7 +9014,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="135" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B160" s="100"/>
       <c r="C160" s="100"/>
@@ -9035,7 +9035,7 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="135" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B161" s="100"/>
       <c r="C161" s="100"/>
@@ -9050,7 +9050,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B162" s="100"/>
       <c r="C162" s="100"/>
@@ -9072,7 +9072,7 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B163" s="100"/>
       <c r="C163" s="100"/>
@@ -9117,7 +9117,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="135" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B166" s="100"/>
       <c r="C166" s="100"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="J171" s="147"/>
       <c r="K171" s="52" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L171" s="57">
         <v>12000</v>
@@ -9228,7 +9228,7 @@
     </row>
     <row r="172" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B172" s="150"/>
       <c r="C172" s="150"/>
@@ -9251,7 +9251,7 @@
     </row>
     <row r="173" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B173" s="73"/>
       <c r="C173" s="73"/>
@@ -9279,7 +9279,7 @@
     </row>
     <row r="174" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B174" s="73"/>
       <c r="C174" s="73"/>
@@ -9302,7 +9302,7 @@
     </row>
     <row r="175" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B175" s="73"/>
       <c r="C175" s="73"/>
@@ -9325,7 +9325,7 @@
     </row>
     <row r="176" spans="1:12" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B176" s="73"/>
       <c r="C176" s="73"/>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="177" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B177" s="73"/>
       <c r="C177" s="73"/>
@@ -9371,7 +9371,7 @@
     </row>
     <row r="178" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B178" s="73"/>
       <c r="C178" s="73"/>
@@ -9394,7 +9394,7 @@
     </row>
     <row r="179" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B179" s="73"/>
       <c r="C179" s="73"/>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="180" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B180" s="73"/>
       <c r="C180" s="73"/>
@@ -9440,7 +9440,7 @@
     </row>
     <row r="181" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B181" s="73"/>
       <c r="C181" s="73"/>
@@ -9463,7 +9463,7 @@
     </row>
     <row r="182" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B182" s="73"/>
       <c r="C182" s="73"/>
@@ -9486,7 +9486,7 @@
     </row>
     <row r="183" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B183" s="73"/>
       <c r="C183" s="73"/>
@@ -9509,7 +9509,7 @@
     </row>
     <row r="184" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B184" s="73"/>
       <c r="C184" s="73"/>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="185" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B185" s="73"/>
       <c r="C185" s="73"/>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="186" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B186" s="79"/>
       <c r="C186" s="79"/>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="187" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B187" s="79"/>
       <c r="C187" s="79"/>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="188" spans="1:10" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="94" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B188" s="79"/>
       <c r="C188" s="79"/>
@@ -9614,7 +9614,7 @@
         <f>+G188</f>
         <v>32000</v>
       </c>
-      <c r="I188" s="155">
+      <c r="I188" s="154">
         <f>+G188</f>
         <v>32000</v>
       </c>
@@ -9622,7 +9622,7 @@
     </row>
     <row r="189" spans="1:10" s="11" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
-        <v>129</v>
+        <v>237</v>
       </c>
       <c r="B189" s="90"/>
       <c r="C189" s="90"/>
@@ -9644,7 +9644,7 @@
     </row>
     <row r="190" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="78" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B190" s="111"/>
       <c r="C190" s="112"/>
@@ -9703,7 +9703,7 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B193" s="76"/>
       <c r="C193" s="76"/>
@@ -9723,7 +9723,7 @@
         <v>16640</v>
       </c>
       <c r="K193" s="52" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L193" s="57">
         <v>16640</v>
@@ -9731,7 +9731,7 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B194" s="76"/>
       <c r="C194" s="76"/>
@@ -9751,7 +9751,7 @@
         <v>9600</v>
       </c>
       <c r="K194" s="52" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L194" s="57">
         <v>9600</v>
@@ -9759,7 +9759,7 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B195" s="76"/>
       <c r="C195" s="76"/>
@@ -9782,7 +9782,7 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B196" s="76"/>
       <c r="C196" s="76"/>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B197" s="76"/>
       <c r="C197" s="76"/>
@@ -9832,7 +9832,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B198" s="76"/>
       <c r="C198" s="76"/>
@@ -9854,7 +9854,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B199" s="76"/>
       <c r="C199" s="76"/>
@@ -9876,7 +9876,7 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B200" s="76"/>
       <c r="C200" s="76"/>
@@ -9898,7 +9898,7 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B201" s="76"/>
       <c r="C201" s="76"/>
@@ -9920,7 +9920,7 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B202" s="76"/>
       <c r="C202" s="76"/>
@@ -9942,7 +9942,7 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B203" s="76"/>
       <c r="C203" s="76"/>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B204" s="76"/>
       <c r="C204" s="76"/>
@@ -9986,7 +9986,7 @@
     </row>
     <row r="205" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B205" s="76"/>
       <c r="C205" s="76"/>
@@ -10008,7 +10008,7 @@
     </row>
     <row r="206" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B206" s="76"/>
       <c r="C206" s="76"/>
@@ -10030,7 +10030,7 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="54" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B207" s="76"/>
       <c r="C207" s="76"/>
@@ -10051,7 +10051,7 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B208" s="76"/>
       <c r="C208" s="76"/>
@@ -10073,7 +10073,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B209" s="76"/>
       <c r="C209" s="76"/>
@@ -10095,7 +10095,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B210" s="76"/>
       <c r="C210" s="76"/>
@@ -10117,7 +10117,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B211" s="76"/>
       <c r="C211" s="76"/>
@@ -10139,7 +10139,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B212" s="76"/>
       <c r="C212" s="76"/>
@@ -10205,7 +10205,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B215" s="76"/>
       <c r="C215" s="76"/>
@@ -10227,7 +10227,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B216" s="76"/>
       <c r="C216" s="76"/>
@@ -10249,7 +10249,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B217" s="76"/>
       <c r="C217" s="76"/>
@@ -10271,7 +10271,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B218" s="76"/>
       <c r="C218" s="76"/>
@@ -10293,7 +10293,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B219" s="76"/>
       <c r="C219" s="76"/>
@@ -10315,7 +10315,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B220" s="76"/>
       <c r="C220" s="76"/>
@@ -10337,7 +10337,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B221" s="76"/>
       <c r="C221" s="76"/>
@@ -10381,7 +10381,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B223" s="76"/>
       <c r="C223" s="76"/>
@@ -10403,7 +10403,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B224" s="76"/>
       <c r="C224" s="76"/>
@@ -10424,7 +10424,7 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B225" s="76"/>
       <c r="C225" s="76"/>
@@ -10446,7 +10446,7 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B226" s="76"/>
       <c r="C226" s="76"/>
@@ -10468,7 +10468,7 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B227" s="76"/>
       <c r="C227" s="76"/>
@@ -10490,7 +10490,7 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B228" s="76"/>
       <c r="C228" s="76"/>
@@ -10512,7 +10512,7 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B229" s="76"/>
       <c r="C229" s="76"/>
@@ -10533,7 +10533,7 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B230" s="76"/>
       <c r="C230" s="76"/>
@@ -10554,7 +10554,7 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="54" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B231" s="76"/>
       <c r="C231" s="76"/>
@@ -10575,7 +10575,7 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="54" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B232" s="76"/>
       <c r="C232" s="76"/>
@@ -10596,7 +10596,7 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B233" s="76"/>
       <c r="C233" s="76"/>
@@ -10618,7 +10618,7 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B234" s="76"/>
       <c r="C234" s="76"/>
@@ -10640,7 +10640,7 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B235" s="76"/>
       <c r="C235" s="76"/>
@@ -10660,7 +10660,7 @@
         <v>106880</v>
       </c>
       <c r="K235" s="52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L235" s="57">
         <v>106880</v>
@@ -10668,7 +10668,7 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B236" s="76"/>
       <c r="C236" s="76"/>
@@ -10690,7 +10690,7 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B237" s="76"/>
       <c r="C237" s="76"/>
@@ -10712,7 +10712,7 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B238" s="76"/>
       <c r="C238" s="76"/>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B239" s="76"/>
       <c r="C239" s="76"/>
@@ -10756,7 +10756,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B240" s="76"/>
       <c r="C240" s="76"/>
@@ -10778,7 +10778,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B241" s="76"/>
       <c r="C241" s="76"/>
@@ -10800,7 +10800,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B242" s="76"/>
       <c r="C242" s="76"/>
@@ -10822,7 +10822,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B243" s="76"/>
       <c r="C243" s="76"/>
@@ -10844,7 +10844,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B244" s="76"/>
       <c r="C244" s="76"/>
@@ -10866,7 +10866,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B245" s="76"/>
       <c r="C245" s="76"/>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B246" s="76"/>
       <c r="C246" s="76"/>
@@ -10910,7 +10910,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B247" s="76"/>
       <c r="C247" s="76"/>
@@ -10932,7 +10932,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B248" s="76"/>
       <c r="C248" s="76"/>
@@ -10954,7 +10954,7 @@
     </row>
     <row r="249" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="94" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B249" s="95"/>
       <c r="C249" s="95"/>
@@ -11016,7 +11016,7 @@
     </row>
     <row r="252" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="78" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B252" s="111"/>
       <c r="C252" s="85"/>
@@ -11037,7 +11037,7 @@
     </row>
     <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B253" s="75"/>
       <c r="C253" s="75"/>
@@ -11060,7 +11060,7 @@
     </row>
     <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B254" s="73"/>
       <c r="C254" s="73"/>
@@ -11083,7 +11083,7 @@
     </row>
     <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B255" s="73"/>
       <c r="C255" s="73"/>
@@ -11106,7 +11106,7 @@
     </row>
     <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B256" s="73"/>
       <c r="C256" s="73"/>
@@ -11127,7 +11127,7 @@
     </row>
     <row r="257" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B257" s="90"/>
       <c r="C257" s="90"/>
@@ -11148,7 +11148,7 @@
     </row>
     <row r="258" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="78" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B258" s="111"/>
       <c r="C258" s="85"/>
@@ -11169,7 +11169,7 @@
     </row>
     <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B259" s="75"/>
       <c r="C259" s="75"/>
@@ -11190,7 +11190,7 @@
     </row>
     <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B260" s="73"/>
       <c r="C260" s="73"/>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -2553,7 +2553,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A252" authorId="0" shapeId="0">
+    <comment ref="A253" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2577,7 +2577,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A258" authorId="0" shapeId="0">
+    <comment ref="A259" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2606,7 +2606,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="238">
   <si>
     <t>CONVENIOS</t>
   </si>
@@ -4862,7 +4862,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L260"/>
+  <dimension ref="A1:L261"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
@@ -9693,7 +9693,7 @@
       <c r="F192" s="62"/>
       <c r="G192" s="62"/>
       <c r="H192" s="62">
-        <f t="shared" ref="H192:I232" si="17">+G192</f>
+        <f t="shared" ref="H192:I233" si="17">+G192</f>
         <v>0</v>
       </c>
       <c r="I192" s="80">
@@ -10595,30 +10595,29 @@
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A233" s="8" t="s">
-        <v>187</v>
+      <c r="A233" s="54" t="s">
+        <v>237</v>
       </c>
       <c r="B233" s="76"/>
       <c r="C233" s="76"/>
       <c r="D233" s="76"/>
       <c r="E233" s="76"/>
       <c r="F233" s="76"/>
-      <c r="G233" s="76">
-        <f>+$L$235</f>
-        <v>106880</v>
+      <c r="G233" s="77">
+        <v>75000</v>
       </c>
       <c r="H233" s="76">
-        <f t="shared" ref="H233:I248" si="31">+$L$235</f>
-        <v>106880</v>
+        <f t="shared" si="17"/>
+        <v>75000</v>
       </c>
       <c r="I233" s="81">
-        <f t="shared" si="31"/>
-        <v>106880</v>
+        <f t="shared" si="17"/>
+        <v>75000</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B234" s="76"/>
       <c r="C234" s="76"/>
@@ -10626,11 +10625,11 @@
       <c r="E234" s="76"/>
       <c r="F234" s="76"/>
       <c r="G234" s="76">
-        <f t="shared" ref="G234:I249" si="32">+$L$235</f>
+        <f>+$L$236</f>
         <v>106880</v>
       </c>
       <c r="H234" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="H234:I249" si="31">+$L$236</f>
         <v>106880</v>
       </c>
       <c r="I234" s="81">
@@ -10640,7 +10639,7 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B235" s="76"/>
       <c r="C235" s="76"/>
@@ -10648,7 +10647,7 @@
       <c r="E235" s="76"/>
       <c r="F235" s="76"/>
       <c r="G235" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="G235:I250" si="32">+$L$236</f>
         <v>106880</v>
       </c>
       <c r="H235" s="76">
@@ -10659,16 +10658,10 @@
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
-      <c r="K235" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="L235" s="57">
-        <v>106880</v>
-      </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B236" s="76"/>
       <c r="C236" s="76"/>
@@ -10687,10 +10680,16 @@
         <f t="shared" si="31"/>
         <v>106880</v>
       </c>
+      <c r="K236" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="L236" s="57">
+        <v>106880</v>
+      </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B237" s="76"/>
       <c r="C237" s="76"/>
@@ -10712,7 +10711,7 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B238" s="76"/>
       <c r="C238" s="76"/>
@@ -10734,7 +10733,7 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B239" s="76"/>
       <c r="C239" s="76"/>
@@ -10756,7 +10755,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B240" s="76"/>
       <c r="C240" s="76"/>
@@ -10778,7 +10777,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B241" s="76"/>
       <c r="C241" s="76"/>
@@ -10800,7 +10799,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B242" s="76"/>
       <c r="C242" s="76"/>
@@ -10822,7 +10821,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B243" s="76"/>
       <c r="C243" s="76"/>
@@ -10844,7 +10843,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B244" s="76"/>
       <c r="C244" s="76"/>
@@ -10866,7 +10865,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B245" s="76"/>
       <c r="C245" s="76"/>
@@ -10888,7 +10887,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B246" s="76"/>
       <c r="C246" s="76"/>
@@ -10910,7 +10909,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B247" s="76"/>
       <c r="C247" s="76"/>
@@ -10932,7 +10931,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B248" s="76"/>
       <c r="C248" s="76"/>
@@ -10952,138 +10951,137 @@
         <v>106880</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="94" t="s">
-        <v>202</v>
-      </c>
-      <c r="B249" s="95"/>
-      <c r="C249" s="95"/>
-      <c r="D249" s="95"/>
-      <c r="E249" s="95"/>
-      <c r="F249" s="95"/>
-      <c r="G249" s="95">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B249" s="76"/>
+      <c r="C249" s="76"/>
+      <c r="D249" s="76"/>
+      <c r="E249" s="76"/>
+      <c r="F249" s="76"/>
+      <c r="G249" s="76">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="H249" s="95">
+      <c r="H249" s="76">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+      <c r="I249" s="81">
+        <f t="shared" si="31"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="94" t="s">
+        <v>202</v>
+      </c>
+      <c r="B250" s="95"/>
+      <c r="C250" s="95"/>
+      <c r="D250" s="95"/>
+      <c r="E250" s="95"/>
+      <c r="F250" s="95"/>
+      <c r="G250" s="95">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-      <c r="I249" s="96">
+      <c r="H250" s="95">
         <f t="shared" si="32"/>
         <v>106880</v>
       </c>
-    </row>
-    <row r="250" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="78" t="s">
+      <c r="I250" s="96">
+        <f t="shared" si="32"/>
+        <v>106880</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B250" s="111"/>
-      <c r="C250" s="112"/>
-      <c r="D250" s="112"/>
-      <c r="E250" s="85"/>
-      <c r="F250" s="85"/>
-      <c r="G250" s="85" t="s">
+      <c r="B251" s="111"/>
+      <c r="C251" s="112"/>
+      <c r="D251" s="112"/>
+      <c r="E251" s="85"/>
+      <c r="F251" s="85"/>
+      <c r="G251" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="H250" s="86" t="s">
+      <c r="H251" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="I250" s="86" t="s">
+      <c r="I251" s="86" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="21" t="s">
+    <row r="252" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B251" s="98"/>
-      <c r="C251" s="98"/>
-      <c r="D251" s="98"/>
-      <c r="E251" s="98"/>
-      <c r="F251" s="98"/>
-      <c r="G251" s="97">
+      <c r="B252" s="98"/>
+      <c r="C252" s="98"/>
+      <c r="D252" s="98"/>
+      <c r="E252" s="98"/>
+      <c r="F252" s="98"/>
+      <c r="G252" s="97">
         <v>40000</v>
       </c>
-      <c r="H251" s="98">
-        <f>+G251</f>
+      <c r="H252" s="98">
+        <f>+G252</f>
         <v>40000</v>
       </c>
-      <c r="I251" s="99">
-        <f>+G251</f>
+      <c r="I252" s="99">
+        <f>+G252</f>
         <v>40000</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="78" t="s">
+    <row r="253" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="78" t="s">
         <v>206</v>
       </c>
-      <c r="B252" s="111"/>
-      <c r="C252" s="85"/>
-      <c r="D252" s="85"/>
-      <c r="E252" s="85"/>
-      <c r="F252" s="85" t="s">
+      <c r="B253" s="111"/>
+      <c r="C253" s="85"/>
+      <c r="D253" s="85"/>
+      <c r="E253" s="85"/>
+      <c r="F253" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G252" s="85" t="s">
+      <c r="G253" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="H252" s="85" t="s">
+      <c r="H253" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="I252" s="86" t="s">
+      <c r="I253" s="86" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A253" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="B253" s="75"/>
-      <c r="C253" s="75"/>
-      <c r="D253" s="75"/>
-      <c r="E253" s="75"/>
-      <c r="F253" s="92">
-        <v>15000</v>
-      </c>
-      <c r="G253" s="92">
-        <v>15000</v>
-      </c>
-      <c r="H253" s="75">
-        <f>+$G$253</f>
-        <v>15000</v>
-      </c>
-      <c r="I253" s="93">
-        <f>+$G$253</f>
-        <v>15000</v>
       </c>
     </row>
     <row r="254" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="B254" s="73"/>
-      <c r="C254" s="73"/>
-      <c r="D254" s="73"/>
-      <c r="E254" s="73"/>
-      <c r="F254" s="74">
-        <v>18000</v>
-      </c>
-      <c r="G254" s="74">
+        <v>132</v>
+      </c>
+      <c r="B254" s="75"/>
+      <c r="C254" s="75"/>
+      <c r="D254" s="75"/>
+      <c r="E254" s="75"/>
+      <c r="F254" s="92">
         <v>15000</v>
       </c>
-      <c r="H254" s="73">
-        <f>+G254</f>
+      <c r="G254" s="92">
         <v>15000</v>
       </c>
-      <c r="I254" s="88">
-        <f>+G254</f>
+      <c r="H254" s="75">
+        <f>+$G$254</f>
+        <v>15000</v>
+      </c>
+      <c r="I254" s="93">
+        <f>+$G$254</f>
         <v>15000</v>
       </c>
     </row>
     <row r="255" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B255" s="73"/>
       <c r="C255" s="73"/>
@@ -11106,106 +11104,129 @@
     </row>
     <row r="256" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="22" t="s">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="B256" s="73"/>
       <c r="C256" s="73"/>
       <c r="D256" s="73"/>
       <c r="E256" s="73"/>
-      <c r="F256" s="73"/>
+      <c r="F256" s="74">
+        <v>18000</v>
+      </c>
       <c r="G256" s="74">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="H256" s="73">
         <f>+G256</f>
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="I256" s="88">
         <f>+G256</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A257" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B257" s="73"/>
+      <c r="C257" s="73"/>
+      <c r="D257" s="73"/>
+      <c r="E257" s="73"/>
+      <c r="F257" s="73"/>
+      <c r="G257" s="74">
         <v>20000</v>
       </c>
-    </row>
-    <row r="257" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="B257" s="90"/>
-      <c r="C257" s="90"/>
-      <c r="D257" s="90"/>
-      <c r="E257" s="90"/>
-      <c r="F257" s="90"/>
-      <c r="G257" s="89">
-        <v>20000</v>
-      </c>
-      <c r="H257" s="90">
+      <c r="H257" s="73">
         <f>+G257</f>
         <v>20000</v>
       </c>
-      <c r="I257" s="91">
+      <c r="I257" s="88">
         <f>+G257</f>
         <v>20000</v>
       </c>
     </row>
     <row r="258" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="78" t="s">
+      <c r="A258" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B258" s="90"/>
+      <c r="C258" s="90"/>
+      <c r="D258" s="90"/>
+      <c r="E258" s="90"/>
+      <c r="F258" s="90"/>
+      <c r="G258" s="89">
+        <v>20000</v>
+      </c>
+      <c r="H258" s="90">
+        <f>+G258</f>
+        <v>20000</v>
+      </c>
+      <c r="I258" s="91">
+        <f>+G258</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="78" t="s">
         <v>226</v>
       </c>
-      <c r="B258" s="111"/>
-      <c r="C258" s="85"/>
-      <c r="D258" s="85"/>
-      <c r="E258" s="85"/>
-      <c r="F258" s="85" t="s">
+      <c r="B259" s="111"/>
+      <c r="C259" s="85"/>
+      <c r="D259" s="85"/>
+      <c r="E259" s="85"/>
+      <c r="F259" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G258" s="85" t="s">
+      <c r="G259" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="H258" s="85" t="s">
+      <c r="H259" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="I258" s="86" t="s">
+      <c r="I259" s="86" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A259" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="B259" s="75"/>
-      <c r="C259" s="75"/>
-      <c r="D259" s="75"/>
-      <c r="E259" s="75"/>
-      <c r="F259" s="75"/>
-      <c r="G259" s="92">
-        <v>35000</v>
-      </c>
-      <c r="H259" s="75">
-        <f>+G259</f>
-        <v>35000</v>
-      </c>
-      <c r="I259" s="93">
-        <f>+G259</f>
-        <v>35000</v>
       </c>
     </row>
     <row r="260" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="B260" s="73"/>
-      <c r="C260" s="73"/>
-      <c r="D260" s="73"/>
-      <c r="E260" s="73"/>
-      <c r="F260" s="73"/>
-      <c r="G260" s="74">
+        <v>227</v>
+      </c>
+      <c r="B260" s="75"/>
+      <c r="C260" s="75"/>
+      <c r="D260" s="75"/>
+      <c r="E260" s="75"/>
+      <c r="F260" s="75"/>
+      <c r="G260" s="92">
         <v>35000</v>
       </c>
-      <c r="H260" s="73">
+      <c r="H260" s="75">
         <f>+G260</f>
         <v>35000</v>
       </c>
-      <c r="I260" s="88">
+      <c r="I260" s="93">
         <f>+G260</f>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A261" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="B261" s="73"/>
+      <c r="C261" s="73"/>
+      <c r="D261" s="73"/>
+      <c r="E261" s="73"/>
+      <c r="F261" s="73"/>
+      <c r="G261" s="74">
+        <v>35000</v>
+      </c>
+      <c r="H261" s="73">
+        <f>+G261</f>
+        <v>35000</v>
+      </c>
+      <c r="I261" s="88">
+        <f>+G261</f>
         <v>35000</v>
       </c>
     </row>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -857,7 +857,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="46">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -933,17 +933,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1276,48 +1265,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1445,28 +1392,31 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1475,7 +1425,7 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1484,10 +1434,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1500,6 +1447,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1509,7 +1459,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1518,74 +1468,71 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1596,80 +1543,65 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2372,20 +2304,20 @@
         <v>84</v>
       </c>
       <c r="C19" s="57"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="74">
+      <c r="D19" s="72"/>
+      <c r="E19" s="69">
         <v>17220</v>
       </c>
-      <c r="F19" s="78">
+      <c r="F19" s="70">
         <v>14760</v>
       </c>
-      <c r="G19" s="78">
+      <c r="G19" s="70">
         <v>6300</v>
       </c>
-      <c r="H19" s="78">
+      <c r="H19" s="70">
         <v>6300</v>
       </c>
-      <c r="I19" s="81">
+      <c r="I19" s="71">
         <v>15200</v>
       </c>
     </row>
@@ -2397,12 +2329,22 @@
         <v>84</v>
       </c>
       <c r="C20" s="57"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="82"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="69">
+        <v>17220</v>
+      </c>
+      <c r="F20" s="70">
+        <v>14760</v>
+      </c>
+      <c r="G20" s="70">
+        <v>6300</v>
+      </c>
+      <c r="H20" s="70">
+        <v>6300</v>
+      </c>
+      <c r="I20" s="71">
+        <v>15200</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="44" t="s">
@@ -2412,12 +2354,22 @@
         <v>84</v>
       </c>
       <c r="C21" s="57"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="82"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="69">
+        <v>17220</v>
+      </c>
+      <c r="F21" s="70">
+        <v>14760</v>
+      </c>
+      <c r="G21" s="70">
+        <v>6300</v>
+      </c>
+      <c r="H21" s="70">
+        <v>6300</v>
+      </c>
+      <c r="I21" s="71">
+        <v>15200</v>
+      </c>
     </row>
     <row r="22" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="44" t="s">
@@ -2427,12 +2379,22 @@
         <v>84</v>
       </c>
       <c r="C22" s="57"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="83"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="69">
+        <v>17220</v>
+      </c>
+      <c r="F22" s="70">
+        <v>14760</v>
+      </c>
+      <c r="G22" s="70">
+        <v>6300</v>
+      </c>
+      <c r="H22" s="70">
+        <v>6300</v>
+      </c>
+      <c r="I22" s="71">
+        <v>15200</v>
+      </c>
     </row>
     <row r="23" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="50" t="s">
@@ -3027,23 +2989,23 @@
         <v>72</v>
       </c>
       <c r="C44" s="60"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="21">
+      <c r="D44" s="40"/>
+      <c r="E44" s="27">
         <f t="shared" si="2"/>
         <v>63054.6</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="28">
         <f t="shared" si="0"/>
         <v>54046.799999999996</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="28">
         <v>24977</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="28">
         <f t="shared" si="1"/>
         <v>24977</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="12">
         <v>90078</v>
       </c>
     </row>
@@ -3055,20 +3017,20 @@
         <v>85</v>
       </c>
       <c r="C45" s="56"/>
-      <c r="D45" s="72"/>
-      <c r="E45" s="84">
+      <c r="D45" s="75"/>
+      <c r="E45" s="78">
         <v>8400</v>
       </c>
-      <c r="F45" s="84">
+      <c r="F45" s="78">
         <v>7200</v>
       </c>
-      <c r="G45" s="84">
+      <c r="G45" s="78">
         <v>0</v>
       </c>
-      <c r="H45" s="84">
+      <c r="H45" s="78">
         <v>0</v>
       </c>
-      <c r="I45" s="85">
+      <c r="I45" s="79">
         <v>5300</v>
       </c>
     </row>
@@ -3080,12 +3042,22 @@
         <v>86</v>
       </c>
       <c r="C46" s="57"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="76"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="76"/>
-      <c r="H46" s="76"/>
-      <c r="I46" s="86"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="77">
+        <v>8400</v>
+      </c>
+      <c r="F46" s="77">
+        <v>7200</v>
+      </c>
+      <c r="G46" s="77">
+        <v>0</v>
+      </c>
+      <c r="H46" s="77">
+        <v>0</v>
+      </c>
+      <c r="I46" s="80">
+        <v>5300</v>
+      </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="44" t="s">
@@ -3095,12 +3067,22 @@
         <v>87</v>
       </c>
       <c r="C47" s="57"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="76"/>
-      <c r="I47" s="86"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="77">
+        <v>8400</v>
+      </c>
+      <c r="F47" s="77">
+        <v>7200</v>
+      </c>
+      <c r="G47" s="77">
+        <v>0</v>
+      </c>
+      <c r="H47" s="77">
+        <v>0</v>
+      </c>
+      <c r="I47" s="80">
+        <v>5300</v>
+      </c>
     </row>
     <row r="48" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="45" t="s">
@@ -3110,12 +3092,22 @@
         <v>88</v>
       </c>
       <c r="C48" s="58"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="77"/>
-      <c r="I48" s="87"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="81">
+        <v>8400</v>
+      </c>
+      <c r="F48" s="81">
+        <v>7200</v>
+      </c>
+      <c r="G48" s="81">
+        <v>0</v>
+      </c>
+      <c r="H48" s="81">
+        <v>0</v>
+      </c>
+      <c r="I48" s="82">
+        <v>5300</v>
+      </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="47" t="s">
@@ -3148,17 +3140,17 @@
         <v>89</v>
       </c>
       <c r="C50" s="57"/>
-      <c r="D50" s="69"/>
-      <c r="E50" s="74">
+      <c r="D50" s="72"/>
+      <c r="E50" s="69">
         <v>10500</v>
       </c>
-      <c r="F50" s="74">
+      <c r="F50" s="69">
         <v>9000</v>
       </c>
-      <c r="G50" s="74">
+      <c r="G50" s="69">
         <v>4900</v>
       </c>
-      <c r="H50" s="74">
+      <c r="H50" s="69">
         <v>4900</v>
       </c>
       <c r="I50" s="5"/>
@@ -3171,11 +3163,19 @@
         <v>90</v>
       </c>
       <c r="C51" s="57"/>
-      <c r="D51" s="71"/>
-      <c r="E51" s="75"/>
-      <c r="F51" s="75"/>
-      <c r="G51" s="75"/>
-      <c r="H51" s="75"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="69">
+        <v>10500</v>
+      </c>
+      <c r="F51" s="69">
+        <v>9000</v>
+      </c>
+      <c r="G51" s="69">
+        <v>4900</v>
+      </c>
+      <c r="H51" s="69">
+        <v>4900</v>
+      </c>
       <c r="I51" s="5"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -3186,17 +3186,17 @@
         <v>91</v>
       </c>
       <c r="C52" s="57"/>
-      <c r="D52" s="69"/>
-      <c r="E52" s="74">
+      <c r="D52" s="72"/>
+      <c r="E52" s="69">
         <v>14000</v>
       </c>
-      <c r="F52" s="74">
+      <c r="F52" s="69">
         <v>12000</v>
       </c>
-      <c r="G52" s="78">
+      <c r="G52" s="70">
         <v>3400</v>
       </c>
-      <c r="H52" s="78">
+      <c r="H52" s="70">
         <v>3400</v>
       </c>
       <c r="I52" s="5"/>
@@ -3209,11 +3209,19 @@
         <v>92</v>
       </c>
       <c r="C53" s="57"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="76"/>
-      <c r="F53" s="76"/>
-      <c r="G53" s="79"/>
-      <c r="H53" s="79"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="69">
+        <v>14000</v>
+      </c>
+      <c r="F53" s="69">
+        <v>12000</v>
+      </c>
+      <c r="G53" s="70">
+        <v>3400</v>
+      </c>
+      <c r="H53" s="70">
+        <v>3400</v>
+      </c>
       <c r="I53" s="5"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -3224,11 +3232,19 @@
         <v>93</v>
       </c>
       <c r="C54" s="57"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="76"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="79"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="69">
+        <v>14000</v>
+      </c>
+      <c r="F54" s="69">
+        <v>12000</v>
+      </c>
+      <c r="G54" s="70">
+        <v>3400</v>
+      </c>
+      <c r="H54" s="70">
+        <v>3400</v>
+      </c>
       <c r="I54" s="5"/>
     </row>
     <row r="55" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3239,9 +3255,13 @@
         <v>94</v>
       </c>
       <c r="C55" s="58"/>
-      <c r="D55" s="73"/>
-      <c r="E55" s="77"/>
-      <c r="F55" s="77"/>
+      <c r="D55" s="76"/>
+      <c r="E55" s="69">
+        <v>14000</v>
+      </c>
+      <c r="F55" s="69">
+        <v>12000</v>
+      </c>
       <c r="G55" s="6">
         <v>5700</v>
       </c>
@@ -6459,29 +6479,11 @@
   <sortState ref="B89:B126">
     <sortCondition ref="B89"/>
   </sortState>
-  <mergeCells count="22">
-    <mergeCell ref="F19:F22"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="E45:E48"/>
-    <mergeCell ref="F45:F48"/>
-    <mergeCell ref="G45:G48"/>
-    <mergeCell ref="H45:H48"/>
-    <mergeCell ref="I45:I48"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="E52:E55"/>
-    <mergeCell ref="F52:F55"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="H52:H54"/>
+  <mergeCells count="4">
     <mergeCell ref="D19:D22"/>
     <mergeCell ref="D45:D48"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="D52:D55"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="E19:E22"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="27" orientation="portrait" r:id="rId1"/>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -32,7 +32,7 @@
     <author>Administracion</author>
   </authors>
   <commentList>
-    <comment ref="A23" authorId="0" shapeId="0">
+    <comment ref="A22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A191" authorId="0" shapeId="0">
+    <comment ref="A190" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A196" authorId="0" shapeId="0">
+    <comment ref="A195" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="221">
   <si>
     <t>ENFERMERIA</t>
   </si>
@@ -352,9 +352,6 @@
     <t xml:space="preserve">BONO SOLIDARIO </t>
   </si>
   <si>
-    <t>Valor por sesion</t>
-  </si>
-  <si>
     <t>Valor por consulta</t>
   </si>
   <si>
@@ -752,9 +749,6 @@
   </si>
   <si>
     <t>CONSULTA KINESIOLOGIA</t>
-  </si>
-  <si>
-    <t>CONSULTA FONOAUDIOLOGIA</t>
   </si>
   <si>
     <t>CONSULTA ODONTOLOGICA</t>
@@ -857,7 +851,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1309,19 +1303,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1392,7 +1373,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1543,12 +1524,12 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1560,7 +1541,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1569,21 +1550,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1890,7 +1856,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I198"/>
+  <dimension ref="A1:I197"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.42578125" style="16" customWidth="1"/>
@@ -1906,7 +1872,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D1" s="29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>75</v>
@@ -1918,15 +1884,15 @@
         <v>77</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="43" t="s">
         <v>33</v>
@@ -1937,7 +1903,7 @@
         <v>5550</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G2" s="13">
         <v>4550</v>
@@ -1949,10 +1915,10 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C3" s="58"/>
       <c r="D3" s="31"/>
@@ -1960,7 +1926,7 @@
         <v>5550</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6">
@@ -1971,10 +1937,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="47" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C4" s="59"/>
       <c r="D4" s="30"/>
@@ -1990,10 +1956,10 @@
     </row>
     <row r="5" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="60"/>
       <c r="D5" s="31"/>
@@ -2052,7 +2018,7 @@
         <v>78</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="32"/>
@@ -2073,7 +2039,7 @@
         <v>78</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="32"/>
@@ -2094,7 +2060,7 @@
         <v>78</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="32"/>
@@ -2115,7 +2081,7 @@
         <v>78</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="58"/>
       <c r="D11" s="31"/>
@@ -2135,7 +2101,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B12" s="48" t="s">
         <v>11</v>
@@ -2156,9 +2122,9 @@
       </c>
       <c r="I12" s="14"/>
     </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B13" s="41" t="s">
         <v>12</v>
@@ -2179,76 +2145,84 @@
       </c>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:9" s="17" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="50" t="s">
-        <v>214</v>
-      </c>
-      <c r="B14" s="51" t="s">
+    <row r="14" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="B14" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="6">
+      <c r="C14" s="67"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="24">
+        <v>14000</v>
+      </c>
+      <c r="F14" s="25">
         <v>12000</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" spans="1:9" s="17" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="B15" s="64" t="s">
+      <c r="G14" s="25">
+        <v>5400</v>
+      </c>
+      <c r="H14" s="25">
+        <v>0</v>
+      </c>
+      <c r="I14" s="26">
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="67"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="24">
-        <v>14000</v>
-      </c>
-      <c r="F15" s="25">
-        <v>12000</v>
-      </c>
-      <c r="G15" s="25">
-        <v>5400</v>
-      </c>
-      <c r="H15" s="25">
-        <v>0</v>
-      </c>
-      <c r="I15" s="26">
-        <v>17400</v>
+      <c r="C15" s="59"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="21">
+        <v>159834</v>
+      </c>
+      <c r="F15" s="3">
+        <v>137000</v>
+      </c>
+      <c r="G15" s="3">
+        <v>74000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>74000</v>
+      </c>
+      <c r="I15" s="8">
+        <v>199000</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" s="48" t="s">
+      <c r="A16" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="59"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="21">
-        <v>159834</v>
-      </c>
-      <c r="F16" s="3">
-        <v>137000</v>
-      </c>
-      <c r="G16" s="3">
-        <v>74000</v>
-      </c>
-      <c r="H16" s="3">
-        <v>74000</v>
-      </c>
-      <c r="I16" s="8">
-        <v>199000</v>
+      <c r="C16" s="57"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="15">
+        <v>50400</v>
+      </c>
+      <c r="F16" s="2">
+        <v>43200</v>
+      </c>
+      <c r="G16" s="2">
+        <v>16800</v>
+      </c>
+      <c r="H16" s="2">
+        <v>16800</v>
+      </c>
+      <c r="I16" s="5">
+        <v>43400</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="44" t="s">
-        <v>30</v>
+        <v>208</v>
       </c>
       <c r="B17" s="41" t="s">
         <v>83</v>
@@ -2256,55 +2230,55 @@
       <c r="C17" s="57"/>
       <c r="D17" s="32"/>
       <c r="E17" s="15">
-        <v>50400</v>
+        <v>23100</v>
       </c>
       <c r="F17" s="2">
-        <v>43200</v>
+        <v>19800</v>
       </c>
       <c r="G17" s="2">
-        <v>16800</v>
+        <v>10800</v>
       </c>
       <c r="H17" s="2">
-        <v>16800</v>
+        <v>10800</v>
       </c>
       <c r="I17" s="5">
-        <v>43400</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" s="57"/>
       <c r="D18" s="32"/>
-      <c r="E18" s="15">
-        <v>23100</v>
-      </c>
-      <c r="F18" s="2">
-        <v>19800</v>
-      </c>
-      <c r="G18" s="2">
-        <v>10800</v>
-      </c>
-      <c r="H18" s="2">
-        <v>10800</v>
-      </c>
-      <c r="I18" s="5">
-        <v>20300</v>
+      <c r="E18" s="69">
+        <v>17220</v>
+      </c>
+      <c r="F18" s="70">
+        <v>14760</v>
+      </c>
+      <c r="G18" s="70">
+        <v>6300</v>
+      </c>
+      <c r="H18" s="70">
+        <v>6300</v>
+      </c>
+      <c r="I18" s="71">
+        <v>15200</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
-        <v>27</v>
+        <v>209</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" s="57"/>
-      <c r="D19" s="72"/>
+      <c r="D19" s="32"/>
       <c r="E19" s="69">
         <v>17220</v>
       </c>
@@ -2321,15 +2295,15 @@
         <v>15200</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
         <v>210</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" s="57"/>
-      <c r="D20" s="73"/>
+      <c r="D20" s="32"/>
       <c r="E20" s="69">
         <v>17220</v>
       </c>
@@ -2346,15 +2320,15 @@
         <v>15200</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44" t="s">
         <v>211</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="57"/>
-      <c r="D21" s="73"/>
+      <c r="D21" s="32"/>
       <c r="E21" s="69">
         <v>17220</v>
       </c>
@@ -2371,82 +2345,85 @@
         <v>15200</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="44" t="s">
-        <v>212</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="57"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="69">
-        <v>17220</v>
-      </c>
-      <c r="F22" s="70">
-        <v>14760</v>
-      </c>
-      <c r="G22" s="70">
-        <v>6300</v>
-      </c>
-      <c r="H22" s="70">
-        <v>6300</v>
-      </c>
-      <c r="I22" s="71">
-        <v>15200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="50" t="s">
+    <row r="22" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="23">
+      <c r="B22" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="60"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="23">
         <v>50400</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F22" s="6">
         <v>43200</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G22" s="6">
         <v>16800</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H22" s="6">
         <v>16800</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I22" s="7">
         <v>43400</v>
       </c>
     </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="56"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="21">
+        <f>+I23*0.7</f>
+        <v>62220.2</v>
+      </c>
+      <c r="F23" s="3">
+        <f>+I23*0.6</f>
+        <v>53331.6</v>
+      </c>
+      <c r="G23" s="3">
+        <v>24647</v>
+      </c>
+      <c r="H23" s="3">
+        <f>+G23</f>
+        <v>24647</v>
+      </c>
+      <c r="I23" s="8">
+        <v>88886</v>
+      </c>
+    </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="33"/>
+      <c r="B24" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="57"/>
+      <c r="D24" s="32"/>
       <c r="E24" s="21">
         <f>+I24*0.7</f>
-        <v>62220.2</v>
+        <v>72592.099999999991</v>
       </c>
       <c r="F24" s="3">
-        <f>+I24*0.6</f>
-        <v>53331.6</v>
+        <f t="shared" ref="F24:F43" si="0">+I24*0.6</f>
+        <v>62221.799999999996</v>
       </c>
       <c r="G24" s="3">
-        <v>24647</v>
+        <v>28755</v>
       </c>
       <c r="H24" s="3">
-        <f>+G24</f>
-        <v>24647</v>
-      </c>
-      <c r="I24" s="8">
-        <v>88886</v>
+        <f t="shared" ref="H24:H43" si="1">+G24</f>
+        <v>28755</v>
+      </c>
+      <c r="I24" s="5">
+        <v>103703</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -2454,27 +2431,27 @@
         <v>55</v>
       </c>
       <c r="B25" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C25" s="57"/>
       <c r="D25" s="32"/>
       <c r="E25" s="21">
-        <f>+I25*0.7</f>
-        <v>72592.099999999991</v>
+        <f t="shared" ref="E25:E43" si="2">+I25*0.7</f>
+        <v>122310.29999999999</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" ref="F25:F44" si="0">+I25*0.6</f>
-        <v>62221.799999999996</v>
+        <f t="shared" si="0"/>
+        <v>104837.4</v>
       </c>
       <c r="G25" s="3">
-        <v>28755</v>
+        <v>48449</v>
       </c>
       <c r="H25" s="3">
-        <f t="shared" ref="H25:H44" si="1">+G25</f>
-        <v>28755</v>
+        <f t="shared" si="1"/>
+        <v>48449</v>
       </c>
       <c r="I25" s="5">
-        <v>103703</v>
+        <v>174729</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -2482,27 +2459,27 @@
         <v>55</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" s="57"/>
       <c r="D26" s="32"/>
       <c r="E26" s="21">
-        <f t="shared" ref="E26:E44" si="2">+I26*0.7</f>
-        <v>122310.29999999999</v>
+        <f t="shared" si="2"/>
+        <v>15556.099999999999</v>
       </c>
       <c r="F26" s="3">
         <f t="shared" si="0"/>
-        <v>104837.4</v>
+        <v>13333.8</v>
       </c>
       <c r="G26" s="3">
-        <v>48449</v>
+        <v>6162</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="1"/>
-        <v>48449</v>
+        <v>6162</v>
       </c>
       <c r="I26" s="5">
-        <v>174729</v>
+        <v>22223</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -2510,60 +2487,60 @@
         <v>55</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C27" s="57"/>
       <c r="D27" s="32"/>
       <c r="E27" s="21">
         <f t="shared" si="2"/>
-        <v>15556.099999999999</v>
+        <v>77777</v>
       </c>
       <c r="F27" s="3">
         <f t="shared" si="0"/>
-        <v>13333.8</v>
+        <v>66666</v>
       </c>
       <c r="G27" s="3">
-        <v>6162</v>
+        <v>30809</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="1"/>
-        <v>6162</v>
+        <v>30809</v>
       </c>
       <c r="I27" s="5">
-        <v>22223</v>
+        <v>111110</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="C28" s="57"/>
       <c r="D28" s="32"/>
       <c r="E28" s="21">
         <f t="shared" si="2"/>
-        <v>77777</v>
+        <v>218880.19999999998</v>
       </c>
       <c r="F28" s="3">
         <f t="shared" si="0"/>
-        <v>66666</v>
+        <v>187611.6</v>
       </c>
       <c r="G28" s="3">
-        <v>30809</v>
+        <v>85421</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="1"/>
-        <v>30809</v>
+        <v>85421</v>
       </c>
       <c r="I28" s="5">
-        <v>111110</v>
+        <v>312686</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B29" s="41" t="s">
         <v>114</v>
@@ -2572,26 +2549,26 @@
       <c r="D29" s="32"/>
       <c r="E29" s="21">
         <f t="shared" si="2"/>
-        <v>218880.19999999998</v>
+        <v>244806.09999999998</v>
       </c>
       <c r="F29" s="3">
         <f t="shared" si="0"/>
-        <v>187611.6</v>
+        <v>209833.8</v>
       </c>
       <c r="G29" s="3">
-        <v>85421</v>
+        <v>95539</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="1"/>
-        <v>85421</v>
+        <v>95539</v>
       </c>
       <c r="I29" s="5">
-        <v>312686</v>
+        <v>349723</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B30" s="41" t="s">
         <v>115</v>
@@ -2600,49 +2577,49 @@
       <c r="D30" s="32"/>
       <c r="E30" s="21">
         <f t="shared" si="2"/>
-        <v>244806.09999999998</v>
+        <v>312211.19999999995</v>
       </c>
       <c r="F30" s="3">
         <f t="shared" si="0"/>
-        <v>209833.8</v>
+        <v>267609.59999999998</v>
       </c>
       <c r="G30" s="3">
-        <v>95539</v>
+        <v>121845</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" si="1"/>
-        <v>95539</v>
+        <v>121845</v>
       </c>
       <c r="I30" s="5">
-        <v>349723</v>
+        <v>446016</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44" t="s">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="C31" s="57"/>
       <c r="D31" s="32"/>
       <c r="E31" s="21">
         <f t="shared" si="2"/>
-        <v>312211.19999999995</v>
+        <v>90134.099999999991</v>
       </c>
       <c r="F31" s="3">
         <f t="shared" si="0"/>
-        <v>267609.59999999998</v>
+        <v>77257.8</v>
       </c>
       <c r="G31" s="3">
-        <v>121845</v>
+        <v>35704</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="1"/>
-        <v>121845</v>
+        <v>35704</v>
       </c>
       <c r="I31" s="5">
-        <v>446016</v>
+        <v>128763</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -2650,55 +2627,55 @@
         <v>57</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C32" s="57"/>
       <c r="D32" s="32"/>
       <c r="E32" s="21">
         <f t="shared" si="2"/>
-        <v>90134.099999999991</v>
+        <v>139833.4</v>
       </c>
       <c r="F32" s="3">
         <f t="shared" si="0"/>
-        <v>77257.8</v>
+        <v>119857.2</v>
       </c>
       <c r="G32" s="3">
-        <v>35704</v>
+        <v>55391</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" si="1"/>
-        <v>35704</v>
+        <v>55391</v>
       </c>
       <c r="I32" s="5">
-        <v>128763</v>
+        <v>199762</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C33" s="57"/>
       <c r="D33" s="32"/>
       <c r="E33" s="21">
         <f t="shared" si="2"/>
-        <v>139833.4</v>
+        <v>334390.69999999995</v>
       </c>
       <c r="F33" s="3">
         <f t="shared" si="0"/>
-        <v>119857.2</v>
+        <v>286620.59999999998</v>
       </c>
       <c r="G33" s="3">
-        <v>55391</v>
+        <v>132458</v>
       </c>
       <c r="H33" s="3">
         <f t="shared" si="1"/>
-        <v>55391</v>
+        <v>132458</v>
       </c>
       <c r="I33" s="5">
-        <v>199762</v>
+        <v>477701</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -2706,27 +2683,27 @@
         <v>60</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C34" s="57"/>
       <c r="D34" s="32"/>
       <c r="E34" s="21">
         <f t="shared" si="2"/>
-        <v>334390.69999999995</v>
+        <v>165561.19999999998</v>
       </c>
       <c r="F34" s="3">
         <f t="shared" si="0"/>
-        <v>286620.59999999998</v>
+        <v>141909.6</v>
       </c>
       <c r="G34" s="3">
-        <v>132458</v>
+        <v>65582</v>
       </c>
       <c r="H34" s="3">
         <f t="shared" si="1"/>
-        <v>132458</v>
+        <v>65582</v>
       </c>
       <c r="I34" s="5">
-        <v>477701</v>
+        <v>236516</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2734,27 +2711,27 @@
         <v>60</v>
       </c>
       <c r="B35" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C35" s="57"/>
       <c r="D35" s="32"/>
       <c r="E35" s="21">
         <f t="shared" si="2"/>
-        <v>165561.19999999998</v>
+        <v>192411.09999999998</v>
       </c>
       <c r="F35" s="3">
         <f t="shared" si="0"/>
-        <v>141909.6</v>
+        <v>164923.79999999999</v>
       </c>
       <c r="G35" s="3">
-        <v>65582</v>
+        <v>76217</v>
       </c>
       <c r="H35" s="3">
         <f t="shared" si="1"/>
-        <v>65582</v>
+        <v>76217</v>
       </c>
       <c r="I35" s="5">
-        <v>236516</v>
+        <v>274873</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2762,55 +2739,55 @@
         <v>60</v>
       </c>
       <c r="B36" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C36" s="57"/>
       <c r="D36" s="32"/>
       <c r="E36" s="21">
         <f t="shared" si="2"/>
-        <v>192411.09999999998</v>
+        <v>219242.09999999998</v>
       </c>
       <c r="F36" s="3">
         <f t="shared" si="0"/>
-        <v>164923.79999999999</v>
+        <v>187921.8</v>
       </c>
       <c r="G36" s="3">
-        <v>76217</v>
+        <v>86846</v>
       </c>
       <c r="H36" s="3">
         <f t="shared" si="1"/>
-        <v>76217</v>
+        <v>86846</v>
       </c>
       <c r="I36" s="5">
-        <v>274873</v>
+        <v>313203</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="44" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B37" s="41" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C37" s="57"/>
       <c r="D37" s="32"/>
       <c r="E37" s="21">
         <f t="shared" si="2"/>
-        <v>219242.09999999998</v>
+        <v>97786.5</v>
       </c>
       <c r="F37" s="3">
         <f t="shared" si="0"/>
-        <v>187921.8</v>
+        <v>83817</v>
       </c>
       <c r="G37" s="3">
-        <v>86846</v>
+        <v>38735</v>
       </c>
       <c r="H37" s="3">
         <f t="shared" si="1"/>
-        <v>86846</v>
+        <v>38735</v>
       </c>
       <c r="I37" s="5">
-        <v>313203</v>
+        <v>139695</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2818,27 +2795,27 @@
         <v>65</v>
       </c>
       <c r="B38" s="41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C38" s="57"/>
       <c r="D38" s="32"/>
       <c r="E38" s="21">
         <f t="shared" si="2"/>
-        <v>97786.5</v>
+        <v>107361.09999999999</v>
       </c>
       <c r="F38" s="3">
         <f t="shared" si="0"/>
-        <v>83817</v>
+        <v>92023.8</v>
       </c>
       <c r="G38" s="3">
-        <v>38735</v>
+        <v>42528</v>
       </c>
       <c r="H38" s="3">
         <f t="shared" si="1"/>
-        <v>38735</v>
+        <v>42528</v>
       </c>
       <c r="I38" s="5">
-        <v>139695</v>
+        <v>153373</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2846,27 +2823,27 @@
         <v>65</v>
       </c>
       <c r="B39" s="41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C39" s="57"/>
       <c r="D39" s="32"/>
       <c r="E39" s="21">
         <f t="shared" si="2"/>
-        <v>107361.09999999999</v>
+        <v>128830.79999999999</v>
       </c>
       <c r="F39" s="3">
         <f t="shared" si="0"/>
-        <v>92023.8</v>
+        <v>110426.4</v>
       </c>
       <c r="G39" s="3">
-        <v>42528</v>
+        <v>51032</v>
       </c>
       <c r="H39" s="3">
         <f t="shared" si="1"/>
-        <v>42528</v>
+        <v>51032</v>
       </c>
       <c r="I39" s="5">
-        <v>153373</v>
+        <v>184044</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2874,55 +2851,55 @@
         <v>65</v>
       </c>
       <c r="B40" s="41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C40" s="57"/>
       <c r="D40" s="32"/>
       <c r="E40" s="21">
         <f t="shared" si="2"/>
-        <v>128830.79999999999</v>
+        <v>34354.6</v>
       </c>
       <c r="F40" s="3">
         <f t="shared" si="0"/>
-        <v>110426.4</v>
+        <v>29446.799999999999</v>
       </c>
       <c r="G40" s="3">
-        <v>51032</v>
+        <v>13608</v>
       </c>
       <c r="H40" s="3">
         <f t="shared" si="1"/>
-        <v>51032</v>
+        <v>13608</v>
       </c>
       <c r="I40" s="5">
-        <v>184044</v>
+        <v>49078</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="44" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B41" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C41" s="57"/>
       <c r="D41" s="32"/>
       <c r="E41" s="21">
         <f t="shared" si="2"/>
-        <v>34354.6</v>
+        <v>463303.39999999997</v>
       </c>
       <c r="F41" s="3">
         <f t="shared" si="0"/>
-        <v>29446.799999999999</v>
+        <v>397117.2</v>
       </c>
       <c r="G41" s="3">
-        <v>13608</v>
+        <v>183523</v>
       </c>
       <c r="H41" s="3">
         <f t="shared" si="1"/>
-        <v>13608</v>
+        <v>183523</v>
       </c>
       <c r="I41" s="5">
-        <v>49078</v>
+        <v>661862</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2930,107 +2907,104 @@
         <v>73</v>
       </c>
       <c r="B42" s="41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C42" s="57"/>
       <c r="D42" s="32"/>
       <c r="E42" s="21">
         <f t="shared" si="2"/>
-        <v>463303.39999999997</v>
+        <v>484789.19999999995</v>
       </c>
       <c r="F42" s="3">
         <f t="shared" si="0"/>
-        <v>397117.2</v>
+        <v>415533.6</v>
       </c>
       <c r="G42" s="3">
-        <v>183523</v>
+        <v>192034</v>
       </c>
       <c r="H42" s="3">
         <f t="shared" si="1"/>
-        <v>183523</v>
+        <v>192034</v>
       </c>
       <c r="I42" s="5">
-        <v>661862</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="44" t="s">
+        <v>692556</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="B43" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="C43" s="57"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="21">
-        <f t="shared" si="2"/>
-        <v>484789.19999999995</v>
-      </c>
-      <c r="F43" s="3">
-        <f t="shared" si="0"/>
-        <v>415533.6</v>
-      </c>
-      <c r="G43" s="3">
-        <v>192034</v>
-      </c>
-      <c r="H43" s="3">
-        <f t="shared" si="1"/>
-        <v>192034</v>
-      </c>
-      <c r="I43" s="5">
-        <v>692556</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="51" t="s">
+      <c r="B43" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="60"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="27">
+      <c r="C43" s="60"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="27">
         <f t="shared" si="2"/>
         <v>63054.6</v>
       </c>
-      <c r="F44" s="28">
+      <c r="F43" s="28">
         <f t="shared" si="0"/>
         <v>54046.799999999996</v>
       </c>
-      <c r="G44" s="28">
+      <c r="G43" s="28">
         <v>24977</v>
       </c>
-      <c r="H44" s="28">
+      <c r="H43" s="28">
         <f t="shared" si="1"/>
         <v>24977</v>
       </c>
-      <c r="I44" s="12">
+      <c r="I43" s="12">
         <v>90078</v>
       </c>
     </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="56"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="73">
+        <v>8400</v>
+      </c>
+      <c r="F44" s="73">
+        <v>7200</v>
+      </c>
+      <c r="G44" s="73">
+        <v>0</v>
+      </c>
+      <c r="H44" s="73">
+        <v>0</v>
+      </c>
+      <c r="I44" s="74">
+        <v>5300</v>
+      </c>
+    </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B45" s="43" t="s">
+      <c r="B45" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C45" s="56"/>
-      <c r="D45" s="75"/>
-      <c r="E45" s="78">
+      <c r="C45" s="57"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="72">
         <v>8400</v>
       </c>
-      <c r="F45" s="78">
+      <c r="F45" s="72">
         <v>7200</v>
       </c>
-      <c r="G45" s="78">
+      <c r="G45" s="72">
         <v>0</v>
       </c>
-      <c r="H45" s="78">
+      <c r="H45" s="72">
         <v>0</v>
       </c>
-      <c r="I45" s="79">
+      <c r="I45" s="75">
         <v>5300</v>
       </c>
     </row>
@@ -3042,95 +3016,93 @@
         <v>86</v>
       </c>
       <c r="C46" s="57"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="77">
+      <c r="D46" s="32"/>
+      <c r="E46" s="72">
         <v>8400</v>
       </c>
-      <c r="F46" s="77">
+      <c r="F46" s="72">
         <v>7200</v>
       </c>
-      <c r="G46" s="77">
+      <c r="G46" s="72">
         <v>0</v>
       </c>
-      <c r="H46" s="77">
+      <c r="H46" s="72">
         <v>0</v>
       </c>
-      <c r="I46" s="80">
+      <c r="I46" s="75">
         <v>5300</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="44" t="s">
+    <row r="47" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B47" s="41" t="s">
+      <c r="B47" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="57"/>
-      <c r="D47" s="73"/>
-      <c r="E47" s="77">
+      <c r="C47" s="58"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="76">
         <v>8400</v>
       </c>
-      <c r="F47" s="77">
+      <c r="F47" s="76">
         <v>7200</v>
       </c>
-      <c r="G47" s="77">
+      <c r="G47" s="76">
         <v>0</v>
       </c>
-      <c r="H47" s="77">
+      <c r="H47" s="76">
         <v>0</v>
       </c>
-      <c r="I47" s="80">
+      <c r="I47" s="77">
         <v>5300</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="46" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="C48" s="59"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="21">
+        <v>14000</v>
+      </c>
+      <c r="F48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G48" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H48" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I48" s="8"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="C48" s="58"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="81">
-        <v>8400</v>
-      </c>
-      <c r="F48" s="81">
-        <v>7200</v>
-      </c>
-      <c r="G48" s="81">
-        <v>0</v>
-      </c>
-      <c r="H48" s="81">
-        <v>0</v>
-      </c>
-      <c r="I48" s="82">
-        <v>5300</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B49" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="C49" s="59"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="21">
-        <v>14000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>12000</v>
-      </c>
-      <c r="G49" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H49" s="3">
-        <v>4100</v>
-      </c>
-      <c r="I49" s="8"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="69">
+        <v>10500</v>
+      </c>
+      <c r="F49" s="69">
+        <v>9000</v>
+      </c>
+      <c r="G49" s="69">
+        <v>4900</v>
+      </c>
+      <c r="H49" s="69">
+        <v>4900</v>
+      </c>
+      <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="44" t="s">
@@ -3140,7 +3112,7 @@
         <v>89</v>
       </c>
       <c r="C50" s="57"/>
-      <c r="D50" s="72"/>
+      <c r="D50" s="32"/>
       <c r="E50" s="69">
         <v>10500</v>
       </c>
@@ -3163,18 +3135,18 @@
         <v>90</v>
       </c>
       <c r="C51" s="57"/>
-      <c r="D51" s="74"/>
+      <c r="D51" s="32"/>
       <c r="E51" s="69">
-        <v>10500</v>
+        <v>14000</v>
       </c>
       <c r="F51" s="69">
-        <v>9000</v>
-      </c>
-      <c r="G51" s="69">
-        <v>4900</v>
-      </c>
-      <c r="H51" s="69">
-        <v>4900</v>
+        <v>12000</v>
+      </c>
+      <c r="G51" s="70">
+        <v>3400</v>
+      </c>
+      <c r="H51" s="70">
+        <v>3400</v>
       </c>
       <c r="I51" s="5"/>
     </row>
@@ -3186,7 +3158,7 @@
         <v>91</v>
       </c>
       <c r="C52" s="57"/>
-      <c r="D52" s="72"/>
+      <c r="D52" s="32"/>
       <c r="E52" s="69">
         <v>14000</v>
       </c>
@@ -3209,7 +3181,7 @@
         <v>92</v>
       </c>
       <c r="C53" s="57"/>
-      <c r="D53" s="73"/>
+      <c r="D53" s="32"/>
       <c r="E53" s="69">
         <v>14000</v>
       </c>
@@ -3224,266 +3196,271 @@
       </c>
       <c r="I53" s="5"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="44" t="s">
+    <row r="54" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B54" s="41" t="s">
+      <c r="B54" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="C54" s="57"/>
-      <c r="D54" s="73"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="32"/>
       <c r="E54" s="69">
         <v>14000</v>
       </c>
       <c r="F54" s="69">
         <v>12000</v>
       </c>
-      <c r="G54" s="70">
-        <v>3400</v>
-      </c>
-      <c r="H54" s="70">
-        <v>3400</v>
-      </c>
-      <c r="I54" s="5"/>
+      <c r="G54" s="6">
+        <v>5700</v>
+      </c>
+      <c r="H54" s="6">
+        <v>5700</v>
+      </c>
+      <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="B55" s="46" t="s">
+      <c r="A55" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="C55" s="58"/>
-      <c r="D55" s="76"/>
-      <c r="E55" s="69">
+      <c r="C55" s="68"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="24">
+        <v>9000</v>
+      </c>
+      <c r="F55" s="25">
+        <v>7500</v>
+      </c>
+      <c r="G55" s="25">
+        <v>2700</v>
+      </c>
+      <c r="H55" s="25">
+        <v>0</v>
+      </c>
+      <c r="I55" s="26"/>
+    </row>
+    <row r="56" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="63" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="67"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="27">
+        <v>8400</v>
+      </c>
+      <c r="F56" s="28">
+        <v>7200</v>
+      </c>
+      <c r="G56" s="28">
+        <v>3900</v>
+      </c>
+      <c r="H56" s="28">
+        <v>2700</v>
+      </c>
+      <c r="I56" s="36"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="59"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="22">
         <v>14000</v>
       </c>
-      <c r="F55" s="69">
+      <c r="F57" s="13">
         <v>12000</v>
       </c>
-      <c r="G55" s="6">
-        <v>5700</v>
-      </c>
-      <c r="H55" s="6">
-        <v>5700</v>
-      </c>
-      <c r="I55" s="7"/>
-    </row>
-    <row r="56" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="B56" s="65" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" s="68"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="24">
-        <v>9000</v>
-      </c>
-      <c r="F56" s="25">
-        <v>7500</v>
-      </c>
-      <c r="G56" s="25">
-        <v>2700</v>
-      </c>
-      <c r="H56" s="25">
-        <v>0</v>
-      </c>
-      <c r="I56" s="26"/>
-    </row>
-    <row r="57" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="B57" s="64" t="s">
+      <c r="G57" s="13">
+        <v>5500</v>
+      </c>
+      <c r="H57" s="13">
+        <v>5500</v>
+      </c>
+      <c r="I57" s="14"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="C57" s="67"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="27">
+      <c r="B58" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="57"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="15">
+        <v>21000</v>
+      </c>
+      <c r="F58" s="2">
+        <v>18000</v>
+      </c>
+      <c r="G58" s="2">
         <v>8400</v>
       </c>
-      <c r="F57" s="28">
-        <v>7200</v>
-      </c>
-      <c r="G57" s="28">
-        <v>3900</v>
-      </c>
-      <c r="H57" s="28">
-        <v>2700</v>
-      </c>
-      <c r="I57" s="36"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="B58" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="59"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="22">
-        <v>14000</v>
-      </c>
-      <c r="F58" s="13">
-        <v>12000</v>
-      </c>
-      <c r="G58" s="13">
-        <v>5500</v>
-      </c>
-      <c r="H58" s="13">
-        <v>5500</v>
-      </c>
-      <c r="I58" s="14"/>
+      <c r="H58" s="2">
+        <v>8400</v>
+      </c>
+      <c r="I58" s="5"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B59" s="41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C59" s="57"/>
       <c r="D59" s="32"/>
       <c r="E59" s="15">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="F59" s="2">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="G59" s="2">
-        <v>8400</v>
+        <v>5000</v>
       </c>
       <c r="H59" s="2">
-        <v>8400</v>
+        <v>5000</v>
       </c>
       <c r="I59" s="5"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B60" s="41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C60" s="57"/>
       <c r="D60" s="32"/>
       <c r="E60" s="15">
-        <v>14000</v>
+        <v>21000</v>
       </c>
       <c r="F60" s="2">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="G60" s="2">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="H60" s="2">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="I60" s="5"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="44" t="s">
+    <row r="61" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B61" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="60"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="23">
+        <v>21000</v>
+      </c>
+      <c r="F61" s="6">
+        <v>18000</v>
+      </c>
+      <c r="G61" s="6">
+        <v>7900</v>
+      </c>
+      <c r="H61" s="6">
+        <v>7900</v>
+      </c>
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="B61" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" s="57"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="15">
-        <v>21000</v>
-      </c>
-      <c r="F61" s="2">
-        <v>18000</v>
-      </c>
-      <c r="G61" s="2">
-        <v>5200</v>
-      </c>
-      <c r="H61" s="2">
-        <v>5200</v>
-      </c>
-      <c r="I61" s="5"/>
-    </row>
-    <row r="62" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B62" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="60"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="23">
-        <v>21000</v>
-      </c>
-      <c r="F62" s="6">
-        <v>18000</v>
-      </c>
-      <c r="G62" s="6">
-        <v>7900</v>
-      </c>
-      <c r="H62" s="6">
-        <v>7900</v>
-      </c>
-      <c r="I62" s="7"/>
+      <c r="D62" s="30">
+        <v>111000</v>
+      </c>
+      <c r="E62" s="22">
+        <v>77700</v>
+      </c>
+      <c r="F62" s="13">
+        <v>66600</v>
+      </c>
+      <c r="G62" s="13">
+        <v>46700</v>
+      </c>
+      <c r="H62" s="13">
+        <f t="shared" ref="H62:H69" si="3">+G62</f>
+        <v>46700</v>
+      </c>
+      <c r="I62" s="14"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="42" t="s">
+      <c r="A63" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B63" s="43" t="s">
+      <c r="B63" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="56" t="s">
-        <v>99</v>
-      </c>
-      <c r="D63" s="30">
-        <v>111000</v>
-      </c>
-      <c r="E63" s="22">
-        <v>77700</v>
-      </c>
-      <c r="F63" s="13">
-        <v>66600</v>
-      </c>
-      <c r="G63" s="13">
-        <v>46700</v>
-      </c>
-      <c r="H63" s="13">
-        <f t="shared" ref="H63:H70" si="3">+G63</f>
-        <v>46700</v>
-      </c>
-      <c r="I63" s="14"/>
+      <c r="C63" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="D63" s="32">
+        <v>51000</v>
+      </c>
+      <c r="E63" s="15">
+        <v>35700</v>
+      </c>
+      <c r="F63" s="2">
+        <v>30600</v>
+      </c>
+      <c r="G63" s="2">
+        <v>21300</v>
+      </c>
+      <c r="H63" s="2">
+        <f t="shared" si="3"/>
+        <v>21300</v>
+      </c>
+      <c r="I63" s="5"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="44" t="s">
         <v>5</v>
       </c>
       <c r="B64" s="41" t="s">
-        <v>6</v>
+        <v>201</v>
       </c>
       <c r="C64" s="57" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D64" s="32">
-        <v>51000</v>
+        <v>241000</v>
       </c>
       <c r="E64" s="15">
-        <v>35700</v>
+        <v>168700</v>
       </c>
       <c r="F64" s="2">
-        <v>30600</v>
+        <v>144600</v>
       </c>
       <c r="G64" s="2">
-        <v>21300</v>
+        <v>76000</v>
       </c>
       <c r="H64" s="2">
         <f t="shared" si="3"/>
-        <v>21300</v>
+        <v>76000</v>
       </c>
       <c r="I64" s="5"/>
     </row>
@@ -3492,26 +3469,26 @@
         <v>5</v>
       </c>
       <c r="B65" s="41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C65" s="57" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D65" s="32">
-        <v>241000</v>
+        <v>68000</v>
       </c>
       <c r="E65" s="15">
-        <v>168700</v>
+        <v>47600</v>
       </c>
       <c r="F65" s="2">
-        <v>144600</v>
+        <v>40800</v>
       </c>
       <c r="G65" s="2">
-        <v>76000</v>
+        <v>48000</v>
       </c>
       <c r="H65" s="2">
         <f t="shared" si="3"/>
-        <v>76000</v>
+        <v>48000</v>
       </c>
       <c r="I65" s="5"/>
     </row>
@@ -3520,26 +3497,26 @@
         <v>5</v>
       </c>
       <c r="B66" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C66" s="57" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D66" s="32">
-        <v>68000</v>
+        <v>551000</v>
       </c>
       <c r="E66" s="15">
-        <v>47600</v>
+        <v>385700</v>
       </c>
       <c r="F66" s="2">
-        <v>40800</v>
+        <v>330600</v>
       </c>
       <c r="G66" s="2">
-        <v>48000</v>
+        <v>209000</v>
       </c>
       <c r="H66" s="2">
         <f t="shared" si="3"/>
-        <v>48000</v>
+        <v>209000</v>
       </c>
       <c r="I66" s="5"/>
     </row>
@@ -3548,26 +3525,26 @@
         <v>5</v>
       </c>
       <c r="B67" s="41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C67" s="57" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="D67" s="32">
-        <v>551000</v>
+        <v>132000</v>
       </c>
       <c r="E67" s="15">
-        <v>385700</v>
+        <v>92400</v>
       </c>
       <c r="F67" s="2">
-        <v>330600</v>
+        <v>79200</v>
       </c>
       <c r="G67" s="2">
-        <v>209000</v>
+        <v>75000</v>
       </c>
       <c r="H67" s="2">
         <f t="shared" si="3"/>
-        <v>209000</v>
+        <v>75000</v>
       </c>
       <c r="I67" s="5"/>
     </row>
@@ -3576,279 +3553,277 @@
         <v>5</v>
       </c>
       <c r="B68" s="41" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C68" s="57" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="D68" s="32">
-        <v>132000</v>
+        <v>962000</v>
       </c>
       <c r="E68" s="15">
-        <v>92400</v>
+        <v>673400</v>
       </c>
       <c r="F68" s="2">
-        <v>79200</v>
+        <v>577200</v>
       </c>
       <c r="G68" s="2">
-        <v>75000</v>
+        <v>464000</v>
       </c>
       <c r="H68" s="2">
         <f t="shared" si="3"/>
-        <v>75000</v>
+        <v>464000</v>
       </c>
       <c r="I68" s="5"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="44" t="s">
+    <row r="69" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B69" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="C69" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="D69" s="32">
-        <v>962000</v>
-      </c>
-      <c r="E69" s="15">
-        <v>673400</v>
-      </c>
-      <c r="F69" s="2">
-        <v>577200</v>
-      </c>
-      <c r="G69" s="2">
-        <v>464000</v>
-      </c>
-      <c r="H69" s="2">
-        <f t="shared" si="3"/>
-        <v>464000</v>
-      </c>
-      <c r="I69" s="5"/>
-    </row>
-    <row r="70" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B70" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="C70" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="D70" s="31">
+      <c r="B69" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="C69" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="D69" s="31">
         <v>203000</v>
       </c>
-      <c r="E70" s="23">
+      <c r="E69" s="23">
         <v>142100</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F69" s="6">
         <v>121800</v>
       </c>
-      <c r="G70" s="6">
+      <c r="G69" s="6">
         <v>139000</v>
       </c>
-      <c r="H70" s="6">
+      <c r="H69" s="6">
         <f t="shared" si="3"/>
         <v>139000</v>
       </c>
-      <c r="I70" s="7"/>
+      <c r="I69" s="7"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="59"/>
+      <c r="D70" s="30">
+        <v>176000</v>
+      </c>
+      <c r="E70" s="22">
+        <f>+D70</f>
+        <v>176000</v>
+      </c>
+      <c r="F70" s="13">
+        <f>+D70</f>
+        <v>176000</v>
+      </c>
+      <c r="G70" s="13">
+        <f>+D70</f>
+        <v>176000</v>
+      </c>
+      <c r="H70" s="13">
+        <f>+D70</f>
+        <v>176000</v>
+      </c>
+      <c r="I70" s="14"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="47" t="s">
+      <c r="A71" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B71" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="C71" s="59"/>
-      <c r="D71" s="30">
-        <v>176000</v>
-      </c>
-      <c r="E71" s="22">
+      <c r="B71" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" s="57"/>
+      <c r="D71" s="32">
+        <v>233000</v>
+      </c>
+      <c r="E71" s="15">
         <f>+D71</f>
-        <v>176000</v>
-      </c>
-      <c r="F71" s="13">
+        <v>233000</v>
+      </c>
+      <c r="F71" s="2">
         <f>+D71</f>
-        <v>176000</v>
-      </c>
-      <c r="G71" s="13">
+        <v>233000</v>
+      </c>
+      <c r="G71" s="2">
         <f>+D71</f>
-        <v>176000</v>
-      </c>
-      <c r="H71" s="13">
+        <v>233000</v>
+      </c>
+      <c r="H71" s="2">
         <f>+D71</f>
-        <v>176000</v>
-      </c>
-      <c r="I71" s="14"/>
+        <v>233000</v>
+      </c>
+      <c r="I71" s="5"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B72" s="41" t="s">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="C72" s="57"/>
       <c r="D72" s="32">
-        <v>233000</v>
+        <v>41000</v>
       </c>
       <c r="E72" s="15">
         <f>+D72</f>
-        <v>233000</v>
+        <v>41000</v>
       </c>
       <c r="F72" s="2">
         <f>+D72</f>
-        <v>233000</v>
+        <v>41000</v>
       </c>
       <c r="G72" s="2">
         <f>+D72</f>
-        <v>233000</v>
+        <v>41000</v>
       </c>
       <c r="H72" s="2">
         <f>+D72</f>
-        <v>233000</v>
+        <v>41000</v>
       </c>
       <c r="I72" s="5"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="44" t="s">
+    <row r="73" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B73" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C73" s="57"/>
-      <c r="D73" s="32">
-        <v>41000</v>
-      </c>
-      <c r="E73" s="15">
+      <c r="B73" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="60"/>
+      <c r="D73" s="31">
+        <v>7700</v>
+      </c>
+      <c r="E73" s="23">
         <f>+D73</f>
-        <v>41000</v>
-      </c>
-      <c r="F73" s="2">
+        <v>7700</v>
+      </c>
+      <c r="F73" s="6">
         <f>+D73</f>
-        <v>41000</v>
-      </c>
-      <c r="G73" s="2">
+        <v>7700</v>
+      </c>
+      <c r="G73" s="6">
         <f>+D73</f>
-        <v>41000</v>
-      </c>
-      <c r="H73" s="2">
+        <v>7700</v>
+      </c>
+      <c r="H73" s="6">
         <f>+D73</f>
-        <v>41000</v>
-      </c>
-      <c r="I73" s="5"/>
+        <v>7700</v>
+      </c>
+      <c r="I73" s="7"/>
     </row>
     <row r="74" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="50" t="s">
-        <v>7</v>
-      </c>
-      <c r="B74" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="60"/>
-      <c r="D74" s="31">
-        <v>7700</v>
-      </c>
-      <c r="E74" s="23">
+      <c r="A74" s="63" t="s">
+        <v>122</v>
+      </c>
+      <c r="B74" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="67"/>
+      <c r="D74" s="34">
+        <v>64600</v>
+      </c>
+      <c r="E74" s="24">
         <f>+D74</f>
-        <v>7700</v>
-      </c>
-      <c r="F74" s="6">
+        <v>64600</v>
+      </c>
+      <c r="F74" s="25">
         <f>+D74</f>
-        <v>7700</v>
-      </c>
-      <c r="G74" s="6">
+        <v>64600</v>
+      </c>
+      <c r="G74" s="25">
         <f>+D74</f>
-        <v>7700</v>
-      </c>
-      <c r="H74" s="6">
+        <v>64600</v>
+      </c>
+      <c r="H74" s="25">
         <f>+D74</f>
-        <v>7700</v>
-      </c>
-      <c r="I74" s="7"/>
-    </row>
-    <row r="75" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="63" t="s">
-        <v>123</v>
-      </c>
-      <c r="B75" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="C75" s="67"/>
-      <c r="D75" s="34">
         <v>64600</v>
       </c>
-      <c r="E75" s="24">
-        <f>+D75</f>
-        <v>64600</v>
-      </c>
-      <c r="F75" s="25">
-        <f>+D75</f>
-        <v>64600</v>
-      </c>
-      <c r="G75" s="25">
-        <f>+D75</f>
-        <v>64600</v>
-      </c>
-      <c r="H75" s="25">
-        <f>+D75</f>
-        <v>64600</v>
-      </c>
-      <c r="I75" s="26"/>
+      <c r="I74" s="26"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B75" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="C75" s="59"/>
+      <c r="D75" s="30">
+        <v>97000</v>
+      </c>
+      <c r="E75" s="22">
+        <v>67900</v>
+      </c>
+      <c r="F75" s="13">
+        <v>58200</v>
+      </c>
+      <c r="G75" s="13">
+        <v>23500</v>
+      </c>
+      <c r="H75" s="13">
+        <f t="shared" ref="H75:H84" si="4">+G75</f>
+        <v>23500</v>
+      </c>
+      <c r="I75" s="14"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="47" t="s">
+      <c r="A76" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B76" s="48" t="s">
-        <v>200</v>
-      </c>
-      <c r="C76" s="59"/>
-      <c r="D76" s="30">
-        <v>97000</v>
-      </c>
-      <c r="E76" s="22">
-        <v>67900</v>
-      </c>
-      <c r="F76" s="13">
-        <v>58200</v>
-      </c>
-      <c r="G76" s="13">
-        <v>23500</v>
-      </c>
-      <c r="H76" s="13">
-        <f t="shared" ref="H76:H85" si="4">+G76</f>
-        <v>23500</v>
-      </c>
-      <c r="I76" s="14"/>
+      <c r="B76" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C76" s="57"/>
+      <c r="D76" s="32">
+        <v>282000</v>
+      </c>
+      <c r="E76" s="15">
+        <v>197400</v>
+      </c>
+      <c r="F76" s="2">
+        <v>169200</v>
+      </c>
+      <c r="G76" s="2">
+        <v>72000</v>
+      </c>
+      <c r="H76" s="2">
+        <f t="shared" si="4"/>
+        <v>72000</v>
+      </c>
+      <c r="I76" s="5"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="44" t="s">
         <v>20</v>
       </c>
       <c r="B77" s="41" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C77" s="57"/>
       <c r="D77" s="32">
-        <v>282000</v>
+        <v>256000</v>
       </c>
       <c r="E77" s="15">
-        <v>197400</v>
+        <v>179200</v>
       </c>
       <c r="F77" s="2">
-        <v>169200</v>
+        <v>153600</v>
       </c>
       <c r="G77" s="2">
-        <v>72000</v>
+        <v>62000</v>
       </c>
       <c r="H77" s="2">
         <f t="shared" si="4"/>
-        <v>72000</v>
+        <v>62000</v>
       </c>
       <c r="I77" s="5"/>
     </row>
@@ -3857,499 +3832,496 @@
         <v>20</v>
       </c>
       <c r="B78" s="41" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C78" s="57"/>
       <c r="D78" s="32">
-        <v>256000</v>
+        <v>508000</v>
       </c>
       <c r="E78" s="15">
-        <v>179200</v>
+        <v>355600</v>
       </c>
       <c r="F78" s="2">
-        <v>153600</v>
+        <v>304800</v>
       </c>
       <c r="G78" s="2">
-        <v>62000</v>
+        <v>124000</v>
       </c>
       <c r="H78" s="2">
         <f t="shared" si="4"/>
-        <v>62000</v>
+        <v>124000</v>
       </c>
       <c r="I78" s="5"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="44" t="s">
+    <row r="79" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B79" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="C79" s="57"/>
-      <c r="D79" s="32">
-        <v>508000</v>
-      </c>
-      <c r="E79" s="15">
-        <v>355600</v>
-      </c>
-      <c r="F79" s="2">
-        <v>304800</v>
-      </c>
-      <c r="G79" s="2">
-        <v>124000</v>
-      </c>
-      <c r="H79" s="2">
-        <f t="shared" si="4"/>
-        <v>124000</v>
-      </c>
-      <c r="I79" s="5"/>
-    </row>
-    <row r="80" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="B80" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="C80" s="60"/>
-      <c r="D80" s="31">
+      <c r="B79" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="C79" s="60"/>
+      <c r="D79" s="31">
         <v>8200</v>
       </c>
-      <c r="E80" s="23">
+      <c r="E79" s="23">
         <v>5740</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F79" s="6">
         <v>4920</v>
       </c>
-      <c r="G80" s="6">
+      <c r="G79" s="6">
         <v>2500</v>
       </c>
-      <c r="H80" s="6">
+      <c r="H79" s="6">
         <f t="shared" si="4"/>
         <v>2500</v>
       </c>
-      <c r="I80" s="7"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="42" t="s">
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B81" s="43" t="s">
-        <v>216</v>
-      </c>
-      <c r="C81" s="56"/>
-      <c r="D81" s="32">
+      <c r="B80" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="C80" s="56"/>
+      <c r="D80" s="32">
         <v>104000</v>
       </c>
-      <c r="E81" s="15">
+      <c r="E80" s="15">
         <v>72800</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F80" s="2">
         <v>62400</v>
       </c>
-      <c r="G81" s="2">
+      <c r="G80" s="2">
         <v>41600</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H80" s="2">
         <f t="shared" si="4"/>
         <v>41600</v>
       </c>
-      <c r="I81" s="5"/>
-    </row>
-    <row r="82" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="45" t="s">
+      <c r="I80" s="5"/>
+    </row>
+    <row r="81" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="46" t="s">
-        <v>217</v>
-      </c>
-      <c r="C82" s="58"/>
-      <c r="D82" s="31">
+      <c r="B81" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" s="58"/>
+      <c r="D81" s="31">
         <v>144750</v>
       </c>
-      <c r="E82" s="23">
+      <c r="E81" s="23">
         <v>101325</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F81" s="6">
         <v>86850</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G81" s="6">
         <v>57900</v>
       </c>
-      <c r="H82" s="6">
+      <c r="H81" s="6">
         <f t="shared" si="4"/>
         <v>57900</v>
       </c>
-      <c r="I82" s="7"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="47" t="s">
+      <c r="I81" s="7"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B83" s="48" t="s">
+      <c r="B82" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C83" s="59"/>
-      <c r="D83" s="30">
+      <c r="C82" s="59"/>
+      <c r="D82" s="30">
         <v>13429</v>
       </c>
-      <c r="E83" s="22">
+      <c r="E82" s="22">
         <v>9400</v>
       </c>
-      <c r="F83" s="13">
+      <c r="F82" s="13">
         <v>8057</v>
       </c>
-      <c r="G83" s="13">
+      <c r="G82" s="13">
         <v>0</v>
       </c>
-      <c r="H83" s="13">
+      <c r="H82" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I83" s="14"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="44" t="s">
+      <c r="I82" s="14"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B84" s="41" t="s">
+      <c r="B83" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="C84" s="57"/>
-      <c r="D84" s="32">
+      <c r="C83" s="57"/>
+      <c r="D83" s="32">
         <v>19714</v>
       </c>
-      <c r="E84" s="15">
+      <c r="E83" s="15">
         <v>13800</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F83" s="2">
         <v>11829</v>
       </c>
-      <c r="G84" s="2">
+      <c r="G83" s="2">
         <v>0</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H83" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I84" s="5"/>
-    </row>
-    <row r="85" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="50" t="s">
+      <c r="I83" s="5"/>
+    </row>
+    <row r="84" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B85" s="51" t="s">
+      <c r="B84" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C85" s="60"/>
-      <c r="D85" s="31">
+      <c r="C84" s="60"/>
+      <c r="D84" s="31">
         <v>19714</v>
       </c>
-      <c r="E85" s="23">
+      <c r="E84" s="23">
         <v>13800</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F84" s="6">
         <v>11829</v>
       </c>
-      <c r="G85" s="6">
+      <c r="G84" s="6">
         <v>0</v>
       </c>
-      <c r="H85" s="6">
+      <c r="H84" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I85" s="7"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="42" t="s">
+      <c r="I84" s="7"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B86" s="43" t="s">
+      <c r="B85" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="56"/>
-      <c r="D86" s="30">
+      <c r="C85" s="56"/>
+      <c r="D85" s="30">
         <v>55600</v>
       </c>
-      <c r="E86" s="22">
+      <c r="E85" s="22">
         <v>38920</v>
       </c>
-      <c r="F86" s="13">
+      <c r="F85" s="13">
         <v>33360</v>
       </c>
-      <c r="G86" s="13">
+      <c r="G85" s="13">
         <v>26800</v>
       </c>
-      <c r="H86" s="13">
+      <c r="H85" s="13">
+        <f>+G85</f>
+        <v>26800</v>
+      </c>
+      <c r="I85" s="14"/>
+    </row>
+    <row r="86" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B86" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C86" s="58"/>
+      <c r="D86" s="40">
+        <v>13900</v>
+      </c>
+      <c r="E86" s="20">
+        <v>9730</v>
+      </c>
+      <c r="F86" s="4">
+        <v>8340</v>
+      </c>
+      <c r="G86" s="4">
+        <v>13900</v>
+      </c>
+      <c r="H86" s="4">
         <f>+G86</f>
-        <v>26800</v>
-      </c>
-      <c r="I86" s="14"/>
-    </row>
-    <row r="87" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="B87" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C87" s="58"/>
-      <c r="D87" s="40">
         <v>13900</v>
       </c>
-      <c r="E87" s="20">
-        <v>9730</v>
-      </c>
-      <c r="F87" s="4">
-        <v>8340</v>
-      </c>
-      <c r="G87" s="4">
-        <v>13900</v>
-      </c>
-      <c r="H87" s="4">
-        <f>+G87</f>
-        <v>13900</v>
-      </c>
-      <c r="I87" s="12"/>
+      <c r="I86" s="12"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="B87" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C87" s="59"/>
+      <c r="D87" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13">
+        <v>99890</v>
+      </c>
+      <c r="G87" s="37">
+        <f>+F87</f>
+        <v>99890</v>
+      </c>
+      <c r="H87" s="37">
+        <f>+F87</f>
+        <v>99890</v>
+      </c>
+      <c r="I87" s="14"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="B88" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C88" s="59"/>
-      <c r="D88" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13">
-        <v>99890</v>
-      </c>
-      <c r="G88" s="37">
-        <f>+F88</f>
-        <v>99890</v>
-      </c>
-      <c r="H88" s="37">
-        <f>+F88</f>
-        <v>99890</v>
-      </c>
-      <c r="I88" s="14"/>
+      <c r="A88" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="B88" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="C88" s="57"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2">
+        <v>90026</v>
+      </c>
+      <c r="G88" s="49">
+        <f t="shared" ref="G88:G107" si="5">+F88</f>
+        <v>90026</v>
+      </c>
+      <c r="H88" s="49">
+        <f t="shared" ref="H88:H107" si="6">+F88</f>
+        <v>90026</v>
+      </c>
+      <c r="I88" s="5"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B89" s="41" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C89" s="57"/>
       <c r="D89" s="32"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2">
-        <v>90026</v>
+        <v>49945</v>
       </c>
       <c r="G89" s="49">
-        <f t="shared" ref="G89:G108" si="5">+F89</f>
-        <v>90026</v>
+        <f t="shared" si="5"/>
+        <v>49945</v>
       </c>
       <c r="H89" s="49">
-        <f t="shared" ref="H89:H108" si="6">+F89</f>
-        <v>90026</v>
+        <f t="shared" si="6"/>
+        <v>49945</v>
       </c>
       <c r="I89" s="5"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B90" s="41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C90" s="57"/>
       <c r="D90" s="32"/>
       <c r="E90" s="2"/>
       <c r="F90" s="2">
-        <v>49945</v>
+        <v>95529</v>
       </c>
       <c r="G90" s="49">
         <f t="shared" si="5"/>
-        <v>49945</v>
+        <v>95529</v>
       </c>
       <c r="H90" s="49">
         <f t="shared" si="6"/>
-        <v>49945</v>
+        <v>95529</v>
       </c>
       <c r="I90" s="5"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B91" s="41" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C91" s="57"/>
       <c r="D91" s="32"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2">
-        <v>95529</v>
+        <v>14952</v>
       </c>
       <c r="G91" s="49">
         <f t="shared" si="5"/>
-        <v>95529</v>
+        <v>14952</v>
       </c>
       <c r="H91" s="49">
         <f t="shared" si="6"/>
-        <v>95529</v>
+        <v>14952</v>
       </c>
       <c r="I91" s="5"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B92" s="41" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C92" s="57"/>
       <c r="D92" s="32"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2">
-        <v>14952</v>
+        <v>21390</v>
       </c>
       <c r="G92" s="49">
         <f t="shared" si="5"/>
-        <v>14952</v>
+        <v>21390</v>
       </c>
       <c r="H92" s="49">
         <f t="shared" si="6"/>
-        <v>14952</v>
+        <v>21390</v>
       </c>
       <c r="I92" s="5"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B93" s="41" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="C93" s="57"/>
       <c r="D93" s="32"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2">
-        <v>21390</v>
+        <v>17029</v>
       </c>
       <c r="G93" s="49">
         <f t="shared" si="5"/>
-        <v>21390</v>
+        <v>17029</v>
       </c>
       <c r="H93" s="49">
         <f t="shared" si="6"/>
-        <v>21390</v>
+        <v>17029</v>
       </c>
       <c r="I93" s="5"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B94" s="41" t="s">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="C94" s="57"/>
       <c r="D94" s="32"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2">
-        <v>17029</v>
+        <v>36239</v>
       </c>
       <c r="G94" s="49">
         <f t="shared" si="5"/>
-        <v>17029</v>
+        <v>36239</v>
       </c>
       <c r="H94" s="49">
         <f t="shared" si="6"/>
-        <v>17029</v>
+        <v>36239</v>
       </c>
       <c r="I94" s="5"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B95" s="41" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="C95" s="57"/>
       <c r="D95" s="32"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2">
-        <v>36239</v>
+        <v>17756</v>
       </c>
       <c r="G95" s="49">
         <f t="shared" si="5"/>
-        <v>36239</v>
+        <v>17756</v>
       </c>
       <c r="H95" s="49">
         <f t="shared" si="6"/>
-        <v>36239</v>
+        <v>17756</v>
       </c>
       <c r="I95" s="5"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B96" s="41" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="C96" s="57"/>
       <c r="D96" s="32"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2">
-        <v>17756</v>
+        <v>20560</v>
       </c>
       <c r="G96" s="49">
         <f t="shared" si="5"/>
-        <v>17756</v>
+        <v>20560</v>
       </c>
       <c r="H96" s="49">
         <f t="shared" si="6"/>
-        <v>17756</v>
+        <v>20560</v>
       </c>
       <c r="I96" s="5"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B97" s="41" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C97" s="57"/>
       <c r="D97" s="32"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2">
-        <v>20560</v>
+        <v>17237</v>
       </c>
       <c r="G97" s="49">
         <f t="shared" si="5"/>
-        <v>20560</v>
+        <v>17237</v>
       </c>
       <c r="H97" s="49">
         <f t="shared" si="6"/>
-        <v>20560</v>
+        <v>17237</v>
       </c>
       <c r="I97" s="5"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B98" s="41" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C98" s="57"/>
       <c r="D98" s="32"/>
@@ -4358,21 +4330,19 @@
         <v>17237</v>
       </c>
       <c r="G98" s="49">
-        <f t="shared" si="5"/>
         <v>17237</v>
       </c>
       <c r="H98" s="49">
-        <f t="shared" si="6"/>
         <v>17237</v>
       </c>
       <c r="I98" s="5"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B99" s="41" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="C99" s="57"/>
       <c r="D99" s="32"/>
@@ -4381,261 +4351,261 @@
         <v>17237</v>
       </c>
       <c r="G99" s="49">
+        <f t="shared" si="5"/>
         <v>17237</v>
       </c>
       <c r="H99" s="49">
+        <f t="shared" si="6"/>
         <v>17237</v>
       </c>
       <c r="I99" s="5"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B100" s="41" t="s">
-        <v>150</v>
+        <v>39</v>
       </c>
       <c r="C100" s="57"/>
       <c r="D100" s="32"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2">
-        <v>17237</v>
+        <v>12772</v>
       </c>
       <c r="G100" s="49">
         <f t="shared" si="5"/>
-        <v>17237</v>
+        <v>12772</v>
       </c>
       <c r="H100" s="49">
         <f t="shared" si="6"/>
-        <v>17237</v>
+        <v>12772</v>
       </c>
       <c r="I100" s="5"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B101" s="41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C101" s="57"/>
       <c r="D101" s="32"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2">
-        <v>12772</v>
+        <v>14226</v>
       </c>
       <c r="G101" s="49">
         <f t="shared" si="5"/>
-        <v>12772</v>
+        <v>14226</v>
       </c>
       <c r="H101" s="49">
         <f t="shared" si="6"/>
-        <v>12772</v>
+        <v>14226</v>
       </c>
       <c r="I101" s="5"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B102" s="41" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C102" s="57"/>
       <c r="D102" s="32"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2">
-        <v>14226</v>
+        <v>14329</v>
       </c>
       <c r="G102" s="49">
         <f t="shared" si="5"/>
-        <v>14226</v>
+        <v>14329</v>
       </c>
       <c r="H102" s="49">
         <f t="shared" si="6"/>
-        <v>14226</v>
+        <v>14329</v>
       </c>
       <c r="I102" s="5"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B103" s="41" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C103" s="57"/>
       <c r="D103" s="32"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2">
-        <v>14329</v>
+        <v>18067</v>
       </c>
       <c r="G103" s="49">
         <f t="shared" si="5"/>
-        <v>14329</v>
+        <v>18067</v>
       </c>
       <c r="H103" s="49">
         <f t="shared" si="6"/>
-        <v>14329</v>
+        <v>18067</v>
       </c>
       <c r="I103" s="5"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B104" s="41" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="C104" s="57"/>
       <c r="D104" s="32"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2">
-        <v>18067</v>
+        <v>17237</v>
       </c>
       <c r="G104" s="49">
-        <f t="shared" si="5"/>
-        <v>18067</v>
+        <v>17237</v>
       </c>
       <c r="H104" s="49">
-        <f t="shared" si="6"/>
-        <v>18067</v>
+        <v>17237</v>
       </c>
       <c r="I104" s="5"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B105" s="41" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="C105" s="57"/>
       <c r="D105" s="32"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2">
-        <v>17237</v>
+        <v>17029</v>
       </c>
       <c r="G105" s="49">
-        <v>17237</v>
+        <f t="shared" si="5"/>
+        <v>17029</v>
       </c>
       <c r="H105" s="49">
-        <v>17237</v>
+        <f t="shared" si="6"/>
+        <v>17029</v>
       </c>
       <c r="I105" s="5"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B106" s="41" t="s">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="C106" s="57"/>
       <c r="D106" s="32"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2">
-        <v>17029</v>
+        <v>70000</v>
       </c>
       <c r="G106" s="49">
         <f t="shared" si="5"/>
-        <v>17029</v>
+        <v>70000</v>
       </c>
       <c r="H106" s="49">
         <f t="shared" si="6"/>
-        <v>17029</v>
+        <v>70000</v>
       </c>
       <c r="I106" s="5"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="B107" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="C107" s="57"/>
-      <c r="D107" s="32"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2">
-        <v>70000</v>
-      </c>
-      <c r="G107" s="49">
-        <f t="shared" si="5"/>
-        <v>70000</v>
-      </c>
-      <c r="H107" s="49">
-        <f t="shared" si="6"/>
-        <v>70000</v>
-      </c>
-      <c r="I107" s="5"/>
-    </row>
-    <row r="108" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="B108" s="46" t="s">
+    <row r="107" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B107" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="C108" s="58"/>
-      <c r="D108" s="31"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6">
+      <c r="C107" s="58"/>
+      <c r="D107" s="31"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6">
         <v>38835</v>
       </c>
-      <c r="G108" s="38">
+      <c r="G107" s="38">
         <f t="shared" si="5"/>
         <v>38835</v>
       </c>
-      <c r="H108" s="38">
+      <c r="H107" s="38">
         <f t="shared" si="6"/>
         <v>38835</v>
       </c>
-      <c r="I108" s="7"/>
+      <c r="I107" s="7"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B108" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="C108" s="59"/>
+      <c r="D108" s="33"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G108" s="3">
+        <f>+F108</f>
+        <v>12000</v>
+      </c>
+      <c r="H108" s="3">
+        <f>+F108</f>
+        <v>12000</v>
+      </c>
+      <c r="I108" s="8"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="47" t="s">
+      <c r="A109" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B109" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="C109" s="59"/>
-      <c r="D109" s="33"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3">
-        <v>12000</v>
-      </c>
-      <c r="G109" s="3">
+      <c r="B109" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="C109" s="57"/>
+      <c r="D109" s="32"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2">
+        <v>25000</v>
+      </c>
+      <c r="G109" s="2">
         <f>+F109</f>
-        <v>12000</v>
-      </c>
-      <c r="H109" s="3">
+        <v>25000</v>
+      </c>
+      <c r="H109" s="2">
         <f>+F109</f>
-        <v>12000</v>
-      </c>
-      <c r="I109" s="8"/>
+        <v>25000</v>
+      </c>
+      <c r="I109" s="5"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="44" t="s">
         <v>2</v>
       </c>
       <c r="B110" s="41" t="s">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="C110" s="57"/>
       <c r="D110" s="32"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="G110" s="2">
-        <f>+F110</f>
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="H110" s="2">
-        <f>+F110</f>
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="I110" s="5"/>
     </row>
@@ -4770,7 +4740,7 @@
         <v>2</v>
       </c>
       <c r="B117" s="41" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="C117" s="57"/>
       <c r="D117" s="32"/>
@@ -4791,7 +4761,7 @@
         <v>2</v>
       </c>
       <c r="B118" s="41" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="C118" s="57"/>
       <c r="D118" s="32"/>
@@ -4854,19 +4824,19 @@
         <v>2</v>
       </c>
       <c r="B121" s="41" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="C121" s="57"/>
       <c r="D121" s="32"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2">
-        <v>22000</v>
+        <v>32000</v>
       </c>
       <c r="G121" s="2">
-        <v>22000</v>
+        <v>32000</v>
       </c>
       <c r="H121" s="2">
-        <v>22000</v>
+        <v>32000</v>
       </c>
       <c r="I121" s="5"/>
     </row>
@@ -4917,7 +4887,7 @@
         <v>2</v>
       </c>
       <c r="B124" s="41" t="s">
-        <v>207</v>
+        <v>130</v>
       </c>
       <c r="C124" s="57"/>
       <c r="D124" s="32"/>
@@ -4933,450 +4903,450 @@
       </c>
       <c r="I124" s="5"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="44" t="s">
+    <row r="125" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B125" s="41" t="s">
-        <v>131</v>
-      </c>
-      <c r="C125" s="57"/>
-      <c r="D125" s="32"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2">
-        <v>32000</v>
-      </c>
-      <c r="G125" s="2">
-        <v>32000</v>
-      </c>
-      <c r="H125" s="2">
-        <v>32000</v>
-      </c>
-      <c r="I125" s="5"/>
-    </row>
-    <row r="126" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="50" t="s">
-        <v>2</v>
-      </c>
-      <c r="B126" s="51" t="s">
-        <v>208</v>
-      </c>
-      <c r="C126" s="60"/>
-      <c r="D126" s="40"/>
-      <c r="E126" s="4"/>
-      <c r="F126" s="4">
-        <v>32000</v>
-      </c>
-      <c r="G126" s="4">
-        <v>32000</v>
-      </c>
-      <c r="H126" s="4">
-        <v>32000</v>
-      </c>
-      <c r="I126" s="12"/>
+      <c r="B125" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="C125" s="60"/>
+      <c r="D125" s="40"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4">
+        <v>32000</v>
+      </c>
+      <c r="G125" s="4">
+        <v>32000</v>
+      </c>
+      <c r="H125" s="4">
+        <v>32000</v>
+      </c>
+      <c r="I125" s="12"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" s="56"/>
+      <c r="D126" s="30"/>
+      <c r="E126" s="13"/>
+      <c r="F126" s="13">
+        <v>24000</v>
+      </c>
+      <c r="G126" s="13">
+        <v>24000</v>
+      </c>
+      <c r="H126" s="13">
+        <v>24000</v>
+      </c>
+      <c r="I126" s="14"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="B127" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="C127" s="56"/>
-      <c r="D127" s="30"/>
-      <c r="E127" s="13"/>
-      <c r="F127" s="13">
-        <v>24000</v>
-      </c>
-      <c r="G127" s="13">
-        <v>24000</v>
-      </c>
-      <c r="H127" s="13">
-        <v>24000</v>
-      </c>
-      <c r="I127" s="14"/>
+      <c r="A127" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="B127" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="C127" s="57"/>
+      <c r="D127" s="32"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2">
+        <v>72000</v>
+      </c>
+      <c r="G127" s="2">
+        <v>72000</v>
+      </c>
+      <c r="H127" s="2">
+        <v>72000</v>
+      </c>
+      <c r="I127" s="5"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B128" s="41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C128" s="57"/>
       <c r="D128" s="32"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2">
-        <v>72000</v>
+        <v>87200</v>
       </c>
       <c r="G128" s="2">
-        <v>72000</v>
+        <v>87200</v>
       </c>
       <c r="H128" s="2">
-        <v>72000</v>
+        <v>87200</v>
       </c>
       <c r="I128" s="5"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B129" s="41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C129" s="57"/>
       <c r="D129" s="32"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2">
-        <v>87200</v>
+        <v>35000</v>
       </c>
       <c r="G129" s="2">
-        <v>87200</v>
+        <v>35000</v>
       </c>
       <c r="H129" s="2">
-        <v>87200</v>
+        <v>35000</v>
       </c>
       <c r="I129" s="5"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" s="41" t="s">
         <v>136</v>
-      </c>
-      <c r="B130" s="41" t="s">
-        <v>221</v>
       </c>
       <c r="C130" s="57"/>
       <c r="D130" s="32"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2">
-        <v>35000</v>
+        <v>16640</v>
       </c>
       <c r="G130" s="2">
-        <v>35000</v>
+        <v>16640</v>
       </c>
       <c r="H130" s="2">
-        <v>35000</v>
+        <v>16640</v>
       </c>
       <c r="I130" s="5"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B131" s="41" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C131" s="57"/>
       <c r="D131" s="32"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="G131" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="H131" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="I131" s="5"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B132" s="41" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C132" s="57"/>
       <c r="D132" s="32"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="G132" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="H132" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="I132" s="5"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B133" s="41" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C133" s="57"/>
       <c r="D133" s="32"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="G133" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="H133" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="I133" s="5"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B134" s="41" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C134" s="57"/>
       <c r="D134" s="32"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="G134" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="H134" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="I134" s="5"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B135" s="41" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C135" s="57"/>
       <c r="D135" s="32"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="G135" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="H135" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="I135" s="5"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B136" s="41" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C136" s="57"/>
       <c r="D136" s="32"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="G136" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="H136" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="I136" s="5"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B137" s="41" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C137" s="57"/>
       <c r="D137" s="32"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="G137" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="H137" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="I137" s="5"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B138" s="41" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="C138" s="57"/>
       <c r="D138" s="32"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="G138" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="H138" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="I138" s="5"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B139" s="41" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C139" s="57"/>
       <c r="D139" s="32"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="G139" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="H139" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="I139" s="5"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B140" s="41" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C140" s="57"/>
       <c r="D140" s="32"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="G140" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="H140" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="I140" s="5"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B141" s="41" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C141" s="57"/>
       <c r="D141" s="32"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="G141" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="H141" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="I141" s="5"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B142" s="41" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="C142" s="57"/>
       <c r="D142" s="32"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="G142" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="H142" s="2">
-        <v>9600</v>
+        <v>16640</v>
       </c>
       <c r="I142" s="5"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B143" s="41" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C143" s="57"/>
       <c r="D143" s="32"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="G143" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="H143" s="2">
-        <v>16640</v>
+        <v>9600</v>
       </c>
       <c r="I143" s="5"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B144" s="41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C144" s="57"/>
       <c r="D144" s="32"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2">
-        <v>9600</v>
+        <v>36000</v>
       </c>
       <c r="G144" s="2">
-        <v>9600</v>
+        <v>36000</v>
       </c>
       <c r="H144" s="2">
-        <v>9600</v>
+        <v>36000</v>
       </c>
       <c r="I144" s="5"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B145" s="41" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C145" s="57"/>
       <c r="D145" s="32"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2">
-        <v>36000</v>
+        <v>32000</v>
       </c>
       <c r="G145" s="2">
-        <v>36000</v>
+        <v>32000</v>
       </c>
       <c r="H145" s="2">
-        <v>36000</v>
+        <v>32000</v>
       </c>
       <c r="I145" s="5"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B146" s="41" t="s">
         <v>144</v>
@@ -5397,7 +5367,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B147" s="41" t="s">
         <v>145</v>
@@ -5418,7 +5388,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B148" s="41" t="s">
         <v>146</v>
@@ -5439,7 +5409,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B149" s="41" t="s">
         <v>147</v>
@@ -5460,10 +5430,10 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B150" s="41" t="s">
-        <v>148</v>
+        <v>41</v>
       </c>
       <c r="C150" s="57"/>
       <c r="D150" s="32"/>
@@ -5481,10 +5451,10 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B151" s="41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C151" s="57"/>
       <c r="D151" s="32"/>
@@ -5502,10 +5472,10 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B152" s="41" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="C152" s="57"/>
       <c r="D152" s="32"/>
@@ -5523,7 +5493,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B153" s="41" t="s">
         <v>149</v>
@@ -5544,7 +5514,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B154" s="41" t="s">
         <v>150</v>
@@ -5565,7 +5535,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B155" s="41" t="s">
         <v>151</v>
@@ -5586,7 +5556,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B156" s="41" t="s">
         <v>152</v>
@@ -5607,7 +5577,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B157" s="41" t="s">
         <v>153</v>
@@ -5628,7 +5598,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B158" s="41" t="s">
         <v>154</v>
@@ -5649,10 +5619,10 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B159" s="41" t="s">
-        <v>155</v>
+        <v>39</v>
       </c>
       <c r="C159" s="57"/>
       <c r="D159" s="32"/>
@@ -5670,10 +5640,10 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B160" s="41" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="C160" s="57"/>
       <c r="D160" s="32"/>
@@ -5691,7 +5661,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B161" s="41" t="s">
         <v>156</v>
@@ -5700,19 +5670,19 @@
       <c r="D161" s="32"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="G161" s="2">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="H161" s="2">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="I161" s="5"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B162" s="41" t="s">
         <v>157</v>
@@ -5721,61 +5691,61 @@
       <c r="D162" s="32"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2">
-        <v>35000</v>
+        <v>32000</v>
       </c>
       <c r="G162" s="2">
-        <v>35000</v>
+        <v>32000</v>
       </c>
       <c r="H162" s="2">
-        <v>35000</v>
+        <v>32000</v>
       </c>
       <c r="I162" s="5"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B163" s="41" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="C163" s="57"/>
       <c r="D163" s="32"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2">
-        <v>32000</v>
+        <v>68000</v>
       </c>
       <c r="G163" s="2">
-        <v>32000</v>
+        <v>68000</v>
       </c>
       <c r="H163" s="2">
-        <v>32000</v>
+        <v>68000</v>
       </c>
       <c r="I163" s="5"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B164" s="41" t="s">
-        <v>222</v>
+        <v>158</v>
       </c>
       <c r="C164" s="57"/>
       <c r="D164" s="32"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2">
-        <v>68000</v>
+        <v>32000</v>
       </c>
       <c r="G164" s="2">
-        <v>68000</v>
+        <v>32000</v>
       </c>
       <c r="H164" s="2">
-        <v>68000</v>
+        <v>32000</v>
       </c>
       <c r="I164" s="5"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B165" s="41" t="s">
         <v>159</v>
@@ -5796,7 +5766,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B166" s="41" t="s">
         <v>160</v>
@@ -5817,49 +5787,49 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B167" s="41" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="C167" s="57"/>
       <c r="D167" s="32"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2">
-        <v>32000</v>
+        <v>78000</v>
       </c>
       <c r="G167" s="2">
-        <v>32000</v>
+        <v>78000</v>
       </c>
       <c r="H167" s="2">
-        <v>32000</v>
+        <v>78000</v>
       </c>
       <c r="I167" s="5"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B168" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C168" s="57"/>
       <c r="D168" s="32"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2">
-        <v>78000</v>
+        <v>60000</v>
       </c>
       <c r="G168" s="2">
-        <v>78000</v>
+        <v>60000</v>
       </c>
       <c r="H168" s="2">
-        <v>78000</v>
+        <v>60000</v>
       </c>
       <c r="I168" s="5"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B169" s="41" t="s">
         <v>129</v>
@@ -5868,19 +5838,19 @@
       <c r="D169" s="32"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="G169" s="2">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="H169" s="2">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="I169" s="5"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B170" s="41" t="s">
         <v>130</v>
@@ -5889,22 +5859,22 @@
       <c r="D170" s="32"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="G170" s="2">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="H170" s="2">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="I170" s="5"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B171" s="41" t="s">
-        <v>131</v>
+        <v>207</v>
       </c>
       <c r="C171" s="57"/>
       <c r="D171" s="32"/>
@@ -5922,28 +5892,28 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B172" s="41" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="C172" s="57"/>
       <c r="D172" s="32"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2">
-        <v>75000</v>
+        <v>106880</v>
       </c>
       <c r="G172" s="2">
-        <v>75000</v>
+        <v>106880</v>
       </c>
       <c r="H172" s="2">
-        <v>75000</v>
+        <v>106880</v>
       </c>
       <c r="I172" s="5"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B173" s="41" t="s">
         <v>162</v>
@@ -5964,7 +5934,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B174" s="41" t="s">
         <v>163</v>
@@ -5985,7 +5955,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B175" s="41" t="s">
         <v>164</v>
@@ -6006,7 +5976,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B176" s="41" t="s">
         <v>165</v>
@@ -6027,10 +5997,10 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B177" s="41" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C177" s="57"/>
       <c r="D177" s="32"/>
@@ -6048,10 +6018,10 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B178" s="41" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C178" s="57"/>
       <c r="D178" s="32"/>
@@ -6069,7 +6039,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B179" s="41" t="s">
         <v>167</v>
@@ -6090,7 +6060,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B180" s="41" t="s">
         <v>168</v>
@@ -6111,7 +6081,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B181" s="41" t="s">
         <v>169</v>
@@ -6132,7 +6102,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B182" s="41" t="s">
         <v>170</v>
@@ -6153,7 +6123,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B183" s="41" t="s">
         <v>171</v>
@@ -6174,7 +6144,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B184" s="41" t="s">
         <v>172</v>
@@ -6195,7 +6165,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B185" s="41" t="s">
         <v>173</v>
@@ -6216,7 +6186,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B186" s="41" t="s">
         <v>174</v>
@@ -6237,7 +6207,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B187" s="41" t="s">
         <v>175</v>
@@ -6256,95 +6226,97 @@
       </c>
       <c r="I187" s="5"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="B188" s="41" t="s">
+    <row r="188" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="B188" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="C188" s="57"/>
-      <c r="D188" s="32"/>
-      <c r="E188" s="2"/>
-      <c r="F188" s="2">
+      <c r="C188" s="60"/>
+      <c r="D188" s="40"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4">
         <v>106880</v>
       </c>
-      <c r="G188" s="2">
+      <c r="G188" s="4">
         <v>106880</v>
       </c>
-      <c r="H188" s="2">
+      <c r="H188" s="4">
         <v>106880</v>
       </c>
-      <c r="I188" s="5"/>
+      <c r="I188" s="12"/>
     </row>
     <row r="189" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="B189" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="C189" s="60"/>
-      <c r="D189" s="40"/>
-      <c r="E189" s="4"/>
-      <c r="F189" s="4">
-        <v>106880</v>
-      </c>
-      <c r="G189" s="4">
-        <v>106880</v>
-      </c>
-      <c r="H189" s="4">
-        <v>106880</v>
-      </c>
-      <c r="I189" s="12"/>
-    </row>
-    <row r="190" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="52" t="s">
+      <c r="A189" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B190" s="53" t="s">
+      <c r="B189" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="C190" s="61"/>
-      <c r="D190" s="62"/>
-      <c r="E190" s="54"/>
-      <c r="F190" s="54">
+      <c r="C189" s="61"/>
+      <c r="D189" s="62"/>
+      <c r="E189" s="54"/>
+      <c r="F189" s="54">
         <v>40000</v>
       </c>
-      <c r="G190" s="54">
+      <c r="G189" s="54">
         <v>40000</v>
       </c>
-      <c r="H190" s="54">
+      <c r="H189" s="54">
         <v>40000</v>
       </c>
-      <c r="I190" s="55"/>
+      <c r="I189" s="55"/>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="B190" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C190" s="56"/>
+      <c r="D190" s="30"/>
+      <c r="E190" s="13">
+        <v>15000</v>
+      </c>
+      <c r="F190" s="13">
+        <v>15000</v>
+      </c>
+      <c r="G190" s="13">
+        <v>15000</v>
+      </c>
+      <c r="H190" s="13">
+        <v>15000</v>
+      </c>
+      <c r="I190" s="14"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191" s="42" t="s">
-        <v>180</v>
-      </c>
-      <c r="B191" s="43" t="s">
+      <c r="A191" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="B191" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="C191" s="56"/>
-      <c r="D191" s="30"/>
-      <c r="E191" s="13">
+      <c r="C191" s="57"/>
+      <c r="D191" s="32"/>
+      <c r="E191" s="2">
+        <v>18000</v>
+      </c>
+      <c r="F191" s="2">
         <v>15000</v>
       </c>
-      <c r="F191" s="13">
+      <c r="G191" s="2">
         <v>15000</v>
       </c>
-      <c r="G191" s="13">
+      <c r="H191" s="2">
         <v>15000</v>
       </c>
-      <c r="H191" s="13">
-        <v>15000</v>
-      </c>
-      <c r="I191" s="14"/>
+      <c r="I191" s="5"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B192" s="41" t="s">
         <v>110</v>
@@ -6367,124 +6339,95 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B193" s="41" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="C193" s="57"/>
       <c r="D193" s="32"/>
-      <c r="E193" s="2">
-        <v>18000</v>
-      </c>
+      <c r="E193" s="2"/>
       <c r="F193" s="2">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="G193" s="2">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H193" s="2">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="I193" s="5"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="B194" s="41" t="s">
+    <row r="194" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="45" t="s">
         <v>179</v>
       </c>
-      <c r="C194" s="57"/>
-      <c r="D194" s="32"/>
-      <c r="E194" s="2"/>
-      <c r="F194" s="2">
+      <c r="B194" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C194" s="58"/>
+      <c r="D194" s="31"/>
+      <c r="E194" s="6"/>
+      <c r="F194" s="6">
         <v>20000</v>
       </c>
-      <c r="G194" s="2">
+      <c r="G194" s="6">
         <v>20000</v>
       </c>
-      <c r="H194" s="2">
+      <c r="H194" s="6">
         <v>20000</v>
       </c>
-      <c r="I194" s="5"/>
-    </row>
-    <row r="195" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="B195" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="C195" s="58"/>
-      <c r="D195" s="31"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6">
-        <v>20000</v>
-      </c>
-      <c r="G195" s="6">
-        <v>20000</v>
-      </c>
-      <c r="H195" s="6">
-        <v>20000</v>
-      </c>
-      <c r="I195" s="7"/>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="47" t="s">
+      <c r="I194" s="7"/>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="B195" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="B196" s="48" t="s">
+      <c r="C195" s="59"/>
+      <c r="D195" s="33"/>
+      <c r="E195" s="3"/>
+      <c r="F195" s="3">
+        <v>35000</v>
+      </c>
+      <c r="G195" s="3">
+        <v>35000</v>
+      </c>
+      <c r="H195" s="3">
+        <v>35000</v>
+      </c>
+      <c r="I195" s="8"/>
+    </row>
+    <row r="196" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="B196" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="C196" s="59"/>
-      <c r="D196" s="33"/>
-      <c r="E196" s="3"/>
-      <c r="F196" s="3">
+      <c r="C196" s="58"/>
+      <c r="D196" s="31"/>
+      <c r="E196" s="6"/>
+      <c r="F196" s="6">
         <v>35000</v>
       </c>
-      <c r="G196" s="3">
+      <c r="G196" s="6">
         <v>35000</v>
       </c>
-      <c r="H196" s="3">
+      <c r="H196" s="6">
         <v>35000</v>
       </c>
-      <c r="I196" s="8"/>
-    </row>
-    <row r="197" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="B197" s="46" t="s">
-        <v>199</v>
-      </c>
-      <c r="C197" s="58"/>
-      <c r="D197" s="31"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6">
-        <v>35000</v>
-      </c>
-      <c r="G197" s="6">
-        <v>35000</v>
-      </c>
-      <c r="H197" s="6">
-        <v>35000</v>
-      </c>
-      <c r="I197" s="7"/>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="1"/>
+      <c r="I196" s="7"/>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="1"/>
     </row>
   </sheetData>
   <sortState ref="B89:B126">
     <sortCondition ref="B89"/>
   </sortState>
-  <mergeCells count="4">
-    <mergeCell ref="D19:D22"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D52:D55"/>
-  </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="27" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -105,12 +105,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="A197" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Administracion:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="226">
   <si>
     <t>ENFERMERIA</t>
   </si>
@@ -773,6 +797,21 @@
   </si>
   <si>
     <t>PRESUROMETRIA/MONIT. PRESION ART.</t>
+  </si>
+  <si>
+    <t>PILETA</t>
+  </si>
+  <si>
+    <t>INDIVIDUAL</t>
+  </si>
+  <si>
+    <t>GRUPO FAMILIAR</t>
+  </si>
+  <si>
+    <t>POR FAMILIAR (C/U)</t>
+  </si>
+  <si>
+    <t>COLONIA</t>
   </si>
 </sst>
 </file>
@@ -1856,7 +1895,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I197"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.42578125" style="16" customWidth="1"/>
@@ -6422,7 +6461,94 @@
       <c r="I196" s="7"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="1"/>
+      <c r="A197" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="B197" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="C197" s="56"/>
+      <c r="D197" s="30">
+        <v>200000</v>
+      </c>
+      <c r="E197" s="13">
+        <v>150000</v>
+      </c>
+      <c r="F197" s="13">
+        <v>75000</v>
+      </c>
+      <c r="G197" s="13">
+        <v>50000</v>
+      </c>
+      <c r="H197" s="13">
+        <v>50000</v>
+      </c>
+      <c r="I197" s="14"/>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="B198" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="C198" s="57"/>
+      <c r="D198" s="32"/>
+      <c r="E198" s="2"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="2">
+        <v>80000</v>
+      </c>
+      <c r="H198" s="2">
+        <v>80000</v>
+      </c>
+      <c r="I198" s="5"/>
+    </row>
+    <row r="199" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="50" t="s">
+        <v>221</v>
+      </c>
+      <c r="B199" s="51" t="s">
+        <v>224</v>
+      </c>
+      <c r="C199" s="60"/>
+      <c r="D199" s="40">
+        <v>200000</v>
+      </c>
+      <c r="E199" s="4">
+        <v>80000</v>
+      </c>
+      <c r="F199" s="4">
+        <v>40000</v>
+      </c>
+      <c r="G199" s="4"/>
+      <c r="H199" s="4"/>
+      <c r="I199" s="12"/>
+    </row>
+    <row r="200" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="B200" s="64" t="s">
+        <v>222</v>
+      </c>
+      <c r="C200" s="67"/>
+      <c r="D200" s="34">
+        <v>280000</v>
+      </c>
+      <c r="E200" s="25">
+        <v>225000</v>
+      </c>
+      <c r="F200" s="25">
+        <v>180000</v>
+      </c>
+      <c r="G200" s="25">
+        <v>120000</v>
+      </c>
+      <c r="H200" s="25">
+        <v>120000</v>
+      </c>
+      <c r="I200" s="26"/>
     </row>
   </sheetData>
   <sortState ref="B89:B126">

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -811,7 +811,7 @@
     <t>POR FAMILIAR (C/U)</t>
   </si>
   <si>
-    <t>COLONIA</t>
+    <t>COLONIA VERANO</t>
   </si>
 </sst>
 </file>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -3514,13 +3514,13 @@
         <v>120</v>
       </c>
       <c r="D65" s="32">
-        <v>68000</v>
+        <v>70000</v>
       </c>
       <c r="E65" s="15">
-        <v>47600</v>
+        <v>63000</v>
       </c>
       <c r="F65" s="2">
-        <v>40800</v>
+        <v>56000</v>
       </c>
       <c r="G65" s="2">
         <v>48000</v>

--- a/precios.xlsx
+++ b/precios.xlsx
@@ -5835,13 +5835,13 @@
       <c r="D167" s="32"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2">
-        <v>78000</v>
+        <v>75000</v>
       </c>
       <c r="G167" s="2">
-        <v>78000</v>
+        <v>75000</v>
       </c>
       <c r="H167" s="2">
-        <v>78000</v>
+        <v>75000</v>
       </c>
       <c r="I167" s="5"/>
     </row>
